--- a/docs/data/bandi_veneto.xlsx
+++ b/docs/data/bandi_veneto.xlsx
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22116,20 +22116,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" s="2" t="n"/>
-      <c r="H337" s="3" t="n"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H337" s="3" t="n">
+        <v>45457</v>
+      </c>
       <c r="I337" s="3" t="n">
         <v>45504</v>
       </c>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Con DDR n. 826 del 27/06/2024 sono stati prorogati i termini per la presentazione dei progetti al 31/07/2024 Avviso pubblico "Restauro 2024: sviluppo capacità professionali per interventi di conservazione del patrimonio storico, artistico, architettonico". La Giunta regionale ha stabilito, nell'ambito del Programma regionale Veneto FSE+ 2021-2027 - Obiettivo “Investimenti per l’occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 1 Occupazione - Obiettivo specifico a) e Priorità 2 - Istruzione e Formazione - Obiettivo specifico g), l'apertura dei termini per la presentazione…</t>
+        </is>
+      </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22164,18 +22184,32 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" s="2" t="n"/>
-      <c r="H338" s="3" t="n"/>
+      <c r="H338" s="3" t="n">
+        <v>45457</v>
+      </c>
       <c r="I338" s="3" t="n">
         <v>45502</v>
       </c>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Cona la DGR n. 646 del 10/06/2024 sono stati approvazti i criteri, termini e le modalità di assegnazione di contributi per il pagamento delle rette, sostenute nel corso dell’anno 2023, relativamente all’inserimento di minori in unità d’offerta residenziali, di cui alle DGR n. 84/2007 e n. 242/2012 ad essi dedicate, da assegnare a Comuni con popolazione non superiore ai 20.000 abitanti, ad Aziende ULSS e ad Unioni di Comuni, se delegate, per la sola quota relativa ai Comuni con popolazione non superiore ai 20.000 abitanti. L'ambito di intervento riguarda gli inserimenti consensuali e/o giudiziali in strutture di accoglienza per minori, con…</t>
+        </is>
+      </c>
       <c r="O338" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22208,20 +22242,38 @@
           <t>Unita' Organizzativa Famiglia, Minori, Giovani E Servizio Civile</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G339" s="2" t="n"/>
-      <c r="H339" s="3" t="n"/>
+      <c r="H339" s="3" t="n">
+        <v>45457</v>
+      </c>
       <c r="I339" s="3" t="n">
         <v>45502</v>
       </c>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Con DGR n. 646 del 10 giugno 2024 sono stati approvati criteri, termini e modalità di assegnazione di contributi per il pagamento delle rette, sostenute nel corso dell’anno 2023, relativamente all’inserimento di minori in unità d’offerta residenziali, di cui alle DGR n. 84/2007 e n. 242/2012 ad essi dedicate, da assegnare a Comuni con popolazione non superiore ai 20.000 abitanti, ad Aziende ULSS e ad Unioni di Comuni, se delegate, per la sola quota relativa ai Comuni con popolazione non superiore ai 20.000 abitanti. Sono stati approvati anche i seguenti Allegati quali parti integranti del provvedimento di cui sopra: Allegato A recante…</t>
+        </is>
+      </c>
       <c r="O339" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22246,7 +22298,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -22254,20 +22306,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" s="2" t="n"/>
-      <c r="H340" s="3" t="n"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H340" s="3" t="n">
+        <v>45450</v>
+      </c>
       <c r="I340" s="3" t="n">
         <v>45495</v>
       </c>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Bando 2024 per la concessione di contributi a sostegno delle attività di promozione e valorizzazione turistica, culturale, folcloristica ed enogastronomica locale realizzate dalle forme associate delle Pro Loco. Legge regionale n. 34/2014. Dgr n. 589 del 27 Maggio 2024. Data apertura presentazione domande il 07 Giugno 2024 Data scadenza presentazione domande il 22 Luglio 2024 entro le ore 23:59.</t>
+        </is>
+      </c>
       <c r="O340" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22300,20 +22372,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" s="2" t="n"/>
-      <c r="H341" s="3" t="n"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="H341" s="3" t="n">
+        <v>45440</v>
+      </c>
       <c r="I341" s="3" t="n">
         <v>45492</v>
       </c>
-      <c r="K341" t="inlineStr"/>
-      <c r="L341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Piano strategico della Politica agricola comune 2023-2027 - PSP Italia 2023-2027 - Intervento settoriale vitivinicolo Promozione e comunicazione realizzate nei paesi terzi. Bando regionale per la presentazione dei progetti per la campagna 2024/2025 (fondi 2025). Regolamento (UE) n. 2021/2115, articolo 58. DGR n. 588 el 27 maggio 2024 . Possono presentare domanda le organizzazioni professionali purché abbiano tra i loro scopi, la promozione dei prodotti agricoli, le organizzazioni di produttori di vino come definite dall’art. 152 del reg.to UE 1308/2013 (di seguito reg.to UE), le associazioni di organizzazioni di produttori…</t>
+        </is>
+      </c>
       <c r="O341" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22338,7 +22430,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -22346,20 +22438,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" s="2" t="n"/>
-      <c r="H342" s="3" t="n"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>7214206</v>
+      </c>
+      <c r="H342" s="3" t="n">
+        <v>45394</v>
+      </c>
       <c r="I342" s="3" t="n">
         <v>45491</v>
       </c>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 2, OS “Promuovere la transizione verso un’economia circolare ed efficiente sotto il profilo delle risorse (FESR)”. Azione 2.6.1 “Riutilizzo efficiente delle risorse attraverso l’economia circolare e sostegno ai processi di produzione ed efficientamento nelle PMI” Dgr n. 379 del 9 aprile 2024 Data apertura domande: 23 aprile 2024 ore 10:00 Data chiusura domande: 18 luglio 2024 ore 17:00</t>
+        </is>
+      </c>
       <c r="O342" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22392,20 +22504,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" s="2" t="n"/>
-      <c r="H343" s="3" t="n"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>3240540</v>
+      </c>
+      <c r="H343" s="3" t="n">
+        <v>45471</v>
+      </c>
       <c r="I343" s="3" t="n">
         <v>45491</v>
       </c>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Interventi di Istruzione e Formazione Professionale per la qualifica professionale degli ex Centri di Formazione Professionale della Provincia di Treviso e della Città Metropolitana di Venezia, DGR n. 822 del 08/06/2018. L.R. 31/03/2017, n. 8. Proroga per l'anno formativo 2024/2025 dell'affidamento ai soggetti attuatori. Approvazione dell'Avviso pubblico per la presentazione di progetti volti alla realizzazione di attività IeFP.</t>
+        </is>
+      </c>
       <c r="O343" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22438,20 +22570,40 @@
           <t>Direzione Comunicazione E Informazione</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" s="2" t="n"/>
-      <c r="H344" s="3" t="n"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H344" s="3" t="n">
+        <v>45436</v>
+      </c>
       <c r="I344" s="3" t="n">
         <v>45488</v>
       </c>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Comunicazione e informazione</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Bando per l’erogazione di contributi, per l’anno 2024, per le emittenti radiotelevisive locali e le testate giornalistiche on line locali, ai sensi dell’art. 11 della legge regionale 15 dicembre 2021, n. 34, istitutivo del «Fondo per il pluralismo e l’innovazione dell’informazione».</t>
+        </is>
+      </c>
       <c r="O344" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22476,7 +22628,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -22484,20 +22636,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" s="2" t="n"/>
-      <c r="H345" s="3" t="n"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>17024</v>
+      </c>
+      <c r="H345" s="3" t="n">
+        <v>45443</v>
+      </c>
       <c r="I345" s="3" t="n">
         <v>45488</v>
       </c>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi a sostegno di iniziative volte alla sensibilizzazione della comunità regionale in occasione e secondo le finalità previste dalla Giornata ecologica regionale – Anno 2024 (Legge regionale 24 maggio 2023, n. 10), da programmarsi nel periodo settembre-novembre 2024.</t>
+        </is>
+      </c>
       <c r="O345" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22530,20 +22702,38 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Riconoscimento</t>
+        </is>
+      </c>
       <c r="G346" s="2" t="n"/>
-      <c r="H346" s="3" t="n"/>
+      <c r="H346" s="3" t="n">
+        <v>45464</v>
+      </c>
       <c r="I346" s="3" t="n">
         <v>45485</v>
       </c>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Piano regionale dei percorsi di Istruzione e Formazione Professionale realizzabili in offerta sussidiaria negli Istituti Professionali di Stato. Approvazione dell’Avviso pubblico per la presentazione di domande di attivazione di percorsi triennali per il conseguimento della qualifica professionale nel triennio formativo 2024-2027 o di percorsi di quarto anno per il conseguimento del diploma professionale nell’Anno Formativo 2024-2025. Decreto legislativo 13 aprile 2017, n. 61.</t>
+        </is>
+      </c>
       <c r="O346" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22568,7 +22758,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -22576,20 +22766,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" s="2" t="n"/>
-      <c r="H347" s="3" t="n"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H347" s="3" t="n">
+        <v>45415</v>
+      </c>
       <c r="I347" s="3" t="n">
         <v>45485</v>
       </c>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Aiuti previsti per la misura ristrutturazione e riconversione dei vigneti del Piano Strategico per la PAC - Annualità 2024/2025. DESTINATARI: Conduttori di superfici vitate (viticoltori) NORMATIVA DI RIFERIMENTO: Regolamenti (UE) n. 2115/2021, artt. 58- 59, n. 1308/2013, art. 46 FINALITA’: Favorire attraverso un regime di aiuti, la riconversione e la ristrutturazione dei vigneti con lo scopo di aumentare la competitività. ULTERIORI INFORMAZIONI: Le aziende che intendono presentare domanda di intervento di ristrutturazione e riconversione dei vigneti, devono fare riferimento per quanto riguarda l’entità della spesa massima…</t>
+        </is>
+      </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22622,20 +22832,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
       <c r="G348" s="2" t="n"/>
-      <c r="H348" s="3" t="n"/>
+      <c r="H348" s="3" t="n">
+        <v>45447</v>
+      </c>
       <c r="I348" s="3" t="n">
         <v>45484</v>
       </c>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Assunzione di un mutuo, con oneri a carico della Regione, fino a Euro 22.000.000,00 per il finanziamento di spese di investimento specifiche relative all’esercizio 2024 destinate a interventi relativi alla Tutela e Sicurezza del Territorio ai sensi dell’art. 4 della L.R. 32/2023. LINK PIATTAFORMA APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/ppgare_bandi_lista.wp?actionPath=/ExtStr2/do/FrontEnd/Bandi/view.action&amp;currentFrame=7&amp;codice=G01092&amp;_csrf=GAGNEZ999AXUUY5MGLGYO1YI3RGSGPFA LINK PIATTAFORMA VALORE LEGALE ANAC: https://pubblicitalegale.anticorruzione.it/bandi/d4b342c7-a5d9-4467-a049-be1e1d3b92ee LINK PIATTAFORMA…</t>
+        </is>
+      </c>
       <c r="O348" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22668,20 +22896,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" s="2" t="n"/>
-      <c r="H349" s="3" t="n"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="n">
+        <v>84640125</v>
+      </c>
+      <c r="H349" s="3" t="n">
+        <v>45450</v>
+      </c>
       <c r="I349" s="3" t="n">
         <v>45481</v>
       </c>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Piano Annuale di Formazione Iniziale. Anno Formativo 2024/2025. Approvazione Rivalutazione delle Unita' Di Costo Standard - Costi Standard (art. 53 c.1b Reg. UE 1060/2021 e s.m.i.). Approvazione "Documento di programmazione regionale dell'offerta formativa 'Sistema Duale' finanziata a valere sul PNRR - anno finanziario 2023". Interventi finanziabili con risorse nazionali, del Programma Regionale FSE+ 2021-2027 Priorità 4 Occupazione Giovanile e del Piano nazionale di ripresa e resilienza (PNRR); missione 5 - componente 1 - investimento 1.4 "Sistema Duale". Approvazione dell'Avviso pubblico per la presentazione di progetti per il primo, il…</t>
+        </is>
+      </c>
       <c r="O349" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22714,20 +22962,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" s="2" t="n"/>
-      <c r="H350" s="3" t="n"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H350" s="3" t="n">
+        <v>45443</v>
+      </c>
       <c r="I350" s="3" t="n">
         <v>45473</v>
       </c>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Fondo Comuni Confinanti (L. 23 Dicembre 2009, n.191 e s.m.i.) Progetto strategico finanziato “Miglioramento dell’offerta turistica di alta montagna nelle aree di confine della provincia di Belluno”. CUP assegnato al progetto: H56J17000490001. Approvazione bando pubblico per la concessione di contributi per interventi sui bivacchi fissi alpini. (L.R. 14 giugno 2013, n.11, art. 48 bis, comma 2 lett. d). Beneficiari: proprietari/concessionari bivacchi fissi alpini Scadenza presentazione domande: 30 giugno 2024</t>
+        </is>
+      </c>
       <c r="O350" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22760,20 +23028,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" s="2" t="n"/>
-      <c r="H351" s="3" t="n"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="n">
+        <v>8001655</v>
+      </c>
+      <c r="H351" s="3" t="n">
+        <v>45450</v>
+      </c>
       <c r="I351" s="3" t="n">
         <v>45470</v>
       </c>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Sistema Duale nell'ambito dell'Istruzione e Formazione Professionale. Piano Nazionale di Ripresa e Resilienza (PNRR) - Missione 5 - componente 1 - investimento 1.4 "Sistema Duale". Approvazione dell'Avviso pubblico per la presentazione di progetti formativi per la realizzazione nell'Anno Formativo 2024/2025 di percorsi di quarto anno di Istruzione e Formazione Professionale per il conseguimento del diploma professionale di tecnico nelle sezioni comparti vari ed edilizia, e prosecuzione di una sperimentazione per percorsi di tecnico nella sezione benessere. Sistema Duale. Accordo in Conferenza Stato Regioni del 24/9/2015. Protocollo di Intesa…</t>
+        </is>
+      </c>
       <c r="O351" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22808,18 +23096,32 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" s="2" t="n"/>
-      <c r="H352" s="3" t="n"/>
+      <c r="H352" s="3" t="n">
+        <v>45408</v>
+      </c>
       <c r="I352" s="3" t="n">
         <v>45468</v>
       </c>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per i progetti di cooperazione allo sviluppo sostenibile finalizzati alla costruzione e al ripristino di pozzi e di sistemi di attingimento dell'acqua nel continente africano per l'annualità 2024. DGR n. 171 del 27 febbraio 2024: "Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile". L.R. 21 giugno 2018, n. 21.</t>
+        </is>
+      </c>
       <c r="O352" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22844,7 +23146,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -22852,20 +23154,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" s="2" t="n"/>
-      <c r="H353" s="3" t="n"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H353" s="3" t="n">
+        <v>45429</v>
+      </c>
       <c r="I353" s="3" t="n">
         <v>45463</v>
       </c>
-      <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Con il presente provvedimento, si avvia la procedura per la concessione di contributi a favore della pratica sportiva per l'acquisto di piccole attrezzature sportive di modico valore, indispensabili per lo svolgimento dell 'attività delle associazioni e delle società sportive dilettantistiche. Presentazione domande: dal 21 maggio al 20 giugno 2024 Esiti del bando DDR n. 344 del 24/09/2024: Approvazione esiti istruttori ed assegnazione dei contributi .</t>
+        </is>
+      </c>
       <c r="O353" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22898,20 +23220,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" s="2" t="n"/>
-      <c r="H354" s="3" t="n"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="H354" s="3" t="n">
+        <v>45433</v>
+      </c>
       <c r="I354" s="3" t="n">
         <v>45463</v>
       </c>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>Approvazione dell’Avviso pubblico e della Direttiva “Specialisti per il Domani - Percorsi di Specializzazione Tecnica Superiore (IFTS) 2024-2025” per la presentazione di progetti formativi per i percorsi di istruzione e formazione tecnica superiore 2023-2024 nell’ambito del Fondo per lo Sviluppo e la Coesione 2014-2020 in continuità con il Programma Operativo Regionale - Fondo Sociale Europeo 2014-2020. I percorsi di specializzazione tecnica – IFTS, sono prevalentemente rivolti ai seguenti destinatari: soggetti in possesso del diploma professionale di tecnico. Sono ammessi anche coloro che sono in possesso del diploma di Stato (secondaria II…</t>
+        </is>
+      </c>
       <c r="O354" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22944,20 +23286,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" s="2" t="n"/>
-      <c r="H355" s="3" t="n"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="H355" s="3" t="n">
+        <v>45401</v>
+      </c>
       <c r="I355" s="3" t="n">
         <v>45461</v>
       </c>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Lavoro | Sociale</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 425 del 16 aprile 2024 è stato approvato l'Avviso pubblico per la presentazione di progetti nell’ambito dell’iniziativa denominata “ PASSI Percorsi di Attivazione per lo Sviluppo Sociale e l’Inserimento lavorativo ” a valere sulle risorse del PR FSE+ 2021/27. Con tale iniziativa si intende incentivare l’inclusione attiva per promuovere le pari opportunità, la non discriminazione e la partecipazione attiva e migliorare l’occupabilità, in particolare dei gruppi svantaggiati. Nello specifico, si intende intercettare le persone che fino ad ora non sono state ancora coinvolte nei percorsi di politica attiva anche offrendo…</t>
+        </is>
+      </c>
       <c r="O355" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -22990,20 +23352,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" s="2" t="n"/>
-      <c r="H356" s="3" t="n"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="H356" s="3" t="n">
+        <v>45415</v>
+      </c>
       <c r="I356" s="3" t="n">
         <v>45461</v>
       </c>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>P.R. Veneto FSE+ 2021-2027, Obiettivo "Investimenti per l'occupazione e la crescita" - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 2, Obiettivo specifico ESO4.6 (O.S. f. del Reg. UE 2021/1057). Approvazione dell'Avviso pubblico “MOVE 2024 - Certificazione linguistica in mobilità transnazionale per giovani studenti” per la presentazione di progetti formativi. Obiettivo generale della presente iniziativa è quello di favorire esperienze di mobilità transnazionale per gli studenti iscritti alla classe terza o quarta del secondo ciclo di istruzione e dei percorsi IeFP del Veneto, per l’anno scolastico…</t>
+        </is>
+      </c>
       <c r="O356" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23036,20 +23418,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" s="2" t="n"/>
-      <c r="H357" s="3" t="n"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="H357" s="3" t="n">
+        <v>45335</v>
+      </c>
       <c r="I357" s="3" t="n">
         <v>45460</v>
       </c>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 115 del 12/02/2024 è stato approvato l'Avviso pubblico per la presentazione di progetti nell’ambito dell’iniziativa denominata “ 1.000 GIORNI DI NOI. Interventi di supporto alla genitorialità nella cura di bambini e bambine nei primi tre anni di vita ” a valere sulle risorse del PR FSE+ 2021/27. I progetti dovranno essere presentati secondo i requisiti richiesti dalla Linea 1 progetti verticali , riguardante interventi dedicati allo sviluppo di azioni per il supporto alla genitorialità e alla cura dei minori, e dalla Linea 2 progetto trasversale , riguardante interventi dedicati al coordinamento, al supporto e…</t>
+        </is>
+      </c>
       <c r="O357" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23074,7 +23476,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -23082,20 +23484,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" s="2" t="n"/>
-      <c r="H358" s="3" t="n"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H358" s="3" t="n">
+        <v>45419</v>
+      </c>
       <c r="I358" s="3" t="n">
         <v>45460</v>
       </c>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Istruzione</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per la concessione del contributo regionale " Buono - Scuola" per l'Anno scolastico-formativo 2023-2024. L.R 19 gennaio 2001, n. 1. Deliberazione/CR n.38 del 16/04/2024</t>
+        </is>
+      </c>
       <c r="O358" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23120,7 +23542,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -23128,20 +23550,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" s="2" t="n"/>
-      <c r="H359" s="3" t="n"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="H359" s="3" t="n">
+        <v>45366</v>
+      </c>
       <c r="I359" s="3" t="n">
         <v>45457</v>
       </c>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Aiuti previsti per la misura investimenti del settore vitivinicolo - Annualità 2025/2026 (per anticipo fondi 2025). DESTINATARI: Imprese agricole e aziende di trasformazione e commercializzazione del settore vitivinicolo; NORMATIVA DI RIFERIMENTO: Regolamento (UE) 2115/2021, articoli 58 e 59 FINALITA’: Sostenere lo sviluppo del comparto. L’importo a bando è pari a 9.500.000,00, ripartiti equamente in Euro 4.750.000,00 tra “Azione A - Investimenti nelle aziende agricole vitivinicole bando biennale 2025-2026” e in Euro per l“Azione B – Investimenti per la trasformazione e commercializzazione bando biennale 2025/2026”. Per l’…</t>
+        </is>
+      </c>
       <c r="O359" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23176,18 +23618,32 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" s="2" t="n"/>
-      <c r="H360" s="3" t="n"/>
+      <c r="H360" s="3" t="n">
+        <v>45398</v>
+      </c>
       <c r="I360" s="3" t="n">
         <v>45457</v>
       </c>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Cittadino Impresa</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Indizione e organizzazione del Premio letterario "Regione del Veneto - Leonilde e Arnaldo Settembrini - Mestre", sessantunesima edizione, anno 2024. L.R 49/1989</t>
+        </is>
+      </c>
       <c r="O360" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23220,20 +23676,40 @@
           <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" s="2" t="n"/>
-      <c r="H361" s="3" t="n"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="n">
+        <v>404280</v>
+      </c>
+      <c r="H361" s="3" t="n">
+        <v>45366</v>
+      </c>
       <c r="I361" s="3" t="n">
         <v>45456</v>
       </c>
-      <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Apertura dei termini per la presentazione della domanda di contributo per interventi per il recupero, la conservazione e la valorizzazione del patrimonio culturale risalente alla Repubblica Serenissima di Venezia nell'Istria, nella Dalmazia e nell'area mediterrranea, ai sensi della L.R. 25 settembre 2019, n. 39 - DDR n. 25 del 11.03.2024 (pubblicato BURV n. 35 del 15.03.2024)</t>
+        </is>
+      </c>
       <c r="O361" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23268,18 +23744,32 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" s="2" t="n"/>
-      <c r="H362" s="3" t="n"/>
+      <c r="H362" s="3" t="n">
+        <v>45408</v>
+      </c>
       <c r="I362" s="3" t="n">
         <v>45453</v>
       </c>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per la realizzazione, nel corso del 2024, dell'evento fieristico per la promozione del commercio equo e solidale prevista dall'art. 8 della L.R. 22 gennaio 2010, n. 6. DGR n. 171 del 27 febbraio 2024: "Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile per il triennio 2023-2025. Programmazione degli interventi per l'annualità 2024". Azione 2 a) Interventi a supporto del commercio equo e solidale. L.R. 22 gennaio 2010, n. 6.</t>
+        </is>
+      </c>
       <c r="O362" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23312,20 +23802,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Riconoscimento</t>
+        </is>
+      </c>
       <c r="G363" s="2" t="n"/>
-      <c r="H363" s="3" t="n"/>
+      <c r="H363" s="3" t="n">
+        <v>45279</v>
+      </c>
       <c r="I363" s="3" t="n">
         <v>45446</v>
       </c>
-      <c r="K363" t="inlineStr"/>
-      <c r="L363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>BANDI PREMIO COMPRAVERDE VENETO 2024 - IMPRESE E STAZIONI APPALTANTI</t>
+        </is>
+      </c>
       <c r="O363" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23358,20 +23866,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" s="2" t="n"/>
-      <c r="H364" s="3" t="n"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H364" s="3" t="n">
+        <v>45230</v>
+      </c>
       <c r="I364" s="3" t="n">
         <v>45443</v>
       </c>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Lavoro</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 1304 del 30/10/2023 è stato approvato l'Avviso pubblico/Direttiva per la presentazione di progetti nell’ambito dell’iniziativa denominata " FORTI - FORmazione e TIrocinio " Work Experience breve, dedicata ai disoccupati di età superiore ai 18 anni (o inferiore se hanno assolto l’obbligo formativo) a valere sulle risorse del PR FSE+ 2021/27. Con tale iniziativa si intende garantire una risposta immediata ai fabbisogni formativi delle persone in cerca di lavoro in Veneto, e a quelli professionali delle imprese, attraverso lo sviluppo e l’attuazione di un’offerta di orientamento, formazione e tirocinio taylor made ,…</t>
+        </is>
+      </c>
       <c r="O364" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23404,20 +23932,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" s="2" t="n"/>
-      <c r="H365" s="3" t="n"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="n">
+        <v>24779436</v>
+      </c>
+      <c r="H365" s="3" t="n">
+        <v>45282</v>
+      </c>
       <c r="I365" s="3" t="n">
         <v>45443</v>
       </c>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Approvazione del bando e dello schema di Convenzione tra Regione del Veneto e Agenzia Veneta per i Pagamenti (AVEPA) per l'attuazione delle procedure relative all'Investimento 2.3. "Innovazione e meccanizzazione del settore agricolo e alimentare" - Sottomisura "Ammodernamento delle macchine agricole che permettano l'introduzione di tecniche di agricoltura di precisione" della Misura 2, Missione 2 - Rivoluzione verde e transizione ecologica, Componente 1 - Economia circolare e agricoltura sostenibile (M2C1), finanziato dall'Unione europea - NextGenerationEU. DGR 1599/2023, Allegato A - Testo coordinato con DGR 76 /2024, con…</t>
+        </is>
+      </c>
       <c r="O365" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23450,20 +23998,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" s="2" t="n"/>
-      <c r="H366" s="3" t="n"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>45377</v>
+      </c>
       <c r="I366" s="3" t="n">
         <v>45437</v>
       </c>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Bando per l’assegnazione di contributi destinati a interventi di salvaguardia di beni mobili di particolare valore storico e artistico. DGR n. 195 del 27.2.2024 “Piano annuale degli interventi per la cultura 2024”. L.R. n. 17/2019, art. 17. Link al modulo di domanda Esiti del bando DDR n. 259 del 04/07/2024 - Approvazione delle risultanze di istruttoria e valutazione, della graduatoria e assegnazione dei contributi</t>
+        </is>
+      </c>
       <c r="O366" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23496,20 +24064,40 @@
           <t>Unità Organizzativa Lavori Pubblici</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" s="2" t="n"/>
-      <c r="H367" s="3" t="n"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="H367" s="3" t="n">
+        <v>45387</v>
+      </c>
       <c r="I367" s="3" t="n">
         <v>45432</v>
       </c>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Sostegno finanziario a favore di opere di miglioria, anche strutturale, di impianti sportivi – Approvazione Bando anno 2024 di finanziamento per l’erogazione di contributi a supporto dell’attività degli Enti Locali. (Legge regionale 11 maggio 2015, n. 8, art. 11).</t>
+        </is>
+      </c>
       <c r="O367" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23542,20 +24130,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" s="2" t="n"/>
-      <c r="H368" s="3" t="n"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>45401</v>
+      </c>
       <c r="I368" s="3" t="n">
         <v>45432</v>
       </c>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per l’assegnazione di contributi a musei, archivi e biblioteche riconosciuti, per progetti mirati al raggiungimento o al mantenimento dei livelli minimi di qualità e valorizzazione. DGR n. 195 del 27.2.2024 “Piano annuale degli interventi per la cultura 2024”. L.R. n. 17/2019, artt. 22-24. Esiti del bando DDR n. 313 del 19/08/2024: Approvazione delle risultanze di istruttoria, valutazione e relativa graduatoria di merito, assegnazione dei contributi.</t>
+        </is>
+      </c>
       <c r="O368" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23580,7 +24188,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -23588,20 +24196,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" s="2" t="n"/>
-      <c r="H369" s="3" t="n"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H369" s="3" t="n">
+        <v>45401</v>
+      </c>
       <c r="I369" s="3" t="n">
         <v>45429</v>
       </c>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Concessione di contributi, derivanti dal trasferimento di competenze di cui al D.Lgs 31 marzo 1998, n. 112, a sostegno dell’installazione di impianti di videosorveglianza presso i centri di raccolta e in particolari siti dei territori comunali al fine di prevenire il deposito incontrollato di rifiuti.</t>
+        </is>
+      </c>
       <c r="O369" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23626,7 +24254,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -23634,20 +24262,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" s="2" t="n"/>
-      <c r="H370" s="3" t="n"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H370" s="3" t="n">
+        <v>45289</v>
+      </c>
       <c r="I370" s="3" t="n">
         <v>45428</v>
       </c>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 1 "Un'Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle TIC" OS 1.2 "Permettere ai cittadini, alle imprese, alle organizzazioni di ricerca e alle autorità pubbliche di cogliere i vantaggi della digitalizzazione" Azione 1.2.4 "Organizzazione dell'offerta turistica sul digitale attraverso l'utilizzo del DMS regionale e azioni pilota per Ecosistema Digitale Veneto" Dgr n. 1639 del 22 dicembre 2023 Data apertura domande : 18 gennaio 2024 alle ore 10:00 Data chiusura domande : 16 maggio…</t>
+        </is>
+      </c>
       <c r="O370" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23672,7 +24320,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -23680,20 +24328,38 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
       <c r="G371" s="2" t="n"/>
-      <c r="H371" s="3" t="n"/>
+      <c r="H371" s="3" t="n">
+        <v>45380</v>
+      </c>
       <c r="I371" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Enti locali</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>Contributi regionali alle Intese Programmatiche d'Area finalizzati alla copertura delle spese correnti per il funzionamento delle stesse ed eventuali spese relative alle progettualità. Documentazione da trasmettere entro il 15 maggio 2024 alla Direzione Enti Locali, Procedimenti Elettorali e Grandi Eventi all'indirizzo: entilocaligrandieventi@pec.regione.veneto.it Per informazioni: tel. 041-2794301</t>
+        </is>
+      </c>
       <c r="O371" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23726,20 +24392,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G372" s="2" t="n"/>
-      <c r="H372" s="3" t="n"/>
+      <c r="H372" s="3" t="n">
+        <v>45338</v>
+      </c>
       <c r="I372" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 117 del 12/02/2024, la Giunta regionale ha approvato il bando e disposto l’apertura dei termini di presentazione delle domande di conferma per l’anno 2024 da parte dei beneficiari che si sono impegnati volontariamente ad adottare tecniche agronomiche di gestione agricola o di allevamento definite nei bandi relativi agli interventi del Complemento regionale per lo Sviluppo Rurale del PSN PAC 2023-2027 riportati di seguito. La deliberazione n. 117 è stata pubblicata sul bollettino ufficiale n. 23 del 16 febbraio 2024. Interventi SRA03 - Tecniche di lavorazione ridotta dei suoli; SRA8 Azione 8.1 - Gestione sostenibile dei…</t>
+        </is>
+      </c>
       <c r="O372" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23772,20 +24456,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G373" s="2" t="n"/>
-      <c r="H373" s="3" t="n"/>
+      <c r="H373" s="3" t="n">
+        <v>45338</v>
+      </c>
       <c r="I373" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 118 del 12/02/2024, la Giunta regionale ha approvato il bando e disposto l’apertura dei termini di presentazione delle domande di conferma per l’anno 2024 da parte dei beneficiari che si sono impegnati volontariamente ad adottare tecniche agronomiche di gestione agricola o di allevamento definite nei bandi relativi ai tipi di intervento del Programma di Sviluppo Rurale 2014-2022 riportati di seguito. La deliberazione n. 118 è stata pubblicata sul bollettino ufficiale n. 23 del 16 febbraio 2024. Tipo di intervento 10.1.2 - Ottimizzazione ambientale delle tecniche agronomiche e irrigue, 10.1.6 - Tutela ed incremento degli…</t>
+        </is>
+      </c>
       <c r="O373" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23818,20 +24520,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G374" s="2" t="n"/>
-      <c r="H374" s="3" t="n"/>
+      <c r="H374" s="3" t="n">
+        <v>45338</v>
+      </c>
       <c r="I374" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 119 del 12/02/2024, la Giunta regionale ha approvato il bando e disposto l’apertura dei termini di presentazione delle domande di conferma per l’anno 2024 da parte dei beneficiari che si sono impegnati volontariamente ad adottare tecniche agronomiche di gestione agricola o di allevamento definite nei bandi relativi ai tipi di intervento del Programma di Sviluppo Rurale 2014-2022 riportati di seguito. A tali beneficiari viene data la possibilità di adeguare volontariamente gli impegni agro climatico ambientali, in corso di esecuzione con il prolungamento della durata dell'impegno stesso attraverso la presentazione delle…</t>
+        </is>
+      </c>
       <c r="O374" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23864,20 +24584,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G375" s="2" t="n"/>
-      <c r="H375" s="3" t="n"/>
+      <c r="H375" s="3" t="n">
+        <v>45338</v>
+      </c>
       <c r="I375" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 116 del 12/02/2024, la Giunta regionale ha approvato il bando e disposto l’apertura dei termini di presentazione delle domande di conferma per l’anno 2024 da parte dei beneficiari che hanno aderito, prima del 2012, alla Misura 221 - Primo imboschimento dei terreni agricoli del Programma di Sviluppo Rurale 2007-2013. Scadenza : 15 maggio 2024 Contatti Per informazioni specifiche sul bando: Direzione Agroambiente, programmazione e gestione ittica e faunistico-venatoria Tel. 041 279 5419 e-mail: agroambientecacciapesca@regione.veneto.it Per informazioni generali sui bandi e la loro pianificazione: Direzione ADG FEASR…</t>
+        </is>
+      </c>
       <c r="O375" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23910,20 +24648,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" s="2" t="n"/>
-      <c r="H376" s="3" t="n"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H376" s="3" t="n">
+        <v>45377</v>
+      </c>
       <c r="I376" s="3" t="n">
         <v>45422</v>
       </c>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per il sostegno a biblioteche di ente locale in Comuni fino a 5.000 abitanti. Deliberazione di Giunta regionale n. 195 del 27 febbraio 2024. Piano annuale degli interventi per la cultura 2024. L.R. n. 17/2019, artt. 22-24. Link al modulo di domanda Elenco aggiornato delle biblioteche riconosciute Esiti del bando DDR n. 262 del 04/07/2024: Approvazione delle risultanze di istruttoria, valutazione e relativa graduatoria di merito, assegnazione dei contributi</t>
+        </is>
+      </c>
       <c r="O376" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -23958,18 +24716,32 @@
       </c>
       <c r="F377" t="inlineStr"/>
       <c r="G377" s="2" t="n"/>
-      <c r="H377" s="3" t="n"/>
+      <c r="H377" s="3" t="n">
+        <v>45387</v>
+      </c>
       <c r="I377" s="3" t="n">
         <v>45422</v>
       </c>
-      <c r="K377" t="inlineStr"/>
-      <c r="L377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Istruzione</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Approvazione dell’Avviso pubblico e della Direttiva per la presentazione di progetti per l’ampliamento dell’offerta formativa nelle Scuole dell’infanzia, nelle Istituzioni scolastiche statali e paritarie del primo e secondo ciclo di istruzione e nelle Scuole di Formazione Professionale del Veneto. Anno Scolastico-Formativo 2024/2025. Legge regionale 13 aprile 2001, n. 11, art. 138, comma 1, lett. f).</t>
+        </is>
+      </c>
       <c r="O377" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24002,20 +24774,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" s="2" t="n"/>
-      <c r="H378" s="3" t="n"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H378" s="3" t="n">
+        <v>45391</v>
+      </c>
       <c r="I378" s="3" t="n">
         <v>45421</v>
       </c>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi a sostegno di iniziative volte alla sensibilizzazione della comunità regionale in occasione e secondo le finalità previste dalla Giornata ecologica regionale – Anno 2024 (Legge regionale 24 maggio 2023, n. 10).</t>
+        </is>
+      </c>
       <c r="O378" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24048,20 +24840,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" s="2" t="n"/>
-      <c r="H379" s="3" t="n"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H379" s="3" t="n">
+        <v>45366</v>
+      </c>
       <c r="I379" s="3" t="n">
         <v>45421</v>
       </c>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Approvazione dell'Avviso pubblico ""Formazione Continua. Un'opportunità per la crescita e lo sviluppo delle competenze dei lavoratori" per la presentazione di progetti formativi. PR Veneto FSE+ 2021-2027, Obiettivo “Investimenti per l'occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1.8.2022 - Priorità 1, Obiettivo specifico d) ESO4.4. La presente iniziativa ha la finalità di promuovere l’adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, favorendo lo sviluppo delle capacità necessarie per favorire l’introduzione di soluzioni innovative nei prodotti, processi e…</t>
+        </is>
+      </c>
       <c r="O379" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24094,20 +24906,40 @@
           <t>Unità Organizzativa Tutela dell'Atmosfera</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" s="2" t="n"/>
-      <c r="H380" s="3" t="n"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H380" s="3" t="n">
+        <v>45058</v>
+      </c>
       <c r="I380" s="3" t="n">
         <v>45419</v>
       </c>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi finalizzati alla rottamazione ed acquisto di impianti termici domestici alimentati a biomassa legnosa e pompe di calore elettriche</t>
+        </is>
+      </c>
       <c r="O380" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24140,20 +24972,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" s="2" t="n"/>
-      <c r="H381" s="3" t="n"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H381" s="3" t="n">
+        <v>45387</v>
+      </c>
       <c r="I381" s="3" t="n">
         <v>45418</v>
       </c>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per il sostegno di interventi di valorizzazione del patrimonio archeologico veneto. DGR n. 195 del 27.2.2024, Piano annuale degli interventi per la cultura 2024. L.R. n. 17/2019, artt. 3 e 17. Link al modulo di domanda Esiti del bando DDR n. 260 del 04/07/2024: Approvazione delle risultanze di istruttoria, valutazione e della relativa graduatoria di merito e concessione del contributo</t>
+        </is>
+      </c>
       <c r="O381" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24178,7 +25030,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -24187,19 +25039,35 @@
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" s="2" t="n"/>
-      <c r="H382" s="3" t="n"/>
+      <c r="G382" s="2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H382" s="3" t="n">
+        <v>45335</v>
+      </c>
       <c r="I382" s="3" t="n">
         <v>45415</v>
       </c>
-      <c r="K382" t="inlineStr"/>
-      <c r="L382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Appalto specifico per l’acquisto di cinque isole di armadi rack e dei relativi quadri elettrici d’isola, sistemi di contenimento e compartimentazione, nonché il software di gestione e supporto, nell’ambito del sistema dinamico di acquisizione della pubblica amministrazione (SDAPA) per la fornitura di prodotti e servizi per l'informatica e le telecomunicazioni- ID 2681. Art. 32 D.Lgs. n. 36/2023. Con Decreto n. 24 del 13/03/2024 del Direttore della Direzione ICT e Agenda Digitale è stata nominata la commissione giudicatrice delle offerte</t>
+        </is>
+      </c>
       <c r="O382" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24232,20 +25100,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G383" s="2" t="n"/>
-      <c r="H383" s="3" t="n"/>
+      <c r="H383" s="3" t="n">
+        <v>45293</v>
+      </c>
       <c r="I383" s="3" t="n">
         <v>45413</v>
       </c>
-      <c r="K383" t="inlineStr"/>
-      <c r="L383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste | Attività produttive</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 1635 del 22/12/2023, la Giunta regionale ha approvato il bando e disposto l’apertura dei termini di presentazione delle domande per il tipo di intervento 4.2.1 Investimenti per la trasformazione e commercializzazione dei prodotti agricoli del Programma di Sviluppo Rurale per il Veneto 2014-2022. La deliberazione n. 1635 è stata pubblicata sul bollettino ufficiale n. 2 del 02/01/2024. Tipo di intervento 4.2.1 “Investimenti per la trasformazione e commercializzazione dei prodotti agricoli” Beneficiari: Imprese agroalimentari che svolgono sia l’attività di trasformazione che di commercializzazione di prodotti agricoli…</t>
+        </is>
+      </c>
       <c r="O383" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24278,20 +25164,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" s="2" t="n"/>
-      <c r="H384" s="3" t="n"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H384" s="3" t="n">
+        <v>45373</v>
+      </c>
       <c r="I384" s="3" t="n">
         <v>45412</v>
       </c>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Programma annuale 2024 degli interventi per la celebrazione del Giorno della Memoria e il contrasto all’antisemitismo con la promozione della conoscenza della cultura ebraica. Art. 4, comma 1, Legge regionale 3 febbraio 2020, n. 5 Esiti del bando DDR n. 265 del 05/07/2024: Approvazione dei risultati d'istruttoria, valutazione, delle relative graduatorie e assegnazione dei contributi</t>
+        </is>
+      </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24324,20 +25230,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" s="2" t="n"/>
-      <c r="H385" s="3" t="n"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H385" s="3" t="n">
+        <v>45380</v>
+      </c>
       <c r="I385" s="3" t="n">
         <v>45411</v>
       </c>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per la concessione di contributi per il sostegno a premi e concorsi regionali, nazionali, europei e internazionali di ambito culturale. DGR n. 195/2024 "Piano annuale degli interventi per la cultura 2024". L.R. n. 17/2019, art. 32. Link al modulo di domanda Esiti del bando DDR n. 255 del 02/07/2024: Approvazione della graduatoria dei progetti di Premi culturali. Bando per la concessione di contributi a sostegno di premi e concorsi regionali, nazionali, europei e internazionali di ambito culturale. Anno 2024 DGR n. 822 del 12/07/2024: Assegnazione contributi ai soggetti beneficiari del bando a sostegno dei Premi…</t>
+        </is>
+      </c>
       <c r="O385" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24370,20 +25296,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" s="2" t="n"/>
-      <c r="H386" s="3" t="n"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H386" s="3" t="n">
+        <v>45380</v>
+      </c>
       <c r="I386" s="3" t="n">
         <v>45411</v>
       </c>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Approvazione del bando 2024 per la concessione di contributi a sostegno di iniziative di promozione della cultura cinematografica. DGR n. 195/2024 "Piano annuale degli interventi per la cultura 2024". L.R. n. 17/2019, artt. 4, 9 e 36. Link al modulo di domanda Esiti del bando DDR n. 245 del 19/06/2024: Approvazione della graduatoria dei progetti di promozione della cultura cinematografica anno 2024 DGR n. 823 del 12/07/2024: Assegnazione contributi ai soggetti beneficiari del bando a sostegno di iniziative di promozione della cultura cinematografica e audiovisiva anno 2024</t>
+        </is>
+      </c>
       <c r="O386" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24416,20 +25362,40 @@
           <t>Direzione Agroambiente, Programmazione e Gestione Ittica e Faunistico-Venatoria</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" s="2" t="n"/>
-      <c r="H387" s="3" t="n"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H387" s="3" t="n">
+        <v>45380</v>
+      </c>
       <c r="I387" s="3" t="n">
         <v>45411</v>
       </c>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Bando per l'erogazione di sovvenzioni in regime "de minimis" al Consorzio Cooperative Pescatori del Polesine e alle imprese che gestiscono mercati ittici che operano nelle aree lagunari del Delta del Po Veneto per la cattura e lo smaltimento di esemplari non commercializzabili della specie aliena denominata Granchio blu (Callinectes sapidus).</t>
+        </is>
+      </c>
       <c r="O387" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24462,20 +25428,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G388" s="2" t="n"/>
-      <c r="H388" s="3" t="n"/>
+      <c r="H388" s="3" t="n">
+        <v>45289</v>
+      </c>
       <c r="I388" s="3" t="n">
         <v>45409</v>
       </c>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste | Agriturismo | Ambiente | Attività produttive | Ricerca e innovazione</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Con deliberazione n. 1597 del 19/12/2023, pubblicata sul bollettino ufficiale n.172 del 29/12/2023, la Giunta regionale ha approvato i bandi e disposto l’apertura dei termini di presentazione delle domande per i seguenti interventi del Complemento regionale per lo sviluppo rurale della PAC 2023-2027 del Veneto. Pacchetto giovani Il “ Pacchetto Giovani ” è composto dalla combinazione del seguente intervento: SRE01 – Insediamento giovani agricoltori (intervento obbligatorio) Beneficiari: giovani agricoltori di età maggiore di 18 anni e inferiore a 41 anni, che si insediano per la prima volta in un’azienda agricola in qualità di capo…</t>
+        </is>
+      </c>
       <c r="O388" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24508,20 +25492,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" s="2" t="n"/>
-      <c r="H389" s="3" t="n"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H389" s="3" t="n">
+        <v>45377</v>
+      </c>
       <c r="I389" s="3" t="n">
         <v>45408</v>
       </c>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi a sostegno di interventi di welfare e rigenerazione umana da realizzare all’interno di istituti e luoghi culturali o, in collaborazione con essi, in sedi di ricovero assistenziali, di cura medica e socio assistenziale, case di riposo, istituti di detenzione. Link al modulo di domanda Esiti del bando DDR n. 258 del 04/07/2024: Approvazione delle risultanze di istruttoria, valutazione, della relativa graduatoria di merito e assegnazione dei contributi</t>
+        </is>
+      </c>
       <c r="O389" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24554,20 +25558,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" s="2" t="n"/>
-      <c r="H390" s="3" t="n"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H390" s="3" t="n">
+        <v>45377</v>
+      </c>
       <c r="I390" s="3" t="n">
         <v>45408</v>
       </c>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Approvazione del bando per la concessione di contributi a sostegno alle attività di istituzioni, enti e soggetti culturali per studi, ricerche e iniziative culturali. DGR n. 195/2024 "Piano annuale degli interventi per la cultura 2024". L.R. n. 17/2019, art. 32. Link al modulo di domanda Esiti del bando DDR n. 249 del 25/06/2024: Approvazione della graduatoria dei progetti di Attività Culturali. Bando per la concessione di contributi a sostegno delle attività di istituzioni, enti e soggetti culturali per studi, ricerche e iniziative culturali. Anno 2024 DGR n. 826 del 12/07/2024: Assegnazione dei contributi ai soggetti beneficiari del bando…</t>
+        </is>
+      </c>
       <c r="O390" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24592,7 +25616,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -24600,20 +25624,38 @@
           <t>Area Risorse Finanziarie, Strumentali, Ict Ed Enti Locali</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G391" s="2" t="n"/>
-      <c r="H391" s="3" t="n"/>
+      <c r="H391" s="3" t="n">
+        <v>45387</v>
+      </c>
       <c r="I391" s="3" t="n">
         <v>45405</v>
       </c>
-      <c r="K391" t="inlineStr"/>
-      <c r="L391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Cittadino Impresa</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Bilancio ragioneria e programmazione | Sociale</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>NOVITA' Fra gli allegati è pubblicato il Decreto n. 34 del 17.06.2024. Approvazione e pubblicazione degli elenchi delle domande dei “cedenti” relative alla “Manifestazione di interesse” di cui alla DGR 202/2024, in materia di cessione dei “Bonus fiscali edilizi”. FINALITÀ E OGGETTO DELLA MANIFESTAZIONE DI INTERESSE La Regione del Veneto intende formare un elenco di cittadini e imprese del territorio della Regione Veneto che hanno manifestato l’interesse a cedere crediti d’imposta derivanti da interventi di edilizia privata di tipo Superbonus (artt. 119 e 121 del Decreto Legge 19 maggio 2020, n. 34 e successive modificazioni) di cui sono…</t>
+        </is>
+      </c>
       <c r="O391" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24646,20 +25688,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" s="2" t="n"/>
-      <c r="H392" s="3" t="n"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H392" s="3" t="n">
+        <v>45373</v>
+      </c>
       <c r="I392" s="3" t="n">
         <v>45404</v>
       </c>
-      <c r="K392" t="inlineStr"/>
-      <c r="L392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Bando per la promozione e il sostegno di attività di spettacolo dal vivo professionistico programmate e realizzate per l’anno 2024, relative a musica, teatro, danza, circo contemporaneo, multidisciplinarietà. Link al modulo di domanda I moduli da allegare alla domanda sono pubblicati in fondo a questa pagina. Esiti del bando DDR n. 254 del 02/07/2024: Approvazione della graduatoria dei progetti annuali dello spettacolo dal vivo professionistico anno 2024 DGR n. 825 del 12/07/2024: Assegnazione dei contributi ai beneficiari del bando per il sostegno delle attività dei soggetti operanti nel territorio del Veneto nel settore dello spettacolo…</t>
+        </is>
+      </c>
       <c r="O392" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24692,20 +25754,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" s="2" t="n"/>
-      <c r="H393" s="3" t="n"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H393" s="3" t="n">
+        <v>45366</v>
+      </c>
       <c r="I393" s="3" t="n">
         <v>45397</v>
       </c>
-      <c r="K393" t="inlineStr"/>
-      <c r="L393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Approvazione del bando 2024 per la concessione di contributi per attività di Audience Development. DGR n. 195/2024 “Piano annuale degli interventi per la cultura 2024”. L.R. n. 17/2019, art. 4. Link al modulo di domanda Esiti del bando DDR n. 244 del 19/06/2024: Approvazione della graduatoria dei progetti di Audience Development anno 2024 DGR n. 824 del 12/07/2024: Assegnazione contributi ai soggetti beneficiari del bando a sostegno di progetti di Audience Development anno 2024</t>
+        </is>
+      </c>
       <c r="O393" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24730,7 +25812,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -24738,20 +25820,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" s="2" t="n"/>
-      <c r="H394" s="3" t="n"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H394" s="3" t="n">
+        <v>45289</v>
+      </c>
       <c r="I394" s="3" t="n">
         <v>45393</v>
       </c>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 1 "Un'Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle TIC" OS 1.3 "Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR)" Azione 1.3.8 "Rigenerazione e innovazione delle imprese. Interventi finalizzati a sostenere la valorizzazione turistica del territorio". Dgr n. 1640 del 22 dicembre 2023 Data apertura domande : 25 gennaio 2024 ore 10:00 Data chiusura domande : 11 aprile 2024 ore…</t>
+        </is>
+      </c>
       <c r="O394" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24784,20 +25886,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G395" s="2" t="n"/>
-      <c r="H395" s="3" t="n"/>
+      <c r="H395" s="3" t="n">
+        <v>45352</v>
+      </c>
       <c r="I395" s="3" t="n">
         <v>45391</v>
       </c>
-      <c r="K395" t="inlineStr"/>
-      <c r="L395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Indizione di una procedura aperta telematica, ai sensi dell’articolo 71 del D.lgs. 31 marzo 2023, n. 36, per l’affidamento del pacchetto di servizi di comunicazione per il Programma Interreg VI A Italia-Croazia 2021-2027. Approvazione atti di gara. Codice Gara Apptel: G00721 - CUP: H79B22000260007 – CUI: S80007580279202300164, CIG: B09613F3D0.</t>
+        </is>
+      </c>
       <c r="O395" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24830,20 +25950,40 @@
           <t>Direzione Ict e Agenda Digitale</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" s="2" t="n"/>
-      <c r="H396" s="3" t="n"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>19022000</v>
+      </c>
+      <c r="H396" s="3" t="n">
+        <v>45356</v>
+      </c>
       <c r="I396" s="3" t="n">
         <v>45390</v>
       </c>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Indizione di una procedura d’acquisto ristretta telematica sopra soglia comunitaria, ex art. 72 D.Lgs. 36/2023, per l’acquisto dei servizi di conduzione e manutenzione del sistema di comunicazione radio di Regione del Veneto della durata di 60 mesi, con opzione di proroga tecnica di n. 12 mesi e di aumento delle prestazioni entro il quinto dell’importo contrattuale. CIG B09CFF82D9, CUP H17G24000030002, CUI S80007580279202300106. A tal fine, sarà utilizzato il criterio dell’offerta economicamente più vantaggiosa ex art. 108, co. 1, del D.Lgs. n. 36/2023, per un importo a base d’asta di complessivi € 19.022.000,00=IVA esclusa. La procedura di…</t>
+        </is>
+      </c>
       <c r="O396" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24876,20 +26016,40 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" s="2" t="n"/>
-      <c r="H397" s="3" t="n"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>37512746</v>
+      </c>
+      <c r="H397" s="3" t="n">
+        <v>45363</v>
+      </c>
       <c r="I397" s="3" t="n">
         <v>45387</v>
       </c>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Assunzione di un mutuo fino a Euro 43.500.000,00= per il finanziamento di spese di investimento specifiche relative all' esercizio 2024 destinate a interventi relativi ai Giochi Olimpici e Paralimpici invernali Milano Cortina 2026, ai sensi dell'art. 4 della L.R. 32/2023. CIG: B0B919AF4F APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/homepage.wp?actionPath=/ExtStr2/do/FrontEnd/Bandi/view.action&amp;currentFrame=7&amp;codice=G00752&amp;_csrf=MJM2QPI534QDO0VCYOY15SDDINMW94W3 PIATTAFORMA VALORE LEGALE ANAC: https://pubblicitalegale.anticorruzione.it/bandi/b497c6e6-620c-4fa5-9d36-59a134cc6a41 PIATTAFORMA UNICA TRASPARENZA BDNCP:…</t>
+        </is>
+      </c>
       <c r="O397" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24922,20 +26082,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" s="2" t="n"/>
-      <c r="H398" s="3" t="n"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H398" s="3" t="n">
+        <v>45338</v>
+      </c>
       <c r="I398" s="3" t="n">
         <v>45386</v>
       </c>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Con DDR n. 295 del 04 marzo 2024 sono stati prorogati i termini per la presentazione dei progetti al 04 aprile 2024, ore 13.00 La Giunta regionale ha stabilito, nell’ambito del Programma Regionale Veneto per il sostegno del Fondo Sociale Europeo Plus per il ciclo di programmazione 2021-2027 Obiettivo “Investimenti per l’occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 1 Obiettivo specifico d), l'apertura dei termini per la presentazione di progetti formativi finalizzati a promuovere interventi per l’adattamento delle persone ai cambiamenti complessi del mercato del lavoro,…</t>
+        </is>
+      </c>
       <c r="O398" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -24968,20 +26148,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" s="2" t="n"/>
-      <c r="H399" s="3" t="n"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H399" s="3" t="n">
+        <v>45267</v>
+      </c>
       <c r="I399" s="3" t="n">
         <v>45381</v>
       </c>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Fondo Sociale Europeo</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Con DDR n. 220 del 13 febbraio 2024 sono stati prorogati i termini per la presentazione dei progetti al 30 marzo 2024, ore 13.00 Avviso pubblico "Lo sviluppo delle competenze nel settore dell’occhialeria 2023-2025". La Giunta regionale ha stabilito, nell’ambito del Programma Regionale Veneto per il sostegno del Fondo Sociale Europeo Plus per il ciclo di programmazione 2021-2027 Obiettivo “Investimenti per l’occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 1 Obiettivo specifico d) e in attuazione del Protocollo d’Intesa di cui alla DGR n. 1729 del 30.12.2022 tra Regione del…</t>
+        </is>
+      </c>
       <c r="O399" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25014,20 +26214,40 @@
           <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" s="2" t="n"/>
-      <c r="H400" s="3" t="n"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>270000</v>
+      </c>
+      <c r="H400" s="3" t="n">
+        <v>45335</v>
+      </c>
       <c r="I400" s="3" t="n">
         <v>45380</v>
       </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Protezione civile</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi finalizzati alla manutenzione straordinaria di mezzi e attrezzature delle organizzazioni di volontariato impiegati nelle emergenze regionali, ai sensi della DGR n. 1385 del 20.11.2023.</t>
+        </is>
+      </c>
       <c r="O400" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25060,20 +26280,40 @@
           <t>Direzione Edilizia Ospedaliera A Finalita' Collettiva</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" s="2" t="n"/>
-      <c r="H401" s="3" t="n"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Fondo di rotazione</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>24870000</v>
+      </c>
+      <c r="H401" s="3" t="n">
+        <v>45349</v>
+      </c>
       <c r="I401" s="3" t="n">
         <v>45379</v>
       </c>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Con Deliberazione di Giunta n. 144 del 20/02/2024 si approvano le modalità e i termini per l'ammissione a finanziamento regionale in conto capitale a rimborso graduale, secondo quote annuali costanti, senza oneri per interessi per la realizzazione di interventi edilizi sul patrimonio immoniliare di proprietà di soggetti pubblici o soggetti privati non a scopo di lucro nel settore sociale e socio-sanitario ( art. 44 della LR 45 del 29/12/2017 " Collegato alla legge di stabilità regionale 2018" e s.m.i.)</t>
+        </is>
+      </c>
       <c r="O401" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25106,20 +26346,40 @@
           <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" s="2" t="n"/>
-      <c r="H402" s="3" t="n"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H402" s="3" t="n">
+        <v>45335</v>
+      </c>
       <c r="I402" s="3" t="n">
         <v>45370</v>
       </c>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Attività produttive</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Bando per l'erogazione di contributi alle PMI giovanili. Anno 2024. Legge regionale 24 dicembre 1999, n. 57. Approvato con DGR n. 92 del 12 febbraio 2024. ULTERIORI INFORMAZIONI La domanda di sostegno deve essere compilata e presentata esclusivamente per via telematica, attraverso il Sistema Informativo Unificato della Programmazione Unitaria (SIU) della Regione, previa richiesta delle credenziali di accesso al sistema, tramite l’applicativo GUSI, attivo al seguente link: https://siu.regione.veneto.it/GUSI/ . La domanda può essere presentata a partire dalle ore 10.00 di martedì 5 marzo 2024, fino alle ore 12.00 di martedì 19 marzo 2024. Per…</t>
+        </is>
+      </c>
       <c r="O402" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25144,7 +26404,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -25152,20 +26412,40 @@
           <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" s="2" t="n"/>
-      <c r="H403" s="3" t="n"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H403" s="3" t="n">
+        <v>45324</v>
+      </c>
       <c r="I403" s="3" t="n">
         <v>45369</v>
       </c>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Avviso pubblico per l’approvazione di progetti da parte delle Amministrazioni locali venete in cui si parla in friulano per attivare eventi culturali nell’ambito dell’iniziativa PRIMIS PLUS “Storie di multiculturalità: viaggio sensoriale attraverso il prisma delle minoranze”, CUP H39I23000550007, finanziato dal Programma Interreg VI A Italia-Slovenia 2021-2027- Primo bando per la selezione di progetti di capitalizzazione (n. 01/2022)</t>
+        </is>
+      </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25198,20 +26478,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" s="2" t="n"/>
-      <c r="H404" s="3" t="n"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>7966000</v>
+      </c>
+      <c r="H404" s="3" t="n">
+        <v>45300</v>
+      </c>
       <c r="I404" s="3" t="n">
         <v>45365</v>
       </c>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Lavoro</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Con Deliberazione n. 1688 del 29 dicembre 2023 è stato approvato l'Avviso n. 7 che norma la presentazione di proposte progettuali per l’attuazione del Percorso 4 - Lavoro e Inclusione Annualità 2023-2024 nell'ambito del Programma Garanzia Occupabilità dei Lavovoratori (GOL). I progetti per il Percorso 4, uno per ognuna delle 9 ULSS venete, dovranno strutturarsi in coerenza con il sistema territoriale di servizi e misure rivolti ai soggetti svantaggiati, creando partenariati ampi e multidisciplinari, per incrementare la capacità della rete di rispondere efficacemente ai bisogni complessi dei beneficiari. Particolare attenzione deve essere…</t>
+        </is>
+      </c>
       <c r="O404" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25244,20 +26544,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" s="2" t="n"/>
-      <c r="H405" s="3" t="n"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H405" s="3" t="n">
+        <v>45287</v>
+      </c>
       <c r="I405" s="3" t="n">
         <v>45363</v>
       </c>
-      <c r="K405" t="inlineStr"/>
-      <c r="L405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>FESR | Istruzione</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Il bando intende sostenere le Scuole della Formazione Professionale del territorio regionale nell'acquisizione di dotazioni infrastrutturali e laboratoriali assicurando alla popolazione giovanile strumenti efficaci in termini di adattamento alle esigenze del mercato del lavoro, la garanzia di un apprendimento di qualità, il sostegno dell'adeguamento sostenibile, inclusivo ed efficace dei sistemi di istruzione e formazione, in coerenza con la LR . 8/2017 "Il sistema educativo della Regione Veneto". Ai fini del presente bando sono ammissibili al sostegno gli interventi volti a: a) potenziamento delle dotazioni laboratoriali (es. allestimento…</t>
+        </is>
+      </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25290,20 +26610,40 @@
           <t>Unità Organizzativa Lavori Pubblici</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" s="2" t="n"/>
-      <c r="H406" s="3" t="n"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="H406" s="3" t="n">
+        <v>45250</v>
+      </c>
       <c r="I406" s="3" t="n">
         <v>45351</v>
       </c>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>PR Veneto FESR 2021-2027. Priorità 2 “Un’Europa resiliente, più verde e a basse emissioni di carbonio ma in transizione verso un’energia pulita ed equa, di investimenti verdi e blu, dell’economia circolare, dell’adattamento ai cambiamenti climatici e della loro mitigazione, della gestione e prevenzione dei rischi nonché della mobilità urbana sostenibile” OS i “Promuovere l'efficienza energetica e ridurre le emissioni di gas a effetto serra”. Azione 2.1.1 “Efficienza energetica edifici pubblici (non residenziale)”. Approvazione bando per l’erogazione di contributi. DDR n. 2 del 24.01.204:¿ Proroga dei termini per la presentazione delle…</t>
+        </is>
+      </c>
       <c r="O406" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25336,20 +26676,40 @@
           <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" s="2" t="n"/>
-      <c r="H407" s="3" t="n"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>45275</v>
+      </c>
       <c r="I407" s="3" t="n">
         <v>45351</v>
       </c>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Il Bando sostiene la creazione e lo sviluppo delle nuove Comunità di Energia Rinnovabile. I beneficiari del contributo sono le Comunità Energetiche Rinnovabili, costituite in conformità con la Dir. 2018/2001/UE e con le norme nazionali di recepimento della stessa (Dl 162/2019 conv. L. 8/2020 e D.Lgs. 199/2021). Possono presentare domanda di sostegno i soggetti in possesso dei requisiti previsti dal bando, che soddisfano i requisiti per essere membri di una CER, con la condizione che al momento della sua costituzione il soggetto faccia formalmente parte della Comunità Energetica Rinnovabile. In caso di CER già costituita, la domanda di…</t>
+        </is>
+      </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25374,7 +26734,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -25384,18 +26744,32 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" s="2" t="n"/>
-      <c r="H408" s="3" t="n"/>
+      <c r="H408" s="3" t="n">
+        <v>45272</v>
+      </c>
       <c r="I408" s="3" t="n">
         <v>45341</v>
       </c>
-      <c r="K408" t="inlineStr"/>
-      <c r="L408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Ambiente | Territorio</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Opere di laminazione sul fiume Monticano - Comune di Fontanelle - TV. Stralcio n. 1 dell'intervento di ampliamento e regimazione della cassa di espansione di Pra' dei Gai per la laminazione delle piene del fiume Livenza alla confluenza con il fiume Meduna. CUP: H52B22003430001 Importo complessivo di € 8.750.000,00 Affidamento dei lavori. Importo a base di gara complessivo pari ad € 6.355.896,41 Importo stimato dell’appalto pari ad € 7.627.075,69 CIG: A03B8D1ACA – APPTEL: G00632 Gara indetta con Decreto n. 466 del 14/12/2023 La documentazione di gara è disponibile al seguente link : https://sharing.regione.veneto.it/index.php/s/ZK3TzCK4djgs5i5</t>
+        </is>
+      </c>
       <c r="O408" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25428,20 +26802,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" s="2" t="n"/>
-      <c r="H409" s="3" t="n"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Riconoscimento</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H409" s="3" t="n">
+        <v>45317</v>
+      </c>
       <c r="I409" s="3" t="n">
         <v>45341</v>
       </c>
-      <c r="K409" t="inlineStr"/>
-      <c r="L409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Città veneta della cultura - Bando di concorso per l’anno 2024 - LR n. 20/2021 e s.m.i. DGR n. 1110 /2021 Esiti del bando DPGR n. 47 del 20/05/2024: Conferimento del titolo di "Città veneta della cultura" per l'anno 2024 al Comune di San Giovanni Lupatoto (VR)</t>
+        </is>
+      </c>
       <c r="O409" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25474,20 +26868,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" s="2" t="n"/>
-      <c r="H410" s="3" t="n"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>915227</v>
+      </c>
+      <c r="H410" s="3" t="n">
+        <v>45226</v>
+      </c>
       <c r="I410" s="3" t="n">
         <v>45337</v>
       </c>
-      <c r="K410" t="inlineStr"/>
-      <c r="L410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Approvazione del bando e dello schema di Convenzione tra Regione del Veneto e Agenzia Veneta per i Pagamenti (AVEPA) per l'attuazione delle procedure relative all'Investimento 2.3. "Innovazione e meccanizzazione del settore agricolo e alimentare" - Sottomisura "Ammodernamento frantoi oleari" della Misura 2, Missione 2 - Rivoluzione verde e transizione ecologica, Componente 1 - Economia circolare e agricoltura sostenibile (M2C1), finanziato dall'Unione europea - NextGenerationEU. NORMATIVA DI RIFERIMENTO: Regolamento (UE) 2021/241 del Parlamento Europeo e del Consiglio; ULTERIORI INFORMAZIONI: DGR n. 1234 del 10 ottobre 2023…</t>
+        </is>
+      </c>
       <c r="O410" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25520,20 +26934,40 @@
           <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" s="2" t="n"/>
-      <c r="H411" s="3" t="n"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H411" s="3" t="n">
+        <v>45261</v>
+      </c>
       <c r="I411" s="3" t="n">
         <v>45337</v>
       </c>
-      <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Attività produttive | FESR | Formazione | Ricerca e innovazione</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Il bando finanzia un'azione “pilota” dedicata alle imprese (PMI) che già aderiscono alla data 01/12/2023 a una delle Reti Innovative Regionali riconosciute dalla Regione del Veneto. È finanziata l’attuazione di un percorso di sviluppo di competenze specifiche per la transizione industriale e per la specializzazione intelligente (S3 Veneto) articolato nelle seguenti due fasi: Fase 1: Check up dell’innovazione . L’impresa beneficiaria effettua presso la propria sede un assessment aziendale per l’innovazione al fine di focalizzare i fabbisogni di innovazione tenendo conto delle principali sfide tecnologiche e di sostenibilità. Il servizio di…</t>
+        </is>
+      </c>
       <c r="O411" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25558,7 +26992,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -25568,18 +27002,32 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" s="2" t="n"/>
-      <c r="H412" s="3" t="n"/>
+      <c r="H412" s="3" t="n">
+        <v>45279</v>
+      </c>
       <c r="I412" s="3" t="n">
         <v>45327</v>
       </c>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Ambiente | Territorio</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Progetto di un’opera di invaso (cosiddetta “Anconetta”) sul fiume Agno-Guà-Santa Caterina nei Comuni di Sant’Urbano e Vighizzolo d’Este (PD) – ID Piano 212. Opere di 1° stralcio afferenti il potenziamento della botte tre canne. 1° stralcio: CUP H87B20008890002 - Codice ReNDiS 05IR347/G1 Completamento: CUP H82B22004060001 - Codice ReNDiS 05IR001/MT Importo complessivo di € 14.697.329,45 Affidamento dei lavori di 1° stralcio e completamento. Importo a base di gara complessivo pari ad € 10.837.727,26. Importo stimato dell’appalto pari ad € 13.005.272,71. CIG: A039AD083B – APPTEL: G00631 Gara indetta con Decreto n. 464 del 14/12/2023 La…</t>
+        </is>
+      </c>
       <c r="O412" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25612,20 +27060,40 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" s="2" t="n"/>
-      <c r="H413" s="3" t="n"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>45279</v>
+      </c>
       <c r="I413" s="3" t="n">
         <v>45322</v>
       </c>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Programmi Operativi della Regione del Veneto Fondo Europeo di Sviluppo Regionale 2021-2027 (PR FESR 2021-2027) e Fondo Sociale Europeo Plus 2021-2027 (PR FSE + 2021-2027). Priorità Assistenza tecnica. Acquisizione del Servizio di valutazione unitaria del PR Veneto FESR 2021-2027 e del PR Veneto FSE+ 2021-2027, ai sensi degli art. 71 e 108 del D.Lgs. 31 marzo 2023 n. 36. Indizione gara e approvazione dei relativi atti. CUP H71C23000500009 (QUOTA FESR) - CUP H71C23000510009 (QUOTA FSE) - CIG: A037A6BCA0 - CUI: S80007580279202300140. Responsabile Unico del Progetto - Dott. Stefano Tinazzi (nominato con DDR n. 3 del 11/05/2026) in sostituzione…</t>
+        </is>
+      </c>
       <c r="O413" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25658,20 +27126,38 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
       <c r="G414" s="2" t="n"/>
-      <c r="H414" s="3" t="n"/>
+      <c r="H414" s="3" t="n">
+        <v>45289</v>
+      </c>
       <c r="I414" s="3" t="n">
         <v>45320</v>
       </c>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>DELIBERAZIONE DELLA GIUNTA REGIONALE N. 1415 del 20/11/2023 Bando per il sostegno alle imprese agricole colpite dalla flavescenza dorata della vite. Anno 2023. Legge 29 dicembre 2022 n. 197, art. 1, comma 433. Decreto del Ministero dell'agricoltura, della sovranità alimentare e delle foreste 6 giugno 2023 n. 291933. CONDUTTORE: AVEPA DESTINATARI: Imprese. NORMATIVA DI RIFERIMENTO Legge 29 dicembre 2022 n. 197, art. 1, comma 433. FINALITA’: l’erogazione di un contributo pubblico a favore delle imprese agricole che hanno subito danni alle produzioni causati dalla flavescenza dorata della vite finalizzato al ripristino del potenziale…</t>
+        </is>
+      </c>
       <c r="O414" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25696,7 +27182,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -25705,19 +27191,35 @@
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" s="2" t="n"/>
-      <c r="H415" s="3" t="n"/>
+      <c r="G415" s="2" t="n">
+        <v>5816600</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>45219</v>
+      </c>
       <c r="I415" s="3" t="n">
         <v>45320</v>
       </c>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>ICT | Informatica e-government</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Attuazione del P.N.R.R. Approvazione del secondo avviso pubblico rivolto ai Comuni veneti relativo al Progetto "Rete di Servizi di Facilitazione Digitale" per l'attuazione del Piano Operativo della Regione del Veneto approvato con DGR n. 1384/2022, nell'ambito della Misura 1.7.2 (Missione 1, Componente 1, Asse 1) del Piano Nazionale di Ripresa e Resilienza (PNRR). Con DDR n. 9 del 05/02/2024 del Direttore della Direzione ICT e Agenda Digitale è stata nominata la Commissione Tecnica di Valutazione (CTV)</t>
+        </is>
+      </c>
       <c r="O415" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25742,7 +27244,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -25752,18 +27254,32 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" s="2" t="n"/>
-      <c r="H416" s="3" t="n"/>
+      <c r="H416" s="3" t="n">
+        <v>45267</v>
+      </c>
       <c r="I416" s="3" t="n">
         <v>45319</v>
       </c>
-      <c r="K416" t="inlineStr"/>
-      <c r="L416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Ricerca e innovazione</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Con il presente provvedimento vengono modificati gli artt. 6 "Spese ammesse" comma 4 e 7 "Spese non ammesse" comma 2, dell'Allegato A "Bando per il sostegno agli investimenti nelle Infrastrutture di ricerca" alla DGR n. 1237 del 10 ottobre 2023, ridefinendo l'ammissibilità del costo relativo all'IVA ai sensi dell'articolo 7 del Regolamento (UE) n. 651/2014 come modificato dal Regolamento (UE) n. 1315/2023.</t>
+        </is>
+      </c>
       <c r="O416" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25788,7 +27304,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -25796,20 +27312,40 @@
           <t>Direzione Servizi Sociali</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" s="2" t="n"/>
-      <c r="H417" s="3" t="n"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="H417" s="3" t="n">
+        <v>45293</v>
+      </c>
       <c r="I417" s="3" t="n">
         <v>45311</v>
       </c>
-      <c r="K417" t="inlineStr"/>
-      <c r="L417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Avviso di indizione di istruttoria pubblica per la manifestazione di interesse alla co-progettazione di interventi di assistenza a favore delle vittime di tratta e grave sfruttamento, nell’ambito del Bando 6/2023 della Presidenza del Consiglio dei Ministri - Dipartimento per le Pari Opportunità. DGR n. 1685 del 29 dicembre 2023.</t>
+        </is>
+      </c>
       <c r="O417" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25842,20 +27378,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G418" s="2" t="n"/>
-      <c r="H418" s="3" t="n"/>
+      <c r="H418" s="3" t="n">
+        <v>45258</v>
+      </c>
       <c r="I418" s="3" t="n">
         <v>45306</v>
       </c>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Indizione di una procedura aperta telematica, ai sensi dell’articolo 71 del D.lgs. 31 marzo 2023, n. 36, per l’affidamento del servizio di ideazione e realizzazione degli interventi di informazione e pubblicità del PR Veneto FSE + 2021 – 2027 e del PR Veneto FESR 2021 – 2027. Approvazione atti di gara. CIG A02C24991F CUP: H79B23000050009 - H79B23000060009. CUI S80007580279202300135.</t>
+        </is>
+      </c>
       <c r="O418" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25888,20 +27442,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" s="2" t="n"/>
-      <c r="H419" s="3" t="n"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="H419" s="3" t="n">
+        <v>45275</v>
+      </c>
       <c r="I419" s="3" t="n">
         <v>45300</v>
       </c>
-      <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Azioni di accompagnamento, sviluppo e rafforzamento del sistema duale nell'ambito dell'Istruzione e Formazione Professionale. Approvazione dell'Avviso pubblico per la presentazione di progetti formativi per la realizzazione, in modalità duale, di percorsi triennali di Istruzione e Formazione Professionale per il triennio 2024-2027 finalizzati al conseguimento della qualifica professionale nelle sezioni comparti vari ed edilizia. Accordo rep. atti n. 158/CSR del 24 settembre 2015. Con il provvedimento si approva l’avviso pubblico per la presentazione di progetti formativi per la realizzazione di percorsi triennali di Istruzione e Formazione…</t>
+        </is>
+      </c>
       <c r="O419" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25934,20 +27508,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" s="2" t="n"/>
-      <c r="H420" s="3" t="n"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H420" s="3" t="n">
+        <v>45275</v>
+      </c>
       <c r="I420" s="3" t="n">
         <v>45300</v>
       </c>
-      <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Azioni di accompagnamento, sviluppo e rafforzamento del sistema duale nell'ambito dell'Istruzione e Formazione Professionale. Approvazione dell'Avviso pubblico per la presentazione di progetti formativi per la realizzazione, in modalità duale, di percorsi triennali di Istruzione e Formazione Professionale per il triennio 2024-2027, finalizzati al conseguimento della qualifica professionale nella sezione servizi del benessere. Accordo rep. atti n. 158/CSR del 24 settembre 2015. Con il provvedimento si approvano l’Avviso pubblico per la presentazione di progetti formativi per la realizzazione di percorsi triennali di Istruzione e Formazione…</t>
+        </is>
+      </c>
       <c r="O420" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -25980,20 +27574,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G421" s="2" t="n"/>
-      <c r="H421" s="3" t="n"/>
+      <c r="H421" s="3" t="n">
+        <v>45121</v>
+      </c>
       <c r="I421" s="3" t="n">
         <v>45291</v>
       </c>
-      <c r="K421" t="inlineStr"/>
-      <c r="L421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>La Giunta Regionale del Veneto con deliberazione n. 865 del 11 luglio 2023 ha approvato l'attivazione dei bandi relativi ai seguenti interventi del Complemento Regionale per lo Sviluppo rurale (CSR 2023-2027) del Veneto I bandi sono pubblicati nel Bollettino Ufficiale della Regione del Veneto n. 94 del 14 luglio 2023 . Di seguito sono riepilogati gli interventi e le azioni d i cui sono aperti i termini: SRA 16 - Conservazione agrobiodiversità - banche del germoplasma. L’intervento prevede un pagamento volto al riconoscimento delle spese materiali e immateriali effettivamente sostenute dai beneficiari per realizzare attività riguardanti la…</t>
+        </is>
+      </c>
       <c r="O421" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26018,7 +27630,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -26027,19 +27639,35 @@
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
-      <c r="G422" s="2" t="n"/>
-      <c r="H422" s="3" t="n"/>
+      <c r="G422" s="2" t="n">
+        <v>91988</v>
+      </c>
+      <c r="H422" s="3" t="n">
+        <v>45254</v>
+      </c>
       <c r="I422" s="3" t="n">
         <v>45291</v>
       </c>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Ambiente | Turismo</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Aggiudicazione immediatamente efficace ed impegno di spesa a favore dell’operatore economico Francesca Sironi, per il servizio di “Ideazione, sviluppo e gestione della campagna di promozione dei parchi del Veneto denominata "Veneto? Naturale!" Anni 2023 – 2024”. CUP H21G23000060002. CIG A011065A4E Link BDNCP: https://dati.anticorruzione.it/superset/dashboard/dettaglio_cig/?UUID=eb2a5969-cfcf-40f8-b4ca-f52350e9c625&amp;cig=A011065A4E</t>
+        </is>
+      </c>
       <c r="O422" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26073,19 +27701,35 @@
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
-      <c r="G423" s="2" t="n"/>
-      <c r="H423" s="3" t="n"/>
+      <c r="G423" s="2" t="n">
+        <v>103500</v>
+      </c>
+      <c r="H423" s="3" t="n">
+        <v>45247</v>
+      </c>
       <c r="I423" s="3" t="n">
         <v>45290</v>
       </c>
-      <c r="K423" t="inlineStr"/>
-      <c r="L423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>DELIBERAZIONE DELLA GIUNTA REGIONALE N. 1308 del 30/10/2023 Bando per la capitalizzazione dei fondi di mutualizzazione per le fitopatie della vite. L.R. 12 dicembre 2003 n. 40, articolo 64. CONDUTTORE: AVEPA DESTINATARI: Imprese. NORMATIVA DI RIFERIMENTO L.R. 12 dicembre 2003 n. 40, articolo 64. FINALITA’: l’erogazione di un contributo pubblico finalizzato ad incrementare le disponibilità finanziarie dei fondi di mutualizzazione delle fitopatie della vite a favore dei soggetti gestori dei fondi riconosciuti dal MIPAAF ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare il dott. Giuliano Nicolin al seguente numero di telefono: 041…</t>
+        </is>
+      </c>
       <c r="O423" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26118,20 +27762,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" s="2" t="n"/>
-      <c r="H424" s="3" t="n"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H424" s="3" t="n">
+        <v>45209</v>
+      </c>
       <c r="I424" s="3" t="n">
         <v>45289</v>
       </c>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Bando finalizzato a incentivare la rottamazione di autoveicoli di categoria M1, con contestuale acquisto di mezzi a basso impatto ambientale di nuova immatricolazione, rivolto a soggetti privati residenti in Veneto Per informazioni: pagina del Bando Auto 2023</t>
+        </is>
+      </c>
       <c r="O424" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26156,7 +27820,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -26164,20 +27828,38 @@
           <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
       <c r="G425" s="2" t="n"/>
-      <c r="H425" s="3" t="n"/>
+      <c r="H425" s="3" t="n">
+        <v>45184</v>
+      </c>
       <c r="I425" s="3" t="n">
         <v>45274</v>
       </c>
-      <c r="K425" t="inlineStr"/>
-      <c r="L425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>La Giunta Regionale del Veneto con deliberazione n.1100 del 12 settembre 2023 ha approvato l'attivazione dei bandi relativi ai seguenti interventi del Complemento Regionale per lo Sviluppo rurale (CSR) del Veneto. I bandi sono pubblicati nel Bollettino Ufficiale della Regione del Veneto n. 122 del 15 settembre 2023 . Di seguito sono riepilogati gli interventi e le azioni d i cui sono aperti i termini: SRA04 - Apporto di sostanza organica nei suoli L’intervento prevede un pagamento per i beneficiari che si impegnano a migliorare le caratteristiche strutturali e chimico-fisiche dei suoli agricoli mediante l’apporto e il mantenimento diretto di…</t>
+        </is>
+      </c>
       <c r="O425" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26210,20 +27892,40 @@
           <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" s="2" t="n"/>
-      <c r="H426" s="3" t="n"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H426" s="3" t="n">
+        <v>45142</v>
+      </c>
       <c r="I426" s="3" t="n">
         <v>45273</v>
       </c>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Attività produttive | FESR</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Il Bando a supporto di progetti finalizzati alla rigenerazione urbana e alla ripresa economica nell'ambito dei distretti del commercio - Anno 2023 , dà attuazione al PR FESR 2021-2027 della Regione del Veneto , Obiettivo Specifico 1.3 “Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR)”, Azione 1.3.7 “Sostegno alla competitività del sistema commerciale e valorizzazione dei distretti del commercio”. Con il presente Bando la Regione del Veneto, in coerenza con le politiche attive indirizzate alla salvaguardia ed alla riqualificazione del…</t>
+        </is>
+      </c>
       <c r="O426" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26256,20 +27958,38 @@
           <t>U.O. Edilizia Pubblica</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
       <c r="G427" s="2" t="n"/>
-      <c r="H427" s="3" t="n"/>
+      <c r="H427" s="3" t="n">
+        <v>45226</v>
+      </c>
       <c r="I427" s="3" t="n">
         <v>45271</v>
       </c>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Edilizia scolastica</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Il presente provvedimento avvia una procedura di selezione “a sportello” per interventi urgenti di edilizia scolastica da sostenere finanziariamente con risorse regionali stanziate dalla legge regionale n. 59/1999 per l'anno 2023.</t>
+        </is>
+      </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26304,18 +28024,32 @@
       </c>
       <c r="F428" t="inlineStr"/>
       <c r="G428" s="2" t="n"/>
-      <c r="H428" s="3" t="n"/>
+      <c r="H428" s="3" t="n">
+        <v>45233</v>
+      </c>
       <c r="I428" s="3" t="n">
         <v>45261</v>
       </c>
-      <c r="K428" t="inlineStr"/>
-      <c r="L428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Istruzione</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Interventi per lo sviluppo delle competenze in materia di storia e cultura del Veneto nelle Istituzioni scolastiche, statali e paritarie, del primo e del secondo ciclo di istruzione e nelle Scuole di Formazione Professionale del Veneto. Approvazione Avviso pubblico e Direttiva per la presentazione di progetti formativi da realizzare nell’anno scolastico-formativo 2023/2024.Legge regionale 13 aprile 2001, n. 11, art. 138, comma 1, lett. f). Legge regionale 31 marzo 2017, n.8, art.2, comma 4.</t>
+        </is>
+      </c>
       <c r="O428" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26348,20 +28082,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" s="2" t="n"/>
-      <c r="H429" s="3" t="n"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H429" s="3" t="n">
+        <v>45216</v>
+      </c>
       <c r="I429" s="3" t="n">
         <v>45260</v>
       </c>
-      <c r="K429" t="inlineStr"/>
-      <c r="L429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Enti locali</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Contributi per supporto attività avvio proposte di inserimento territori nelle liste propositive nazionali di candidature siti Unesco. Approvazione schema bando finanziamento anno 2023. Scadenza: 30 novembre 2023.</t>
+        </is>
+      </c>
       <c r="O429" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26386,7 +28140,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -26394,20 +28148,40 @@
           <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" s="2" t="n"/>
-      <c r="H430" s="3" t="n"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H430" s="3" t="n">
+        <v>45212</v>
+      </c>
       <c r="I430" s="3" t="n">
         <v>45260</v>
       </c>
-      <c r="K430" t="inlineStr"/>
-      <c r="L430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>FESR | Ricerca e innovazione</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Il bando sostiene le Infrastrutture di Ricerca (IR) già censite dall’Amministrazione regionale, tramite un processo di mappatura i cui esiti sono stati approvati con DGR n. 1459 del 3 novembre 2020, con l’obiettivo di un loro ammodernamento ed il potenziamento dell’operatività. Il bando è destinato a sostenere gli investimenti nelle Infrastrutture di ricerca volti a potenziare la ricerca applicata nel Veneto, per rispondere efficacemente ai fabbisogni di innovazione ed internazionalizzazione dell’ecosistema regionale dell’innovazione, contribuendo a rafforzare la competitività del tessuto produttivo ed il tasso di attrattività del territorio…</t>
+        </is>
+      </c>
       <c r="O430" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26440,20 +28214,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" s="2" t="n"/>
-      <c r="H431" s="3" t="n"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H431" s="3" t="n">
+        <v>45030</v>
+      </c>
       <c r="I431" s="3" t="n">
         <v>45244</v>
       </c>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>PR Veneto FESR 2021-2027. Priorità 1 OS 1.3 Azione 1.3.11 “Interventi a sostegno delle imprese culturali, creative e dell’audiovisivo - Sub C - Produzione audiovisiva". Approvazione bando “Erogazione di contributi a favore della produzione cinematografica e audiovisiva”. La domanda va presentata esclusivamente per via telematica al seguente link: http://www.regione.veneto.it/web/programmi-comunitari/siu dalle ore 10:00 del 19 aprile 2023 alle ore 17:00 del 30 maggio 2023 - Primo sportello importo - € 2.500.000,00 dalle ore 10:00 del 03 ottobre 2023 alle ore 17:00 del 14 novembre 2023 - Secondo sportello - importo € 2.500.000,00 FAQ bando…</t>
+        </is>
+      </c>
       <c r="O431" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26478,7 +28272,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -26487,19 +28281,35 @@
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
-      <c r="G432" s="2" t="n"/>
-      <c r="H432" s="3" t="n"/>
+      <c r="G432" s="2" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="H432" s="3" t="n">
+        <v>45198</v>
+      </c>
       <c r="I432" s="3" t="n">
         <v>45239</v>
       </c>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>ICT | Informatica e-government</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Appalto specifico per l’acquisto di apparati aggiuntivi per l’ampliamento dei sistemi ingegnerizzati Oracle Exadata della Regione del Veneto, comprensivo di servizi di assistenza e supporto per la durata di n. 12 mesi, nell’ambito del sistema dinamico di acquisizione della pubblica amministrazione (SDAPA) per la fornitura di prodotti e servizi per l'informatica e le telecomunicazioni ID 2681. Programma Operativo Complementare (POC) della Regione del Veneto al POR FESR 2014-2020 (art. 242 del DL 19 maggio 2020 n. 34). Delibera CIPESS n. 41 del 09/06/2021. Accordo tra la Regione del Veneto e il Ministero per il Sud e la Coesione territoriale…</t>
+        </is>
+      </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26524,7 +28334,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -26532,20 +28342,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G433" s="2" t="n"/>
-      <c r="H433" s="3" t="n"/>
+      <c r="H433" s="3" t="n">
+        <v>45202</v>
+      </c>
       <c r="I433" s="3" t="n">
         <v>45239</v>
       </c>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N433" t="inlineStr"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Indizione di una procedura aperta telematica, ai sensi dell’art. 71 del D.lgs. 36/2023, per la conclusione di un accordo quadro con un unico operatore economico ex art. 59 comma 3, per il servizio sostitutivo di mensa mediante buoni pasto elettronici per il personale dipendente della Regione del Veneto e di alcuni Enti e Società regionali. Approvazione atti di gara e prenotazione della spesa. CIG: A0155BE48D; CUI: S80007580279202200091. CPV: 30199770-8.</t>
+        </is>
+      </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26580,18 +28408,32 @@
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" s="2" t="n"/>
-      <c r="H434" s="3" t="n"/>
+      <c r="H434" s="3" t="n">
+        <v>45209</v>
+      </c>
       <c r="I434" s="3" t="n">
         <v>45239</v>
       </c>
-      <c r="K434" t="inlineStr"/>
-      <c r="L434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Bando per l'erogazione di contributi, a favore dei Comuni, dei Consorzi di Bonifica/Autorità di bacino, degli Enti gestori dei Parchi e delle Riserve e degli Enti gestori dei siti di Rete Natura 2000 regionali, per un importo complessivo di 200.000,00 €, finalizzati al sostegno di interventi in applicazione del Piano di controllo della specie nutria, approvato con DGR n. 1069/2021 (L. n. 157/1992, art. 19) per l’anno 2023 e 2024.</t>
+        </is>
+      </c>
       <c r="O434" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26624,20 +28466,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" s="2" t="n"/>
-      <c r="H435" s="3" t="n"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H435" s="3" t="n">
+        <v>45212</v>
+      </c>
       <c r="I435" s="3" t="n">
         <v>45236</v>
       </c>
-      <c r="K435" t="inlineStr"/>
-      <c r="L435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N435" t="inlineStr"/>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Bando rivolto alle Amministrazioni comunali del Veneto che individua le modalità di assegnazione di contributi derivanti dal trasferimento di competenze di cui al D.Lgs 31 marzo 1998, n. 112, a sostegno di interventi di rimozione e smaltimento di rifiuti.</t>
+        </is>
+      </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26670,20 +28532,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" s="2" t="n"/>
-      <c r="H436" s="3" t="n"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H436" s="3" t="n">
+        <v>45212</v>
+      </c>
       <c r="I436" s="3" t="n">
         <v>45232</v>
       </c>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N436" t="inlineStr"/>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Bando per la concessione di contributi per il recupero, la conservazione e la valorizzazione del patrimonio immobiliare culturale del Veneto, la cui partecipazione è riservata agli enti locali del territorio.</t>
+        </is>
+      </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26716,20 +28598,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" s="2" t="n"/>
-      <c r="H437" s="3" t="n"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H437" s="3" t="n">
+        <v>45076</v>
+      </c>
       <c r="I437" s="3" t="n">
         <v>45230</v>
       </c>
-      <c r="K437" t="inlineStr"/>
-      <c r="L437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Enti locali</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Criteri e modalità per l’assegnazione e l’erogazione di contributi per l’elaborazione di studi di fattibilità finalizzati alla fusione di Comuni e per la costituzione e la riorganizzazione delle Unioni di Comuni (art. 32 D.Lgs n. 267/2000) e delle Unioni montane (L.R. 40/2012), nonché indicazioni per le attività di sondaggio in materia di fusioni di comuni ai sensi dell’art. 7 bis LR n. 25/92. Anno 2023. DESTINATARI - Unioni di Comuni - Unioni Montane - Comuni - NORMATIVA DI RIFERIMENTO Legge Regionale 27.04.2012 n. 18 artt. 3 e 3bis FINALITÀ Contributi a favore dei Comuni, delle Unioni di Comuni e delle Unioni Montane a sostegno delle spese…</t>
+        </is>
+      </c>
       <c r="O437" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26754,7 +28656,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -26762,20 +28664,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" s="2" t="n"/>
-      <c r="H438" s="3" t="n"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="n">
+        <v>12212818</v>
+      </c>
+      <c r="H438" s="3" t="n">
+        <v>45100</v>
+      </c>
       <c r="I438" s="3" t="n">
         <v>45230</v>
       </c>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Aiuti previsti per la misura investimenti del settore vitivinicolo - Annualità 2024/2025 (per anticipo fondi 2024). DESTINATARI: Imprese agricole e aziende di trasformazione e commercializzazione del settore vitivinicolo; NORMATIVA DI RIFERIMENTO: Regolamento (UE) n. 1308/2013, art. 50 FINALITA’: Sostenere lo sviluppo del comparto. L’importo a bando è pari a 12.212.817,88 (DGR 734/2023 e DDR 101 del 23 giugno 2023 ) , ripartiti equamente in Euro 6.106.408,94 tra “Azione A - Investimenti nelle aziende agricole vitivinicole bando biennale 2024-2025” e in Euro per l“Azione B – Investimenti per la trasformazione e…</t>
+        </is>
+      </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26800,7 +28722,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -26808,20 +28730,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" s="2" t="n"/>
-      <c r="H439" s="3" t="n"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="n">
+        <v>3284218</v>
+      </c>
+      <c r="H439" s="3" t="n">
+        <v>45198</v>
+      </c>
       <c r="I439" s="3" t="n">
         <v>45230</v>
       </c>
-      <c r="K439" t="inlineStr"/>
-      <c r="L439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Bando per l’assegnazione di contributi ai Comuni e alle Province del Veneto per piccoli interventi di bonifica ambientale di siti inquinati – Contributi agli investimenti (art. 1, comma 135, Legge 30/12/2018, n. 145). Annualità 2023-2024.</t>
+        </is>
+      </c>
       <c r="O439" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26846,7 +28788,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -26854,20 +28796,38 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
       <c r="G440" s="2" t="n"/>
-      <c r="H440" s="3" t="n"/>
+      <c r="H440" s="3" t="n">
+        <v>45135</v>
+      </c>
       <c r="I440" s="3" t="n">
         <v>45229</v>
       </c>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Il presente provvedimento autorizza la partecipazione di personale regionale a corsi di formazione a catalogo organizzati da soggetti esterni.</t>
+        </is>
+      </c>
       <c r="O440" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26900,20 +28860,40 @@
           <t>Direzione Servizi Sociali</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" s="2" t="n"/>
-      <c r="H441" s="3" t="n"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H441" s="3" t="n">
+        <v>45191</v>
+      </c>
       <c r="I441" s="3" t="n">
         <v>45221</v>
       </c>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Bando per il finanziamento di iniziative socio-educative a favore di persone detenute negli istituti penitenziari del Veneto e di persone in area penale esterna. Attuazione della Linea 2 del "Programma regionale triennale di interventi cofinanziati dalla Cassa delle Ammende" da realizzarsi nel periodo dicembre 2023 - dicembre 2025. DGR n. 1405 del 11 novembre 2022. CUP H11J22000410001.</t>
+        </is>
+      </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26946,20 +28926,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" s="2" t="n"/>
-      <c r="H442" s="3" t="n"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H442" s="3" t="n">
+        <v>45156</v>
+      </c>
       <c r="I442" s="3" t="n">
         <v>45215</v>
       </c>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Enti locali</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Criteri e modalità per l’assegnazione e l’erogazione di contributi, per l’avvio e l’ampliamento dell’esercizio associato di funzioni fondamentali nella forma dell’Unione di Comuni, dell’Unione montana e della Convenzione tra Comuni, nonché per l’erogazione del contributo regionale ordinario. Anno 2023. Deliberazione/CR n. 73 del 11 luglio 2023. DESTINATARI: - Unioni di Comuni - Unioni Montane - Comuni capofila di convenzioni NORMATIVA DI RIFERIMENTO: Legge Regionale 27.04.2012 n. 18 art. 10 FINALITA' : Contributi a favore delle Unioni di Comuni, Unioni Montane e Convenzioni tra Comuni destinati a sostenere l'avvio e lo sviluppo delle…</t>
+        </is>
+      </c>
       <c r="O442" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -26992,20 +28992,40 @@
           <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" s="2" t="n"/>
-      <c r="H443" s="3" t="n"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H443" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I443" s="3" t="n">
         <v>45211</v>
       </c>
-      <c r="K443" t="inlineStr"/>
-      <c r="L443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Attività produttive | FESR | Ricerca e innovazione</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Il bando dà attuazione al PR FESR 2021-2027 della Regione del Veneto , Obiettivo Specifico 1.1. “Sviluppare e rafforzare le capacità di ricerca e di innovazione e l'introduzione di tecnologie avanzate”, Azione 1.1.5 “Sostegno alla gestione e al funzionamento delle Reti Innovative Regionali”. Possono presentare domanda di sostegno i soggetti giuridici che rappresentano le Reti Innovative Regionali , le quali sono state oggetto di riconoscimento dalla Giunta regionale entro la data di pubblicazione del bando sul Bollettino Ufficiale della Regione. Il bando finanzia progetti di consolidamento delle Reti Innovative Regionali (RIR) incentrati sul…</t>
+        </is>
+      </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27038,20 +29058,38 @@
           <t>Unita' Organizzativa Famiglia, Minori, Giovani E Servizio Civile</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G444" s="2" t="n"/>
-      <c r="H444" s="3" t="n"/>
+      <c r="H444" s="3" t="n">
+        <v>45163</v>
+      </c>
       <c r="I444" s="3" t="n">
         <v>45208</v>
       </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Con DGR n. 995 del 18 agosto 2023 sono stati approvati criteri, termini, modalità di assegnazione di contributi per il pagamento delle rette, sostenute nel corso dell’anno 2022, relativamente all’inserimento di minori in unità d’offerta residenziali, di cui alle DGR n. 84/2007 e n. 242/2012 ad essi dedicate, da assegnare a Comuni con popolazione non superiore ai 20.000 abitanti, ad Aziende ULSS e ad Unioni di Comuni, se delegate, per la sola quota relativa ai Comuni con popolazione non superiore ai 20.000 abitanti. Sono stati approvati anche i seguenti Allegati quali parti integranti del provvedimento di cui sopra: Allegato A recante “ Bando…</t>
+        </is>
+      </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27084,20 +29122,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" s="2" t="n"/>
-      <c r="H445" s="3" t="n"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="H445" s="3" t="n">
+        <v>45104</v>
+      </c>
       <c r="I445" s="3" t="n">
         <v>45203</v>
       </c>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>Approvazione dell'Avviso pubblico e della Direttiva “Venezia I.C.O.N.A. - Intelligenze, Competenze, Organizzazione per una Nuova Autenticità”, per la presentazione di progetti tesi a sostenere e promuovere le competenze in grado di favorire lo sviluppo del contesto socio-economico veneziano del centro storico nell’ambito del Programma Regionale Veneto per il sostegno del Fondo Sociale Europeo Plus nel ciclo di programmazione 2021-2027. Con DDR n. 1308 del 07/09/2023 è stata disposta la proroga dei termini per la presentazione delle domande di finanziamento nell’ambito delle iniziative “Venezia I.C.O.N.A. - Intelligenze, Competenze,…</t>
+        </is>
+      </c>
       <c r="O445" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27122,7 +29180,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -27130,20 +29188,38 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
       <c r="G446" s="2" t="n"/>
-      <c r="H446" s="3" t="n"/>
+      <c r="H446" s="3" t="n">
+        <v>45135</v>
+      </c>
       <c r="I446" s="3" t="n">
         <v>45201</v>
       </c>
-      <c r="K446" t="inlineStr"/>
-      <c r="L446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N446" t="inlineStr"/>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Bando per la presentazione delle domande di contributo per il settore apicoltura per l'annualità FEAGA 2023/2024. Sottoprogramma regionale per l'apicoltura 2023/2027. Regolamento (UE) n. 2021/2115 del 2 dicembre 2021, Decreto del Ministro dell'agricoltura, della sovranità alimentare e delle foreste 30 novembre 2022 n. 614768 e ss.mm.ii. DGR n. 68/CR del 27 giugno 2023.</t>
+        </is>
+      </c>
       <c r="O446" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27168,7 +29244,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -27178,18 +29254,32 @@
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" s="2" t="n"/>
-      <c r="H447" s="3" t="n"/>
+      <c r="H447" s="3" t="n">
+        <v>45170</v>
+      </c>
       <c r="I447" s="3" t="n">
         <v>45201</v>
       </c>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Lavori pubblici | Territorio</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando per la concessione di contributi ai Comuni veneti per investimenti per la progettazione e per la realizzazione di opere pubbliche per la messa in sicurezza del territorio a rischio idrogeologico (art. 1, comma 135, Legge n. 145 del 30/12/2018 "Bilancio di previsione dello Stato per l'anno finanziario 2019 e bilancio pluriennale per il triennio 2019-2021"). Competenza annualità 2024.</t>
+        </is>
+      </c>
       <c r="O447" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27222,20 +29312,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" s="2" t="n"/>
-      <c r="H448" s="3" t="n"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="n">
+        <v>1502</v>
+      </c>
+      <c r="H448" s="3" t="n">
+        <v>45167</v>
+      </c>
       <c r="I448" s="3" t="n">
         <v>45199</v>
       </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N448" t="inlineStr"/>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Con il presente atto si procede all’acquisizione del servizio per l’attivazione del corso online in differita “Il nuovo codice dei contratti pubblici (D.lgs. 31 marzo 2023 n. 36) – principali novità”.</t>
+        </is>
+      </c>
       <c r="O448" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27260,7 +29370,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -27268,20 +29378,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" s="2" t="n"/>
-      <c r="H449" s="3" t="n"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="n">
+        <v>5456</v>
+      </c>
+      <c r="H449" s="3" t="n">
+        <v>45135</v>
+      </c>
       <c r="I449" s="3" t="n">
         <v>45199</v>
       </c>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N449" t="inlineStr"/>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Il presente provvedimento autorizza la partecipazione di personale regionale a corsi di formazione a catalogo organizzati da soggetti esterni.</t>
+        </is>
+      </c>
       <c r="O449" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27306,7 +29436,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -27314,20 +29444,40 @@
           <t>Direzione Beni Attività Culturali E Sport</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" s="2" t="n"/>
-      <c r="H450" s="3" t="n"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H450" s="3" t="n">
+        <v>45128</v>
+      </c>
       <c r="I450" s="3" t="n">
         <v>45198</v>
       </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N450" t="inlineStr"/>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Si avvia la procedura per la concessione di contributi a favore delle iniziative di promozione della pratica sportiva degli atleti con disabilità.</t>
+        </is>
+      </c>
       <c r="O450" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27360,20 +29510,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" s="2" t="n"/>
-      <c r="H451" s="3" t="n"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H451" s="3" t="n">
+        <v>45104</v>
+      </c>
       <c r="I451" s="3" t="n">
         <v>45195</v>
       </c>
-      <c r="K451" t="inlineStr"/>
-      <c r="L451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Lavoro</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N451" t="inlineStr"/>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Con Deliberazione n. 729 del 22 giugno 2023 è stato approvato l'Avviso pubblico e la Direttiva " GIOVANI ENERGIE - Azioni sperimentali per l'attivazione dei giovani nella definizione del proprio percorso formativo e professionale ", per la presentazione di progetti finalizzati ad offrire ai giovani opportunità di scoperta dei propri talenti e competenze chiave per l'autonomia sociale ed economica. L'obiettivo è quello di favorire, da un lato l'avvicinamento dei giovani al mercato del lavoro, dall'altro il rientro in percorsi formativi dei minori "in dispersione". La dotazione finanziaria per l’attuazione degli interventi è di €…</t>
+        </is>
+      </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27406,20 +29576,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" s="2" t="n"/>
-      <c r="H452" s="3" t="n"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>45163</v>
+      </c>
       <c r="I452" s="3" t="n">
         <v>45195</v>
       </c>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N452" t="inlineStr"/>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Avviso pubblico "Istituti Tecnici Superiori - Academy" - Presentazione di progetti formativi per percorsi di tecnico superiore per il biennio 2023-2025. NORMATIVA DI RIFERIMENTO: La Giunta Regionale ha stabilito, nell’ambito del PNRR Missione 4 “Sviluppo del sistema di formazione professionale terziaria - ITS” e del Programma regionale Veneto FSE+ 2021-2027 - Obiettivo “Investimenti per l'occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 01/08/2022 - Priorità 2 Istruzione e Formazione - Obiettivo specifico f), l’apertura dei termini per la presentazione di progetti formativi per lo svolgimento…</t>
+        </is>
+      </c>
       <c r="O452" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27452,20 +29642,40 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" s="2" t="n"/>
-      <c r="H453" s="3" t="n"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H453" s="3" t="n">
+        <v>45163</v>
+      </c>
       <c r="I453" s="3" t="n">
         <v>45195</v>
       </c>
-      <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N453" t="inlineStr"/>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Avviso pubblico "Restauro 2023: sviluppo capacità professionali per interventi di conservazione del patrimonio storico, artistico, architettonico". La Giunta regionale ha stabilito, nell'ambito del Programma regionale Veneto FSE+ 2021-2027 - Obiettivo “Investimenti per l’occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 1 Occupazione - Obiettivo specifico a) e Priorità 2 - Istruzione e Formazione - Obiettivo specifico g), l'apertura dei termini per la presentazione di progetti formativi. I progetti formativi per "Tecnico per il restauro di beni culturali", sono volti alla…</t>
+        </is>
+      </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27498,20 +29708,38 @@
           <t>Direzione Difesa del Suolo e della Costa</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G454" s="2" t="n"/>
-      <c r="H454" s="3" t="n"/>
+      <c r="H454" s="3" t="n">
+        <v>45132</v>
+      </c>
       <c r="I454" s="3" t="n">
         <v>45194</v>
       </c>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Ambiente | Attività produttive | Territorio</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N454" t="inlineStr"/>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Indizione di procedure a evidenza pubblica per il conferimento di concessioni minerarie di acqua termale in Comune di Abano Terme (PD). Approvazione del disciplinare. L.R. 40/1989 - DD.G.R. n.994/2014 e n.1827/2014. Decreto n. 266 del 13 luglio 2023</t>
+        </is>
+      </c>
       <c r="O454" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27544,20 +29772,40 @@
           <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" s="2" t="n"/>
-      <c r="H455" s="3" t="n"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H455" s="3" t="n">
+        <v>45146</v>
+      </c>
       <c r="I455" s="3" t="n">
         <v>45191</v>
       </c>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N455" t="inlineStr"/>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Interventi per la diffusione del commercio equo e solidale. Anno 2023 Destinatari: soggetti iscritti nell'elenco regionale delle organizzazioni del commercio equo e solidale, come previsto dall'articolo 6, comma 2, della L.R. n. 6/2010. Normativa: L.R. n. 6 del 22.01.2010 Finalità: I progetti devono riguardare i settori di intervento previsti dall'articolo 6 della L.R. n. 6/2010 e devono essere conformi a quanto prescritto dal Piano annuale 2023 di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile.</t>
+        </is>
+      </c>
       <c r="O455" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27582,7 +29830,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -27590,20 +29838,38 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G456" s="2" t="n"/>
-      <c r="H456" s="3" t="n"/>
+      <c r="H456" s="3" t="n">
+        <v>45135</v>
+      </c>
       <c r="I456" s="3" t="n">
         <v>45187</v>
       </c>
-      <c r="K456" t="inlineStr"/>
-      <c r="L456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N456" t="inlineStr"/>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>TITOLO COMPLETO: Bando per l'assegnazione di un terreno ricompreso nella banca della terra veneta. L.R. 8 agosto 2014 n. 26 DESTINATARI: Persone fisiche maggiorenni o giuridiche che intendano ampliare od iniziare un’attività imprenditoriale agricola. NORMATIVA DI RIFERIMENTO: Legge regionale n. 26 del 8/08/2014 FINALITA’: valorizzare le terre agricole incolte o abbandonate, al fine di contenere il degrado ambientale, salvaguardare il suolo e gli equilibri idrogeologici, limitare gli incendi boschivi, favorire l'ottimale assetto del territorio attraverso lo svolgimento delle attività agricole nonché favorire l'insediamento di giovani…</t>
+        </is>
+      </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27636,20 +29902,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" s="2" t="n"/>
-      <c r="H457" s="3" t="n"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H457" s="3" t="n">
+        <v>45114</v>
+      </c>
       <c r="I457" s="3" t="n">
         <v>45184</v>
       </c>
-      <c r="K457" t="inlineStr"/>
-      <c r="L457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Comunicazione e informazione</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N457" t="inlineStr"/>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Iniziative editoriali e digitali di promozione e valorizzazione degli eventi regionali ai sensi della programmazione delle attività di cui alla DGR n. 512 del 9 maggio 2023 . ULTERIORI INFORMAZIONI La richiesta dovrà essere presentata entro il termine perentorio del giorno 15 settembre 2023 , esclusivamente tramite posta elettronica certificata al seguente indirizzo: entilocaligrandieventi@pec.regione.veneto.it Per informazioni: tel. 041-2795748.</t>
+        </is>
+      </c>
       <c r="O457" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27682,20 +29968,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" s="2" t="n"/>
-      <c r="H458" s="3" t="n"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H458" s="3" t="n">
+        <v>45114</v>
+      </c>
       <c r="I458" s="3" t="n">
         <v>45184</v>
       </c>
-      <c r="K458" t="inlineStr"/>
-      <c r="L458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Lavoro</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N458" t="inlineStr"/>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Con Deliberazione n. 827 del 4 luglio 2023 è stato approvato l'Avviso pubblico " Lavori di Pubblica Utilità e Cittadinanza Attiva. Progetti per l'inserimento lavorativo temporaneo di disoccupati privi di tutele - Anno 2023 " a valere sul Programma Regionale Veneto Fondo Sociale Europeo Plus (PR Veneto FSE+) 2021-2027. I progetti di pubblica utilità e cittadinanza attiva sono a favore di soggetti svantaggiati esclusi dal mercato del lavoro attraverso la realizzazione di esperienze di lavoro correlate ad azioni di orientamento e accompagnamento che ne favoriscano l’inclusione. La dotazione finanziaria per l’attuazione degli interventi è di €…</t>
+        </is>
+      </c>
       <c r="O458" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27728,20 +30034,40 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" s="2" t="n"/>
-      <c r="H459" s="3" t="n"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H459" s="3" t="n">
+        <v>45114</v>
+      </c>
       <c r="I459" s="3" t="n">
         <v>45184</v>
       </c>
-      <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Cittadino Ente</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Lavoro | Sociale</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N459" t="inlineStr"/>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Con Deliberazione n. 828 del 4 luglio 2023 è stato approvato l'Avviso pubblico "ReStart 2 - Interventi per l'occupabilità e l'inclusione sociale attiva di persone in esecuzione penale" a valere sul Programma regionale triennale di interventi cofinanziati da Cassa delle Ammende. I progetti sono rivolti alle persone in esecuzione penale con l’obiettivo di favorirne l’inclusione lavorativa e sociale. La dotazione finanziaria per l’attuazione degli interventi è di € 600.000,00. Maggiori informazioni e documentazione in questa pagina web: https://spazio-operatori.regione.veneto.it/w/bandi/2023/restart2/828</t>
+        </is>
+      </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27775,19 +30101,35 @@
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
-      <c r="G460" s="2" t="n"/>
-      <c r="H460" s="3" t="n"/>
+      <c r="G460" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>45051</v>
+      </c>
       <c r="I460" s="3" t="n">
         <v>45184</v>
       </c>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N460" t="inlineStr"/>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando di concorso per l’assegnazione del “Premio per saggi brevi, inediti e originali sulla storia dell’emigrazione veneta" - 1^ Edizione. Programma anno 2023 - L.R. 25 luglio 2008, n. 8".</t>
+        </is>
+      </c>
       <c r="O460" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27820,20 +30162,40 @@
           <t>Direzione Pianificazione Territoriale</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" s="2" t="n"/>
-      <c r="H461" s="3" t="n"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H461" s="3" t="n">
+        <v>45152</v>
+      </c>
       <c r="I461" s="3" t="n">
         <v>45182</v>
       </c>
-      <c r="K461" t="inlineStr"/>
-      <c r="L461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Territorio</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N461" t="inlineStr"/>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Assegnazione di contributi a supporto dei Comuni per la redazione del Piano di Assetto del Territorio Comunale o Intercomunale in adeguamento alla disciplina della legge regionale 23 aprile 2004, n. 11 "Norme per il governo del Territorio e in materia di paesaggio". Definizione criteri e approvazione bando 2023. Deliberazione n. 76/Cr del 11 luglio 2023. Articolo 47, comma 2 della legge regionale 23 aprile 2004 n. 11. Approvazione della graduatoria per la concessione di un contributo a supporto dei Comuni per la redazione del Piano di Assetto del Territorio Comunale o Intercomunale in adeguamento alla disciplina della legge regionale 23…</t>
+        </is>
+      </c>
       <c r="O461" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27866,20 +30228,40 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" s="2" t="n"/>
-      <c r="H462" s="3" t="n"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H462" s="3" t="n">
+        <v>45149</v>
+      </c>
       <c r="I462" s="3" t="n">
         <v>45182</v>
       </c>
-      <c r="K462" t="inlineStr"/>
-      <c r="L462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N462" t="inlineStr"/>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Bando regionale per la presentazione dei progetti multiregionali e regionali per la campagna 2023/2024 per la misura promozione dei vini nei mercati dei Paesi terzi. Possono presentare domanda le organizzazioni professionali purché abbiano tra i loro scopi, la promozione dei prodotti agricoli, le organizzazioni di produttori di vino come definite dall’art. 152 del reg.to UE 1308/2013 (di seguito reg.to UE), le associazioni di organizzazioni di produttori di vino, come definite dall’art. 156 del reg.to UE, le organizzazioni interprofessionali, come definite dall’art. 157 del reg.to UE, i consorzi di tutela, riconosciuti ai sensi dell’art. 41…</t>
+        </is>
+      </c>
       <c r="O462" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27904,7 +30286,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -27912,20 +30294,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" s="2" t="n"/>
-      <c r="H463" s="3" t="n"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H463" s="3" t="n">
+        <v>45051</v>
+      </c>
       <c r="I463" s="3" t="n">
         <v>45181</v>
       </c>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N463" t="inlineStr"/>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>PR Veneto FESR 2021-2027. Priorità 1 OS 1.3 Azione 1.3.10. "Bando per il consolidamento di aggregazioni di PMI per interventi sui mercati nazionali e internazionali già beneficiarie di misure POR FESR 2014-2020". Data apertura presentazione domande: 10 maggio 2023 ore 10:00 Data chiusura presentazione domande: 12 settembre 2023 ore 17:00</t>
+        </is>
+      </c>
       <c r="O463" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27950,7 +30352,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -27959,19 +30361,35 @@
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
-      <c r="G464" s="2" t="n"/>
-      <c r="H464" s="3" t="n"/>
+      <c r="G464" s="2" t="n">
+        <v>2622</v>
+      </c>
+      <c r="H464" s="3" t="n">
+        <v>45142</v>
+      </c>
       <c r="I464" s="3" t="n">
         <v>45180</v>
       </c>
-      <c r="K464" t="inlineStr"/>
-      <c r="L464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N464" t="inlineStr"/>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Acquisizione mediante trattativa diretta sulla piattaforma Consip MEPA ex art. 36, comma 2, lett. a), d. lgs.50/2016 e ss.mm.ii. di un servizio di consulenza specialistica di “First Level Controller” per il Progetto europeo OD4GROWTH (Programma INTERREG EUROPE) della Regione del Veneto, per la durata di 4 anni. CIG n. Y183B42669 CUP n. H16G23000000007</t>
+        </is>
+      </c>
       <c r="O464" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -27996,7 +30414,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -28005,19 +30423,35 @@
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
-      <c r="G465" s="2" t="n"/>
-      <c r="H465" s="3" t="n"/>
+      <c r="G465" s="2" t="n">
+        <v>39871</v>
+      </c>
+      <c r="H465" s="3" t="n">
+        <v>45142</v>
+      </c>
       <c r="I465" s="3" t="n">
         <v>45180</v>
       </c>
-      <c r="K465" t="inlineStr"/>
-      <c r="L465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N465" t="inlineStr"/>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Acquisizione mediante trattativa diretta sulla piattaforma Consip MEPA ex artt. 36, comma 2, lett. a), del D.lgs n. 50/2016 e ss.mm.ii. di una fornitura di n.7 linee dati con banda garantita 1Gb per 5 mesi al fine di ampliare l’esistente infrastruttura di rete regionale della sanità di Regione del Veneto. CIG. n. YE43BAB317. CUP H77H23000860002</t>
+        </is>
+      </c>
       <c r="O465" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28051,19 +30485,35 @@
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
-      <c r="G466" s="2" t="n"/>
-      <c r="H466" s="3" t="n"/>
+      <c r="G466" s="2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>45146</v>
+      </c>
       <c r="I466" s="3" t="n">
         <v>45176</v>
       </c>
-      <c r="K466" t="inlineStr"/>
-      <c r="L466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N466" t="inlineStr"/>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Avviso di istruttoria pubblica per l’acquisizione di manifestazioni di interesse finalizzate alla co-progettazione, ai sensi dell’art. 55, commi 1 e 3, del D.lgs. n. 117/2017, degli interventi di inclusione abitativa a favore delle persone in esecuzione penale previsti dalla Linea 3 del “Programma regionale triennale di interventi cofinanziati dalla Cassa delle Ammende” da realizzarsi nel triennio febbraio 2023 – febbraio 2026. DGR n. 1405 del 11 novembre 2022. CUP H11J22000410001.</t>
+        </is>
+      </c>
       <c r="O466" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28088,7 +30538,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -28097,19 +30547,35 @@
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
-      <c r="G467" s="2" t="n"/>
-      <c r="H467" s="3" t="n"/>
+      <c r="G467" s="2" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="H467" s="3" t="n">
+        <v>45155</v>
+      </c>
       <c r="I467" s="3" t="n">
         <v>45175</v>
       </c>
-      <c r="K467" t="inlineStr"/>
-      <c r="L467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N467" t="inlineStr"/>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Appalto specifico per l’acquisto di apparati per l’ampliamento dei sistemi iperconvergenti, del sistema NAS e del sistema di protezione e backup dei dati della Regione del Veneto, comprensivo di servizi di assistenza e supporto per 36 mesi.Sdapa per la fornitura di prodotti e servizi per l’informatica e le telecomunicazioni - ID 2681 LOTTO 1 CIG N. A002DA291B, CUP N. H77H23001230002 LOTTO 2 CIG N. A002DDA752, CUP N. H77H23001240002 LOTTO 3 CIG N. A002DF2B1F, CUP N. H77H23001250002 LOTTO 4 CIG N. A002E09E19, CUP N. H77H23001260002</t>
+        </is>
+      </c>
       <c r="O467" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28142,20 +30608,40 @@
           <t>Unità Organizzativa Lavori Pubblici</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr"/>
-      <c r="G468" s="2" t="n"/>
-      <c r="H468" s="3" t="n"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="H468" s="3" t="n">
+        <v>45128</v>
+      </c>
       <c r="I468" s="3" t="n">
         <v>45173</v>
       </c>
-      <c r="K468" t="inlineStr"/>
-      <c r="L468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Lavori pubblici</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N468" t="inlineStr"/>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Sostegno finanziario ai lavori pubblici di interesse locale di importo fino a 200.000,00 euro - Anno 2023. (L.R. 7 novembre 2003, n. 27, art. 50), a valere sulle risorse di cui alla L. 30 dicembre 2018, n. 145, art. 1, commi 134-138). Approvazione Bando. Con DR 116 del 31.07.2023 pubblicato sul BUR n. 102 del 01.08.2023 sono state apportate alcune rettifiche al bando e disposta la proroga del termine di presentazione delle istanze a tutto il 04.09.2023.</t>
+        </is>
+      </c>
       <c r="O468" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28189,19 +30675,35 @@
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
-      <c r="G469" s="2" t="n"/>
-      <c r="H469" s="3" t="n"/>
+      <c r="G469" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H469" s="3" t="n">
+        <v>45058</v>
+      </c>
       <c r="I469" s="3" t="n">
         <v>45173</v>
       </c>
-      <c r="K469" t="inlineStr"/>
-      <c r="L469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N469" t="inlineStr"/>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>Bando per il sostegno all’arte contemporanea, per la selezione e assegnazione di premi a opere realizzate da artisti, con attenzione agli under 40, alla parità di genere e all’inclusività. L’azione è finalizzata a promuovere la cultura artistica contemporanea nelle sue diverse espressioni, a offrire opportunità di visibilità, a favorire la conoscenza e la fruizione dei linguaggi culturali dell’arte contemporanea, anche come strumento di sviluppo e riqualificazione urbana. DDR n. 403 del 30/11/2023: Approvazione delle risultanze istruttorie, assegnazione dei premi in denaro ai vincitori (consulta il documento nella sezione allegati)</t>
+        </is>
+      </c>
       <c r="O469" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28226,7 +30728,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -28236,18 +30738,32 @@
       </c>
       <c r="F470" t="inlineStr"/>
       <c r="G470" s="2" t="n"/>
-      <c r="H470" s="3" t="n"/>
+      <c r="H470" s="3" t="n">
+        <v>45125</v>
+      </c>
       <c r="I470" s="3" t="n">
         <v>45169</v>
       </c>
-      <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Acquisti Verdi - Politiche Sostenibili | L'atto non appartiene alla categoria "Acquisti Verdi" | L'atto non appartiene alla categoria "Politiche Sostenibili"</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N470" t="inlineStr"/>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Affidamento diretto alla ditta Lifebrain Veneto S.r.l. con sede legale in Via Marconi, 30 – Piombino Dese (PD) - Partita IVA IT 01462770288, del servizio per l’esecuzione degli esami ematochimici di cui all'art. 41, co. 4 del D.lgs. 81/2008, necessari per la corretta applicazione del protocollo sanitario per la sorveglianza sanitaria dei Lavoratori della Giunta Regionale della Regione del Veneto, la cui sede di lavoro è collocata nel territorio comunale del Comune di Venezia ad esclusione del personale in servizio presso le sedi della Unità Organizzativa Genio Civile di Venezia e per il personale in servizio presso la sede dell’Ispettorato…</t>
+        </is>
+      </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28280,20 +30796,38 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Riconoscimento</t>
+        </is>
+      </c>
       <c r="G471" s="2" t="n"/>
-      <c r="H471" s="3" t="n"/>
+      <c r="H471" s="3" t="n">
+        <v>45142</v>
+      </c>
       <c r="I471" s="3" t="n">
         <v>45169</v>
       </c>
-      <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N471" t="inlineStr"/>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Piano regionale dei percorsi di Istruzione e Formazione Professionale realizzabili in offerta sussidiaria negli Istituti Professionali di Stato. Approvazione dell'Avviso pubblico e della Direttiva per la presentazione delle domande di attivazione di percorsi triennali di Istruzione e Formazione Professionale per il conseguimento della qualifica professionale da realizzare nel triennio formativo 2023-24, 2024-25, 2025-26 o di percorsi di quarto anno di Istruzione e Formazione Professionale per il conseguimento del diploma professionale da realizzare nell'Anno Formativo 2023-24. Legge 28/03/2003, n. 53. Il provvedimento approva l’Avviso…</t>
+        </is>
+      </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28326,20 +30860,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" s="2" t="n"/>
-      <c r="H472" s="3" t="n"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="n">
+        <v>1502</v>
+      </c>
+      <c r="H472" s="3" t="n">
+        <v>45135</v>
+      </c>
       <c r="I472" s="3" t="n">
         <v>45169</v>
       </c>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N472" t="inlineStr"/>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Con il presente atto si procede all’acquisizione del servizio per l’attivazione del corso “Elementi di contabilità finanziaria degli enti locali per dipendenti dei servizi non finanziari ed amministratori”.</t>
+        </is>
+      </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28372,20 +30926,40 @@
           <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" s="2" t="n"/>
-      <c r="H473" s="3" t="n"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H473" s="3" t="n">
+        <v>45121</v>
+      </c>
       <c r="I473" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N473" t="inlineStr"/>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per i progetti di cooperazione allo sviluppo sostenibile finalizzati alla costruzione e al ripristino di pozzi e di sistemi di attingimento dell'acqua nel continente africano per l'annualità 2023. DGR n. 313 del 29 marzo 2023: "Piano annuale 2023 di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile". L.R. 21 giugno 2018, n. 21.</t>
+        </is>
+      </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28410,7 +30984,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -28418,20 +30992,40 @@
           <t>Direzione Ambiente E Transizione Ecologica</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" s="2" t="n"/>
-      <c r="H474" s="3" t="n"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H474" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I474" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N474" t="inlineStr"/>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>Bando per l’assegnazione di Contributi ai Comuni e alle Province del Veneto per le bonifiche ambientali di siti inquinati – contributi agli investimenti ( art. 1, comma 135, L. 30.12.2018, n. 145) . Annualità 2024.</t>
+        </is>
+      </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28464,20 +31058,38 @@
           <t>Direzione Difesa del Suolo e della Costa</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G475" s="2" t="n"/>
-      <c r="H475" s="3" t="n"/>
+      <c r="H475" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I475" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Ambiente | Lavori pubblici</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N475" t="inlineStr"/>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Procedura aperta per l’affidamento dei servizi di architettura e ingegneria per la progettazione definitiva, la progettazione esecutiva, l’ufficio della Direzione Lavori e il Coordinamento per la Sicurezza in fase di Esecuzione dell’intervento denominato “Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - 1° stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento.” - Bando di avviso Tagliamento</t>
+        </is>
+      </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28510,20 +31122,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" s="2" t="n"/>
-      <c r="H476" s="3" t="n"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="n">
+        <v>1181</v>
+      </c>
+      <c r="H476" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I476" s="3" t="n">
         <v>45161</v>
       </c>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N476" t="inlineStr"/>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>Con il presente atto si procede all’acquisizione del servizio di attivazione di un corso di formazione “REVIT” individuale in modalità videoconferenza – MANUTENZIONE ed ASSISTENZA COMPUTERS s.r.l. - Durata totale 30 ore.</t>
+        </is>
+      </c>
       <c r="O476" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28556,20 +31188,40 @@
           <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
-      <c r="F477" t="inlineStr"/>
-      <c r="G477" s="2" t="n"/>
-      <c r="H477" s="3" t="n"/>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H477" s="3" t="n">
+        <v>45114</v>
+      </c>
       <c r="I477" s="3" t="n">
         <v>45159</v>
       </c>
-      <c r="K477" t="inlineStr"/>
-      <c r="L477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Relazioni internazionali</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N477" t="inlineStr"/>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per le iniziative di promozione della cultura dei diritti umani anno 2023. DGR n. 313 del 29 marzo 2023: "Piano annuale 2023 di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile". L.R. 21 giugno 2018, n. 21.</t>
+        </is>
+      </c>
       <c r="O477" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28602,20 +31254,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr"/>
-      <c r="G478" s="2" t="n"/>
-      <c r="H478" s="3" t="n"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H478" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I478" s="3" t="n">
         <v>45154</v>
       </c>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N478" t="inlineStr"/>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>Il presente atto provvede all’acquisizione del servizio di formazione linguistica individuale a favore del Dott. Carlo Clini – Direttore dell’Unità Organizzativa Rapporti con l'Unione Europea.</t>
+        </is>
+      </c>
       <c r="O478" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28640,7 +31312,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -28648,20 +31320,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" s="2" t="n"/>
-      <c r="H479" s="3" t="n"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H479" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I479" s="3" t="n">
         <v>45154</v>
       </c>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N479" t="inlineStr"/>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>Il presente provvedimento autorizza la partecipazione di personale regionale a corsi di formazione a catalogo organizzati da soggetti esterni.</t>
+        </is>
+      </c>
       <c r="O479" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28686,7 +31378,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -28694,20 +31386,40 @@
           <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" s="2" t="n"/>
-      <c r="H480" s="3" t="n"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="H480" s="3" t="n">
+        <v>45107</v>
+      </c>
       <c r="I480" s="3" t="n">
         <v>45153</v>
       </c>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N480" t="inlineStr"/>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>Il presente provvedimento autorizza la partecipazione di personale regionale a corsi di formazione a catalogo organizzati da soggetti esterni.</t>
+        </is>
+      </c>
       <c r="O480" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28740,20 +31452,40 @@
           <t>Direzione Verifica e Gestione Atti del Presidente e della Giunta</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr"/>
-      <c r="G481" s="2" t="n"/>
-      <c r="H481" s="3" t="n"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="n">
+        <v>5577</v>
+      </c>
+      <c r="H481" s="3" t="n">
+        <v>44782</v>
+      </c>
       <c r="I481" s="3" t="n">
         <v>45145</v>
       </c>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Cittadino</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Demanio e patrimonio</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N481" t="inlineStr"/>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>Acquisto di riviste, banca dati online e pubblicazioni per le Strutture afferenti all’Area della Segreteria della Giunta regionale e relativo impegno di spesa, ai sensi dell’articolo 1, comma 2, lett. a) del D.L. 76/2020, (Decreto Semplificazioni), convertito, con modificazioni, dalla legge 11 settembre 2020, n. 120 e s.m.i. (CIG Z5B36CE04C - CIG ZBD36CE32E - CIG ZB136CE3DE).</t>
+        </is>
+      </c>
       <c r="O481" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28786,20 +31518,38 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
       <c r="G482" s="2" t="n"/>
-      <c r="H482" s="3" t="n"/>
+      <c r="H482" s="3" t="n">
+        <v>45103</v>
+      </c>
       <c r="I482" s="3" t="n">
         <v>45145</v>
       </c>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N482" t="inlineStr"/>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Procedura aperta multilotto ex art. 60 del D.lgs. 50/2016 e ss.mm.ii. per l’acquisizione, dalle Agenzie di Stampa, di servizi di informazione e giornalistici per la Giunta regionale del Veneto con decorrenza dal 1° febbraio 2024.</t>
+        </is>
+      </c>
       <c r="O482" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28832,20 +31582,40 @@
           <t>Direzione Acquisti e AA.GG</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" s="2" t="n"/>
-      <c r="H483" s="3" t="n"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Bando di gara comunitario</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="n">
+        <v>1147000</v>
+      </c>
+      <c r="H483" s="3" t="n">
+        <v>45104</v>
+      </c>
       <c r="I483" s="3" t="n">
         <v>45145</v>
       </c>
-      <c r="K483" t="inlineStr"/>
-      <c r="L483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Affari generali</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N483" t="inlineStr"/>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Gara comunitaria per l'affidamento in concessione del servizio di bistrot e bar presso i locali di Palazzo della Regione del Veneto, Cannaregio 23 - Venezia.</t>
+        </is>
+      </c>
       <c r="O483" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28870,7 +31640,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -28879,19 +31649,35 @@
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
-      <c r="G484" s="2" t="n"/>
-      <c r="H484" s="3" t="n"/>
+      <c r="G484" s="2" t="n">
+        <v>14884</v>
+      </c>
+      <c r="H484" s="3" t="n">
+        <v>44985</v>
+      </c>
       <c r="I484" s="3" t="n">
         <v>45144</v>
       </c>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N484" t="inlineStr"/>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Affidamento diretto del servizio di studi, indagini e statistiche territoriali e impegno di spesa a favore di Itineraria s.r.l. nell’ambito del Programma regionale per la valorizzazione turistica dei Cammini del Veneto. CUP: H18J22001140002. CIG: Z5538E7D3C. Legge regionale 30 gennaio 2020, n. 4 “Disposizioni per il riconoscimento, la valorizzazione e la promozione dei cammini veneti”. DGR n. 1465 del 18 novembre 2022.</t>
+        </is>
+      </c>
       <c r="O484" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28924,20 +31710,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" s="2" t="n"/>
-      <c r="H485" s="3" t="n"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="n">
+        <v>34877</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>44985</v>
+      </c>
       <c r="I485" s="3" t="n">
         <v>45144</v>
       </c>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N485" t="inlineStr"/>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Affidamento diretto del servizio di organizzazione eventi e impegno di spesa a favore di UNPLI VENETO – APS nell’ambito del Programma regionale per la valorizzazione turistica dei Cammini del Veneto. CUP: H18J22001140002. CIG: ZDA38E7BD3. Legge regionale 30 gennaio 2020, n. 4 “Disposizioni per il riconoscimento, la valorizzazione e la promozione dei cammini veneti”. DGR n. 1465 del 18 novembre 2022.</t>
+        </is>
+      </c>
       <c r="O485" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -28962,7 +31768,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -28970,20 +31776,38 @@
           <t>Direzione Difesa del Suolo e della Costa</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
       <c r="G486" s="2" t="n"/>
-      <c r="H486" s="3" t="n"/>
+      <c r="H486" s="3" t="n">
+        <v>45083</v>
+      </c>
       <c r="I486" s="3" t="n">
         <v>45142</v>
       </c>
-      <c r="K486" t="inlineStr"/>
-      <c r="L486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Ambiente | Attività produttive</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N486" t="inlineStr"/>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Indizione delle procedure per il conferimento di concessioni minerarie di acqua termale in Comune di Montegrotto Terme (PD), indicate nel decreto 190/2023 Decreto n. 190 del 19/05/2023 e Allegato A</t>
+        </is>
+      </c>
       <c r="O486" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -50404,7 +53228,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
     </row>
@@ -50426,7 +53250,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/docs/data/bandi_veneto.xlsx
+++ b/docs/data/bandi_veneto.xlsx
@@ -51412,20 +51412,38 @@
           <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Riconoscimento</t>
+        </is>
+      </c>
       <c r="G787" s="2" t="n"/>
-      <c r="H787" s="3" t="n"/>
+      <c r="H787" s="3" t="n">
+        <v>44561</v>
+      </c>
       <c r="I787" s="3" t="n">
         <v>44592</v>
       </c>
-      <c r="K787" t="inlineStr"/>
-      <c r="L787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Formazione</t>
+        </is>
+      </c>
       <c r="M787" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N787" t="inlineStr"/>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Approvazione dell’Avviso pubblico e della Direttiva per la presentazione di progetti per interventi formativi propedeutici all’esame di abilitazione alla conduzione di generatori di vapore. D.Lgs. 14 settembre 2015, n. 151. Decreto Ministeriale n. 94 del 7 agosto 2020. Con la presente Direttiva, si intendono disciplinare i corsi di formazione teorico-pratici di cui all’art. 4, comma 1 del DM 94/2020 propedeutici agli esami di abilitazione per il conseguimento del patentino di abilitazione alla conduzione di generatori di vapore di 1°, 2°, 3° e 4° grado.</t>
+        </is>
+      </c>
       <c r="O787" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51458,20 +51476,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F788" t="inlineStr"/>
-      <c r="G788" s="2" t="n"/>
-      <c r="H788" s="3" t="n"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="n">
+        <v>81967</v>
+      </c>
+      <c r="H788" s="3" t="n">
+        <v>44568</v>
+      </c>
       <c r="I788" s="3" t="n">
         <v>44592</v>
       </c>
-      <c r="K788" t="inlineStr"/>
-      <c r="L788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
       <c r="M788" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N788" t="inlineStr"/>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Procedura per l’affidamento diretto del servizio finalizzato alla “Predisposizione delle misure di conservazione per le ZPS”, finanziato dal Programma di Sviluppo Rurale per il Veneto 2014-2020 ai sensi del Regolamento (UE) n. 1305/2013 del Parlamento Europeo e del Consiglio. Misura 20 Assistenza tecnica 2014-2020. Programma operativo PO. 4 - DGR n. 1394 del 1 ottobre 2019”. CUPH19H21000710006. CIG 8989748EB8. Approvazione degli esiti di gara e aggiudicazione.</t>
+        </is>
+      </c>
       <c r="O788" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51504,20 +51542,40 @@
           <t>Direzione Agroambiente, Programmazione e Gestione Ittica e Faunistico-Venatoria</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr"/>
-      <c r="G789" s="2" t="n"/>
-      <c r="H789" s="3" t="n"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="n">
+        <v>996158</v>
+      </c>
+      <c r="H789" s="3" t="n">
+        <v>44512</v>
+      </c>
       <c r="I789" s="3" t="n">
         <v>44572</v>
       </c>
-      <c r="K789" t="inlineStr"/>
-      <c r="L789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>Agricoltura e foreste</t>
+        </is>
+      </c>
       <c r="M789" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N789" t="inlineStr"/>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Si dispone l'apertura termini per la presentazione delle domande di sostegno per la misura di cui all'articolo 43 par 1 e 3 “Porti, luoghi di sbarco, sale per la vendita all’asta e ripari di pesca” del Reg. (UE) n. 508/2014.</t>
+        </is>
+      </c>
       <c r="O789" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51550,20 +51608,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
-      <c r="G790" s="2" t="n"/>
-      <c r="H790" s="3" t="n"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="n">
+        <v>3025000</v>
+      </c>
+      <c r="H790" s="3" t="n">
+        <v>44544</v>
+      </c>
       <c r="I790" s="3" t="n">
         <v>44572</v>
       </c>
-      <c r="K790" t="inlineStr"/>
-      <c r="L790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M790" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N790" t="inlineStr"/>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Azioni di accompagnamento, sviluppo e rafforzamento del sistema duale nell’ambito dell’Istruzione e Formazione Professionale. Approvazione dell’Avviso pubblico e della Direttiva per la presentazione di progetti formativi per la realizzazione, in modalità duale, di percorsi triennali di Istruzione e Formazione Professionale per il triennio 2022-2025 per il conseguimento della qualifica professionale nelle sezioni comparti vari ed edilizia. L. 53/2003, D.Lgs n. 226/2005, D.Lgs n. 81/2015, Accordo Conferenza Stato-Regioni 24/09/2015, Protocollo d’intesa MLPS –Regioni del 13/01/2016 Con il provvedimento si approvano l’Avviso pubblico e la…</t>
+        </is>
+      </c>
       <c r="O790" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51596,20 +51674,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F791" t="inlineStr"/>
-      <c r="G791" s="2" t="n"/>
-      <c r="H791" s="3" t="n"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="n">
+        <v>2120000</v>
+      </c>
+      <c r="H791" s="3" t="n">
+        <v>44544</v>
+      </c>
       <c r="I791" s="3" t="n">
         <v>44572</v>
       </c>
-      <c r="K791" t="inlineStr"/>
-      <c r="L791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>Formazione | Istruzione</t>
+        </is>
+      </c>
       <c r="M791" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N791" t="inlineStr"/>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>Azioni di accompagnamento, sviluppo e rafforzamento del sistema duale nell’ambito dell’Istruzione e Formazione Professionale. Approvazione dell’Avviso pubblico e della Direttiva per la presentazione di progetti formativi per la realizzazione, in modalità duale, di percorsi triennali di Istruzione e Formazione Professionale per il triennio 2022-2025 per il conseguimento della qualifica professionale nella sezione servizi del benessere. L. 53/2003, D.Lgs n. 226/2005, D.Lgs n. 81/2015, Accordo Conferenza Stato-Regioni 24/09/2015, Protocollo d’intesa MLPS –Regioni del 13/01/2016 Con il provvedimento si approvano l’Avviso pubblico e la Direttiva…</t>
+        </is>
+      </c>
       <c r="O791" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51634,7 +51732,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -51643,19 +51741,35 @@
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
-      <c r="G792" s="2" t="n"/>
-      <c r="H792" s="3" t="n"/>
+      <c r="G792" s="2" t="n">
+        <v>570000</v>
+      </c>
+      <c r="H792" s="3" t="n">
+        <v>44523</v>
+      </c>
       <c r="I792" s="3" t="n">
         <v>44561</v>
       </c>
-      <c r="K792" t="inlineStr"/>
-      <c r="L792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>ICT | Informatica e-government</t>
+        </is>
+      </c>
       <c r="M792" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N792" t="inlineStr"/>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Acquisto mediante procedura aperta telematica sopra soglia comunitaria, ex art. 60 D.Lgs. 50/2016, di servizi di fornitura, personalizzazione, avviamento e gestione in hosting di un destination management system (DMS) della durata di 60 mesi. CIG 8981974F69, CUI S80007580279202000139.</t>
+        </is>
+      </c>
       <c r="O792" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51688,20 +51802,40 @@
           <t>Direzione Turismo</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr"/>
-      <c r="G793" s="2" t="n"/>
-      <c r="H793" s="3" t="n"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="n">
+        <v>81967</v>
+      </c>
+      <c r="H793" s="3" t="n">
+        <v>44526</v>
+      </c>
       <c r="I793" s="3" t="n">
         <v>44556</v>
       </c>
-      <c r="K793" t="inlineStr"/>
-      <c r="L793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Cittadino Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M793" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N793" t="inlineStr"/>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Decreto a contrarre. Indizione procedura di gara ai sensi dell'art. 1 comma 2 lettera a) della L.120/20 ss.mm.ii per l'affidamento diretto del servizio finalizzato alla “Predisposizione delle misure di conservazione per le ZPS”, finanziato dal Programma di Sviluppo Rurale per il Veneto 2014-2020 ai sensi del Regolamento (UE) n. 1305/2013 del Parlamento Europeo e del Consiglio. Misura 20 Assistenza tecnica 2014-2020. Programma operativo PO.4 - DGR n. 1394 del 1 ottobre 2019”. CUPH19H21000710006. CIG 8989748EB8.</t>
+        </is>
+      </c>
       <c r="O793" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51734,20 +51868,40 @@
           <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
-      <c r="F794" t="inlineStr"/>
-      <c r="G794" s="2" t="n"/>
-      <c r="H794" s="3" t="n"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="n">
+        <v>22965005</v>
+      </c>
+      <c r="H794" s="3" t="n">
+        <v>44523</v>
+      </c>
       <c r="I794" s="3" t="n">
         <v>44553</v>
       </c>
-      <c r="K794" t="inlineStr"/>
-      <c r="L794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Attività produttive</t>
+        </is>
+      </c>
       <c r="M794" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N794" t="inlineStr"/>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>La Regione Veneto finanzia tre bandi di ristoro, che verranno gestiti da Unioncamere del Veneto, con una dotazione finanziaria complessiva di euro 22.965.004,74. Nello specifico, per quel che riguarda la suddivisione delle risorse, il primo bando è pensato per imprese venete rientranti nella filiera matrimoni ed eventi privati con una dotazione finanziaria complessiva di complessiva di 20.263.239,48 euro. Il secondo, invece, è rivolto ai parchi tematici, acquari, parchi geologici e giardini zoologici del Veneto con una dotazione finanziaria di 1.350.882,63 euro. Il terzo e ultimo bando con una dotazione di 1.350.882,63 euro a disposizione…</t>
+        </is>
+      </c>
       <c r="O794" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51780,20 +51934,40 @@
           <t>Direzione Ict e Agenda Digitale</t>
         </is>
       </c>
-      <c r="F795" t="inlineStr"/>
-      <c r="G795" s="2" t="n"/>
-      <c r="H795" s="3" t="n"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="n">
+        <v>166203</v>
+      </c>
+      <c r="H795" s="3" t="n">
+        <v>44519</v>
+      </c>
       <c r="I795" s="3" t="n">
         <v>44550</v>
       </c>
-      <c r="K795" t="inlineStr"/>
-      <c r="L795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
       <c r="M795" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N795" t="inlineStr"/>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Il provvedimento autorizza l’adesione al Contratto Quadro Consip per “Servizi di cloud computing, di sicurezza, di realizzazione di portali e servizi online e di cooperazione applicativa per le pubbliche amministrazioni – ID SIGEF 1403 Lotto 1”, cig. 55187486EA, Cig derivato 8980287F41, CUI S80007580279202100070, CUP H79J21009840001 per l’erogazione, dalla sottoscrizione sino al 20 luglio 2022, di Servizi di Cloud Enabling a supporto del Bando Innovation Lab, per l’importo di Euro 166.203,35= iva esclusa. L’acquisto attua interventi a valere sul FSC 2014-2020 – Delibera CIPE (ora CIPESS) n. 39 del 28/07/2020 (copertura degli interventi…</t>
+        </is>
+      </c>
       <c r="O795" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51826,20 +52000,40 @@
           <t>Direzione Beni Attività Culturali e Sport</t>
         </is>
       </c>
-      <c r="F796" t="inlineStr"/>
-      <c r="G796" s="2" t="n"/>
-      <c r="H796" s="3" t="n"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H796" s="3" t="n">
+        <v>44516</v>
+      </c>
       <c r="I796" s="3" t="n">
         <v>44547</v>
       </c>
-      <c r="K796" t="inlineStr"/>
-      <c r="L796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M796" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N796" t="inlineStr"/>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Trattativa diretta n. 1894574 sul Mercato elettronico della Pubblica Amministrazione per l’affidamento, ai sensi dell’art. 36, co.2, lett. a), del servizio di realizzazione di uno spettacolo e di un evento di presentazione e promozione del segmento veneto del “Sentiero della Pace”, nell’ambito del progetto WALKOFPEACE, WP 3.1, ATT 5 dedicata a “Eventi tematici, conferenze e mostre”, finanziato dal Programma Interreg V A Italia-Slovenia 2014 - 2020. CUP: H19F18000510007. CIG: Z7133B726A. Decreto di aggiudicazione definitiva, impegno di spesa, accertamento delle entrate e stipula con Like Srls con sede in Mestre-Venezia.</t>
+        </is>
+      </c>
       <c r="O796" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51872,20 +52066,40 @@
           <t>Direzione Enti Locali, Procedimenti Elettorali E Grandi Eventi</t>
         </is>
       </c>
-      <c r="F797" t="inlineStr"/>
-      <c r="G797" s="2" t="n"/>
-      <c r="H797" s="3" t="n"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H797" s="3" t="n">
+        <v>44526</v>
+      </c>
       <c r="I797" s="3" t="n">
         <v>44545</v>
       </c>
-      <c r="K797" t="inlineStr"/>
-      <c r="L797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M797" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N797" t="inlineStr"/>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Bando di finanziamento per l'assegnazione di contributi per l'avvio del processo di inserimento di territori, beni ed elementi nelle liste propositive nazionali del patrimonio Mondiale Unesco, o all'interno dell'elenco del Programma "L'uomo e la biosfera" - MAB.</t>
+        </is>
+      </c>
       <c r="O797" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51918,20 +52132,40 @@
           <t>Direzione Edilizia Ospedaliera A Finalita' Collettiva</t>
         </is>
       </c>
-      <c r="F798" t="inlineStr"/>
-      <c r="G798" s="2" t="n"/>
-      <c r="H798" s="3" t="n"/>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Fondo di rotazione</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H798" s="3" t="n">
+        <v>44505</v>
+      </c>
       <c r="I798" s="3" t="n">
         <v>44535</v>
       </c>
-      <c r="K798" t="inlineStr"/>
-      <c r="L798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Sociale</t>
+        </is>
+      </c>
       <c r="M798" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N798" t="inlineStr"/>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Con Deliberazione di Giunta n. 1495 del 02 novembre 2021 si approvano le modalità e i termini per l'ammissione a finanziamento regionale in conto capitale a rimborso graduale, secondo quote annuali costanti, senza oneri per interessi per la realizzazione di interventi edilizi sul patrimonio immobiliare di proprietà di soggetti pubblici o soggetti privati non a scopo di lucro nel settore sociale e socio-sanitario (art. 44 della LR n. 45 del 29/12/20217 " Collegato alla legge di stabilità regionale 2018" e s.m.i.)</t>
+        </is>
+      </c>
       <c r="O798" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -51964,20 +52198,40 @@
           <t>Direzione Beni Attività Culturali e Sport</t>
         </is>
       </c>
-      <c r="F799" t="inlineStr"/>
-      <c r="G799" s="2" t="n"/>
-      <c r="H799" s="3" t="n"/>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H799" s="3" t="n">
+        <v>44503</v>
+      </c>
       <c r="I799" s="3" t="n">
         <v>44534</v>
       </c>
-      <c r="K799" t="inlineStr"/>
-      <c r="L799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
       <c r="M799" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N799" t="inlineStr"/>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Decreto a contrarre, ai sensi dell’art. 36, co.2, lett. a), per l’affidamento del servizio di realizzazione di uno spettacolo e di un evento di presentazione e promozione del segmento veneto del “Sentiero della Pace”, nell’ambito del progetto WALKOFPEACE, WP 3.1, ATT 5 dedicata a “Eventi tematici, conferenze e mostre”, finanziato dal Programma Interreg V A Italia-Slovenia 2014 - 2020. CUP: H19F18000510007. CIG: Z7133B726A, mediante trattativa diretta su MEPA.</t>
+        </is>
+      </c>
       <c r="O799" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -52010,20 +52264,40 @@
           <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
-      <c r="F800" t="inlineStr"/>
-      <c r="G800" s="2" t="n"/>
-      <c r="H800" s="3" t="n"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="n">
+        <v>252357</v>
+      </c>
+      <c r="H800" s="3" t="n">
+        <v>44516</v>
+      </c>
       <c r="I800" s="3" t="n">
         <v>44530</v>
       </c>
-      <c r="K800" t="inlineStr"/>
-      <c r="L800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Istruzione</t>
+        </is>
+      </c>
       <c r="M800" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N800" t="inlineStr"/>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Approvazione delle Linee Guida per la realizzazione dell'iniziativa " Le giornate dello sport" nell'Anno Scolastico e Formativo 2021-2022 e previsione delle risorse a sostegno dell'iniziativa. Legge Regionale 31/03/2017, n. 8 e s.m.i. art. 2, comma 4. DDGR n. 764 del 15/06/2021 e n. 937 del 05/07/2021.</t>
+        </is>
+      </c>
       <c r="O800" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -52056,20 +52330,40 @@
           <t>Direzione Ambiente</t>
         </is>
       </c>
-      <c r="F801" t="inlineStr"/>
-      <c r="G801" s="2" t="n"/>
-      <c r="H801" s="3" t="n"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="H801" s="3" t="n">
+        <v>44512</v>
+      </c>
       <c r="I801" s="3" t="n">
         <v>44530</v>
       </c>
-      <c r="K801" t="inlineStr"/>
-      <c r="L801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M801" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N801" t="inlineStr"/>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Bando rivolto alle Amministrazioni comunali a sostegno di interventi di rimozione e smaltimento di rifiuti ai sensi dell'art. 192 del D. Lgs. 152/2006</t>
+        </is>
+      </c>
       <c r="O801" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -52102,20 +52396,40 @@
           <t>Direzione Ambiente</t>
         </is>
       </c>
-      <c r="F802" t="inlineStr"/>
-      <c r="G802" s="2" t="n"/>
-      <c r="H802" s="3" t="n"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="H802" s="3" t="n">
+        <v>44512</v>
+      </c>
       <c r="I802" s="3" t="n">
         <v>44530</v>
       </c>
-      <c r="K802" t="inlineStr"/>
-      <c r="L802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Ambiente</t>
+        </is>
+      </c>
       <c r="M802" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N802" t="inlineStr"/>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Bando per l'assegnazione alle Amministrazioni comunali del Veneto di contributi a sostegno di interventi di adeguamento e/o manutenzione straordinaria di centri comunali di raccolta di rifiuti urbani.</t>
+        </is>
+      </c>
       <c r="O802" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -52140,7 +52454,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -52149,19 +52463,35 @@
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
-      <c r="G803" s="2" t="n"/>
-      <c r="H803" s="3" t="n"/>
+      <c r="G803" s="2" t="n">
+        <v>63000</v>
+      </c>
+      <c r="H803" s="3" t="n">
+        <v>44496</v>
+      </c>
       <c r="I803" s="3" t="n">
         <v>44527</v>
       </c>
-      <c r="K803" t="inlineStr"/>
-      <c r="L803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>ICT | Informatica e-government</t>
+        </is>
+      </c>
       <c r="M803" t="inlineStr">
         <is>
           <t>Portale Bandi Regione Veneto</t>
         </is>
       </c>
-      <c r="N803" t="inlineStr"/>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>Attuazione del Programma biennale degli acquisti di forniture e servizi 2021/2022 approvato con D.G.R. n. 245 del 9 marzo 2021. Presa d’atto dell’esito negativo, a seguito di gara deserta, della procedura autorizzata con Decreto n. 108 del 15/09/2021, CIG 88166219CE per l’acquisto, mediante richiesta di offerta (RdO) sul Mercato Elettronico della Pubblica Amministrazione (MEPA), di servizi di manutenzione evolutiva e servizi informatici per il software “Ispettorati di Porto”. Annullamento delle prenotazioni di spesa n. 1316 e n. 1317 sul Bilancio 2022, n. 508 e n. 509 sul Bilancio 2023, assunte con D.D.R. 108/2021. Reindizione della…</t>
+        </is>
+      </c>
       <c r="O803" s="4" t="inlineStr">
         <is>
           <t>Apri</t>
@@ -59302,7 +59632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 09:13</t>
+          <t>2026-10-25 09:29</t>
         </is>
       </c>
     </row>
@@ -59324,7 +59654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/docs/data/bandi_veneto.xlsx
+++ b/docs/data/bandi_veneto.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi'!$A$1:$O$900</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi'!$A$1:$O$899</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O900"/>
+  <dimension ref="A1:O899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52565,47 +52565,49 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Chiuso</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Reindizione della procedura di gara mediante richiesta di offerta (RdO) sul Mercato Elettronico della Pubblica Amministrazione (MEPA) per l'acquisto servizi di manutenzione evolutiva e servizi informatici per il software "Ispettorati di Porto"</t>
+          <t>Avviso Pubblico - Concessione di aree del demanio marittimo per attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. - Artemisia Società Cooperativa</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Bando</t>
+          <t>Avviso</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>Direzione Ict e Agenda Digitale</t>
-        </is>
-      </c>
-      <c r="F805" t="inlineStr"/>
-      <c r="G805" s="2" t="n">
-        <v>63000</v>
-      </c>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="n"/>
       <c r="H805" s="3" t="n">
-        <v>44496</v>
+        <v>46290</v>
       </c>
       <c r="I805" s="3" t="n">
-        <v>44527</v>
+        <v>46323</v>
       </c>
       <c r="K805" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>ICT | Informatica e-government</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
@@ -52615,7 +52617,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>Attuazione del Programma biennale degli acquisti di forniture e servizi 2021/2022 approvato con D.G.R. n. 245 del 9 marzo 2021. Presa d’atto dell’esito negativo, a seguito di gara deserta, della procedura autorizzata con Decreto n. 108 del 15/09/2021, CIG 88166219CE per l’acquisto, mediante richiesta di offerta (RdO) sul Mercato Elettronico della Pubblica Amministrazione (MEPA), di servizi di manutenzione evolutiva e servizi informatici per il software “Ispettorati di Porto”. Annullamento delle prenotazioni di spesa n. 1316 e n. 1317 sul Bilancio 2022, n. 508 e n. 509 sul Bilancio 2023, assunte con D.D.R. 108/2021. Reindizione della…</t>
+          <t>Unità Organizzativa Genio Civile Rovigo. - Avviso Pubblico - Concessione di aree del demanio marittimo da destinarsi ad attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. Richiedente: Artemisia Società Cooperativa (C.F. 01372020295).</t>
         </is>
       </c>
       <c r="O805" s="4" t="inlineStr">
@@ -52632,7 +52634,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Avviso Pubblico - Concessione di aree del demanio marittimo per attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. - Artemisia Società Cooperativa</t>
+          <t>Avviso pubblico esplorativo di mercato e contestuale raccolta di preventivi non vincolanti per la fornitura di contrassegni per richiami vivi destinati alla caccia appostamento</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -52642,34 +52644,36 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Unità Organizzativa Pianificazione e Gestione Faunistico Venatoria</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G806" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="n">
+        <v>131148</v>
+      </c>
       <c r="H806" s="3" t="n">
-        <v>46290</v>
+        <v>46307</v>
       </c>
       <c r="I806" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="K806" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -52679,7 +52683,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo. - Avviso Pubblico - Concessione di aree del demanio marittimo da destinarsi ad attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. Richiedente: Artemisia Società Cooperativa (C.F. 01372020295).</t>
+          <t>Indagine di mercato finalizzata all’eventuale affidamento diretto della fornitura di contrassegni inamovibili numerati, costituiti da fascette in materiale plastico, per richiami vivi destinati alla caccia da appostamento, ai sensi dell’art. 35-quater della L.R. n. 50/1993, come modificata dalla L.R. n. 15/2025, per le annualità 2026 e 2027.</t>
         </is>
       </c>
       <c r="O806" s="4" t="inlineStr">
@@ -52696,7 +52700,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Avviso pubblico esplorativo di mercato e contestuale raccolta di preventivi non vincolanti per la fornitura di contrassegni per richiami vivi destinati alla caccia appostamento</t>
+          <t>Affidamento del servizio di supporto all'istruttoria in materia di aiuti di Stato a favore del Programma Interreg VI A Italia-Croazia 2021-2027</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -52711,7 +52715,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Pianificazione e Gestione Faunistico Venatoria</t>
+          <t>Unità Organizzativa AdG Italia - Croazia</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
@@ -52720,22 +52724,22 @@
         </is>
       </c>
       <c r="G807" s="2" t="n">
-        <v>131148</v>
+        <v>19500</v>
       </c>
       <c r="H807" s="3" t="n">
-        <v>46307</v>
+        <v>46052</v>
       </c>
       <c r="I807" s="3" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="K807" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Affari generali | Europa | FESR | Interreg</t>
         </is>
       </c>
       <c r="M807" t="inlineStr">
@@ -52745,7 +52749,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>Indagine di mercato finalizzata all’eventuale affidamento diretto della fornitura di contrassegni inamovibili numerati, costituiti da fascette in materiale plastico, per richiami vivi destinati alla caccia da appostamento, ai sensi dell’art. 35-quater della L.R. n. 50/1993, come modificata dalla L.R. n. 15/2025, per le annualità 2026 e 2027.</t>
+          <t>Con il decreto del Direttore dell'Unità Organizzativa AdG Italia-Croazia n. 268 del 23 dicembre 2025, si è proceduto all'affidamento diretto del servizio di supporto all'istruttoria in materia di aiuti di Stato delle proposte progettuali di tipo Standard, pervenute in risposta al terzo bando del Programma Interreg VI A Italia-Croazia 2021-2027, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023 e s.m.i. Con Decreto del Direttore dell'Unità organizzativa AdG Italia-Croazia n. 148 del 6 luglio 2026 si è disposta la sostituzione del RUP per il contratto in oggetto, a seguito della nomina del nuovo Direttore della U.O. AdG…</t>
         </is>
       </c>
       <c r="O807" s="4" t="inlineStr">
@@ -52762,7 +52766,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di supporto all'istruttoria in materia di aiuti di Stato a favore del Programma Interreg VI A Italia-Croazia 2021-2027</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -52772,36 +52776,36 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Unità Organizzativa AdG Italia - Croazia</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G808" s="2" t="n">
-        <v>19500</v>
+        <v>1500</v>
       </c>
       <c r="H808" s="3" t="n">
-        <v>46052</v>
+        <v>46294</v>
       </c>
       <c r="I808" s="3" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L808" t="inlineStr">
         <is>
-          <t>Affari generali | Europa | FESR | Interreg</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
@@ -52811,7 +52815,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>Con il decreto del Direttore dell'Unità Organizzativa AdG Italia-Croazia n. 268 del 23 dicembre 2025, si è proceduto all'affidamento diretto del servizio di supporto all'istruttoria in materia di aiuti di Stato delle proposte progettuali di tipo Standard, pervenute in risposta al terzo bando del Programma Interreg VI A Italia-Croazia 2021-2027, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023 e s.m.i. Con Decreto del Direttore dell'Unità organizzativa AdG Italia-Croazia n. 148 del 6 luglio 2026 si è disposta la sostituzione del RUP per il contratto in oggetto, a seguito della nomina del nuovo Direttore della U.O. AdG…</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="O808" s="4" t="inlineStr">
@@ -52828,7 +52832,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
+          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -52843,31 +52847,31 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Demanio e Gestione del Patrimonio</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Avviso di alienazione</t>
         </is>
       </c>
       <c r="G809" s="2" t="n">
-        <v>1500</v>
+        <v>4237500</v>
       </c>
       <c r="H809" s="3" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I809" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Demanio e patrimonio</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
@@ -52877,7 +52881,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
+          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
         </is>
       </c>
       <c r="O809" s="4" t="inlineStr">
@@ -52894,7 +52898,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -52909,31 +52913,31 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Direzione Demanio e Gestione del Patrimonio</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Avviso di alienazione</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G810" s="2" t="n">
-        <v>4237500</v>
+        <v>5800</v>
       </c>
       <c r="H810" s="3" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="I810" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K810" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>Demanio e patrimonio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -52943,7 +52947,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="O810" s="4" t="inlineStr">
@@ -52960,7 +52964,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
+          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -52970,36 +52974,36 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G811" s="2" t="n">
-        <v>5800</v>
+        <v>55000</v>
       </c>
       <c r="H811" s="3" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="I811" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -53009,7 +53013,7 @@
       </c>
       <c r="N811" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
+          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
         </is>
       </c>
       <c r="O811" s="4" t="inlineStr">
@@ -53026,7 +53030,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
+          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -53041,7 +53045,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
@@ -53050,22 +53054,22 @@
         </is>
       </c>
       <c r="G812" s="2" t="n">
-        <v>55000</v>
+        <v>938</v>
       </c>
       <c r="H812" s="3" t="n">
-        <v>46283</v>
+        <v>46294</v>
       </c>
       <c r="I812" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica | Turismo</t>
+          <t>Pari opportunità</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -53075,7 +53079,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
+          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
         </is>
       </c>
       <c r="O812" s="4" t="inlineStr">
@@ -53092,7 +53096,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -53102,36 +53106,30 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G813" s="2" t="n">
-        <v>938</v>
-      </c>
+          <t>U.O. Genio Civile Venezia</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" s="2" t="n"/>
       <c r="H813" s="3" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I813" s="3" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Pari opportunità</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -53141,7 +53139,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
         </is>
       </c>
       <c r="O813" s="4" t="inlineStr">
@@ -53158,7 +53156,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -53201,7 +53199,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
         </is>
       </c>
       <c r="O814" s="4" t="inlineStr">
@@ -53218,7 +53216,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -53233,25 +53231,31 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>U.O. Genio Civile Venezia</t>
-        </is>
-      </c>
-      <c r="F815" t="inlineStr"/>
-      <c r="G815" s="2" t="n"/>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="n">
+        <v>2075</v>
+      </c>
       <c r="H815" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="I815" s="3" t="n">
-        <v>46328</v>
+        <v>46333</v>
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -53261,7 +53265,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="O815" s="4" t="inlineStr">
@@ -53278,7 +53282,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -53293,31 +53297,25 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G816" s="2" t="n">
-        <v>2075</v>
-      </c>
+          <t>Direzione Infrastrutture E Trasporti</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" s="2" t="n"/>
       <c r="H816" s="3" t="n">
-        <v>46301</v>
+        <v>46275</v>
       </c>
       <c r="I816" s="3" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="K816" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -53327,7 +53325,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="O816" s="4" t="inlineStr">
@@ -53344,7 +53342,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -53359,13 +53357,17 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture E Trasporti</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr"/>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
       <c r="G817" s="2" t="n"/>
       <c r="H817" s="3" t="n">
-        <v>46275</v>
+        <v>46304</v>
       </c>
       <c r="I817" s="3" t="n">
         <v>46335</v>
@@ -53377,7 +53379,7 @@
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -53387,7 +53389,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
         </is>
       </c>
       <c r="O817" s="4" t="inlineStr">
@@ -53404,7 +53406,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -53419,29 +53421,27 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F818" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G818" s="2" t="n"/>
+          <t>Direzione Comunicazione E Informazione</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" s="2" t="n">
+        <v>55000</v>
+      </c>
       <c r="H818" s="3" t="n">
-        <v>46304</v>
+        <v>46290</v>
       </c>
       <c r="I818" s="3" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Comunicazione e informazione</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -53451,7 +53451,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
+          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
         </is>
       </c>
       <c r="O818" s="4" t="inlineStr">
@@ -53463,12 +53463,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>In scadenza</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
+          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -53478,32 +53478,36 @@
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Direzione Comunicazione E Informazione</t>
-        </is>
-      </c>
-      <c r="F819" t="inlineStr"/>
+          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
       <c r="G819" s="2" t="n">
-        <v>55000</v>
+        <v>382342</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>46290</v>
+        <v>46318</v>
       </c>
       <c r="I819" s="3" t="n">
-        <v>46336</v>
+        <v>46338</v>
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Comunicazione e informazione</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -53513,7 +53517,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
+          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
         </is>
       </c>
       <c r="O819" s="4" t="inlineStr">
@@ -53530,7 +53534,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
+          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -53540,21 +53544,17 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
-        </is>
-      </c>
-      <c r="F820" t="inlineStr">
-        <is>
-          <t>Avviso di contributo</t>
-        </is>
-      </c>
+          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr"/>
       <c r="G820" s="2" t="n">
-        <v>382342</v>
+        <v>299601</v>
       </c>
       <c r="H820" s="3" t="n">
         <v>46318</v>
@@ -53564,12 +53564,12 @@
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>Sociale</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -53579,7 +53579,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
+          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
         </is>
       </c>
       <c r="O820" s="4" t="inlineStr">
@@ -53596,7 +53596,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
+          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -53606,17 +53606,21 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
-        </is>
-      </c>
-      <c r="F821" t="inlineStr"/>
+          <t>Direzione Formazione E Istruzione</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
       <c r="G821" s="2" t="n">
-        <v>299601</v>
+        <v>30000</v>
       </c>
       <c r="H821" s="3" t="n">
         <v>46318</v>
@@ -53626,12 +53630,12 @@
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -53641,7 +53645,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
+          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
         </is>
       </c>
       <c r="O821" s="4" t="inlineStr">
@@ -53653,12 +53657,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
+          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -53668,36 +53672,36 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Direzione Formazione E Istruzione</t>
+          <t>U.O. Servizi Forestali</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Avviso di contributo</t>
+          <t>Conferenza di servizi</t>
         </is>
       </c>
       <c r="G822" s="2" t="n">
-        <v>30000</v>
+        <v>1400000</v>
       </c>
       <c r="H822" s="3" t="n">
-        <v>46318</v>
+        <v>46297</v>
       </c>
       <c r="I822" s="3" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -53707,7 +53711,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
+          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
         </is>
       </c>
       <c r="O822" s="4" t="inlineStr">
@@ -53724,7 +53728,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -53739,31 +53743,31 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>U.O. Servizi Forestali</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Conferenza di servizi</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G823" s="2" t="n">
-        <v>1400000</v>
+        <v>6830</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="I823" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -53773,7 +53777,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="O823" s="4" t="inlineStr">
@@ -53785,12 +53789,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -53814,7 +53818,7 @@
         </is>
       </c>
       <c r="G824" s="2" t="n">
-        <v>6830</v>
+        <v>3900</v>
       </c>
       <c r="H824" s="3" t="n">
         <v>46308</v>
@@ -53839,7 +53843,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
         </is>
       </c>
       <c r="O824" s="4" t="inlineStr">
@@ -53851,12 +53855,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
+          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -53871,31 +53875,29 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G825" s="2" t="n">
-        <v>3900</v>
-      </c>
+          <t>Avviso di esproprio</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="n"/>
       <c r="H825" s="3" t="n">
-        <v>46308</v>
+        <v>46286</v>
       </c>
       <c r="I825" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -53905,7 +53907,7 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
+          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
         </is>
       </c>
       <c r="O825" s="4" t="inlineStr">
@@ -53917,12 +53919,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -53937,29 +53939,29 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+          <t>Unità Organizzativa Genio Civile Verona</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Avviso di esproprio</t>
+          <t>Avviso di preinformazione</t>
         </is>
       </c>
       <c r="G826" s="2" t="n"/>
       <c r="H826" s="3" t="n">
-        <v>46286</v>
+        <v>46311</v>
       </c>
       <c r="I826" s="3" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M826" t="inlineStr">
@@ -53969,7 +53971,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="O826" s="4" t="inlineStr">
@@ -53986,7 +53988,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -54033,7 +54035,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="O827" s="4" t="inlineStr">
@@ -54114,7 +54116,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -54129,14 +54131,10 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Verona</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr"/>
       <c r="G829" s="2" t="n"/>
       <c r="H829" s="3" t="n">
         <v>46311</v>
@@ -54146,12 +54144,12 @@
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M829" t="inlineStr">
@@ -54161,7 +54159,7 @@
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
         </is>
       </c>
       <c r="O829" s="4" t="inlineStr">
@@ -54178,7 +54176,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -54221,7 +54219,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
         </is>
       </c>
       <c r="O830" s="4" t="inlineStr">
@@ -54238,7 +54236,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -54253,20 +54251,24 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F831" t="inlineStr"/>
+          <t>Unità Organizzativa Fitosanitario</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
       <c r="G831" s="2" t="n"/>
       <c r="H831" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="I831" s="3" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="K831" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L831" t="inlineStr">
@@ -54281,7 +54283,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
+          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
         </is>
       </c>
       <c r="O831" s="4" t="inlineStr">
@@ -54298,7 +54300,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
+          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -54308,34 +54310,36 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Fitosanitario</t>
+          <t>Direzione Pianificazione Territoriale</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G832" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="n">
+        <v>4260</v>
+      </c>
       <c r="H832" s="3" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="I832" s="3" t="n">
-        <v>46343</v>
+        <v>46345</v>
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -54345,7 +54349,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
+          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
         </is>
       </c>
       <c r="O832" s="4" t="inlineStr">
@@ -54362,7 +54366,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -54372,27 +54376,27 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>Direzione Pianificazione Territoriale</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G833" s="2" t="n">
-        <v>4260</v>
+        <v>4519</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I833" s="3" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="K833" t="inlineStr">
         <is>
@@ -54401,7 +54405,7 @@
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
@@ -54411,7 +54415,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
         </is>
       </c>
       <c r="O833" s="4" t="inlineStr">
@@ -54428,7 +54432,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -54452,7 +54456,7 @@
         </is>
       </c>
       <c r="G834" s="2" t="n">
-        <v>4519</v>
+        <v>3824</v>
       </c>
       <c r="H834" s="3" t="n">
         <v>46315</v>
@@ -54477,7 +54481,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="O834" s="4" t="inlineStr">
@@ -54489,12 +54493,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -54504,36 +54508,36 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Avvocatura</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G835" s="2" t="n">
-        <v>3824</v>
+        <v>39468</v>
       </c>
       <c r="H835" s="3" t="n">
-        <v>46315</v>
+        <v>46286</v>
       </c>
       <c r="I835" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="K835" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L835" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
@@ -54543,7 +54547,7 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
         </is>
       </c>
       <c r="O835" s="4" t="inlineStr">
@@ -54560,7 +54564,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
+          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -54584,10 +54588,10 @@
         </is>
       </c>
       <c r="G836" s="2" t="n">
-        <v>39468</v>
+        <v>1144</v>
       </c>
       <c r="H836" s="3" t="n">
-        <v>46286</v>
+        <v>46301</v>
       </c>
       <c r="I836" s="3" t="n">
         <v>46348</v>
@@ -54609,7 +54613,7 @@
       </c>
       <c r="N836" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
+          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
         </is>
       </c>
       <c r="O836" s="4" t="inlineStr">
@@ -54626,7 +54630,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
+          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -54650,10 +54654,10 @@
         </is>
       </c>
       <c r="G837" s="2" t="n">
-        <v>1144</v>
+        <v>9155</v>
       </c>
       <c r="H837" s="3" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="I837" s="3" t="n">
         <v>46348</v>
@@ -54675,7 +54679,7 @@
       </c>
       <c r="N837" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
+          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
         </is>
       </c>
       <c r="O837" s="4" t="inlineStr">
@@ -54692,7 +54696,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
+          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -54707,7 +54711,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>Avvocatura</t>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -54716,22 +54720,22 @@
         </is>
       </c>
       <c r="G838" s="2" t="n">
-        <v>9155</v>
+        <v>77000</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>46308</v>
+        <v>46318</v>
       </c>
       <c r="I838" s="3" t="n">
-        <v>46348</v>
+        <v>46356</v>
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L838" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Ambiente | Territorio | Turismo</t>
         </is>
       </c>
       <c r="M838" t="inlineStr">
@@ -54741,7 +54745,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
+          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
         </is>
       </c>
       <c r="O838" s="4" t="inlineStr">
@@ -54753,12 +54757,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
+          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -54768,36 +54772,30 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
-        </is>
-      </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G839" s="2" t="n">
-        <v>77000</v>
-      </c>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" s="2" t="n"/>
       <c r="H839" s="3" t="n">
-        <v>46318</v>
+        <v>46161</v>
       </c>
       <c r="I839" s="3" t="n">
         <v>46356</v>
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio | Turismo</t>
+          <t>FESR | Protezione civile</t>
         </is>
       </c>
       <c r="M839" t="inlineStr">
@@ -54807,7 +54805,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="O839" s="4" t="inlineStr">
@@ -54824,7 +54822,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -54834,30 +54832,36 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
-        </is>
-      </c>
-      <c r="F840" t="inlineStr"/>
-      <c r="G840" s="2" t="n"/>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="n">
+        <v>28800</v>
+      </c>
       <c r="H840" s="3" t="n">
-        <v>46161</v>
+        <v>46304</v>
       </c>
       <c r="I840" s="3" t="n">
-        <v>46356</v>
+        <v>46361</v>
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L840" t="inlineStr">
         <is>
-          <t>FESR | Protezione civile</t>
+          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
@@ -54867,7 +54871,7 @@
       </c>
       <c r="N840" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
         </is>
       </c>
       <c r="O840" s="4" t="inlineStr">
@@ -54879,12 +54883,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
+          <t>Avviso di istanza di permesso di ricerca di risorse geotermiche presentata da SANTONI GROUP SRL - Area "GEO GARDA ENERGY".</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -54894,36 +54898,30 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G841" s="2" t="n">
-        <v>28800</v>
-      </c>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr"/>
+      <c r="G841" s="2" t="n"/>
       <c r="H841" s="3" t="n">
-        <v>46304</v>
+        <v>46318</v>
       </c>
       <c r="I841" s="3" t="n">
-        <v>46361</v>
+        <v>46378</v>
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L841" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
+          <t>Ambiente | Attività produttive | Territorio</t>
         </is>
       </c>
       <c r="M841" t="inlineStr">
@@ -54933,7 +54931,7 @@
       </c>
       <c r="N841" t="inlineStr">
         <is>
-          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
+          <t>Si avvisa che la ditta SANTONI GROUP SRL, con sede a Dro (TN), ha presentato domanda di permesso di ricerca di risorse geotermiche in un’area individuata nei Comuni di Castelnuovo del Garda (VR) e Lazise del Garda (VR) da denominare "GEO GARDA ENERGY". Si allegano il testo dell' avviso e le coordinate geografiche dei vertici dell’area richiesta e la relativa individuazione cartografica . È fissato in 60 (sessanta) giorni, successivi e decorrenti dalla data di pubblicazione del presente avviso sul Bollettino Ufficiale della Regione Veneto, il termine per la presentazione di eventuali domande in concorrenza da inviare alla Direzione Difesa del…</t>
         </is>
       </c>
       <c r="O841" s="4" t="inlineStr">
@@ -54945,12 +54943,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Avviso di istanza di permesso di ricerca di risorse geotermiche presentata da SANTONI GROUP SRL - Area "GEO GARDA ENERGY".</t>
+          <t>Affidamento per partecipazione regionale a Fieracavalli 2026</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -54960,30 +54958,36 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
-        </is>
-      </c>
-      <c r="F842" t="inlineStr"/>
-      <c r="G842" s="2" t="n"/>
+          <t>Direzione Turismo E Marketing Territoriale</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="n">
+        <v>196628</v>
+      </c>
       <c r="H842" s="3" t="n">
-        <v>46318</v>
+        <v>46196</v>
       </c>
       <c r="I842" s="3" t="n">
-        <v>46378</v>
+        <v>46387</v>
       </c>
       <c r="K842" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>Ambiente | Attività produttive | Territorio</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M842" t="inlineStr">
@@ -54993,7 +54997,7 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>Si avvisa che la ditta SANTONI GROUP SRL, con sede a Dro (TN), ha presentato domanda di permesso di ricerca di risorse geotermiche in un’area individuata nei Comuni di Castelnuovo del Garda (VR) e Lazise del Garda (VR) da denominare "GEO GARDA ENERGY". Si allegano il testo dell' avviso e le coordinate geografiche dei vertici dell’area richiesta e la relativa individuazione cartografica . È fissato in 60 (sessanta) giorni, successivi e decorrenti dalla data di pubblicazione del presente avviso sul Bollettino Ufficiale della Regione Veneto, il termine per la presentazione di eventuali domande in concorrenza da inviare alla Direzione Difesa del…</t>
+          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica FIERACAVALLI 2026 (Verona, 5-8 novembre 2026). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BDNCP</t>
         </is>
       </c>
       <c r="O842" s="4" t="inlineStr">
@@ -55010,7 +55014,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Affidamento per partecipazione regionale a Fieracavalli 2026</t>
+          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell' Ufficio della Consigliera regionale di Parità, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL.</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -55025,7 +55029,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -55034,22 +55038,22 @@
         </is>
       </c>
       <c r="G843" s="2" t="n">
-        <v>196628</v>
+        <v>2440</v>
       </c>
       <c r="H843" s="3" t="n">
-        <v>46196</v>
+        <v>46294</v>
       </c>
       <c r="I843" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K843" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Lavoro | Pari opportunità</t>
         </is>
       </c>
       <c r="M843" t="inlineStr">
@@ -55059,7 +55063,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica FIERACAVALLI 2026 (Verona, 5-8 novembre 2026). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BDNCP</t>
+          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell’Ufficio della Consigliera regionale di Parità, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL. CIG: BC8EFFBF04. Impegno di spesa e liquidazione. L.R. n. 39/2001.</t>
         </is>
       </c>
       <c r="O843" s="4" t="inlineStr">
@@ -55076,7 +55080,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell' Ufficio della Consigliera regionale di Parità, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL.</t>
+          <t>FESTIVAL DELLE REGIONI 2026 (Firenze 25-27 ottobre 2026)</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -55091,7 +55095,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -55100,22 +55104,22 @@
         </is>
       </c>
       <c r="G844" s="2" t="n">
-        <v>2440</v>
+        <v>3500</v>
       </c>
       <c r="H844" s="3" t="n">
-        <v>46294</v>
+        <v>46304</v>
       </c>
       <c r="I844" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K844" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>Lavoro | Pari opportunità</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -55125,7 +55129,7 @@
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell’Ufficio della Consigliera regionale di Parità, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL. CIG: BC8EFFBF04. Impegno di spesa e liquidazione. L.R. n. 39/2001.</t>
+          <t>Programma regionale per la promozione dei Grandi Eventi. Integrazione mediante inserimento dell'evento"L'Italia delle Regioni" - Festival delle Regioni. Adempimenti procedurali ed organizzativi conseguenti. L.R. n. 7/2016,art. 18. 1. LINK APPTEL 2. LINK BDNCP</t>
         </is>
       </c>
       <c r="O844" s="4" t="inlineStr">
@@ -55142,7 +55146,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>FESTIVAL DELLE REGIONI 2026 (Firenze 25-27 ottobre 2026)</t>
+          <t>Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -55152,36 +55156,30 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
-        </is>
-      </c>
-      <c r="F845" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G845" s="2" t="n">
-        <v>3500</v>
-      </c>
+          <t>Direzione Lavoro</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" s="2" t="n"/>
       <c r="H845" s="3" t="n">
-        <v>46304</v>
+        <v>45611</v>
       </c>
       <c r="I845" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K845" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Lavoro | Pari opportunità</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -55191,7 +55189,7 @@
       </c>
       <c r="N845" t="inlineStr">
         <is>
-          <t>Programma regionale per la promozione dei Grandi Eventi. Integrazione mediante inserimento dell'evento"L'Italia delle Regioni" - Festival delle Regioni. Adempimenti procedurali ed organizzativi conseguenti. L.R. n. 7/2016,art. 18. 1. LINK APPTEL 2. LINK BDNCP</t>
+          <t>D.D.R. n. 651 del 12.11.2024 Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro. L.R. 15 febbraio 2022, n. 3, art. 3 e Regolamento regionale del 12 maggio 2023, n.3, art. 3 e ss. Per informazioni: https://bur.regione.veneto.it/BurvServices/pubblica/DettaglioAvviso.aspx?id=542832</t>
         </is>
       </c>
       <c r="O845" s="4" t="inlineStr">
@@ -55208,7 +55206,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro</t>
+          <t>Affidamento diretto all'Università di Padova del servizio di realizzazione di 6 percorsi formativi per docenti delle scuole dell'infanzia sui temi dell'accettazione e del rispetto dell'altro e delle differenze</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -55218,7 +55216,7 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -55226,22 +55224,28 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F846" t="inlineStr"/>
-      <c r="G846" s="2" t="n"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="n">
+        <v>24000</v>
+      </c>
       <c r="H846" s="3" t="n">
-        <v>45611</v>
+        <v>46021</v>
       </c>
       <c r="I846" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K846" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>Lavoro | Pari opportunità</t>
+          <t>Pari opportunità</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -55251,7 +55255,7 @@
       </c>
       <c r="N846" t="inlineStr">
         <is>
-          <t>D.D.R. n. 651 del 12.11.2024 Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro. L.R. 15 febbraio 2022, n. 3, art. 3 e Regolamento regionale del 12 maggio 2023, n.3, art. 3 e ss. Per informazioni: https://bur.regione.veneto.it/BurvServices/pubblica/DettaglioAvviso.aspx?id=542832</t>
+          <t>Determina a contrarre e contestuale affidamento, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio di realizzazione di 6 percorsi formativi rivolti ai docenti delle scuole dell’infanzia sui temi dell’accettazione e del rispetto dell’altro e delle differenze a favore dell’Università di Padova - Dipartimento di Scienze politiche, giuridiche e studi internazionali, con sede in Padova (PD), Via del Santo n. 28, C.F.80006480281, P.I. 00742430283. CIG: B906940F21. CUP: H13C25000360002. Impegno di spesa e liquidazione sul bilancio per l’esercizio 2025. L.R. n. 39/2001.…</t>
         </is>
       </c>
       <c r="O846" s="4" t="inlineStr">
@@ -55268,7 +55272,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Affidamento diretto all'Università di Padova del servizio di realizzazione di 6 percorsi formativi per docenti delle scuole dell'infanzia sui temi dell'accettazione e del rispetto dell'altro e delle differenze</t>
+          <t>Servizio di esecuzione e gestione del Piano di comunicazione a sostegno del CSR Veneto 2023 - 2027 e della politica di sviluppo rurale post 2027. Approvazione del Piano annuale delle attività di comunicazione 2026.</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -55278,36 +55282,30 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G847" s="2" t="n">
-        <v>24000</v>
-      </c>
+          <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" s="2" t="n"/>
       <c r="H847" s="3" t="n">
-        <v>46021</v>
+        <v>46105</v>
       </c>
       <c r="I847" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K847" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>Pari opportunità</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -55317,7 +55315,7 @@
       </c>
       <c r="N847" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio di realizzazione di 6 percorsi formativi rivolti ai docenti delle scuole dell’infanzia sui temi dell’accettazione e del rispetto dell’altro e delle differenze a favore dell’Università di Padova - Dipartimento di Scienze politiche, giuridiche e studi internazionali, con sede in Padova (PD), Via del Santo n. 28, C.F.80006480281, P.I. 00742430283. CIG: B906940F21. CUP: H13C25000360002. Impegno di spesa e liquidazione sul bilancio per l’esercizio 2025. L.R. n. 39/2001.…</t>
+          <t>Con il Decreto del Direttore della Direzione AdG FEASR Bonifica e Irrigazione n. 11739 del 09/03/2026, pubblicato sul BUR n. 35 del 24/03/2026, è stato approvato il Piano annuale delle azioni di comunicazione 2026 a sostegno del Complemento regionale per lo Sviluppo Rurale del Piano Strategico Nazionale della PAC 2023-2027 e della politica di sviluppo rurale post 2027, predisposto dal RTI Fondazione Giacomo Brodolini e PR Consulting aggiudicatario della gara in oggetto. I documenti sono disponibili negli allegati al presente avviso.</t>
         </is>
       </c>
       <c r="O847" s="4" t="inlineStr">
@@ -55334,7 +55332,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Servizio di esecuzione e gestione del Piano di comunicazione a sostegno del CSR Veneto 2023 - 2027 e della politica di sviluppo rurale post 2027. Approvazione del Piano annuale delle attività di comunicazione 2026.</t>
+          <t>Affidamento all'Ente strumentale regionale Veneto Lavoro dell'attività di Assistenza tecnica per l'attuazione degli interventi a valere sul Programma Regionale Veneto FESR 2021-2027</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -55349,13 +55347,19 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
-        </is>
-      </c>
-      <c r="F848" t="inlineStr"/>
-      <c r="G848" s="2" t="n"/>
+          <t>Direzione Programmazione Unitaria</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="n">
+        <v>5145000</v>
+      </c>
       <c r="H848" s="3" t="n">
-        <v>46105</v>
+        <v>45275</v>
       </c>
       <c r="I848" s="3" t="n">
         <v>46387</v>
@@ -55367,7 +55371,7 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -55377,7 +55381,7 @@
       </c>
       <c r="N848" t="inlineStr">
         <is>
-          <t>Con il Decreto del Direttore della Direzione AdG FEASR Bonifica e Irrigazione n. 11739 del 09/03/2026, pubblicato sul BUR n. 35 del 24/03/2026, è stato approvato il Piano annuale delle azioni di comunicazione 2026 a sostegno del Complemento regionale per lo Sviluppo Rurale del Piano Strategico Nazionale della PAC 2023-2027 e della politica di sviluppo rurale post 2027, predisposto dal RTI Fondazione Giacomo Brodolini e PR Consulting aggiudicatario della gara in oggetto. I documenti sono disponibili negli allegati al presente avviso.</t>
+          <t>PR Veneto FESR 2021-2027 - Affidamento all'Ente strumentale regionale Veneto Lavoro, secondo la procedura in house providing , dell'attività di Assistenza tecnica per l'attuazione del Programma Regionale Veneto FESR, per il ciclo di programmazione 2021-2027. Schema di contratto e Piano di Lavoro approvati con DDR n. 207 del 11/12/2023. Contratto sottoscritto il 14/12/2023 e il 19/12/2023</t>
         </is>
       </c>
       <c r="O848" s="4" t="inlineStr">
@@ -55394,7 +55398,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Affidamento all'Ente strumentale regionale Veneto Lavoro dell'attività di Assistenza tecnica per l'attuazione degli interventi a valere sul Programma Regionale Veneto FESR 2021-2027</t>
+          <t>Bando per concessione contributi a sostegno del sistema degli enti fieristici del Veneto. Approvazione graduatorie.</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -55404,36 +55408,36 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Direzione Programmazione Unitaria</t>
+          <t>Direzione Promozione Economica e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Avviso di contributo</t>
         </is>
       </c>
       <c r="G849" s="2" t="n">
-        <v>5145000</v>
+        <v>594112</v>
       </c>
       <c r="H849" s="3" t="n">
-        <v>45275</v>
+        <v>45422</v>
       </c>
       <c r="I849" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>FESR</t>
+          <t>Attività produttive</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -55443,7 +55447,7 @@
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Affidamento all'Ente strumentale regionale Veneto Lavoro, secondo la procedura in house providing , dell'attività di Assistenza tecnica per l'attuazione del Programma Regionale Veneto FESR, per il ciclo di programmazione 2021-2027. Schema di contratto e Piano di Lavoro approvati con DDR n. 207 del 11/12/2023. Contratto sottoscritto il 14/12/2023 e il 19/12/2023</t>
+          <t>Approvazione delle graduatorie delle domande ammesse e dell’elenco delle domande non ammesse ai sensi dell’articolo 8 del “Bando per la concessione di contributi a fondo perduto per iniziative promozionali e di sostegno al sistema degli enti fieristici del Veneto”. DGR n. 1142 del 19 settembre 2023.</t>
         </is>
       </c>
       <c r="O849" s="4" t="inlineStr">
@@ -55460,7 +55464,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Bando per concessione contributi a sostegno del sistema degli enti fieristici del Veneto. Approvazione graduatorie.</t>
+          <t>Affidamento diretto, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI".</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -55470,36 +55474,36 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Direzione Promozione Economica e Marketing Territoriale</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Avviso di contributo</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G850" s="2" t="n">
-        <v>594112</v>
+        <v>95453</v>
       </c>
       <c r="H850" s="3" t="n">
-        <v>45422</v>
+        <v>45898</v>
       </c>
       <c r="I850" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K850" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>Attività produttive</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -55509,7 +55513,7 @@
       </c>
       <c r="N850" t="inlineStr">
         <is>
-          <t>Approvazione delle graduatorie delle domande ammesse e dell’elenco delle domande non ammesse ai sensi dell’articolo 8 del “Bando per la concessione di contributi a fondo perduto per iniziative promozionali e di sostegno al sistema degli enti fieristici del Veneto”. DGR n. 1142 del 19 settembre 2023.</t>
+          <t>Aggiudicazione, impegno e contestuale accertamento del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI. Interventi di supporto alla genitorialità nella cura di bambini e bambine nei primi tre anni di vita", 2024-2026. PR Veneto FSE+ 2021-2027, Obiettivo Investimenti per l'occupazione e la crescita - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 3, Obiettivo specifico ESO4.11 (OS K del Reg. UE 2021/1057). Affidatario: TRIBE COMMUNICATION S.R.L.…</t>
         </is>
       </c>
       <c r="O850" s="4" t="inlineStr">
@@ -55526,7 +55530,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Affidamento diretto, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI".</t>
+          <t>Servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025 (CUP H13C25000260002, CIG B79E3376C2) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -55536,36 +55540,36 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G851" s="2" t="n">
-        <v>95453</v>
+        <v>7600</v>
       </c>
       <c r="H851" s="3" t="n">
-        <v>45898</v>
+        <v>45877</v>
       </c>
       <c r="I851" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K851" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Protezione civile</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -55575,7 +55579,7 @@
       </c>
       <c r="N851" t="inlineStr">
         <is>
-          <t>Aggiudicazione, impegno e contestuale accertamento del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI. Interventi di supporto alla genitorialità nella cura di bambini e bambine nei primi tre anni di vita", 2024-2026. PR Veneto FSE+ 2021-2027, Obiettivo Investimenti per l'occupazione e la crescita - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 3, Obiettivo specifico ESO4.11 (OS K del Reg. UE 2021/1057). Affidatario: TRIBE COMMUNICATION S.R.L.…</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 394 del 18 luglio 2025 Affidamento diretto del servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H13C25000260002, CIG B79E3376C2. Impegno di spesa a favore di Fondazione CUOA Centro Universitario di Organizzazione aziendale. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B79E3376C2 PIATTAFORMA PVL: https://pubblicitalegale.anticorruzione.it/esiti/7d45ca46-f1c4-4a90-b59e-5e645ee63d00 PORTALE APPTEL:…</t>
         </is>
       </c>
       <c r="O851" s="4" t="inlineStr">
@@ -55592,7 +55596,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025 (CUP H13C25000260002, CIG B79E3376C2) - Esito della procedura di affidamento</t>
+          <t>Servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48 (CUP H19I25000500002, CIG B7456678EA) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -55616,10 +55620,10 @@
         </is>
       </c>
       <c r="G852" s="2" t="n">
-        <v>7600</v>
+        <v>13100</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>45877</v>
+        <v>45849</v>
       </c>
       <c r="I852" s="3" t="n">
         <v>46387</v>
@@ -55631,7 +55635,7 @@
       </c>
       <c r="L852" t="inlineStr">
         <is>
-          <t>Protezione civile</t>
+          <t>Sicurezza e polizia locale</t>
         </is>
       </c>
       <c r="M852" t="inlineStr">
@@ -55641,7 +55645,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 394 del 18 luglio 2025 Affidamento diretto del servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H13C25000260002, CIG B79E3376C2. Impegno di spesa a favore di Fondazione CUOA Centro Universitario di Organizzazione aziendale. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B79E3376C2 PIATTAFORMA PVL: https://pubblicitalegale.anticorruzione.it/esiti/7d45ca46-f1c4-4a90-b59e-5e645ee63d00 PORTALE APPTEL:…</t>
+          <t>DECRTO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 342 del 13 giugno 2025 Affidamento diretto dei servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48, avviata con DGR 522/2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H19I25000500002, CIG B7456678EA. Impegno di spesa a favore di Linea Edizioni di Marra Lisa. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7456678EA PIATTAFORMA PVL:…</t>
         </is>
       </c>
       <c r="O852" s="4" t="inlineStr">
@@ -55658,7 +55662,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48 (CUP H19I25000500002, CIG B7456678EA) - Esito della procedura di affidamento</t>
+          <t>Servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT" (CUP I13C23000400006, CIG B7F37D65B9) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -55682,10 +55686,10 @@
         </is>
       </c>
       <c r="G853" s="2" t="n">
-        <v>13100</v>
+        <v>3328</v>
       </c>
       <c r="H853" s="3" t="n">
-        <v>45849</v>
+        <v>45989</v>
       </c>
       <c r="I853" s="3" t="n">
         <v>46387</v>
@@ -55697,7 +55701,7 @@
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>Sicurezza e polizia locale</t>
+          <t>Europa | Protezione civile</t>
         </is>
       </c>
       <c r="M853" t="inlineStr">
@@ -55707,7 +55711,7 @@
       </c>
       <c r="N853" t="inlineStr">
         <is>
-          <t>DECRTO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 342 del 13 giugno 2025 Affidamento diretto dei servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48, avviata con DGR 522/2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H19I25000500002, CIG B7456678EA. Impegno di spesa a favore di Linea Edizioni di Marra Lisa. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7456678EA PIATTAFORMA PVL:…</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 564 del 29 ottobre 2025 Affidamento diretto del servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT", ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP I13C23000400006, CIG B7F37D65B9. Impegno di spesa a favore del dott. Massimiliano Rosignoli. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7F37D65B9 PORTALE APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/esiti/codice/G02289</t>
         </is>
       </c>
       <c r="O853" s="4" t="inlineStr">
@@ -55724,7 +55728,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT" (CUP I13C23000400006, CIG B7F37D65B9) - Esito della procedura di affidamento</t>
+          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15.</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -55739,31 +55743,29 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+          <t>Area Sanità E Sociale</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G854" s="2" t="n">
-        <v>3328</v>
-      </c>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="n"/>
       <c r="H854" s="3" t="n">
-        <v>45989</v>
+        <v>46203</v>
       </c>
       <c r="I854" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>Europa | Protezione civile</t>
+          <t>Sanità</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
@@ -55773,7 +55775,7 @@
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 564 del 29 ottobre 2025 Affidamento diretto del servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT", ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP I13C23000400006, CIG B7F37D65B9. Impegno di spesa a favore del dott. Massimiliano Rosignoli. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7F37D65B9 PORTALE APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/esiti/codice/G02289</t>
+          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15. La richiesta di intervento sanitario per ragioni umanitarie a favore di cittadini di Paesi non appartenenti all’Unione Europea (cittadini extra UE), di cui al “Programma di assistenza sanitaria per ragioni umanitarie del Servizio Socio - Sanitario Regionale - anno 2026” deve essere presentata da un Ente o da un’Associazione senza scopo di lucro o da un Ente del Terzo Settore, avente sede nel territorio della Regione del Veneto. La richiesta di intervento…</t>
         </is>
       </c>
       <c r="O854" s="4" t="inlineStr">
@@ -55790,7 +55792,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15.</t>
+          <t>Affidamento diretto a Veneto Innovazione per l'incarico di supporto tecnico/organizzativo per la realizzazione del Progetto "Caseus 2026".</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -55800,34 +55802,36 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Area Sanità E Sociale</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G855" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="n">
+        <v>299180</v>
+      </c>
       <c r="H855" s="3" t="n">
-        <v>46203</v>
+        <v>46182</v>
       </c>
       <c r="I855" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>Sanità</t>
+          <t>Promozione enogastronomica</t>
         </is>
       </c>
       <c r="M855" t="inlineStr">
@@ -55837,7 +55841,7 @@
       </c>
       <c r="N855" t="inlineStr">
         <is>
-          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15. La richiesta di intervento sanitario per ragioni umanitarie a favore di cittadini di Paesi non appartenenti all’Unione Europea (cittadini extra UE), di cui al “Programma di assistenza sanitaria per ragioni umanitarie del Servizio Socio - Sanitario Regionale - anno 2026” deve essere presentata da un Ente o da un’Associazione senza scopo di lucro o da un Ente del Terzo Settore, avente sede nel territorio della Regione del Veneto. La richiesta di intervento…</t>
+          <t>Approvazione del Progetto “Caseus 2026” e individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate alla realizzazione del Progetto. Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario anno 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. Link PVL: https://pubblicitalegale.anticorruzione.it/avvisi/e04f949a-e871-4b11-96a6-cdba7ecc72a2?ricercaArchivio=false Link APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/procedure/codice/G03911 Link BDNCP:…</t>
         </is>
       </c>
       <c r="O855" s="4" t="inlineStr">
@@ -55854,7 +55858,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Veneto Innovazione per l'incarico di supporto tecnico/organizzativo per la realizzazione del Progetto "Caseus 2026".</t>
+          <t>Affidamento diretto a Veneto Innovazione S.p.A. per supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale ad iniziative promozionali in Italia nel corso del secondo semestre 2026.</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -55878,10 +55882,10 @@
         </is>
       </c>
       <c r="G856" s="2" t="n">
-        <v>299180</v>
+        <v>505825</v>
       </c>
       <c r="H856" s="3" t="n">
-        <v>46182</v>
+        <v>46203</v>
       </c>
       <c r="I856" s="3" t="n">
         <v>46387</v>
@@ -55893,7 +55897,7 @@
       </c>
       <c r="L856" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M856" t="inlineStr">
@@ -55903,7 +55907,7 @@
       </c>
       <c r="N856" t="inlineStr">
         <is>
-          <t>Approvazione del Progetto “Caseus 2026” e individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate alla realizzazione del Progetto. Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario anno 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. Link PVL: https://pubblicitalegale.anticorruzione.it/avvisi/e04f949a-e871-4b11-96a6-cdba7ecc72a2?ricercaArchivio=false Link APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/procedure/codice/G03911 Link BDNCP:…</t>
+          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma in Italia nel corso del secondo semestre 2026. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. Link PVL : https://pubblicitalegale.anticorruzione.it/avvisi/7959d784-33f2-4a3d-8669-703b940a29ad?ricercaArchivio=false…</t>
         </is>
       </c>
       <c r="O856" s="4" t="inlineStr">
@@ -55920,7 +55924,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Veneto Innovazione S.p.A. per supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale ad iniziative promozionali in Italia nel corso del secondo semestre 2026.</t>
+          <t>EVENTI ESTERO 2° SEMESTRE 2026 - DDR N. 14931 DEL 19/06/2026</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -55935,7 +55939,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
@@ -55944,10 +55948,10 @@
         </is>
       </c>
       <c r="G857" s="2" t="n">
-        <v>505825</v>
+        <v>394109</v>
       </c>
       <c r="H857" s="3" t="n">
-        <v>46203</v>
+        <v>46227</v>
       </c>
       <c r="I857" s="3" t="n">
         <v>46387</v>
@@ -55969,7 +55973,7 @@
       </c>
       <c r="N857" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma in Italia nel corso del secondo semestre 2026. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. Link PVL : https://pubblicitalegale.anticorruzione.it/avvisi/7959d784-33f2-4a3d-8669-703b940a29ad?ricercaArchivio=false…</t>
+          <t>Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l’incarico di supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma all’estero nel corso del secondo semestre 2026. DDR n. 14931 del 19 giugno 2026. DGR n. 423 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii LINK PUBBLICITA' A VALORE LEGALE. LINK APPTEL LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI</t>
         </is>
       </c>
       <c r="O857" s="4" t="inlineStr">
@@ -55986,7 +55990,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>EVENTI ESTERO 2° SEMESTRE 2026 - DDR N. 14931 DEL 19/06/2026</t>
+          <t>Affidamento per la realizzazione del Progetto "Buy Veneto 2026"</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -56010,7 +56014,7 @@
         </is>
       </c>
       <c r="G858" s="2" t="n">
-        <v>394109</v>
+        <v>491803</v>
       </c>
       <c r="H858" s="3" t="n">
         <v>46227</v>
@@ -56035,7 +56039,7 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l’incarico di supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma all’estero nel corso del secondo semestre 2026. DDR n. 14931 del 19 giugno 2026. DGR n. 423 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii LINK PUBBLICITA' A VALORE LEGALE. LINK APPTEL LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI</t>
+          <t>Fondo Unico Nazionale del Turismo di parte corrente 2026. Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l'incarico di supporto tecnico/organizzativo finalizzato a garantire la realizzazione del Progetto “Buy Veneto 2026 - 25° Workshop Internazionale del Turismo in Veneto” (Venezia, 9-13 ottobre 2026). CUP: H78J26000040001. DDR n. 15143 del 25 giugno 2026. DGR n. 423 e n. 425 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BANCA…</t>
         </is>
       </c>
       <c r="O858" s="4" t="inlineStr">
@@ -56052,7 +56056,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Affidamento per la realizzazione del Progetto "Buy Veneto 2026"</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B898BECDB6 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -56067,7 +56071,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
@@ -56076,22 +56080,22 @@
         </is>
       </c>
       <c r="G859" s="2" t="n">
-        <v>491803</v>
+        <v>3861</v>
       </c>
       <c r="H859" s="3" t="n">
-        <v>46227</v>
+        <v>45993</v>
       </c>
       <c r="I859" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K859" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L859" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
         </is>
       </c>
       <c r="M859" t="inlineStr">
@@ -56101,7 +56105,7 @@
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di parte corrente 2026. Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l'incarico di supporto tecnico/organizzativo finalizzato a garantire la realizzazione del Progetto “Buy Veneto 2026 - 25° Workshop Internazionale del Turismo in Veneto” (Venezia, 9-13 ottobre 2026). CUP: H78J26000040001. DDR n. 15143 del 25 giugno 2026. DGR n. 423 e n. 425 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BANCA…</t>
+          <t>Con Decreto n. 71 del 10/10/2025 della Direzione Valutazioni Ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della D.G.R. n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Libreria Scientifica di Ragni Susanna (sede legale in via Giordano Bruno n. 54/b, Cap. 60127, Ancona, C.F. n. RGNSNN54A41A271P, P.IVA n. 00210380424) per la la somma di € 3.861,00= a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1,…</t>
         </is>
       </c>
       <c r="O859" s="4" t="inlineStr">
@@ -56118,7 +56122,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B898BECDB6 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8991C1DC6 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -56142,7 +56146,7 @@
         </is>
       </c>
       <c r="G860" s="2" t="n">
-        <v>3861</v>
+        <v>1693</v>
       </c>
       <c r="H860" s="3" t="n">
         <v>45993</v>
@@ -56167,7 +56171,7 @@
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>Con Decreto n. 71 del 10/10/2025 della Direzione Valutazioni Ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della D.G.R. n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Libreria Scientifica di Ragni Susanna (sede legale in via Giordano Bruno n. 54/b, Cap. 60127, Ancona, C.F. n. RGNSNN54A41A271P, P.IVA n. 00210380424) per la la somma di € 3.861,00= a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1,…</t>
+          <t>Con DDR n. 72 del 10/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con relativo impegno di spesa a favore della ditta ReteAmbiente S.r.l. (sede legale: via G. Bensi n. 12/5, Cap. 20152 - Milano, C.F./P.IVA n. 10966180969) per la somma di € 1.693,10=(IVA al 4% inclusa) quale corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36/2023, di un…</t>
         </is>
       </c>
       <c r="O860" s="4" t="inlineStr">
@@ -56184,7 +56188,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8991C1DC6 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B89C1DE219 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -56208,7 +56212,7 @@
         </is>
       </c>
       <c r="G861" s="2" t="n">
-        <v>1693</v>
+        <v>768</v>
       </c>
       <c r="H861" s="3" t="n">
         <v>45993</v>
@@ -56233,7 +56237,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>Con DDR n. 72 del 10/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con relativo impegno di spesa a favore della ditta ReteAmbiente S.r.l. (sede legale: via G. Bensi n. 12/5, Cap. 20152 - Milano, C.F./P.IVA n. 10966180969) per la somma di € 1.693,10=(IVA al 4% inclusa) quale corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36/2023, di un…</t>
+          <t>Con DDR n. 73 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Maggioli Spa (sede legale in Sant’Arcangelo di Romagna - RN, Via del Carpino n. 8, Cap. 47822, C.F. n. 06188330150; P.IVA n. 02066400405) per la somma di € 768,60 (IVA al 22% inclusa pari a € 138,00) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art.…</t>
         </is>
       </c>
       <c r="O861" s="4" t="inlineStr">
@@ -56250,7 +56254,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B89C1DE219 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B89C143230 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -56274,7 +56278,7 @@
         </is>
       </c>
       <c r="G862" s="2" t="n">
-        <v>768</v>
+        <v>280</v>
       </c>
       <c r="H862" s="3" t="n">
         <v>45993</v>
@@ -56299,7 +56303,7 @@
       </c>
       <c r="N862" t="inlineStr">
         <is>
-          <t>Con DDR n. 73 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Maggioli Spa (sede legale in Sant’Arcangelo di Romagna - RN, Via del Carpino n. 8, Cap. 47822, C.F. n. 06188330150; P.IVA n. 02066400405) per la somma di € 768,60 (IVA al 22% inclusa pari a € 138,00) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art.…</t>
+          <t>Con DDR n. 74 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è sttaa disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Legislazione Tecnica S.r.l. (sede legale: Via dell'Architettura 16, Cap. 00144 - Roma, C.F/P.IVA n. 05383391009) per la somma di € 280,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
         </is>
       </c>
       <c r="O862" s="4" t="inlineStr">
@@ -56316,7 +56320,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B89C143230 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEE61F8D - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -56340,7 +56344,7 @@
         </is>
       </c>
       <c r="G863" s="2" t="n">
-        <v>280</v>
+        <v>138</v>
       </c>
       <c r="H863" s="3" t="n">
         <v>45993</v>
@@ -56365,7 +56369,7 @@
       </c>
       <c r="N863" t="inlineStr">
         <is>
-          <t>Con DDR n. 74 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è sttaa disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Legislazione Tecnica S.r.l. (sede legale: Via dell'Architettura 16, Cap. 00144 - Roma, C.F/P.IVA n. 05383391009) per la somma di € 280,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
+          <t>Con DDR n. 77 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Compagnia delle Foreste Srl (sede legale in via Pietro Aretino n. 8 - cap. 52100 Arezzo, P.IVA/C.F. n. 01726650516) per la somma di € 138,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
         </is>
       </c>
       <c r="O863" s="4" t="inlineStr">
@@ -56382,7 +56386,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEE61F8D - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEDC0AB2 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -56406,7 +56410,7 @@
         </is>
       </c>
       <c r="G864" s="2" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="H864" s="3" t="n">
         <v>45993</v>
@@ -56431,7 +56435,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>Con DDR n. 77 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Compagnia delle Foreste Srl (sede legale in via Pietro Aretino n. 8 - cap. 52100 Arezzo, P.IVA/C.F. n. 01726650516) per la somma di € 138,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
+          <t>Con decreto n. 78 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Cosmo Giuridico Veneto s.a.s. di Marangon Ivonne (sede legale in via Centro n. 80, fraz. Priabona, Cap. 36030 - Monte di Malo (VI) – C.F./P.IVA 03775960242) per la somma di € 260,00=(IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi…</t>
         </is>
       </c>
       <c r="O864" s="4" t="inlineStr">
@@ -56448,7 +56452,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEDC0AB2 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEB178B8 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -56472,7 +56476,7 @@
         </is>
       </c>
       <c r="G865" s="2" t="n">
-        <v>260</v>
+        <v>468</v>
       </c>
       <c r="H865" s="3" t="n">
         <v>45993</v>
@@ -56497,7 +56501,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>Con decreto n. 78 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Cosmo Giuridico Veneto s.a.s. di Marangon Ivonne (sede legale in via Centro n. 80, fraz. Priabona, Cap. 36030 - Monte di Malo (VI) – C.F./P.IVA 03775960242) per la somma di € 260,00=(IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi…</t>
+          <t>Con decreto n. 79 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Giuriconsult S.r.l. (sede legale in via Principe di Paternò n. 74/A, Cap. 90144 - Palermo, C.F./P.IVA. n. 05247730822) per la somma di € 468,00 (IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
         </is>
       </c>
       <c r="O865" s="4" t="inlineStr">
@@ -56514,7 +56518,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEB178B8 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8DE6999C3 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -56538,7 +56542,7 @@
         </is>
       </c>
       <c r="G866" s="2" t="n">
-        <v>468</v>
+        <v>150</v>
       </c>
       <c r="H866" s="3" t="n">
         <v>45993</v>
@@ -56563,7 +56567,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>Con decreto n. 79 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Giuriconsult S.r.l. (sede legale in via Principe di Paternò n. 74/A, Cap. 90144 - Palermo, C.F./P.IVA. n. 05247730822) per la somma di € 468,00 (IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
+          <t>Con decreto n. 85 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore dell’Associazione Idrotecnica Italiana (sede legale: via di Santa Teresa 23, cap. 00198 – Roma, C.F. n. 02162200584 - P.IVA n. 01033911007) per la somma di € 150,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b), del…</t>
         </is>
       </c>
       <c r="O866" s="4" t="inlineStr">
@@ -56580,7 +56584,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8DE6999C3 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8DE5D9B51 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -56604,7 +56608,7 @@
         </is>
       </c>
       <c r="G867" s="2" t="n">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="H867" s="3" t="n">
         <v>45993</v>
@@ -56629,7 +56633,7 @@
       </c>
       <c r="N867" t="inlineStr">
         <is>
-          <t>Con decreto n. 85 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore dell’Associazione Idrotecnica Italiana (sede legale: via di Santa Teresa 23, cap. 00198 – Roma, C.F. n. 02162200584 - P.IVA n. 01033911007) per la somma di € 150,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b), del…</t>
+          <t>Con decreto n. 86 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale conm conseguente impegno di spesa a favore della ditta Tecniche Nuove Spa (sede legale in via Eritrea n. 21, Cap. 20157 - Milano, C.F./P.IVA n. 00753480151) per la somma di € 259,00=(IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
         </is>
       </c>
       <c r="O867" s="4" t="inlineStr">
@@ -56646,7 +56650,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8DE5D9B51 - avviso aggiudicazione</t>
+          <t>Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 - Colli Asolani . Aggiudicazione</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -56661,7 +56665,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
@@ -56670,22 +56674,22 @@
         </is>
       </c>
       <c r="G868" s="2" t="n">
-        <v>259</v>
+        <v>40900</v>
       </c>
       <c r="H868" s="3" t="n">
-        <v>45993</v>
+        <v>46185</v>
       </c>
       <c r="I868" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K868" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
+          <t>Agricoltura e foreste | Ambiente | Territorio | Turismo</t>
         </is>
       </c>
       <c r="M868" t="inlineStr">
@@ -56695,7 +56699,7 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>Con decreto n. 86 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale conm conseguente impegno di spesa a favore della ditta Tecniche Nuove Spa (sede legale in via Eritrea n. 21, Cap. 20157 - Milano, C.F./P.IVA n. 00753480151) per la somma di € 259,00=(IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
+          <t>Decreto a contrarre e di aggiudicazione definitiva ad efficacia condizionata del servizio di “Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 – Colli Asolani”, finanziato dal Programma Operativo PO.3 dell’Assistenza tecnica al CSR 2023-2027. DGR n. 453 del 18.04.2023 e DGR n. 100 del 04.02.2025. Regolamenti (UE) n. 2021/2115 e n. 2021/2116. CUP H79I25000970006. CIG BB81996235 Link alla BDNCP: https://dati.anticorruzione.it/superset/recaptcha/?cig=BB81996235&amp;next=dettaglio_cig .</t>
         </is>
       </c>
       <c r="O868" s="4" t="inlineStr">
@@ -56712,7 +56716,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 - Colli Asolani . Aggiudicazione</t>
+          <t>Affidamento per la realizzaizone del Piano di Comunicazione 2026.</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -56736,22 +56740,22 @@
         </is>
       </c>
       <c r="G869" s="2" t="n">
-        <v>40900</v>
+        <v>869549</v>
       </c>
       <c r="H869" s="3" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="I869" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K869" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L869" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste | Ambiente | Territorio | Turismo</t>
+          <t>Comunicazione e informazione | Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M869" t="inlineStr">
@@ -56761,7 +56765,7 @@
       </c>
       <c r="N869" t="inlineStr">
         <is>
-          <t>Decreto a contrarre e di aggiudicazione definitiva ad efficacia condizionata del servizio di “Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 – Colli Asolani”, finanziato dal Programma Operativo PO.3 dell’Assistenza tecnica al CSR 2023-2027. DGR n. 453 del 18.04.2023 e DGR n. 100 del 04.02.2025. Regolamenti (UE) n. 2021/2115 e n. 2021/2116. CUP H79I25000970006. CIG BB81996235 Link alla BDNCP: https://dati.anticorruzione.it/superset/recaptcha/?cig=BB81996235&amp;next=dettaglio_cig .</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativi finalizzate alla realizzazione del Piano di comunicazione 2026 per la promozione turistica ed enogastronomica della Regione del Veneto. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. LINK Pubblicità a Valore Legale LINK APPTEL LINK Banca Dati Nazionale Contratti Pubblici</t>
         </is>
       </c>
       <c r="O869" s="4" t="inlineStr">
@@ -56778,7 +56782,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Affidamento per la realizzaizone del Piano di Comunicazione 2026.</t>
+          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024.</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -56788,36 +56792,34 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Unità Organizzativa Dipendenze, terzo settore, nuove marginalità ed inclusione sociale</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G870" s="2" t="n">
-        <v>869549</v>
-      </c>
+          <t>Albi e registri</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="n"/>
       <c r="H870" s="3" t="n">
-        <v>46189</v>
+        <v>45674</v>
       </c>
       <c r="I870" s="3" t="n">
-        <v>46387</v>
+        <v>46407</v>
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>Comunicazione e informazione | Promozione enogastronomica | Turismo</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
@@ -56827,7 +56829,7 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativi finalizzate alla realizzazione del Piano di comunicazione 2026 per la promozione turistica ed enogastronomica della Regione del Veneto. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. LINK Pubblicità a Valore Legale LINK APPTEL LINK Banca Dati Nazionale Contratti Pubblici</t>
+          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024. Modalità di presentazione e di inserimento delle richieste. N.B. Per procedere alla richiesta di inserimento nell'elenco, utilizzare il modello di cui all'Allegato B.</t>
         </is>
       </c>
       <c r="O870" s="4" t="inlineStr">
@@ -56844,7 +56846,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024.</t>
+          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della Regione del Veneto.</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -56859,29 +56861,23 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Dipendenze, terzo settore, nuove marginalità ed inclusione sociale</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G871" s="2" t="n"/>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" s="2" t="n">
+        <v>2335000</v>
+      </c>
       <c r="H871" s="3" t="n">
-        <v>45674</v>
+        <v>46220</v>
       </c>
       <c r="I871" s="3" t="n">
-        <v>46407</v>
-      </c>
-      <c r="K871" t="inlineStr">
-        <is>
-          <t>Cittadino</t>
-        </is>
-      </c>
+        <v>46446</v>
+      </c>
+      <c r="K871" t="inlineStr"/>
       <c r="L871" t="inlineStr">
         <is>
-          <t>Sociale</t>
+          <t>FESR | Protezione civile</t>
         </is>
       </c>
       <c r="M871" t="inlineStr">
@@ -56891,7 +56887,7 @@
       </c>
       <c r="N871" t="inlineStr">
         <is>
-          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024. Modalità di presentazione e di inserimento delle richieste. N.B. Per procedere alla richiesta di inserimento nell'elenco, utilizzare il modello di cui all'Allegato B.</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 15409 del 30 giugno 2026 PR Veneto FESR 2021-2027. Priorità 2, Obiettivo Specifico 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della…</t>
         </is>
       </c>
       <c r="O871" s="4" t="inlineStr">
@@ -56908,7 +56904,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della Regione del Veneto.</t>
+          <t>Partecipazione regionale a Fruit Logistica 2027 (Berlino, 3/5 febbraio 2027)</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -56918,28 +56914,36 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr"/>
+          <t>Direzione Turismo e Marketing Territoriale</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
       <c r="G872" s="2" t="n">
-        <v>2335000</v>
+        <v>116475</v>
       </c>
       <c r="H872" s="3" t="n">
-        <v>46220</v>
+        <v>46259</v>
       </c>
       <c r="I872" s="3" t="n">
         <v>46446</v>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>FESR | Protezione civile</t>
+          <t>Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M872" t="inlineStr">
@@ -56949,7 +56953,7 @@
       </c>
       <c r="N872" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 15409 del 30 giugno 2026 PR Veneto FESR 2021-2027. Priorità 2, Obiettivo Specifico 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della…</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “Fruit Logistica 2027” (Berlino, 3-5 febbraio 2027). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
         </is>
       </c>
       <c r="O872" s="4" t="inlineStr">
@@ -56966,7 +56970,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Partecipazione regionale a Fruit Logistica 2027 (Berlino, 3/5 febbraio 2027)</t>
+          <t>PARTECIPAZIONE REGIONALE A "IGTM - International Golf Travel Market" (Cannes, 19-22 ottobre 2026)</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -56990,10 +56994,10 @@
         </is>
       </c>
       <c r="G873" s="2" t="n">
-        <v>116475</v>
+        <v>5695</v>
       </c>
       <c r="H873" s="3" t="n">
-        <v>46259</v>
+        <v>46294</v>
       </c>
       <c r="I873" s="3" t="n">
         <v>46446</v>
@@ -57005,7 +57009,7 @@
       </c>
       <c r="L873" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica | Turismo</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M873" t="inlineStr">
@@ -57015,7 +57019,7 @@
       </c>
       <c r="N873" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “Fruit Logistica 2027” (Berlino, 3-5 febbraio 2027). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “IGTM International Golf Travel Market (Cannes, 19-22 ottobre 2026)”. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
         </is>
       </c>
       <c r="O873" s="4" t="inlineStr">
@@ -57032,7 +57036,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>PARTECIPAZIONE REGIONALE A "IGTM - International Golf Travel Market" (Cannes, 19-22 ottobre 2026)</t>
+          <t>Avviso di Avvenuta approvazione del progetto definitivo del 2° Lotto Funzionale Attraversamento di Vicenza</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -57042,36 +57046,30 @@
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
-        </is>
-      </c>
-      <c r="F874" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G874" s="2" t="n">
-        <v>5695</v>
-      </c>
+          <t>Direzione Infrastrutture E Trasporti</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" s="2" t="n"/>
       <c r="H874" s="3" t="n">
-        <v>46294</v>
+        <v>45127</v>
       </c>
       <c r="I874" s="3" t="n">
-        <v>46446</v>
+        <v>47014</v>
       </c>
       <c r="K874" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L874" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M874" t="inlineStr">
@@ -57081,7 +57079,7 @@
       </c>
       <c r="N874" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “IGTM International Golf Travel Market (Cannes, 19-22 ottobre 2026)”. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
+          <t>Soggetto aggiudicatore: R.F.I. S.p.A. Avviso di Avvenuta approvazione con Ordinanza commissariale n. 15 del 13.07.2023 del progetto definitivo del “2° Lotto Funzionale – Attraversamento di Vicenza” ai sensi del D.Lgs. 50/2016 e del DL 32/2019, convertito con modifiche nella L. 55/2019, nonché ai fini della dichiarazione di pubblica utilità ai sensi degli art. 10 e 12 del D.P.R. 327/2001 e s.m.i.</t>
         </is>
       </c>
       <c r="O874" s="4" t="inlineStr">
@@ -57098,7 +57096,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Avviso di Avvenuta approvazione del progetto definitivo del 2° Lotto Funzionale Attraversamento di Vicenza</t>
+          <t>Avviso di post informazione: determina a contrarre e affidamento a Edizioni l'Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d'uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023.</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -57113,25 +57111,29 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture E Trasporti</t>
-        </is>
-      </c>
-      <c r="F875" t="inlineStr"/>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
       <c r="G875" s="2" t="n"/>
       <c r="H875" s="3" t="n">
-        <v>45127</v>
+        <v>45287</v>
       </c>
       <c r="I875" s="3" t="n">
-        <v>47014</v>
+        <v>47114</v>
       </c>
       <c r="K875" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L875" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M875" t="inlineStr">
@@ -57141,7 +57143,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>Soggetto aggiudicatore: R.F.I. S.p.A. Avviso di Avvenuta approvazione con Ordinanza commissariale n. 15 del 13.07.2023 del progetto definitivo del “2° Lotto Funzionale – Attraversamento di Vicenza” ai sensi del D.Lgs. 50/2016 e del DL 32/2019, convertito con modifiche nella L. 55/2019, nonché ai fini della dichiarazione di pubblica utilità ai sensi degli art. 10 e 12 del D.P.R. 327/2001 e s.m.i.</t>
+          <t>Determina a contrarre e affidamento a Edizioni l’Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d’uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023. FORNITORE: Edizioni l’Informatore Agrario srl AGGIUDICATARIO: Edizioni l’Informatore Agrario srl TEMPI DI COMPLETAMENTO DEL CONTRATTO: 31.12.2027 NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n.…</t>
         </is>
       </c>
       <c r="O875" s="4" t="inlineStr">
@@ -57158,7 +57160,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: determina a contrarre e affidamento a Edizioni l'Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d'uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023.</t>
+          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell'Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -57173,29 +57175,29 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
+          <t>Area Risorse Finanziarie, Strumentali, Ict Ed Enti Locali</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Albi e registri</t>
         </is>
       </c>
       <c r="G876" s="2" t="n"/>
       <c r="H876" s="3" t="n">
-        <v>45287</v>
+        <v>45450</v>
       </c>
       <c r="I876" s="3" t="n">
-        <v>47114</v>
+        <v>47118</v>
       </c>
       <c r="K876" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L876" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M876" t="inlineStr">
@@ -57205,7 +57207,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>Determina a contrarre e affidamento a Edizioni l’Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d’uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023. FORNITORE: Edizioni l’Informatore Agrario srl AGGIUDICATARIO: Edizioni l’Informatore Agrario srl TEMPI DI COMPLETAMENTO DEL CONTRATTO: 31.12.2027 NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n.…</t>
+          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell’Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
         </is>
       </c>
       <c r="O876" s="4" t="inlineStr">
@@ -57222,7 +57224,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell'Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
+          <t>Avviso di aggiudicazione della procedura di affidamento diretto</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -57237,29 +57239,27 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>Area Risorse Finanziarie, Strumentali, Ict Ed Enti Locali</t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G877" s="2" t="n"/>
+          <t>Unità Organizzativa Genio Civile Vicenza</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" s="2" t="n">
+        <v>273</v>
+      </c>
       <c r="H877" s="3" t="n">
-        <v>45450</v>
+        <v>45517</v>
       </c>
       <c r="I877" s="3" t="n">
-        <v>47118</v>
+        <v>47349</v>
       </c>
       <c r="K877" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L877" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Ambiente | Territorio</t>
         </is>
       </c>
       <c r="M877" t="inlineStr">
@@ -57269,7 +57269,7 @@
       </c>
       <c r="N877" t="inlineStr">
         <is>
-          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell’Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
+          <t>Lavori di manutenzione ordinaria dei caselli idraulici - anno 2024 - Affidamento diretto per allacciamento alla rete idrica</t>
         </is>
       </c>
       <c r="O877" s="4" t="inlineStr">
@@ -57286,7 +57286,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Avviso di aggiudicazione della procedura di affidamento diretto</t>
+          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -57296,23 +57296,27 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Vicenza</t>
-        </is>
-      </c>
-      <c r="F878" t="inlineStr"/>
+          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
       <c r="G878" s="2" t="n">
-        <v>273</v>
+        <v>31000000</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>45517</v>
+        <v>45629</v>
       </c>
       <c r="I878" s="3" t="n">
-        <v>47349</v>
+        <v>47483</v>
       </c>
       <c r="K878" t="inlineStr">
         <is>
@@ -57321,7 +57325,7 @@
       </c>
       <c r="L878" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="M878" t="inlineStr">
@@ -57331,7 +57335,7 @@
       </c>
       <c r="N878" t="inlineStr">
         <is>
-          <t>Lavori di manutenzione ordinaria dei caselli idraulici - anno 2024 - Affidamento diretto per allacciamento alla rete idrica</t>
+          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
         </is>
       </c>
       <c r="O878" s="4" t="inlineStr">
@@ -57348,7 +57352,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
+          <t>Avviso di post informazione: Decreto a contrarre mediante affidamento diretto e impegno di spesa per l'acquisto dell'abbonamento annuale per il 2025, cartaceo, alle riviste "Terra è vita" e "Informatore zootecnico" edite dalla Società New Business Media s.r.l. DGR n. 197/2024. Art. 50, co. 1, lett. b) del D.lgs n. 36/2023 e ss.mm.ii.</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -57358,36 +57362,32 @@
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>Avviso di contributo</t>
-        </is>
-      </c>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
       <c r="G879" s="2" t="n">
-        <v>31000000</v>
+        <v>178</v>
       </c>
       <c r="H879" s="3" t="n">
-        <v>45629</v>
+        <v>45758</v>
       </c>
       <c r="I879" s="3" t="n">
-        <v>47483</v>
+        <v>47575</v>
       </c>
       <c r="K879" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L879" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M879" t="inlineStr">
@@ -57397,7 +57397,7 @@
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
+          <t>Affidamento diretto per l’acquisto dell’abbonamento annuale per il 2025, cartaceo, alle riviste “Terra è vita” e “Informatore zootecnico” edite dalla Società New Business Media s.r.l. DGR n. 197/2024. CIG B6470B3C0B FORNITORE: Società New Business Media s.r.l. NORMATIVA DI RIFERIMENTO: Art. 50, co. 1, lett. b) e art. 85 del D.lgs n. 36/2023 e ss.mm.ii Link a BNDCP (Banca Nazionale dei Contratti Pubblici) ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la Sig.ra Daria Scaggiante al seguente numero di telefono: 041 2795548.</t>
         </is>
       </c>
       <c r="O879" s="4" t="inlineStr">
@@ -57414,7 +57414,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Decreto a contrarre mediante affidamento diretto e impegno di spesa per l'acquisto dell'abbonamento annuale per il 2025, cartaceo, alle riviste "Terra è vita" e "Informatore zootecnico" edite dalla Società New Business Media s.r.l. DGR n. 197/2024. Art. 50, co. 1, lett. b) del D.lgs n. 36/2023 e ss.mm.ii.</t>
+          <t>Avviso di post informazione: Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino - Ristrutturazione e riconversione vigneti e l'impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -57432,15 +57432,19 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
       <c r="G880" s="2" t="n">
-        <v>178</v>
+        <v>19800</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>45758</v>
+        <v>45771</v>
       </c>
       <c r="I880" s="3" t="n">
-        <v>47575</v>
+        <v>47597</v>
       </c>
       <c r="K880" t="inlineStr">
         <is>
@@ -57459,7 +57463,7 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>Affidamento diretto per l’acquisto dell’abbonamento annuale per il 2025, cartaceo, alle riviste “Terra è vita” e “Informatore zootecnico” edite dalla Società New Business Media s.r.l. DGR n. 197/2024. CIG B6470B3C0B FORNITORE: Società New Business Media s.r.l. NORMATIVA DI RIFERIMENTO: Art. 50, co. 1, lett. b) e art. 85 del D.lgs n. 36/2023 e ss.mm.ii Link a BNDCP (Banca Nazionale dei Contratti Pubblici) ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la Sig.ra Daria Scaggiante al seguente numero di telefono: 041 2795548.</t>
+          <t>Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino – Ristrutturazione e riconversione vigneti e l’impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023. CIG: B683E5105D CUP: H11J25000140008 FORNITORE: Bioprogramm srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n. 50/2016. IMPORTO: Euro 19.800,00 Link a BNDCP (Banca Nazionale dei Contratti Pubblici)…</t>
         </is>
       </c>
       <c r="O880" s="4" t="inlineStr">
@@ -57476,7 +57480,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino - Ristrutturazione e riconversione vigneti e l'impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023</t>
+          <t>Avviso di post informazione: Determina a contrarre e affidamento alla società Sikura Srl per la fornitura di dotazioni tecniche per i dipendenti della Direzione Agroalimentare addetti alle funzioni di vigilanza e controllo sulle produzioni agricole ed agroalimentari. CIG B900F94F3D. Art. 50, comma 1, lett. b) dello stesso D.Lgs. n. 36/2023.</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -57500,13 +57504,13 @@
         </is>
       </c>
       <c r="G881" s="2" t="n">
-        <v>19800</v>
+        <v>2005</v>
       </c>
       <c r="H881" s="3" t="n">
-        <v>45771</v>
+        <v>45989</v>
       </c>
       <c r="I881" s="3" t="n">
-        <v>47597</v>
+        <v>47818</v>
       </c>
       <c r="K881" t="inlineStr">
         <is>
@@ -57525,7 +57529,7 @@
       </c>
       <c r="N881" t="inlineStr">
         <is>
-          <t>Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino – Ristrutturazione e riconversione vigneti e l’impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023. CIG: B683E5105D CUP: H11J25000140008 FORNITORE: Bioprogramm srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n. 50/2016. IMPORTO: Euro 19.800,00 Link a BNDCP (Banca Nazionale dei Contratti Pubblici)…</t>
+          <t>CIG: B900F94F3D FORNITORE: Sikura Srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’:Trasparenza ai fini del Codice dei Contratti. ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la dott.ssa Giada Solin al seguente numero di telefono: 041 2795540.</t>
         </is>
       </c>
       <c r="O881" s="4" t="inlineStr">
@@ -57542,7 +57546,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Determina a contrarre e affidamento alla società Sikura Srl per la fornitura di dotazioni tecniche per i dipendenti della Direzione Agroalimentare addetti alle funzioni di vigilanza e controllo sulle produzioni agricole ed agroalimentari. CIG B900F94F3D. Art. 50, comma 1, lett. b) dello stesso D.Lgs. n. 36/2023.</t>
+          <t>Avviso per la presentazione delle candidature all'iscrizione nell'elenco regionale degli Esperti per l'erogazione dei servizi di IVC. (In attuazione della DGR n. 627/2022, della DGR n. 352/2024 e della DGR n. 1302/2025)</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -57557,22 +57561,16 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G882" s="2" t="n">
-        <v>2005</v>
-      </c>
+          <t>Direzione Lavoro</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" s="2" t="n"/>
       <c r="H882" s="3" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="I882" s="3" t="n">
-        <v>47818</v>
+        <v>47848</v>
       </c>
       <c r="K882" t="inlineStr">
         <is>
@@ -57581,7 +57579,7 @@
       </c>
       <c r="L882" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M882" t="inlineStr">
@@ -57591,7 +57589,7 @@
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>CIG: B900F94F3D FORNITORE: Sikura Srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’:Trasparenza ai fini del Codice dei Contratti. ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la dott.ssa Giada Solin al seguente numero di telefono: 041 2795540.</t>
+          <t>Con il DDR n. 108 del 19 marzo 2026 , in attuazione della DGR n. 1302 del 20 ottobre 2025, si definiscono i termini e le modalità di presentazione delle candidature a svolgere il ruolo di Esperto per l’erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link: https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. Maggiori informazioni alla pagina web: IVC - Individuazione Validazione e Certificazione delle…</t>
         </is>
       </c>
       <c r="O882" s="4" t="inlineStr">
@@ -57608,7 +57606,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Avviso per la presentazione delle candidature all'iscrizione nell'elenco regionale degli Esperti per l'erogazione dei servizi di IVC. (In attuazione della DGR n. 627/2022, della DGR n. 352/2024 e della DGR n. 1302/2025)</t>
+          <t>Aggiornamento dell'Avviso per la presentazione delle domande di autorizzazione all'esercizio del ruolo di Soggetto Titolato IVC ed iscrizione nel relativo Elenco, approvato con DDR n. 522/2025 e recepimento delle modifiche introdotte dalla DGR n. 1302/2025</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -57629,7 +57627,7 @@
       <c r="F883" t="inlineStr"/>
       <c r="G883" s="2" t="n"/>
       <c r="H883" s="3" t="n">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="I883" s="3" t="n">
         <v>47848</v>
@@ -57651,7 +57649,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>Con il DDR n. 108 del 19 marzo 2026 , in attuazione della DGR n. 1302 del 20 ottobre 2025, si definiscono i termini e le modalità di presentazione delle candidature a svolgere il ruolo di Esperto per l’erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link: https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. Maggiori informazioni alla pagina web: IVC - Individuazione Validazione e Certificazione delle…</t>
+          <t>Con il DDR 203 del 15/05/2026 , in attuazione della DGR n. 1302/2025, si approva l’aggiornamento dell’Avviso per la presentazione delle domande di autorizzazione all’esercizio del ruolo di Soggetto Titolato alla erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. L’accesso al sistema informativo IVC-Titolati è consentito esclusivamente ai soggetti…</t>
         </is>
       </c>
       <c r="O883" s="4" t="inlineStr">
@@ -57668,7 +57666,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Aggiornamento dell'Avviso per la presentazione delle domande di autorizzazione all'esercizio del ruolo di Soggetto Titolato IVC ed iscrizione nel relativo Elenco, approvato con DDR n. 522/2025 e recepimento delle modifiche introdotte dalla DGR n. 1302/2025</t>
+          <t>Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11.</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -57683,16 +57681,22 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F884" t="inlineStr"/>
-      <c r="G884" s="2" t="n"/>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="n">
+        <v>1403511</v>
+      </c>
       <c r="H884" s="3" t="n">
-        <v>46182</v>
+        <v>45287</v>
       </c>
       <c r="I884" s="3" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="K884" t="inlineStr">
         <is>
@@ -57701,7 +57705,7 @@
       </c>
       <c r="L884" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M884" t="inlineStr">
@@ -57711,7 +57715,7 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>Con il DDR 203 del 15/05/2026 , in attuazione della DGR n. 1302/2025, si approva l’aggiornamento dell’Avviso per la presentazione delle domande di autorizzazione all’esercizio del ruolo di Soggetto Titolato alla erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. L’accesso al sistema informativo IVC-Titolati è consentito esclusivamente ai soggetti…</t>
+          <t>Estratto del Bando-Avviso-Finanziamento : Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11. Ente Affidante: Regione del Veneto – Direzione Agroalimentare Affidamento a Organismo in house: Veneto Innovazione Spa Settori di attività : Innovazione e promozione economica Precedente gestore di servizio: Veneto Sviluppo Spa Durata: dal 01/01/2024 al 31/12/2032 Importo complessivo dell’affidamento: 1.403.510,76 Provvedimento di affidamento dell’incarico: DGR n. 1600 del 19/12/2023…</t>
         </is>
       </c>
       <c r="O884" s="4" t="inlineStr">
@@ -57728,7 +57732,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11.</t>
+          <t>Decreto di istituzione dell'Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell'art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto "Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36".</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -57743,31 +57747,29 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
+          <t>Direzione Acquisti, AA.GG. e SOS affidamento servizi e forniture</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G885" s="2" t="n">
-        <v>1403511</v>
-      </c>
+          <t>Albi e registri</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="n"/>
       <c r="H885" s="3" t="n">
-        <v>45287</v>
+        <v>45643</v>
       </c>
       <c r="I885" s="3" t="n">
-        <v>48579</v>
+        <v>73050</v>
       </c>
       <c r="K885" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M885" t="inlineStr">
@@ -57777,7 +57779,7 @@
       </c>
       <c r="N885" t="inlineStr">
         <is>
-          <t>Estratto del Bando-Avviso-Finanziamento : Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11. Ente Affidante: Regione del Veneto – Direzione Agroalimentare Affidamento a Organismo in house: Veneto Innovazione Spa Settori di attività : Innovazione e promozione economica Precedente gestore di servizio: Veneto Sviluppo Spa Durata: dal 01/01/2024 al 31/12/2032 Importo complessivo dell’affidamento: 1.403.510,76 Provvedimento di affidamento dell’incarico: DGR n. 1600 del 19/12/2023…</t>
+          <t>Decreto di istituzione dell’Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell’art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto “Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36”.</t>
         </is>
       </c>
       <c r="O885" s="4" t="inlineStr">
@@ -57794,7 +57796,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Decreto di istituzione dell'Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell'art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto "Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36".</t>
+          <t>Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -57809,7 +57811,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>Direzione Acquisti, AA.GG. e SOS affidamento servizi e forniture</t>
+          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
@@ -57819,19 +57821,19 @@
       </c>
       <c r="G886" s="2" t="n"/>
       <c r="H886" s="3" t="n">
-        <v>45643</v>
+        <v>45401</v>
       </c>
       <c r="I886" s="3" t="n">
         <v>73050</v>
       </c>
       <c r="K886" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L886" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Attività produttive | Comunicazione e informazione | Demanio e patrimonio | Enti locali | Territorio</t>
         </is>
       </c>
       <c r="M886" t="inlineStr">
@@ -57841,7 +57843,7 @@
       </c>
       <c r="N886" t="inlineStr">
         <is>
-          <t>Decreto di istituzione dell’Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell’art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto “Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36”.</t>
+          <t>“Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto” (DGR n. 376 del 09/04/2024). L'Avviso è finalizzato alla rilevazione sul territorio regionale di “ opportunità di insediamento ”, costituite da aree edificabili ed edifici esistenti a vocazione produttiva, di proprietà pubblica o privata, da poter promuovere presso nuovi possibili investitori, anche esteri, attraverso iniziative dedicate e la loro valorizzazione in occasione di eventi di promozione su scala regionale, nazionale e internazionale. L'iniziativa è attuata in coerenza con il “Programma di attività per lo sviluppo di una…</t>
         </is>
       </c>
       <c r="O886" s="4" t="inlineStr">
@@ -57853,59 +57855,62 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto</t>
+          <t>PR Veneto FESR 2021-27 · Azione 1.3.6 · Internazionalizzazione</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Avviso</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
+          <t>Sviluppo Economico, Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G887" s="2" t="n"/>
-      <c r="H887" s="3" t="n">
-        <v>45401</v>
-      </c>
-      <c r="I887" s="3" t="n">
-        <v>73050</v>
+          <t>Sovvenzione</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H887" s="3" t="n"/>
+      <c r="I887" s="3" t="n"/>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Dicembre 2026</t>
+        </is>
       </c>
       <c r="K887" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L887" t="inlineStr">
         <is>
-          <t>Attività produttive | Comunicazione e informazione | Demanio e patrimonio | Enti locali | Territorio</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>Portale Bandi Regione Veneto</t>
+          <t>Calendario inviti FESR 2021-27</t>
         </is>
       </c>
       <c r="N887" t="inlineStr">
         <is>
-          <t>“Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto” (DGR n. 376 del 09/04/2024). L'Avviso è finalizzato alla rilevazione sul territorio regionale di “ opportunità di insediamento ”, costituite da aree edificabili ed edifici esistenti a vocazione produttiva, di proprietà pubblica o privata, da poter promuovere presso nuovi possibili investitori, anche esteri, attraverso iniziative dedicate e la loro valorizzazione in occasione di eventi di promozione su scala regionale, nazionale e internazionale. L'iniziativa è attuata in coerenza con il “Programma di attività per lo sviluppo di una…</t>
+          <t>1.3.6  Sostegno ai programmi di internazionalizzazione delle PMI — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
         </is>
       </c>
       <c r="O887" s="4" t="inlineStr">
@@ -57922,7 +57927,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 1.3.6 · Internazionalizzazione</t>
+          <t>PR Veneto FESR 2021-27 · Azione 1.3.11 Sub B) · Nuove imprese culturali</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -57937,7 +57942,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>Sviluppo Economico, Ricerca e Innovazione</t>
+          <t>Cultura</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -57946,13 +57951,13 @@
         </is>
       </c>
       <c r="G888" s="2" t="n">
-        <v>3000000</v>
+        <v>4294000</v>
       </c>
       <c r="H888" s="3" t="n"/>
       <c r="I888" s="3" t="n"/>
       <c r="J888" t="inlineStr">
         <is>
-          <t>Dicembre 2026</t>
+          <t>Gennaio 2027</t>
         </is>
       </c>
       <c r="K888" t="inlineStr">
@@ -57972,7 +57977,8 @@
       </c>
       <c r="N888" t="inlineStr">
         <is>
-          <t>1.3.6  Sostegno ai programmi di internazionalizzazione delle PMI — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
+          <t>1.3.11 Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo. 
+Sub azione A - Consolidamento di imprese esistenti — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
         </is>
       </c>
       <c r="O888" s="4" t="inlineStr">
@@ -57989,7 +57995,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 1.3.11 Sub B) · Nuove imprese culturali</t>
+          <t>PR Veneto FESR 2021-27 · Azione 2.5 · Resilienza Idrica</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -58004,7 +58010,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Difesa del Suolo</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
@@ -58013,18 +58019,18 @@
         </is>
       </c>
       <c r="G889" s="2" t="n">
-        <v>4294000</v>
+        <v>28000000</v>
       </c>
       <c r="H889" s="3" t="n"/>
       <c r="I889" s="3" t="n"/>
       <c r="J889" t="inlineStr">
         <is>
-          <t>Gennaio 2027</t>
+          <t>Ottobre – Dicembre 2026</t>
         </is>
       </c>
       <c r="K889" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L889" t="inlineStr">
@@ -58039,8 +58045,7 @@
       </c>
       <c r="N889" t="inlineStr">
         <is>
-          <t>1.3.11 Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo. 
-Sub azione A - Consolidamento di imprese esistenti — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
+          <t>2.5. Resilienza Idrica — Promuovere l'accesso sicuro all’acqua, la sua gestione sostenibile, compresa la gestione integrata delle risorse idriche e la resilienza idrica Beneficiari: Regione del Veneto e/o Enti Pubblici Vigilati ai sensi dell’art. 22, c. 1, lett. a) del D.Lgs 33/2013 dalla medesima Regione del Veneto</t>
         </is>
       </c>
       <c r="O889" s="4" t="inlineStr">
@@ -58057,7 +58062,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 2.5 · Resilienza Idrica</t>
+          <t>PR Veneto FESR 2021-27 · Azione 2.1.1 · Housing sociale</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -58072,7 +58077,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>Difesa del Suolo</t>
+          <t>Edilizia Residenziale Pubblica</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
@@ -58080,14 +58085,12 @@
           <t>Sovvenzione</t>
         </is>
       </c>
-      <c r="G890" s="2" t="n">
-        <v>28000000</v>
-      </c>
+      <c r="G890" s="2" t="n"/>
       <c r="H890" s="3" t="n"/>
       <c r="I890" s="3" t="n"/>
       <c r="J890" t="inlineStr">
         <is>
-          <t>Ottobre – Dicembre 2026</t>
+          <t>Settembre - Ottobre 2026</t>
         </is>
       </c>
       <c r="K890" t="inlineStr">
@@ -58107,7 +58110,7 @@
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>2.5. Resilienza Idrica — Promuovere l'accesso sicuro all’acqua, la sua gestione sostenibile, compresa la gestione integrata delle risorse idriche e la resilienza idrica Beneficiari: Regione del Veneto e/o Enti Pubblici Vigilati ai sensi dell’art. 22, c. 1, lett. a) del D.Lgs 33/2013 dalla medesima Regione del Veneto</t>
+          <t xml:space="preserve"> Beneficiari: Nuclei familiari che si trovano in particolari situazioni di disagio economico e soggetti che, per motivi economici o sociali, non possono accedere a soluzioni abitative a condizioni di mercato</t>
         </is>
       </c>
       <c r="O890" s="4" t="inlineStr">
@@ -58124,7 +58127,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 2.1.1 · Housing sociale</t>
+          <t>PR Veneto FESR 2021-27 · Azione 4.2.1 · Infrastrutture per formazione e istruzione</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -58139,7 +58142,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>Edilizia Residenziale Pubblica</t>
+          <t>Edilizia residenziale pubblica, ospedaliera e a finalità collettive</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
@@ -58147,12 +58150,14 @@
           <t>Sovvenzione</t>
         </is>
       </c>
-      <c r="G891" s="2" t="n"/>
+      <c r="G891" s="2" t="n">
+        <v>7063373</v>
+      </c>
       <c r="H891" s="3" t="n"/>
       <c r="I891" s="3" t="n"/>
       <c r="J891" t="inlineStr">
         <is>
-          <t>Settembre - Ottobre 2026</t>
+          <t>Ottobre 2026</t>
         </is>
       </c>
       <c r="K891" t="inlineStr">
@@ -58172,7 +58177,7 @@
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beneficiari: Nuclei familiari che si trovano in particolari situazioni di disagio economico e soggetti che, per motivi economici o sociali, non possono accedere a soluzioni abitative a condizioni di mercato</t>
+          <t>4.2.1 VET Innovation 2026 — Migliorare la parità di accesso a servizi di qualità e inclusivi nel campo dell'istruzione, della formazione e dell'apprendimento permanente mediante lo sviluppo di infrastrutture accessibili, anche promuovendo la resilienza dell'istruzione e della formazione online e a distanza (FESR) Beneficiari: Soggetti iscritti nell’elenco di cui alla L.R. n. 19 del 09/08/2002 (“Istituzione dell'elenco regionale degli organismi di formazione accreditati”) per l’ambito dell’Obbligo Formativo</t>
         </is>
       </c>
       <c r="O891" s="4" t="inlineStr">
@@ -58189,7 +58194,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 4.2.1 · Infrastrutture per formazione e istruzione</t>
+          <t>PR Veneto FSE+ 2021-27 · Politiche attive per soggetti svantaggiati</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -58204,22 +58209,22 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>Edilizia residenziale pubblica, ospedaliera e a finalità collettive</t>
+          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>Sovvenzione</t>
+          <t>Invito FSE+</t>
         </is>
       </c>
       <c r="G892" s="2" t="n">
-        <v>7063373</v>
+        <v>10000000</v>
       </c>
       <c r="H892" s="3" t="n"/>
       <c r="I892" s="3" t="n"/>
       <c r="J892" t="inlineStr">
         <is>
-          <t>Ottobre 2026</t>
+          <t>nov-26</t>
         </is>
       </c>
       <c r="K892" t="inlineStr">
@@ -58229,17 +58234,17 @@
       </c>
       <c r="L892" t="inlineStr">
         <is>
-          <t>FESR</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="M892" t="inlineStr">
         <is>
-          <t>Calendario inviti FESR 2021-27</t>
+          <t>Calendario inviti FSE+</t>
         </is>
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>4.2.1 VET Innovation 2026 — Migliorare la parità di accesso a servizi di qualità e inclusivi nel campo dell'istruzione, della formazione e dell'apprendimento permanente mediante lo sviluppo di infrastrutture accessibili, anche promuovendo la resilienza dell'istruzione e della formazione online e a distanza (FESR) Beneficiari: Soggetti iscritti nell’elenco di cui alla L.R. n. 19 del 09/08/2002 (“Istituzione dell'elenco regionale degli organismi di formazione accreditati”) per l’ambito dell’Obbligo Formativo</t>
+          <t>Incentivare l’inclusione attiva, per promuovere le pari opportunità, la non discriminazione e la partecipazione attiva, e migliorare l’occupabilità, in particolare dei gruppi svantaggiati Richiedenti: Soggetti accreditati Formazione superiore Soggetti accreditati Servizi per il lavoro</t>
         </is>
       </c>
       <c r="O892" s="4" t="inlineStr">
@@ -58256,7 +58261,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Politiche attive per soggetti svantaggiati</t>
+          <t>PR Veneto FSE+ 2021-27 · Borse Universitarie STEM</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -58306,7 +58311,7 @@
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>Incentivare l’inclusione attiva, per promuovere le pari opportunità, la non discriminazione e la partecipazione attiva, e migliorare l’occupabilità, in particolare dei gruppi svantaggiati Richiedenti: Soggetti accreditati Formazione superiore Soggetti accreditati Servizi per il lavoro</t>
+          <t>Migliorare l'accesso all'occupazione e le misure di attivazione per tutte le persone in cerca di lavoro, in particolare i giovani, soprattutto attraverso l'attuazione della garanzia per i giovani, i disoccupati di lungo periodo e i gruppi svantaggiati nel mercato del lavoro, nonché delle persone inattive, anche mediante la promozione del lavoro autonomo e dell'economia sociale Richiedenti: Destinatari finali</t>
         </is>
       </c>
       <c r="O893" s="4" t="inlineStr">
@@ -58323,7 +58328,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Borse Universitarie STEM</t>
+          <t>PR Veneto FSE+ 2021-27 · Formazione Continua</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -58347,13 +58352,13 @@
         </is>
       </c>
       <c r="G894" s="2" t="n">
-        <v>10000000</v>
+        <v>13000000</v>
       </c>
       <c r="H894" s="3" t="n"/>
       <c r="I894" s="3" t="n"/>
       <c r="J894" t="inlineStr">
         <is>
-          <t>nov-26</t>
+          <t>ott-26</t>
         </is>
       </c>
       <c r="K894" t="inlineStr">
@@ -58373,7 +58378,7 @@
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>Migliorare l'accesso all'occupazione e le misure di attivazione per tutte le persone in cerca di lavoro, in particolare i giovani, soprattutto attraverso l'attuazione della garanzia per i giovani, i disoccupati di lungo periodo e i gruppi svantaggiati nel mercato del lavoro, nonché delle persone inattive, anche mediante la promozione del lavoro autonomo e dell'economia sociale Richiedenti: Destinatari finali</t>
+          <t>Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure un ambiente di lavoro sano e adeguato che tenga conto dei rischi per la salute Richiedenti: Soggetti accreditati Formazione continua</t>
         </is>
       </c>
       <c r="O894" s="4" t="inlineStr">
@@ -58385,17 +58390,17 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Formazione Continua</t>
+          <t>Bando PR FESR 21-27 · Azione 1.2.1 · Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasform</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Bando</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -58405,42 +58410,35 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
+          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Invito FSE+</t>
-        </is>
-      </c>
-      <c r="G895" s="2" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="H895" s="3" t="n"/>
-      <c r="I895" s="3" t="n"/>
-      <c r="J895" t="inlineStr">
-        <is>
-          <t>ott-26</t>
-        </is>
-      </c>
-      <c r="K895" t="inlineStr">
-        <is>
-          <t>Ente</t>
-        </is>
-      </c>
+          <t>Digitalizzazione, Regione del Veneto</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="n"/>
+      <c r="H895" s="3" t="n">
+        <v>45300</v>
+      </c>
+      <c r="I895" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="K895" t="inlineStr"/>
       <c r="L895" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M895" t="inlineStr">
         <is>
-          <t>Calendario inviti FSE+</t>
+          <t>Veneto Coesione (Opportunità)</t>
         </is>
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure un ambiente di lavoro sano e adeguato che tenga conto dei rischi per la salute Richiedenti: Soggetti accreditati Formazione continua</t>
+          <t>Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasformazione digitale per cittadini imprese e PA</t>
         </is>
       </c>
       <c r="O895" s="4" t="inlineStr">
@@ -58457,7 +58455,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.2.1 · Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasform</t>
+          <t>Bando PR FESR 21-27 · Azione 1.2.2 · Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei ser</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -58477,7 +58475,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>Digitalizzazione, Regione del Veneto</t>
+          <t xml:space="preserve">Digitalizzazione, Regione del Veneto </t>
         </is>
       </c>
       <c r="G896" s="2" t="n"/>
@@ -58500,7 +58498,7 @@
       </c>
       <c r="N896" t="inlineStr">
         <is>
-          <t>Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasformazione digitale per cittadini imprese e PA</t>
+          <t>Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei servizi della pubblica amministrazione a vantaggio di cittadini e imprese ed in continuità</t>
         </is>
       </c>
       <c r="O896" s="4" t="inlineStr">
@@ -58517,7 +58515,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.2.2 · Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei ser</t>
+          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Region</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -58537,15 +58535,15 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digitalizzazione, Regione del Veneto </t>
+          <t>Accesso al credito, PMI</t>
         </is>
       </c>
       <c r="G897" s="2" t="n"/>
       <c r="H897" s="3" t="n">
-        <v>45300</v>
+        <v>45846</v>
       </c>
       <c r="I897" s="3" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="K897" t="inlineStr"/>
       <c r="L897" t="inlineStr">
@@ -58560,7 +58558,7 @@
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei servizi della pubblica amministrazione a vantaggio di cittadini e imprese ed in continuità</t>
+          <t>Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Regionale Liquidità - Azione 1.3.3</t>
         </is>
       </c>
       <c r="O897" s="4" t="inlineStr">
@@ -58577,7 +58575,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Region</t>
+          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -58602,7 +58600,7 @@
       </c>
       <c r="G898" s="2" t="n"/>
       <c r="H898" s="3" t="n">
-        <v>45846</v>
+        <v>45835</v>
       </c>
       <c r="I898" s="3" t="n">
         <v>46752</v>
@@ -58620,7 +58618,7 @@
       </c>
       <c r="N898" t="inlineStr">
         <is>
-          <t>Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Regionale Liquidità - Azione 1.3.3</t>
+          <t>Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
         </is>
       </c>
       <c r="O898" s="4" t="inlineStr">
@@ -58637,7 +58635,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
+          <t>Progetti PR FESR 21-27 · Azione 2.4.3 · Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi d</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -58657,12 +58655,12 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>Accesso al credito, PMI</t>
+          <t>Bacini e opere di laminazione, Regione del Veneto</t>
         </is>
       </c>
       <c r="G899" s="2" t="n"/>
       <c r="H899" s="3" t="n">
-        <v>45835</v>
+        <v>45535</v>
       </c>
       <c r="I899" s="3" t="n">
         <v>46752</v>
@@ -58680,7 +58678,7 @@
       </c>
       <c r="N899" t="inlineStr">
         <is>
-          <t>Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
+          <t>Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi della rete idrografica principale anche con ealizzazione di opere di laminazione delle piene, Approvazione elenco degli interventi da finanziare.</t>
         </is>
       </c>
       <c r="O899" s="4" t="inlineStr">
@@ -58689,68 +58687,8 @@
         </is>
       </c>
     </row>
-    <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t>Aperto</t>
-        </is>
-      </c>
-      <c r="B900" t="inlineStr">
-        <is>
-          <t>Progetti PR FESR 21-27 · Azione 2.4.3 · Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi d</t>
-        </is>
-      </c>
-      <c r="C900" t="inlineStr">
-        <is>
-          <t>Bando</t>
-        </is>
-      </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>Finanziamenti</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
-        </is>
-      </c>
-      <c r="F900" t="inlineStr">
-        <is>
-          <t>Bacini e opere di laminazione, Regione del Veneto</t>
-        </is>
-      </c>
-      <c r="G900" s="2" t="n"/>
-      <c r="H900" s="3" t="n">
-        <v>45535</v>
-      </c>
-      <c r="I900" s="3" t="n">
-        <v>46752</v>
-      </c>
-      <c r="K900" t="inlineStr"/>
-      <c r="L900" t="inlineStr">
-        <is>
-          <t>FESR</t>
-        </is>
-      </c>
-      <c r="M900" t="inlineStr">
-        <is>
-          <t>Veneto Coesione (Opportunità)</t>
-        </is>
-      </c>
-      <c r="N900" t="inlineStr">
-        <is>
-          <t>Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi della rete idrografica principale anche con ealizzazione di opere di laminazione delle piene, Approvazione elenco degli interventi da finanziare.</t>
-        </is>
-      </c>
-      <c r="O900" s="4" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O900"/>
+  <autoFilter ref="A1:O899"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -59650,7 +59588,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O897" r:id="rId896"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O898" r:id="rId897"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O899" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O900" r:id="rId899"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59689,7 +59626,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:07</t>
+          <t>2026-10-28 10:54</t>
         </is>
       </c>
     </row>
@@ -59700,7 +59637,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4">
@@ -59711,7 +59648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/docs/data/bandi_veneto.xlsx
+++ b/docs/data/bandi_veneto.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi'!$A$1:$O$899</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi'!$A$1:$O$897</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O899"/>
+  <dimension ref="A1:O897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52570,7 +52570,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Avviso Pubblico - Concessione di aree del demanio marittimo per attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. - Artemisia Società Cooperativa</t>
+          <t>Affidamento del servizio di supporto all'istruttoria in materia di aiuti di Stato a favore del Programma Interreg VI A Italia-Croazia 2021-2027</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -52580,34 +52580,36 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Unità Organizzativa AdG Italia - Croazia</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G805" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="n">
+        <v>19500</v>
+      </c>
       <c r="H805" s="3" t="n">
-        <v>46290</v>
+        <v>46052</v>
       </c>
       <c r="I805" s="3" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="K805" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Affari generali | Europa | FESR | Interreg</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
@@ -52617,7 +52619,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo. - Avviso Pubblico - Concessione di aree del demanio marittimo da destinarsi ad attività di venericoltura nel comprensorio Delta del Po a nord del Po di Maistra nei Comuni di Rosolina e Porto Viro (RO). Richiesta di ampliamento ai sensi dell'art.24 del Codice della Navigazione. Richiedente: Artemisia Società Cooperativa (C.F. 01372020295).</t>
+          <t>Con il decreto del Direttore dell'Unità Organizzativa AdG Italia-Croazia n. 268 del 23 dicembre 2025, si è proceduto all'affidamento diretto del servizio di supporto all'istruttoria in materia di aiuti di Stato delle proposte progettuali di tipo Standard, pervenute in risposta al terzo bando del Programma Interreg VI A Italia-Croazia 2021-2027, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023 e s.m.i. Con Decreto del Direttore dell'Unità organizzativa AdG Italia-Croazia n. 148 del 6 luglio 2026 si è disposta la sostituzione del RUP per il contratto in oggetto, a seguito della nomina del nuovo Direttore della U.O. AdG…</t>
         </is>
       </c>
       <c r="O805" s="4" t="inlineStr">
@@ -52634,7 +52636,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Avviso pubblico esplorativo di mercato e contestuale raccolta di preventivi non vincolanti per la fornitura di contrassegni per richiami vivi destinati alla caccia appostamento</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -52644,36 +52646,36 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Pianificazione e Gestione Faunistico Venatoria</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G806" s="2" t="n">
-        <v>131148</v>
+        <v>1500</v>
       </c>
       <c r="H806" s="3" t="n">
-        <v>46307</v>
+        <v>46294</v>
       </c>
       <c r="I806" s="3" t="n">
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="K806" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -52683,7 +52685,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>Indagine di mercato finalizzata all’eventuale affidamento diretto della fornitura di contrassegni inamovibili numerati, costituiti da fascette in materiale plastico, per richiami vivi destinati alla caccia da appostamento, ai sensi dell’art. 35-quater della L.R. n. 50/1993, come modificata dalla L.R. n. 15/2025, per le annualità 2026 e 2027.</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="O806" s="4" t="inlineStr">
@@ -52700,7 +52702,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di supporto all'istruttoria in materia di aiuti di Stato a favore del Programma Interreg VI A Italia-Croazia 2021-2027</t>
+          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -52710,27 +52712,27 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Unità Organizzativa AdG Italia - Croazia</t>
+          <t>Direzione Demanio e Gestione del Patrimonio</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di alienazione</t>
         </is>
       </c>
       <c r="G807" s="2" t="n">
-        <v>19500</v>
+        <v>4237500</v>
       </c>
       <c r="H807" s="3" t="n">
-        <v>46052</v>
+        <v>46297</v>
       </c>
       <c r="I807" s="3" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="K807" t="inlineStr">
         <is>
@@ -52739,7 +52741,7 @@
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>Affari generali | Europa | FESR | Interreg</t>
+          <t>Demanio e patrimonio</t>
         </is>
       </c>
       <c r="M807" t="inlineStr">
@@ -52749,7 +52751,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>Con il decreto del Direttore dell'Unità Organizzativa AdG Italia-Croazia n. 268 del 23 dicembre 2025, si è proceduto all'affidamento diretto del servizio di supporto all'istruttoria in materia di aiuti di Stato delle proposte progettuali di tipo Standard, pervenute in risposta al terzo bando del Programma Interreg VI A Italia-Croazia 2021-2027, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023 e s.m.i. Con Decreto del Direttore dell'Unità organizzativa AdG Italia-Croazia n. 148 del 6 luglio 2026 si è disposta la sostituzione del RUP per il contratto in oggetto, a seguito della nomina del nuovo Direttore della U.O. AdG…</t>
+          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
         </is>
       </c>
       <c r="O807" s="4" t="inlineStr">
@@ -52766,7 +52768,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -52790,7 +52792,7 @@
         </is>
       </c>
       <c r="G808" s="2" t="n">
-        <v>1500</v>
+        <v>5800</v>
       </c>
       <c r="H808" s="3" t="n">
         <v>46294</v>
@@ -52815,7 +52817,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="O808" s="4" t="inlineStr">
@@ -52832,7 +52834,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
+          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -52842,36 +52844,36 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Direzione Demanio e Gestione del Patrimonio</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Avviso di alienazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G809" s="2" t="n">
-        <v>4237500</v>
+        <v>55000</v>
       </c>
       <c r="H809" s="3" t="n">
-        <v>46297</v>
+        <v>46283</v>
       </c>
       <c r="I809" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Demanio e patrimonio</t>
+          <t>Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
@@ -52881,7 +52883,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
+          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
         </is>
       </c>
       <c r="O809" s="4" t="inlineStr">
@@ -52898,7 +52900,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
+          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -52908,21 +52910,21 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G810" s="2" t="n">
-        <v>5800</v>
+        <v>938</v>
       </c>
       <c r="H810" s="3" t="n">
         <v>46294</v>
@@ -52932,12 +52934,12 @@
       </c>
       <c r="K810" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Pari opportunità</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -52947,7 +52949,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
+          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
         </is>
       </c>
       <c r="O810" s="4" t="inlineStr">
@@ -52964,7 +52966,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -52974,36 +52976,30 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
-        </is>
-      </c>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G811" s="2" t="n">
-        <v>55000</v>
-      </c>
+          <t>U.O. Genio Civile Venezia</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" s="2" t="n"/>
       <c r="H811" s="3" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="I811" s="3" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica | Turismo</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -53013,7 +53009,7 @@
       </c>
       <c r="N811" t="inlineStr">
         <is>
-          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
         </is>
       </c>
       <c r="O811" s="4" t="inlineStr">
@@ -53030,7 +53026,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -53040,36 +53036,30 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G812" s="2" t="n">
-        <v>938</v>
-      </c>
+          <t>U.O. Genio Civile Venezia</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" s="2" t="n"/>
       <c r="H812" s="3" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I812" s="3" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Pari opportunità</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -53079,7 +53069,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
         </is>
       </c>
       <c r="O812" s="4" t="inlineStr">
@@ -53096,7 +53086,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -53111,25 +53101,31 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>U.O. Genio Civile Venezia</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr"/>
-      <c r="G813" s="2" t="n"/>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="n">
+        <v>2075</v>
+      </c>
       <c r="H813" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="I813" s="3" t="n">
-        <v>46328</v>
+        <v>46333</v>
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -53139,7 +53135,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="O813" s="4" t="inlineStr">
@@ -53156,7 +53152,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -53171,16 +53167,16 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>U.O. Genio Civile Venezia</t>
+          <t>Direzione Infrastrutture E Trasporti</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
       <c r="G814" s="2" t="n"/>
       <c r="H814" s="3" t="n">
-        <v>46297</v>
+        <v>46275</v>
       </c>
       <c r="I814" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="K814" t="inlineStr">
         <is>
@@ -53189,7 +53185,7 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -53199,7 +53195,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="O814" s="4" t="inlineStr">
@@ -53216,7 +53212,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -53231,31 +53227,29 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Agroalimentare</t>
         </is>
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G815" s="2" t="n">
-        <v>2075</v>
-      </c>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="n"/>
       <c r="H815" s="3" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="I815" s="3" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -53265,7 +53259,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
         </is>
       </c>
       <c r="O815" s="4" t="inlineStr">
@@ -53282,7 +53276,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -53297,25 +53291,27 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture E Trasporti</t>
+          <t>Direzione Comunicazione E Informazione</t>
         </is>
       </c>
       <c r="F816" t="inlineStr"/>
-      <c r="G816" s="2" t="n"/>
+      <c r="G816" s="2" t="n">
+        <v>55000</v>
+      </c>
       <c r="H816" s="3" t="n">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="I816" s="3" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="K816" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Comunicazione e informazione</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -53325,7 +53321,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
         </is>
       </c>
       <c r="O816" s="4" t="inlineStr">
@@ -53342,7 +53338,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -53352,34 +53348,36 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
+          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G817" s="2" t="n"/>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="n">
+        <v>382342</v>
+      </c>
       <c r="H817" s="3" t="n">
-        <v>46304</v>
+        <v>46318</v>
       </c>
       <c r="I817" s="3" t="n">
-        <v>46335</v>
+        <v>46338</v>
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -53389,7 +53387,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
+          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
         </is>
       </c>
       <c r="O817" s="4" t="inlineStr">
@@ -53406,7 +53404,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
+          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -53421,27 +53419,27 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Direzione Comunicazione E Informazione</t>
+          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
         </is>
       </c>
       <c r="F818" t="inlineStr"/>
       <c r="G818" s="2" t="n">
-        <v>55000</v>
+        <v>299601</v>
       </c>
       <c r="H818" s="3" t="n">
-        <v>46290</v>
+        <v>46318</v>
       </c>
       <c r="I818" s="3" t="n">
-        <v>46336</v>
+        <v>46338</v>
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>Comunicazione e informazione</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -53451,7 +53449,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
+          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
         </is>
       </c>
       <c r="O818" s="4" t="inlineStr">
@@ -53463,12 +53461,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
+          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -53483,7 +53481,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
+          <t>Direzione Formazione E Istruzione</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
@@ -53492,7 +53490,7 @@
         </is>
       </c>
       <c r="G819" s="2" t="n">
-        <v>382342</v>
+        <v>30000</v>
       </c>
       <c r="H819" s="3" t="n">
         <v>46318</v>
@@ -53507,7 +53505,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Sociale</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -53517,7 +53515,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
+          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
         </is>
       </c>
       <c r="O819" s="4" t="inlineStr">
@@ -53529,12 +53527,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
+          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -53549,27 +53547,31 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
-        </is>
-      </c>
-      <c r="F820" t="inlineStr"/>
+          <t>U.O. Servizi Forestali</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Conferenza di servizi</t>
+        </is>
+      </c>
       <c r="G820" s="2" t="n">
-        <v>299601</v>
+        <v>1400000</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>46318</v>
+        <v>46297</v>
       </c>
       <c r="I820" s="3" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -53579,7 +53581,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
+          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
         </is>
       </c>
       <c r="O820" s="4" t="inlineStr">
@@ -53591,12 +53593,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -53606,36 +53608,36 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Direzione Formazione E Istruzione</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>Avviso di contributo</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G821" s="2" t="n">
-        <v>30000</v>
+        <v>6830</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>46318</v>
+        <v>46308</v>
       </c>
       <c r="I821" s="3" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -53645,7 +53647,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="O821" s="4" t="inlineStr">
@@ -53662,7 +53664,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -53677,31 +53679,31 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>U.O. Servizi Forestali</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Conferenza di servizi</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G822" s="2" t="n">
-        <v>1400000</v>
+        <v>3900</v>
       </c>
       <c r="H822" s="3" t="n">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="I822" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -53711,7 +53713,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
         </is>
       </c>
       <c r="O822" s="4" t="inlineStr">
@@ -53728,7 +53730,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
+          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -53743,31 +53745,29 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G823" s="2" t="n">
-        <v>6830</v>
-      </c>
+          <t>Avviso di esproprio</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="n"/>
       <c r="H823" s="3" t="n">
-        <v>46308</v>
+        <v>46286</v>
       </c>
       <c r="I823" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
+          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
         </is>
       </c>
       <c r="O823" s="4" t="inlineStr">
@@ -53789,12 +53789,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -53809,22 +53809,20 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Unità Organizzativa Genio Civile Verona</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G824" s="2" t="n">
-        <v>3900</v>
-      </c>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="n"/>
       <c r="H824" s="3" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="I824" s="3" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="K824" t="inlineStr">
         <is>
@@ -53833,7 +53831,7 @@
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
@@ -53843,7 +53841,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="O824" s="4" t="inlineStr">
@@ -53855,12 +53853,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -53875,29 +53873,29 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+          <t>Unità Organizzativa Genio Civile Verona</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Avviso di esproprio</t>
+          <t>Avviso di preinformazione</t>
         </is>
       </c>
       <c r="G825" s="2" t="n"/>
       <c r="H825" s="3" t="n">
-        <v>46286</v>
+        <v>46311</v>
       </c>
       <c r="I825" s="3" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -53907,7 +53905,7 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="O825" s="4" t="inlineStr">
@@ -53924,7 +53922,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -53971,7 +53969,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="O826" s="4" t="inlineStr">
@@ -53988,7 +53986,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -54003,14 +54001,10 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Verona</t>
-        </is>
-      </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr"/>
       <c r="G827" s="2" t="n"/>
       <c r="H827" s="3" t="n">
         <v>46311</v>
@@ -54020,12 +54014,12 @@
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M827" t="inlineStr">
@@ -54035,7 +54029,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
         </is>
       </c>
       <c r="O827" s="4" t="inlineStr">
@@ -54052,7 +54046,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -54067,14 +54061,10 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Verona</t>
-        </is>
-      </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr"/>
       <c r="G828" s="2" t="n"/>
       <c r="H828" s="3" t="n">
         <v>46311</v>
@@ -54084,12 +54074,12 @@
       </c>
       <c r="K828" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L828" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M828" t="inlineStr">
@@ -54099,7 +54089,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
         </is>
       </c>
       <c r="O828" s="4" t="inlineStr">
@@ -54116,7 +54106,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -54131,20 +54121,24 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr"/>
+          <t>Unità Organizzativa Fitosanitario</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
       <c r="G829" s="2" t="n"/>
       <c r="H829" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="I829" s="3" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
@@ -54159,7 +54153,7 @@
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
+          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
         </is>
       </c>
       <c r="O829" s="4" t="inlineStr">
@@ -54176,7 +54170,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -54186,30 +54180,36 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F830" t="inlineStr"/>
-      <c r="G830" s="2" t="n"/>
+          <t>Direzione Pianificazione Territoriale</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="n">
+        <v>4260</v>
+      </c>
       <c r="H830" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="I830" s="3" t="n">
-        <v>46342</v>
+        <v>46345</v>
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M830" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
+          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
         </is>
       </c>
       <c r="O830" s="4" t="inlineStr">
@@ -54236,7 +54236,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -54251,29 +54251,31 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Fitosanitario</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G831" s="2" t="n"/>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="n">
+        <v>4519</v>
+      </c>
       <c r="H831" s="3" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="I831" s="3" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="K831" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L831" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M831" t="inlineStr">
@@ -54283,7 +54285,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
         </is>
       </c>
       <c r="O831" s="4" t="inlineStr">
@@ -54300,7 +54302,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -54310,27 +54312,27 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>Direzione Pianificazione Territoriale</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G832" s="2" t="n">
-        <v>4260</v>
+        <v>3824</v>
       </c>
       <c r="H832" s="3" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I832" s="3" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="K832" t="inlineStr">
         <is>
@@ -54339,7 +54341,7 @@
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -54349,7 +54351,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="O832" s="4" t="inlineStr">
@@ -54361,12 +54363,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -54376,36 +54378,36 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Avvocatura</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G833" s="2" t="n">
-        <v>4519</v>
+        <v>39468</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>46315</v>
+        <v>46286</v>
       </c>
       <c r="I833" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
@@ -54415,7 +54417,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
         </is>
       </c>
       <c r="O833" s="4" t="inlineStr">
@@ -54427,12 +54429,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -54442,36 +54444,36 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Avvocatura</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G834" s="2" t="n">
-        <v>3824</v>
+        <v>1144</v>
       </c>
       <c r="H834" s="3" t="n">
-        <v>46315</v>
+        <v>46301</v>
       </c>
       <c r="I834" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="K834" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L834" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M834" t="inlineStr">
@@ -54481,7 +54483,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
         </is>
       </c>
       <c r="O834" s="4" t="inlineStr">
@@ -54498,7 +54500,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
+          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -54522,10 +54524,10 @@
         </is>
       </c>
       <c r="G835" s="2" t="n">
-        <v>39468</v>
+        <v>9155</v>
       </c>
       <c r="H835" s="3" t="n">
-        <v>46286</v>
+        <v>46308</v>
       </c>
       <c r="I835" s="3" t="n">
         <v>46348</v>
@@ -54547,7 +54549,7 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
+          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
         </is>
       </c>
       <c r="O835" s="4" t="inlineStr">
@@ -54559,12 +54561,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
+          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -54579,7 +54581,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Avvocatura</t>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -54588,22 +54590,22 @@
         </is>
       </c>
       <c r="G836" s="2" t="n">
-        <v>1144</v>
+        <v>77000</v>
       </c>
       <c r="H836" s="3" t="n">
-        <v>46301</v>
+        <v>46318</v>
       </c>
       <c r="I836" s="3" t="n">
-        <v>46348</v>
+        <v>46356</v>
       </c>
       <c r="K836" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L836" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Ambiente | Territorio | Turismo</t>
         </is>
       </c>
       <c r="M836" t="inlineStr">
@@ -54613,7 +54615,7 @@
       </c>
       <c r="N836" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
+          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
         </is>
       </c>
       <c r="O836" s="4" t="inlineStr">
@@ -54630,7 +54632,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
+          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -54640,36 +54642,30 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Avvocatura</t>
-        </is>
-      </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G837" s="2" t="n">
-        <v>9155</v>
-      </c>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" s="2" t="n"/>
       <c r="H837" s="3" t="n">
-        <v>46308</v>
+        <v>46161</v>
       </c>
       <c r="I837" s="3" t="n">
-        <v>46348</v>
+        <v>46356</v>
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>FESR | Protezione civile</t>
         </is>
       </c>
       <c r="M837" t="inlineStr">
@@ -54679,7 +54675,7 @@
       </c>
       <c r="N837" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="O837" s="4" t="inlineStr">
@@ -54691,12 +54687,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
+          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -54720,13 +54716,13 @@
         </is>
       </c>
       <c r="G838" s="2" t="n">
-        <v>77000</v>
+        <v>28800</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>46318</v>
+        <v>46304</v>
       </c>
       <c r="I838" s="3" t="n">
-        <v>46356</v>
+        <v>46361</v>
       </c>
       <c r="K838" t="inlineStr">
         <is>
@@ -54735,7 +54731,7 @@
       </c>
       <c r="L838" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio | Turismo</t>
+          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
         </is>
       </c>
       <c r="M838" t="inlineStr">
@@ -54745,7 +54741,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
+          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
         </is>
       </c>
       <c r="O838" s="4" t="inlineStr">
@@ -54757,12 +54753,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Avviso di istanza di permesso di ricerca di risorse geotermiche presentata da SANTONI GROUP SRL - Area "GEO GARDA ENERGY".</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -54777,25 +54773,25 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F839" t="inlineStr"/>
       <c r="G839" s="2" t="n"/>
       <c r="H839" s="3" t="n">
-        <v>46161</v>
+        <v>46318</v>
       </c>
       <c r="I839" s="3" t="n">
-        <v>46356</v>
+        <v>46378</v>
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>FESR | Protezione civile</t>
+          <t>Ambiente | Attività produttive | Territorio</t>
         </is>
       </c>
       <c r="M839" t="inlineStr">
@@ -54805,7 +54801,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Si avvisa che la ditta SANTONI GROUP SRL, con sede a Dro (TN), ha presentato domanda di permesso di ricerca di risorse geotermiche in un’area individuata nei Comuni di Castelnuovo del Garda (VR) e Lazise del Garda (VR) da denominare "GEO GARDA ENERGY". Si allegano il testo dell' avviso e le coordinate geografiche dei vertici dell’area richiesta e la relativa individuazione cartografica . È fissato in 60 (sessanta) giorni, successivi e decorrenti dalla data di pubblicazione del presente avviso sul Bollettino Ufficiale della Regione Veneto, il termine per la presentazione di eventuali domande in concorrenza da inviare alla Direzione Difesa del…</t>
         </is>
       </c>
       <c r="O839" s="4" t="inlineStr">
@@ -54822,7 +54818,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
+          <t>Affidamento per partecipazione regionale a Fieracavalli 2026</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -54837,7 +54833,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -54846,22 +54842,22 @@
         </is>
       </c>
       <c r="G840" s="2" t="n">
-        <v>28800</v>
+        <v>196628</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>46304</v>
+        <v>46196</v>
       </c>
       <c r="I840" s="3" t="n">
-        <v>46361</v>
+        <v>46387</v>
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L840" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
@@ -54871,7 +54867,7 @@
       </c>
       <c r="N840" t="inlineStr">
         <is>
-          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
+          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica FIERACAVALLI 2026 (Verona, 5-8 novembre 2026). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BDNCP</t>
         </is>
       </c>
       <c r="O840" s="4" t="inlineStr">
@@ -54883,12 +54879,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Avviso di istanza di permesso di ricerca di risorse geotermiche presentata da SANTONI GROUP SRL - Area "GEO GARDA ENERGY".</t>
+          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell' Ufficio della Consigliera regionale di Parità, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL.</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -54898,30 +54894,36 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr"/>
-      <c r="G841" s="2" t="n"/>
+          <t>Direzione Lavoro</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="n">
+        <v>2440</v>
+      </c>
       <c r="H841" s="3" t="n">
-        <v>46318</v>
+        <v>46294</v>
       </c>
       <c r="I841" s="3" t="n">
-        <v>46378</v>
+        <v>46387</v>
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L841" t="inlineStr">
         <is>
-          <t>Ambiente | Attività produttive | Territorio</t>
+          <t>Lavoro | Pari opportunità</t>
         </is>
       </c>
       <c r="M841" t="inlineStr">
@@ -54931,7 +54933,7 @@
       </c>
       <c r="N841" t="inlineStr">
         <is>
-          <t>Si avvisa che la ditta SANTONI GROUP SRL, con sede a Dro (TN), ha presentato domanda di permesso di ricerca di risorse geotermiche in un’area individuata nei Comuni di Castelnuovo del Garda (VR) e Lazise del Garda (VR) da denominare "GEO GARDA ENERGY". Si allegano il testo dell' avviso e le coordinate geografiche dei vertici dell’area richiesta e la relativa individuazione cartografica . È fissato in 60 (sessanta) giorni, successivi e decorrenti dalla data di pubblicazione del presente avviso sul Bollettino Ufficiale della Regione Veneto, il termine per la presentazione di eventuali domande in concorrenza da inviare alla Direzione Difesa del…</t>
+          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell’Ufficio della Consigliera regionale di Parità, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL. CIG: BC8EFFBF04. Impegno di spesa e liquidazione. L.R. n. 39/2001.</t>
         </is>
       </c>
       <c r="O841" s="4" t="inlineStr">
@@ -54948,7 +54950,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Affidamento per partecipazione regionale a Fieracavalli 2026</t>
+          <t>FESTIVAL DELLE REGIONI 2026 (Firenze 25-27 ottobre 2026)</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -54963,7 +54965,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -54972,10 +54974,10 @@
         </is>
       </c>
       <c r="G842" s="2" t="n">
-        <v>196628</v>
+        <v>3500</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>46196</v>
+        <v>46304</v>
       </c>
       <c r="I842" s="3" t="n">
         <v>46387</v>
@@ -54997,7 +54999,7 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica FIERACAVALLI 2026 (Verona, 5-8 novembre 2026). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BDNCP</t>
+          <t>Programma regionale per la promozione dei Grandi Eventi. Integrazione mediante inserimento dell'evento"L'Italia delle Regioni" - Festival delle Regioni. Adempimenti procedurali ed organizzativi conseguenti. L.R. n. 7/2016,art. 18. 1. LINK APPTEL 2. LINK BDNCP</t>
         </is>
       </c>
       <c r="O842" s="4" t="inlineStr">
@@ -55014,7 +55016,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell' Ufficio della Consigliera regionale di Parità, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL.</t>
+          <t>Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -55024,7 +55026,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -55032,23 +55034,17 @@
           <t>Direzione Lavoro</t>
         </is>
       </c>
-      <c r="F843" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G843" s="2" t="n">
-        <v>2440</v>
-      </c>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" s="2" t="n"/>
       <c r="H843" s="3" t="n">
-        <v>46294</v>
+        <v>45611</v>
       </c>
       <c r="I843" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K843" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L843" t="inlineStr">
@@ -55063,7 +55059,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto del servizio di progettazione di azioni di promozione delle iniziative dell’Ufficio della Consigliera regionale di Parità, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023, a mezzo APPTEL. CIG: BC8EFFBF04. Impegno di spesa e liquidazione. L.R. n. 39/2001.</t>
+          <t>D.D.R. n. 651 del 12.11.2024 Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro. L.R. 15 febbraio 2022, n. 3, art. 3 e Regolamento regionale del 12 maggio 2023, n.3, art. 3 e ss. Per informazioni: https://bur.regione.veneto.it/BurvServices/pubblica/DettaglioAvviso.aspx?id=542832</t>
         </is>
       </c>
       <c r="O843" s="4" t="inlineStr">
@@ -55080,7 +55076,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>FESTIVAL DELLE REGIONI 2026 (Firenze 25-27 ottobre 2026)</t>
+          <t>Affidamento diretto all'Università di Padova del servizio di realizzazione di 6 percorsi formativi per docenti delle scuole dell'infanzia sui temi dell'accettazione e del rispetto dell'altro e delle differenze</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -55095,7 +55091,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -55104,22 +55100,22 @@
         </is>
       </c>
       <c r="G844" s="2" t="n">
-        <v>3500</v>
+        <v>24000</v>
       </c>
       <c r="H844" s="3" t="n">
-        <v>46304</v>
+        <v>46021</v>
       </c>
       <c r="I844" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K844" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Pari opportunità</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -55129,7 +55125,7 @@
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>Programma regionale per la promozione dei Grandi Eventi. Integrazione mediante inserimento dell'evento"L'Italia delle Regioni" - Festival delle Regioni. Adempimenti procedurali ed organizzativi conseguenti. L.R. n. 7/2016,art. 18. 1. LINK APPTEL 2. LINK BDNCP</t>
+          <t>Determina a contrarre e contestuale affidamento, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio di realizzazione di 6 percorsi formativi rivolti ai docenti delle scuole dell’infanzia sui temi dell’accettazione e del rispetto dell’altro e delle differenze a favore dell’Università di Padova - Dipartimento di Scienze politiche, giuridiche e studi internazionali, con sede in Padova (PD), Via del Santo n. 28, C.F.80006480281, P.I. 00742430283. CIG: B906940F21. CUP: H13C25000360002. Impegno di spesa e liquidazione sul bilancio per l’esercizio 2025. L.R. n. 39/2001.…</t>
         </is>
       </c>
       <c r="O844" s="4" t="inlineStr">
@@ -55146,7 +55142,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro</t>
+          <t>Servizio di esecuzione e gestione del Piano di comunicazione a sostegno del CSR Veneto 2023 - 2027 e della politica di sviluppo rurale post 2027. Approvazione del Piano annuale delle attività di comunicazione 2026.</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -55161,13 +55157,13 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
       <c r="G845" s="2" t="n"/>
       <c r="H845" s="3" t="n">
-        <v>45611</v>
+        <v>46105</v>
       </c>
       <c r="I845" s="3" t="n">
         <v>46387</v>
@@ -55179,7 +55175,7 @@
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>Lavoro | Pari opportunità</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -55189,7 +55185,7 @@
       </c>
       <c r="N845" t="inlineStr">
         <is>
-          <t>D.D.R. n. 651 del 12.11.2024 Avviso Pubblico per la presentazione delle domande di iscrizione al Registro regionale delle imprese virtuose in materia retributiva di genere e di pari opportunità nel lavoro. L.R. 15 febbraio 2022, n. 3, art. 3 e Regolamento regionale del 12 maggio 2023, n.3, art. 3 e ss. Per informazioni: https://bur.regione.veneto.it/BurvServices/pubblica/DettaglioAvviso.aspx?id=542832</t>
+          <t>Con il Decreto del Direttore della Direzione AdG FEASR Bonifica e Irrigazione n. 11739 del 09/03/2026, pubblicato sul BUR n. 35 del 24/03/2026, è stato approvato il Piano annuale delle azioni di comunicazione 2026 a sostegno del Complemento regionale per lo Sviluppo Rurale del Piano Strategico Nazionale della PAC 2023-2027 e della politica di sviluppo rurale post 2027, predisposto dal RTI Fondazione Giacomo Brodolini e PR Consulting aggiudicatario della gara in oggetto. I documenti sono disponibili negli allegati al presente avviso.</t>
         </is>
       </c>
       <c r="O845" s="4" t="inlineStr">
@@ -55206,7 +55202,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Affidamento diretto all'Università di Padova del servizio di realizzazione di 6 percorsi formativi per docenti delle scuole dell'infanzia sui temi dell'accettazione e del rispetto dell'altro e delle differenze</t>
+          <t>Affidamento all'Ente strumentale regionale Veneto Lavoro dell'attività di Assistenza tecnica per l'attuazione degli interventi a valere sul Programma Regionale Veneto FESR 2021-2027</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -55216,36 +55212,36 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Programmazione Unitaria</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G846" s="2" t="n">
-        <v>24000</v>
+        <v>5145000</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>46021</v>
+        <v>45275</v>
       </c>
       <c r="I846" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K846" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>Pari opportunità</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -55255,7 +55251,7 @@
       </c>
       <c r="N846" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento, ai sensi dell’art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio di realizzazione di 6 percorsi formativi rivolti ai docenti delle scuole dell’infanzia sui temi dell’accettazione e del rispetto dell’altro e delle differenze a favore dell’Università di Padova - Dipartimento di Scienze politiche, giuridiche e studi internazionali, con sede in Padova (PD), Via del Santo n. 28, C.F.80006480281, P.I. 00742430283. CIG: B906940F21. CUP: H13C25000360002. Impegno di spesa e liquidazione sul bilancio per l’esercizio 2025. L.R. n. 39/2001.…</t>
+          <t>PR Veneto FESR 2021-2027 - Affidamento all'Ente strumentale regionale Veneto Lavoro, secondo la procedura in house providing , dell'attività di Assistenza tecnica per l'attuazione del Programma Regionale Veneto FESR, per il ciclo di programmazione 2021-2027. Schema di contratto e Piano di Lavoro approvati con DDR n. 207 del 11/12/2023. Contratto sottoscritto il 14/12/2023 e il 19/12/2023</t>
         </is>
       </c>
       <c r="O846" s="4" t="inlineStr">
@@ -55272,7 +55268,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Servizio di esecuzione e gestione del Piano di comunicazione a sostegno del CSR Veneto 2023 - 2027 e della politica di sviluppo rurale post 2027. Approvazione del Piano annuale delle attività di comunicazione 2026.</t>
+          <t>Bando per concessione contributi a sostegno del sistema degli enti fieristici del Veneto. Approvazione graduatorie.</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -55282,30 +55278,36 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Direzione Adg Feasr Bonifica E Irrigazione</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr"/>
-      <c r="G847" s="2" t="n"/>
+          <t>Direzione Promozione Economica e Marketing Territoriale</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="n">
+        <v>594112</v>
+      </c>
       <c r="H847" s="3" t="n">
-        <v>46105</v>
+        <v>45422</v>
       </c>
       <c r="I847" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K847" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Attività produttive</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -55315,7 +55317,7 @@
       </c>
       <c r="N847" t="inlineStr">
         <is>
-          <t>Con il Decreto del Direttore della Direzione AdG FEASR Bonifica e Irrigazione n. 11739 del 09/03/2026, pubblicato sul BUR n. 35 del 24/03/2026, è stato approvato il Piano annuale delle azioni di comunicazione 2026 a sostegno del Complemento regionale per lo Sviluppo Rurale del Piano Strategico Nazionale della PAC 2023-2027 e della politica di sviluppo rurale post 2027, predisposto dal RTI Fondazione Giacomo Brodolini e PR Consulting aggiudicatario della gara in oggetto. I documenti sono disponibili negli allegati al presente avviso.</t>
+          <t>Approvazione delle graduatorie delle domande ammesse e dell’elenco delle domande non ammesse ai sensi dell’articolo 8 del “Bando per la concessione di contributi a fondo perduto per iniziative promozionali e di sostegno al sistema degli enti fieristici del Veneto”. DGR n. 1142 del 19 settembre 2023.</t>
         </is>
       </c>
       <c r="O847" s="4" t="inlineStr">
@@ -55332,7 +55334,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Affidamento all'Ente strumentale regionale Veneto Lavoro dell'attività di Assistenza tecnica per l'attuazione degli interventi a valere sul Programma Regionale Veneto FESR 2021-2027</t>
+          <t>Affidamento diretto, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI".</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -55342,36 +55344,36 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Direzione Programmazione Unitaria</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G848" s="2" t="n">
-        <v>5145000</v>
+        <v>95453</v>
       </c>
       <c r="H848" s="3" t="n">
-        <v>45275</v>
+        <v>45898</v>
       </c>
       <c r="I848" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K848" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>FESR</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -55381,7 +55383,7 @@
       </c>
       <c r="N848" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Affidamento all'Ente strumentale regionale Veneto Lavoro, secondo la procedura in house providing , dell'attività di Assistenza tecnica per l'attuazione del Programma Regionale Veneto FESR, per il ciclo di programmazione 2021-2027. Schema di contratto e Piano di Lavoro approvati con DDR n. 207 del 11/12/2023. Contratto sottoscritto il 14/12/2023 e il 19/12/2023</t>
+          <t>Aggiudicazione, impegno e contestuale accertamento del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI. Interventi di supporto alla genitorialità nella cura di bambini e bambine nei primi tre anni di vita", 2024-2026. PR Veneto FSE+ 2021-2027, Obiettivo Investimenti per l'occupazione e la crescita - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 3, Obiettivo specifico ESO4.11 (OS K del Reg. UE 2021/1057). Affidatario: TRIBE COMMUNICATION S.R.L.…</t>
         </is>
       </c>
       <c r="O848" s="4" t="inlineStr">
@@ -55398,7 +55400,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Bando per concessione contributi a sostegno del sistema degli enti fieristici del Veneto. Approvazione graduatorie.</t>
+          <t>Servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025 (CUP H13C25000260002, CIG B79E3376C2) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -55408,36 +55410,36 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Direzione Promozione Economica e Marketing Territoriale</t>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Avviso di contributo</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G849" s="2" t="n">
-        <v>594112</v>
+        <v>7600</v>
       </c>
       <c r="H849" s="3" t="n">
-        <v>45422</v>
+        <v>45877</v>
       </c>
       <c r="I849" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>Attività produttive</t>
+          <t>Protezione civile</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -55447,7 +55449,7 @@
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>Approvazione delle graduatorie delle domande ammesse e dell’elenco delle domande non ammesse ai sensi dell’articolo 8 del “Bando per la concessione di contributi a fondo perduto per iniziative promozionali e di sostegno al sistema degli enti fieristici del Veneto”. DGR n. 1142 del 19 settembre 2023.</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 394 del 18 luglio 2025 Affidamento diretto del servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H13C25000260002, CIG B79E3376C2. Impegno di spesa a favore di Fondazione CUOA Centro Universitario di Organizzazione aziendale. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B79E3376C2 PIATTAFORMA PVL: https://pubblicitalegale.anticorruzione.it/esiti/7d45ca46-f1c4-4a90-b59e-5e645ee63d00 PORTALE APPTEL:…</t>
         </is>
       </c>
       <c r="O849" s="4" t="inlineStr">
@@ -55464,7 +55466,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Affidamento diretto, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI".</t>
+          <t>Servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48 (CUP H19I25000500002, CIG B7456678EA) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -55474,36 +55476,36 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G850" s="2" t="n">
-        <v>95453</v>
+        <v>13100</v>
       </c>
       <c r="H850" s="3" t="n">
-        <v>45898</v>
+        <v>45849</v>
       </c>
       <c r="I850" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K850" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Sicurezza e polizia locale</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -55513,7 +55515,7 @@
       </c>
       <c r="N850" t="inlineStr">
         <is>
-          <t>Aggiudicazione, impegno e contestuale accertamento del servizio informativo e di promozione a supporto della genitorialità, nell'ambito dell'Avviso di cui all'Allegato A della DGR n. 115 del 12/02/2024 "1000 GIORNI DI NOI. Interventi di supporto alla genitorialità nella cura di bambini e bambine nei primi tre anni di vita", 2024-2026. PR Veneto FSE+ 2021-2027, Obiettivo Investimenti per l'occupazione e la crescita - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1/08/2022 - Priorità 3, Obiettivo specifico ESO4.11 (OS K del Reg. UE 2021/1057). Affidatario: TRIBE COMMUNICATION S.R.L.…</t>
+          <t>DECRTO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 342 del 13 giugno 2025 Affidamento diretto dei servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48, avviata con DGR 522/2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H19I25000500002, CIG B7456678EA. Impegno di spesa a favore di Linea Edizioni di Marra Lisa. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7456678EA PIATTAFORMA PVL:…</t>
         </is>
       </c>
       <c r="O850" s="4" t="inlineStr">
@@ -55530,7 +55532,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025 (CUP H13C25000260002, CIG B79E3376C2) - Esito della procedura di affidamento</t>
+          <t>Servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT" (CUP I13C23000400006, CIG B7F37D65B9) - Esito della procedura di affidamento</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -55554,10 +55556,10 @@
         </is>
       </c>
       <c r="G851" s="2" t="n">
-        <v>7600</v>
+        <v>3328</v>
       </c>
       <c r="H851" s="3" t="n">
-        <v>45877</v>
+        <v>45989</v>
       </c>
       <c r="I851" s="3" t="n">
         <v>46387</v>
@@ -55569,7 +55571,7 @@
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>Protezione civile</t>
+          <t>Europa | Protezione civile</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -55579,7 +55581,7 @@
       </c>
       <c r="N851" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 394 del 18 luglio 2025 Affidamento diretto del servizio di formazione rivolto ai volontari formatori di Protezione Civile della Regione del Veneto, annualità 2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H13C25000260002, CIG B79E3376C2. Impegno di spesa a favore di Fondazione CUOA Centro Universitario di Organizzazione aziendale. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B79E3376C2 PIATTAFORMA PVL: https://pubblicitalegale.anticorruzione.it/esiti/7d45ca46-f1c4-4a90-b59e-5e645ee63d00 PORTALE APPTEL:…</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 564 del 29 ottobre 2025 Affidamento diretto del servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT", ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP I13C23000400006, CIG B7F37D65B9. Impegno di spesa a favore del dott. Massimiliano Rosignoli. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7F37D65B9 PORTALE APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/esiti/codice/G02289</t>
         </is>
       </c>
       <c r="O851" s="4" t="inlineStr">
@@ -55596,7 +55598,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48 (CUP H19I25000500002, CIG B7456678EA) - Esito della procedura di affidamento</t>
+          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15.</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -55611,31 +55613,29 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+          <t>Area Sanità E Sociale</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G852" s="2" t="n">
-        <v>13100</v>
-      </c>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="n"/>
       <c r="H852" s="3" t="n">
-        <v>45849</v>
+        <v>46203</v>
       </c>
       <c r="I852" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K852" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L852" t="inlineStr">
         <is>
-          <t>Sicurezza e polizia locale</t>
+          <t>Sanità</t>
         </is>
       </c>
       <c r="M852" t="inlineStr">
@@ -55645,7 +55645,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>DECRTO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 342 del 13 giugno 2025 Affidamento diretto dei servizi di realizzazione di n. 3 convegni in materia di legalità e contrasto alla mafia previsti nella Programmazione attuativa 2025-2026 della Legge regionale 28 dicembre 2012, n. 48, avviata con DGR 522/2025, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP H19I25000500002, CIG B7456678EA. Impegno di spesa a favore di Linea Edizioni di Marra Lisa. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7456678EA PIATTAFORMA PVL:…</t>
+          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15. La richiesta di intervento sanitario per ragioni umanitarie a favore di cittadini di Paesi non appartenenti all’Unione Europea (cittadini extra UE), di cui al “Programma di assistenza sanitaria per ragioni umanitarie del Servizio Socio - Sanitario Regionale - anno 2026” deve essere presentata da un Ente o da un’Associazione senza scopo di lucro o da un Ente del Terzo Settore, avente sede nel territorio della Regione del Veneto. La richiesta di intervento…</t>
         </is>
       </c>
       <c r="O852" s="4" t="inlineStr">
@@ -55662,7 +55662,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT" (CUP I13C23000400006, CIG B7F37D65B9) - Esito della procedura di affidamento</t>
+          <t>Affidamento diretto a Veneto Innovazione per l'incarico di supporto tecnico/organizzativo per la realizzazione del Progetto "Caseus 2026".</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -55672,36 +55672,36 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G853" s="2" t="n">
-        <v>3328</v>
+        <v>299180</v>
       </c>
       <c r="H853" s="3" t="n">
-        <v>45989</v>
+        <v>46182</v>
       </c>
       <c r="I853" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>Europa | Protezione civile</t>
+          <t>Promozione enogastronomica</t>
         </is>
       </c>
       <c r="M853" t="inlineStr">
@@ -55711,7 +55711,7 @@
       </c>
       <c r="N853" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 564 del 29 ottobre 2025 Affidamento diretto del servizio di revisione e certificazione delle spese nell'ambito del Progetto "101122710 - rescEU CBRN-DSIM-IT", ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, CUP I13C23000400006, CIG B7F37D65B9. Impegno di spesa a favore del dott. Massimiliano Rosignoli. COLLEGAMENTO ALLA BDNCP: https://dettaglio-cig.anticorruzione.it/cig/B7F37D65B9 PORTALE APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/esiti/codice/G02289</t>
+          <t>Approvazione del Progetto “Caseus 2026” e individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate alla realizzazione del Progetto. Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario anno 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. Link PVL: https://pubblicitalegale.anticorruzione.it/avvisi/e04f949a-e871-4b11-96a6-cdba7ecc72a2?ricercaArchivio=false Link APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/procedure/codice/G03911 Link BDNCP:…</t>
         </is>
       </c>
       <c r="O853" s="4" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15.</t>
+          <t>Affidamento diretto a Veneto Innovazione S.p.A. per supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale ad iniziative promozionali in Italia nel corso del secondo semestre 2026.</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -55738,20 +55738,22 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Area Sanità E Sociale</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G854" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="n">
+        <v>505825</v>
+      </c>
       <c r="H854" s="3" t="n">
         <v>46203</v>
       </c>
@@ -55760,12 +55762,12 @@
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>Sanità</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
@@ -55775,7 +55777,7 @@
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>Programma di assistenza sanitaria per ragioni umanitarie presso le Aziende e gli Enti del Servizio Socio-Sanitario Regionale del Veneto - anno 2026. Legge n. 449/1997, art. 32, comma 15. La richiesta di intervento sanitario per ragioni umanitarie a favore di cittadini di Paesi non appartenenti all’Unione Europea (cittadini extra UE), di cui al “Programma di assistenza sanitaria per ragioni umanitarie del Servizio Socio - Sanitario Regionale - anno 2026” deve essere presentata da un Ente o da un’Associazione senza scopo di lucro o da un Ente del Terzo Settore, avente sede nel territorio della Regione del Veneto. La richiesta di intervento…</t>
+          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma in Italia nel corso del secondo semestre 2026. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. Link PVL : https://pubblicitalegale.anticorruzione.it/avvisi/7959d784-33f2-4a3d-8669-703b940a29ad?ricercaArchivio=false…</t>
         </is>
       </c>
       <c r="O854" s="4" t="inlineStr">
@@ -55792,7 +55794,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Veneto Innovazione per l'incarico di supporto tecnico/organizzativo per la realizzazione del Progetto "Caseus 2026".</t>
+          <t>EVENTI ESTERO 2° SEMESTRE 2026 - DDR N. 14931 DEL 19/06/2026</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -55807,7 +55809,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -55816,10 +55818,10 @@
         </is>
       </c>
       <c r="G855" s="2" t="n">
-        <v>299180</v>
+        <v>394109</v>
       </c>
       <c r="H855" s="3" t="n">
-        <v>46182</v>
+        <v>46227</v>
       </c>
       <c r="I855" s="3" t="n">
         <v>46387</v>
@@ -55831,7 +55833,7 @@
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M855" t="inlineStr">
@@ -55841,7 +55843,7 @@
       </c>
       <c r="N855" t="inlineStr">
         <is>
-          <t>Approvazione del Progetto “Caseus 2026” e individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate alla realizzazione del Progetto. Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario anno 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. Link PVL: https://pubblicitalegale.anticorruzione.it/avvisi/e04f949a-e871-4b11-96a6-cdba7ecc72a2?ricercaArchivio=false Link APPTEL: https://appaltitelematici.regione.veneto.it/PortaleAppalti/it/procedure/codice/G03911 Link BDNCP:…</t>
+          <t>Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l’incarico di supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma all’estero nel corso del secondo semestre 2026. DDR n. 14931 del 19 giugno 2026. DGR n. 423 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii LINK PUBBLICITA' A VALORE LEGALE. LINK APPTEL LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI</t>
         </is>
       </c>
       <c r="O855" s="4" t="inlineStr">
@@ -55858,7 +55860,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Veneto Innovazione S.p.A. per supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale ad iniziative promozionali in Italia nel corso del secondo semestre 2026.</t>
+          <t>Affidamento per la realizzazione del Progetto "Buy Veneto 2026"</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -55873,7 +55875,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
@@ -55882,10 +55884,10 @@
         </is>
       </c>
       <c r="G856" s="2" t="n">
-        <v>505825</v>
+        <v>491803</v>
       </c>
       <c r="H856" s="3" t="n">
-        <v>46203</v>
+        <v>46227</v>
       </c>
       <c r="I856" s="3" t="n">
         <v>46387</v>
@@ -55907,7 +55909,7 @@
       </c>
       <c r="N856" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di Parte Corrente 2026. Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma in Italia nel corso del secondo semestre 2026. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. Link PVL : https://pubblicitalegale.anticorruzione.it/avvisi/7959d784-33f2-4a3d-8669-703b940a29ad?ricercaArchivio=false…</t>
+          <t>Fondo Unico Nazionale del Turismo di parte corrente 2026. Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l'incarico di supporto tecnico/organizzativo finalizzato a garantire la realizzazione del Progetto “Buy Veneto 2026 - 25° Workshop Internazionale del Turismo in Veneto” (Venezia, 9-13 ottobre 2026). CUP: H78J26000040001. DDR n. 15143 del 25 giugno 2026. DGR n. 423 e n. 425 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BANCA…</t>
         </is>
       </c>
       <c r="O856" s="4" t="inlineStr">
@@ -55924,7 +55926,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>EVENTI ESTERO 2° SEMESTRE 2026 - DDR N. 14931 DEL 19/06/2026</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B898BECDB6 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -55939,7 +55941,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
@@ -55948,22 +55950,22 @@
         </is>
       </c>
       <c r="G857" s="2" t="n">
-        <v>394109</v>
+        <v>3861</v>
       </c>
       <c r="H857" s="3" t="n">
-        <v>46227</v>
+        <v>45993</v>
       </c>
       <c r="I857" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K857" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L857" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
         </is>
       </c>
       <c r="M857" t="inlineStr">
@@ -55973,7 +55975,7 @@
       </c>
       <c r="N857" t="inlineStr">
         <is>
-          <t>Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l’incarico di supporto tecnico ed organizzativo finalizzato a garantire la partecipazione regionale e l’organizzazione di iniziative promozionali in programma all’estero nel corso del secondo semestre 2026. DDR n. 14931 del 19 giugno 2026. DGR n. 423 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii LINK PUBBLICITA' A VALORE LEGALE. LINK APPTEL LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI</t>
+          <t>Con Decreto n. 71 del 10/10/2025 della Direzione Valutazioni Ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della D.G.R. n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Libreria Scientifica di Ragni Susanna (sede legale in via Giordano Bruno n. 54/b, Cap. 60127, Ancona, C.F. n. RGNSNN54A41A271P, P.IVA n. 00210380424) per la la somma di € 3.861,00= a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1,…</t>
         </is>
       </c>
       <c r="O857" s="4" t="inlineStr">
@@ -55990,7 +55992,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Affidamento per la realizzazione del Progetto "Buy Veneto 2026"</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8991C1DC6 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -56005,7 +56007,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
@@ -56014,22 +56016,22 @@
         </is>
       </c>
       <c r="G858" s="2" t="n">
-        <v>491803</v>
+        <v>1693</v>
       </c>
       <c r="H858" s="3" t="n">
-        <v>46227</v>
+        <v>45993</v>
       </c>
       <c r="I858" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K858" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L858" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
         </is>
       </c>
       <c r="M858" t="inlineStr">
@@ -56039,7 +56041,7 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>Fondo Unico Nazionale del Turismo di parte corrente 2026. Affidamento diretto e impegno di spesa a favore di Veneto Innovazione S.p.A. (C.F./P.I. 02568090274) per l'incarico di supporto tecnico/organizzativo finalizzato a garantire la realizzazione del Progetto “Buy Veneto 2026 - 25° Workshop Internazionale del Turismo in Veneto” (Venezia, 9-13 ottobre 2026). CUP: H78J26000040001. DDR n. 15143 del 25 giugno 2026. DGR n. 423 e n. 425 del 28 maggio 2026. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. Art. 1, comma 366, Legge 30 dicembre 2021, n. 234. LINK PUBBLICITA' A VALORE LEGALE LINK APPTEL LINK BANCA…</t>
+          <t>Con DDR n. 72 del 10/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con relativo impegno di spesa a favore della ditta ReteAmbiente S.r.l. (sede legale: via G. Bensi n. 12/5, Cap. 20152 - Milano, C.F./P.IVA n. 10966180969) per la somma di € 1.693,10=(IVA al 4% inclusa) quale corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36/2023, di un…</t>
         </is>
       </c>
       <c r="O858" s="4" t="inlineStr">
@@ -56056,7 +56058,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B898BECDB6 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B89C1DE219 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -56080,7 +56082,7 @@
         </is>
       </c>
       <c r="G859" s="2" t="n">
-        <v>3861</v>
+        <v>768</v>
       </c>
       <c r="H859" s="3" t="n">
         <v>45993</v>
@@ -56105,7 +56107,7 @@
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>Con Decreto n. 71 del 10/10/2025 della Direzione Valutazioni Ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della D.G.R. n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Libreria Scientifica di Ragni Susanna (sede legale in via Giordano Bruno n. 54/b, Cap. 60127, Ancona, C.F. n. RGNSNN54A41A271P, P.IVA n. 00210380424) per la la somma di € 3.861,00= a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1,…</t>
+          <t>Con DDR n. 73 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Maggioli Spa (sede legale in Sant’Arcangelo di Romagna - RN, Via del Carpino n. 8, Cap. 47822, C.F. n. 06188330150; P.IVA n. 02066400405) per la somma di € 768,60 (IVA al 22% inclusa pari a € 138,00) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art.…</t>
         </is>
       </c>
       <c r="O859" s="4" t="inlineStr">
@@ -56122,7 +56124,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8991C1DC6 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B89C143230 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -56146,7 +56148,7 @@
         </is>
       </c>
       <c r="G860" s="2" t="n">
-        <v>1693</v>
+        <v>280</v>
       </c>
       <c r="H860" s="3" t="n">
         <v>45993</v>
@@ -56171,7 +56173,7 @@
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>Con DDR n. 72 del 10/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con relativo impegno di spesa a favore della ditta ReteAmbiente S.r.l. (sede legale: via G. Bensi n. 12/5, Cap. 20152 - Milano, C.F./P.IVA n. 10966180969) per la somma di € 1.693,10=(IVA al 4% inclusa) quale corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36/2023, di un…</t>
+          <t>Con DDR n. 74 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è sttaa disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Legislazione Tecnica S.r.l. (sede legale: Via dell'Architettura 16, Cap. 00144 - Roma, C.F/P.IVA n. 05383391009) per la somma di € 280,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
         </is>
       </c>
       <c r="O860" s="4" t="inlineStr">
@@ -56188,7 +56190,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B89C1DE219 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEE61F8D - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -56212,7 +56214,7 @@
         </is>
       </c>
       <c r="G861" s="2" t="n">
-        <v>768</v>
+        <v>138</v>
       </c>
       <c r="H861" s="3" t="n">
         <v>45993</v>
@@ -56237,7 +56239,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>Con DDR n. 73 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Maggioli Spa (sede legale in Sant’Arcangelo di Romagna - RN, Via del Carpino n. 8, Cap. 47822, C.F. n. 06188330150; P.IVA n. 02066400405) per la somma di € 768,60 (IVA al 22% inclusa pari a € 138,00) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art.…</t>
+          <t>Con DDR n. 77 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Compagnia delle Foreste Srl (sede legale in via Pietro Aretino n. 8 - cap. 52100 Arezzo, P.IVA/C.F. n. 01726650516) per la somma di € 138,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
         </is>
       </c>
       <c r="O861" s="4" t="inlineStr">
@@ -56254,7 +56256,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B89C143230 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEDC0AB2 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -56278,7 +56280,7 @@
         </is>
       </c>
       <c r="G862" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="H862" s="3" t="n">
         <v>45993</v>
@@ -56303,7 +56305,7 @@
       </c>
       <c r="N862" t="inlineStr">
         <is>
-          <t>Con DDR n. 74 del 13/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è sttaa disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Legislazione Tecnica S.r.l. (sede legale: Via dell'Architettura 16, Cap. 00144 - Roma, C.F/P.IVA n. 05383391009) per la somma di € 280,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
+          <t>Con decreto n. 78 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Cosmo Giuridico Veneto s.a.s. di Marangon Ivonne (sede legale in via Centro n. 80, fraz. Priabona, Cap. 36030 - Monte di Malo (VI) – C.F./P.IVA 03775960242) per la somma di € 260,00=(IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi…</t>
         </is>
       </c>
       <c r="O862" s="4" t="inlineStr">
@@ -56320,7 +56322,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEE61F8D - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8AEB178B8 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -56344,7 +56346,7 @@
         </is>
       </c>
       <c r="G863" s="2" t="n">
-        <v>138</v>
+        <v>468</v>
       </c>
       <c r="H863" s="3" t="n">
         <v>45993</v>
@@ -56369,7 +56371,7 @@
       </c>
       <c r="N863" t="inlineStr">
         <is>
-          <t>Con DDR n. 77 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Compagnia delle Foreste Srl (sede legale in via Pietro Aretino n. 8 - cap. 52100 Arezzo, P.IVA/C.F. n. 01726650516) per la somma di € 138,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
+          <t>Con decreto n. 79 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Giuriconsult S.r.l. (sede legale in via Principe di Paternò n. 74/A, Cap. 90144 - Palermo, C.F./P.IVA. n. 05247730822) per la somma di € 468,00 (IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
         </is>
       </c>
       <c r="O863" s="4" t="inlineStr">
@@ -56386,7 +56388,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEDC0AB2 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8DE6999C3 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -56410,7 +56412,7 @@
         </is>
       </c>
       <c r="G864" s="2" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="H864" s="3" t="n">
         <v>45993</v>
@@ -56435,7 +56437,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>Con decreto n. 78 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Cosmo Giuridico Veneto s.a.s. di Marangon Ivonne (sede legale in via Centro n. 80, fraz. Priabona, Cap. 36030 - Monte di Malo (VI) – C.F./P.IVA 03775960242) per la somma di € 260,00=(IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi…</t>
+          <t>Con decreto n. 85 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore dell’Associazione Idrotecnica Italiana (sede legale: via di Santa Teresa 23, cap. 00198 – Roma, C.F. n. 02162200584 - P.IVA n. 01033911007) per la somma di € 150,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b), del…</t>
         </is>
       </c>
       <c r="O864" s="4" t="inlineStr">
@@ -56452,7 +56454,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8AEB178B8 - avviso aggiudicazione</t>
+          <t>AFFIDAMENTO DIRETTO CIG n. B8DE5D9B51 - avviso aggiudicazione</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -56476,7 +56478,7 @@
         </is>
       </c>
       <c r="G865" s="2" t="n">
-        <v>468</v>
+        <v>259</v>
       </c>
       <c r="H865" s="3" t="n">
         <v>45993</v>
@@ -56501,7 +56503,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>Con decreto n. 79 del 16/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore della ditta Giuriconsult S.r.l. (sede legale in via Principe di Paternò n. 74/A, Cap. 90144 - Palermo, C.F./P.IVA. n. 05247730822) per la somma di € 468,00 (IVA al 4% inclusa) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs.…</t>
+          <t>Con decreto n. 86 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale conm conseguente impegno di spesa a favore della ditta Tecniche Nuove Spa (sede legale in via Eritrea n. 21, Cap. 20157 - Milano, C.F./P.IVA n. 00753480151) per la somma di € 259,00=(IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
         </is>
       </c>
       <c r="O865" s="4" t="inlineStr">
@@ -56518,7 +56520,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8DE6999C3 - avviso aggiudicazione</t>
+          <t>Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 - Colli Asolani . Aggiudicazione</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -56533,7 +56535,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -56542,22 +56544,22 @@
         </is>
       </c>
       <c r="G866" s="2" t="n">
-        <v>150</v>
+        <v>40900</v>
       </c>
       <c r="H866" s="3" t="n">
-        <v>45993</v>
+        <v>46185</v>
       </c>
       <c r="I866" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K866" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L866" t="inlineStr">
         <is>
-          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
+          <t>Agricoltura e foreste | Ambiente | Territorio | Turismo</t>
         </is>
       </c>
       <c r="M866" t="inlineStr">
@@ -56567,7 +56569,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>Con decreto n. 85 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale con conseguente impegno di spesa a favore dell’Associazione Idrotecnica Italiana (sede legale: via di Santa Teresa 23, cap. 00198 – Roma, C.F. n. 02162200584 - P.IVA n. 01033911007) per la somma di € 150,00 (IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b), del…</t>
+          <t>Decreto a contrarre e di aggiudicazione definitiva ad efficacia condizionata del servizio di “Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 – Colli Asolani”, finanziato dal Programma Operativo PO.3 dell’Assistenza tecnica al CSR 2023-2027. DGR n. 453 del 18.04.2023 e DGR n. 100 del 04.02.2025. Regolamenti (UE) n. 2021/2115 e n. 2021/2116. CUP H79I25000970006. CIG BB81996235 Link alla BDNCP: https://dati.anticorruzione.it/superset/recaptcha/?cig=BB81996235&amp;next=dettaglio_cig .</t>
         </is>
       </c>
       <c r="O866" s="4" t="inlineStr">
@@ -56584,7 +56586,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>AFFIDAMENTO DIRETTO CIG n. B8DE5D9B51 - avviso aggiudicazione</t>
+          <t>Affidamento per la realizzaizone del Piano di Comunicazione 2026.</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -56599,7 +56601,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>Direzione Valutazioni Ambientali, Supporto Giuridico E Contenzioso</t>
+          <t>Direzione Turismo E Marketing Territoriale</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
@@ -56608,22 +56610,22 @@
         </is>
       </c>
       <c r="G867" s="2" t="n">
-        <v>259</v>
+        <v>869549</v>
       </c>
       <c r="H867" s="3" t="n">
-        <v>45993</v>
+        <v>46189</v>
       </c>
       <c r="I867" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K867" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L867" t="inlineStr">
         <is>
-          <t>Abbonamenti a Riviste e Giornali | Ambiente</t>
+          <t>Comunicazione e informazione | Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M867" t="inlineStr">
@@ -56633,7 +56635,7 @@
       </c>
       <c r="N867" t="inlineStr">
         <is>
-          <t>Con decreto n. 86 del 30/10/2025 della Direzione Valutazioni ambientali, Supporto giuridico e Contenzioso è stata disposta, in attuazione della DGR n. 188 del 25/02/2025, la copertura dell’obbligazione passiva giuridicamente perfezionata per debito commerciale conm conseguente impegno di spesa a favore della ditta Tecniche Nuove Spa (sede legale in via Eritrea n. 21, Cap. 20157 - Milano, C.F./P.IVA n. 00753480151) per la somma di € 259,00=(IVA assolta dall’editore) a titolo di corrispettivo per l’acquisizione, tramite procedura di affidamento su piattaforma di negoziazione “AppTEL” ai sensi dell’art. 50, co. 1, lett. b) del D.Lgs. n. 36 del…</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativi finalizzate alla realizzazione del Piano di comunicazione 2026 per la promozione turistica ed enogastronomica della Regione del Veneto. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. LINK Pubblicità a Valore Legale LINK APPTEL LINK Banca Dati Nazionale Contratti Pubblici</t>
         </is>
       </c>
       <c r="O867" s="4" t="inlineStr">
@@ -56650,7 +56652,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 - Colli Asolani . Aggiudicazione</t>
+          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024.</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -56660,36 +56662,34 @@
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
+          <t>Unità Organizzativa Dipendenze, terzo settore, nuove marginalità ed inclusione sociale</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G868" s="2" t="n">
-        <v>40900</v>
-      </c>
+          <t>Albi e registri</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="n"/>
       <c r="H868" s="3" t="n">
-        <v>46185</v>
+        <v>45674</v>
       </c>
       <c r="I868" s="3" t="n">
-        <v>46387</v>
+        <v>46407</v>
       </c>
       <c r="K868" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste | Ambiente | Territorio | Turismo</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="M868" t="inlineStr">
@@ -56699,7 +56699,7 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>Decreto a contrarre e di aggiudicazione definitiva ad efficacia condizionata del servizio di “Revisione della cartografia e aggiornamento del Formulario Standard del sito di Rete Natura 2000 IT3240002 – Colli Asolani”, finanziato dal Programma Operativo PO.3 dell’Assistenza tecnica al CSR 2023-2027. DGR n. 453 del 18.04.2023 e DGR n. 100 del 04.02.2025. Regolamenti (UE) n. 2021/2115 e n. 2021/2116. CUP H79I25000970006. CIG BB81996235 Link alla BDNCP: https://dati.anticorruzione.it/superset/recaptcha/?cig=BB81996235&amp;next=dettaglio_cig .</t>
+          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024. Modalità di presentazione e di inserimento delle richieste. N.B. Per procedere alla richiesta di inserimento nell'elenco, utilizzare il modello di cui all'Allegato B.</t>
         </is>
       </c>
       <c r="O868" s="4" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Affidamento per la realizzaizone del Piano di Comunicazione 2026.</t>
+          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della Regione del Veneto.</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -56726,36 +56726,28 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>Direzione Turismo E Marketing Territoriale</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr"/>
       <c r="G869" s="2" t="n">
-        <v>869549</v>
+        <v>2335000</v>
       </c>
       <c r="H869" s="3" t="n">
-        <v>46189</v>
+        <v>46220</v>
       </c>
       <c r="I869" s="3" t="n">
-        <v>46387</v>
-      </c>
-      <c r="K869" t="inlineStr">
-        <is>
-          <t>Ente Impresa</t>
-        </is>
-      </c>
+        <v>46446</v>
+      </c>
+      <c r="K869" t="inlineStr"/>
       <c r="L869" t="inlineStr">
         <is>
-          <t>Comunicazione e informazione | Promozione enogastronomica | Turismo</t>
+          <t>FESR | Protezione civile</t>
         </is>
       </c>
       <c r="M869" t="inlineStr">
@@ -56765,7 +56757,7 @@
       </c>
       <c r="N869" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativi finalizzate alla realizzazione del Piano di comunicazione 2026 per la promozione turistica ed enogastronomica della Regione del Veneto. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii. LINK Pubblicità a Valore Legale LINK APPTEL LINK Banca Dati Nazionale Contratti Pubblici</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 15409 del 30 giugno 2026 PR Veneto FESR 2021-2027. Priorità 2, Obiettivo Specifico 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della…</t>
         </is>
       </c>
       <c r="O869" s="4" t="inlineStr">
@@ -56782,7 +56774,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024.</t>
+          <t>Partecipazione regionale a Fruit Logistica 2027 (Berlino, 3/5 febbraio 2027)</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -56792,34 +56784,36 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Dipendenze, terzo settore, nuove marginalità ed inclusione sociale</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G870" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="n">
+        <v>116475</v>
+      </c>
       <c r="H870" s="3" t="n">
-        <v>45674</v>
+        <v>46259</v>
       </c>
       <c r="I870" s="3" t="n">
-        <v>46407</v>
+        <v>46446</v>
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>Sociale</t>
+          <t>Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
@@ -56829,7 +56823,7 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>Elenco regionale di idonei alla nomina a direttore di ATS di cui all'art. 10, comma 3 della L.R. n. 9/2024 e della DGR n. 1132 del 1 ottobre 2024. Modalità di presentazione e di inserimento delle richieste. N.B. Per procedere alla richiesta di inserimento nell'elenco, utilizzare il modello di cui all'Allegato B.</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “Fruit Logistica 2027” (Berlino, 3-5 febbraio 2027). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
         </is>
       </c>
       <c r="O870" s="4" t="inlineStr">
@@ -56846,7 +56840,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della Regione del Veneto.</t>
+          <t>PARTECIPAZIONE REGIONALE A "IGTM - International Golf Travel Market" (Cannes, 19-22 ottobre 2026)</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -56856,28 +56850,36 @@
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr"/>
+          <t>Direzione Turismo e Marketing Territoriale</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
       <c r="G871" s="2" t="n">
-        <v>2335000</v>
+        <v>5695</v>
       </c>
       <c r="H871" s="3" t="n">
-        <v>46220</v>
+        <v>46294</v>
       </c>
       <c r="I871" s="3" t="n">
         <v>46446</v>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Ente Impresa</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>FESR | Protezione civile</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M871" t="inlineStr">
@@ -56887,7 +56889,7 @@
       </c>
       <c r="N871" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 15409 del 30 giugno 2026 PR Veneto FESR 2021-2027. Priorità 2, Obiettivo Specifico 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione del quadro esigenziale e del documento di indirizzo alla progettazione per la costruzione di un nuovo magazzino da destinare allo stoccaggio di materiali, attrezzature e mezzi in dotazione alla Protezione Civile della…</t>
+          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “IGTM International Golf Travel Market (Cannes, 19-22 ottobre 2026)”. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
         </is>
       </c>
       <c r="O871" s="4" t="inlineStr">
@@ -56904,7 +56906,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Partecipazione regionale a Fruit Logistica 2027 (Berlino, 3/5 febbraio 2027)</t>
+          <t>Avviso di Avvenuta approvazione del progetto definitivo del 2° Lotto Funzionale Attraversamento di Vicenza</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -56914,36 +56916,30 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G872" s="2" t="n">
-        <v>116475</v>
-      </c>
+          <t>Direzione Infrastrutture E Trasporti</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" s="2" t="n"/>
       <c r="H872" s="3" t="n">
-        <v>46259</v>
+        <v>45127</v>
       </c>
       <c r="I872" s="3" t="n">
-        <v>46446</v>
+        <v>47014</v>
       </c>
       <c r="K872" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica | Turismo</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M872" t="inlineStr">
@@ -56953,7 +56949,7 @@
       </c>
       <c r="N872" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “Fruit Logistica 2027” (Berlino, 3-5 febbraio 2027). Approvazione dello schema di Convenzione. Programma Promozionale del Settore Primario 2026. DGR n. 242 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
+          <t>Soggetto aggiudicatore: R.F.I. S.p.A. Avviso di Avvenuta approvazione con Ordinanza commissariale n. 15 del 13.07.2023 del progetto definitivo del “2° Lotto Funzionale – Attraversamento di Vicenza” ai sensi del D.Lgs. 50/2016 e del DL 32/2019, convertito con modifiche nella L. 55/2019, nonché ai fini della dichiarazione di pubblica utilità ai sensi degli art. 10 e 12 del D.P.R. 327/2001 e s.m.i.</t>
         </is>
       </c>
       <c r="O872" s="4" t="inlineStr">
@@ -56970,7 +56966,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>PARTECIPAZIONE REGIONALE A "IGTM - International Golf Travel Market" (Cannes, 19-22 ottobre 2026)</t>
+          <t>Avviso di post informazione: determina a contrarre e affidamento a Edizioni l'Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d'uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023.</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -56980,36 +56976,34 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Agroalimentare</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G873" s="2" t="n">
-        <v>5695</v>
-      </c>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="n"/>
       <c r="H873" s="3" t="n">
-        <v>46294</v>
+        <v>45287</v>
       </c>
       <c r="I873" s="3" t="n">
-        <v>46446</v>
+        <v>47114</v>
       </c>
       <c r="K873" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L873" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M873" t="inlineStr">
@@ -57019,7 +57013,7 @@
       </c>
       <c r="N873" t="inlineStr">
         <is>
-          <t>Individuazione della Società in house Veneto Innovazione S.p.A. come soggetto gestore delle attività di supporto tecnico ed organizzativo finalizzate a garantire la partecipazione regionale alla manifestazione fieristica “IGTM International Golf Travel Market (Cannes, 19-22 ottobre 2026)”. Approvazione dello schema di Convenzione. Piano Turistico Annuale 2026. Legge regionale n. 11 del 14 giugno 2013 e ss.mm.ii.. 1. LINK PUBBLICITA' A VALORE LEGALE 2. LINK APPTEL 3. LINK BDNCP</t>
+          <t>Determina a contrarre e affidamento a Edizioni l’Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d’uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023. FORNITORE: Edizioni l’Informatore Agrario srl AGGIUDICATARIO: Edizioni l’Informatore Agrario srl TEMPI DI COMPLETAMENTO DEL CONTRATTO: 31.12.2027 NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n.…</t>
         </is>
       </c>
       <c r="O873" s="4" t="inlineStr">
@@ -57036,7 +57030,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Avviso di Avvenuta approvazione del progetto definitivo del 2° Lotto Funzionale Attraversamento di Vicenza</t>
+          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell'Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -57051,16 +57045,20 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture E Trasporti</t>
-        </is>
-      </c>
-      <c r="F874" t="inlineStr"/>
+          <t>Area Risorse Finanziarie, Strumentali, Ict Ed Enti Locali</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Albi e registri</t>
+        </is>
+      </c>
       <c r="G874" s="2" t="n"/>
       <c r="H874" s="3" t="n">
-        <v>45127</v>
+        <v>45450</v>
       </c>
       <c r="I874" s="3" t="n">
-        <v>47014</v>
+        <v>47118</v>
       </c>
       <c r="K874" t="inlineStr">
         <is>
@@ -57069,7 +57067,7 @@
       </c>
       <c r="L874" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M874" t="inlineStr">
@@ -57079,7 +57077,7 @@
       </c>
       <c r="N874" t="inlineStr">
         <is>
-          <t>Soggetto aggiudicatore: R.F.I. S.p.A. Avviso di Avvenuta approvazione con Ordinanza commissariale n. 15 del 13.07.2023 del progetto definitivo del “2° Lotto Funzionale – Attraversamento di Vicenza” ai sensi del D.Lgs. 50/2016 e del DL 32/2019, convertito con modifiche nella L. 55/2019, nonché ai fini della dichiarazione di pubblica utilità ai sensi degli art. 10 e 12 del D.P.R. 327/2001 e s.m.i.</t>
+          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell’Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
         </is>
       </c>
       <c r="O874" s="4" t="inlineStr">
@@ -57096,7 +57094,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: determina a contrarre e affidamento a Edizioni l'Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d'uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023.</t>
+          <t>Avviso di aggiudicazione della procedura di affidamento diretto</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -57111,29 +57109,27 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F875" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G875" s="2" t="n"/>
+          <t>Unità Organizzativa Genio Civile Vicenza</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" s="2" t="n">
+        <v>273</v>
+      </c>
       <c r="H875" s="3" t="n">
-        <v>45287</v>
+        <v>45517</v>
       </c>
       <c r="I875" s="3" t="n">
-        <v>47114</v>
+        <v>47349</v>
       </c>
       <c r="K875" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L875" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Ambiente | Territorio</t>
         </is>
       </c>
       <c r="M875" t="inlineStr">
@@ -57143,7 +57139,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>Determina a contrarre e affidamento a Edizioni l’Informatore Agrario srl della fornitura di un servizio continuativo da utilizzarsi tramite licenza d’uso in somministrazione telematica, corredata di assistenza help desk, relativo a un sistema per la determinazione dei prezzi massimi macchine ed attrezzature agricole. Art. 50, co 1, lett. b), del D.lgs 36/2023. FORNITORE: Edizioni l’Informatore Agrario srl AGGIUDICATARIO: Edizioni l’Informatore Agrario srl TEMPI DI COMPLETAMENTO DEL CONTRATTO: 31.12.2027 NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n.…</t>
+          <t>Lavori di manutenzione ordinaria dei caselli idraulici - anno 2024 - Affidamento diretto per allacciamento alla rete idrica</t>
         </is>
       </c>
       <c r="O875" s="4" t="inlineStr">
@@ -57160,7 +57156,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell'Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
+          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -57170,34 +57166,36 @@
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>Area Risorse Finanziarie, Strumentali, Ict Ed Enti Locali</t>
+          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G876" s="2" t="n"/>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="n">
+        <v>31000000</v>
+      </c>
       <c r="H876" s="3" t="n">
-        <v>45450</v>
+        <v>45629</v>
       </c>
       <c r="I876" s="3" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="K876" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L876" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="M876" t="inlineStr">
@@ -57207,7 +57205,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>Avviso pubblico plurimo per la formazione di un Elenco di professionisti da nominare nei Collegi Consultivi Tecnici per i contratti di servizi e forniture di importo pari o superiore ad un milione di euro, inseriti negli atti di programmazione della Regione del Veneto di competenza dell’Area Risorse Finanziarie, Strumentali, ICT ed Enti Locali Artt. 215-219 del D.Lgs. 36/2023, Allegato V.2 al D.Lgs. n. 36/2023 e DGR n. 261 del 21.3.2024.</t>
+          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
         </is>
       </c>
       <c r="O876" s="4" t="inlineStr">
@@ -57224,7 +57222,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Avviso di aggiudicazione della procedura di affidamento diretto</t>
+          <t>Avviso di post informazione: Decreto a contrarre mediante affidamento diretto e impegno di spesa per l'acquisto dell'abbonamento annuale per il 2025, cartaceo, alle riviste "Terra è vita" e "Informatore zootecnico" edite dalla Società New Business Media s.r.l. DGR n. 197/2024. Art. 50, co. 1, lett. b) del D.lgs n. 36/2023 e ss.mm.ii.</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -57239,27 +57237,27 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Vicenza</t>
+          <t>Direzione Agroalimentare</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
       <c r="G877" s="2" t="n">
-        <v>273</v>
+        <v>178</v>
       </c>
       <c r="H877" s="3" t="n">
-        <v>45517</v>
+        <v>45758</v>
       </c>
       <c r="I877" s="3" t="n">
-        <v>47349</v>
+        <v>47575</v>
       </c>
       <c r="K877" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L877" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M877" t="inlineStr">
@@ -57269,7 +57267,7 @@
       </c>
       <c r="N877" t="inlineStr">
         <is>
-          <t>Lavori di manutenzione ordinaria dei caselli idraulici - anno 2024 - Affidamento diretto per allacciamento alla rete idrica</t>
+          <t>Affidamento diretto per l’acquisto dell’abbonamento annuale per il 2025, cartaceo, alle riviste “Terra è vita” e “Informatore zootecnico” edite dalla Società New Business Media s.r.l. DGR n. 197/2024. CIG B6470B3C0B FORNITORE: Società New Business Media s.r.l. NORMATIVA DI RIFERIMENTO: Art. 50, co. 1, lett. b) e art. 85 del D.lgs n. 36/2023 e ss.mm.ii Link a BNDCP (Banca Nazionale dei Contratti Pubblici) ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la Sig.ra Daria Scaggiante al seguente numero di telefono: 041 2795548.</t>
         </is>
       </c>
       <c r="O877" s="4" t="inlineStr">
@@ -57286,7 +57284,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
+          <t>Avviso di post informazione: Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino - Ristrutturazione e riconversione vigneti e l'impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -57296,36 +57294,36 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
+          <t>Direzione Agroalimentare</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Avviso di contributo</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G878" s="2" t="n">
-        <v>31000000</v>
+        <v>19800</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>45629</v>
+        <v>45771</v>
       </c>
       <c r="I878" s="3" t="n">
-        <v>47483</v>
+        <v>47597</v>
       </c>
       <c r="K878" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L878" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M878" t="inlineStr">
@@ -57335,7 +57333,7 @@
       </c>
       <c r="N878" t="inlineStr">
         <is>
-          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
+          <t>Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino – Ristrutturazione e riconversione vigneti e l’impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023. CIG: B683E5105D CUP: H11J25000140008 FORNITORE: Bioprogramm srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n. 50/2016. IMPORTO: Euro 19.800,00 Link a BNDCP (Banca Nazionale dei Contratti Pubblici)…</t>
         </is>
       </c>
       <c r="O878" s="4" t="inlineStr">
@@ -57352,7 +57350,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Decreto a contrarre mediante affidamento diretto e impegno di spesa per l'acquisto dell'abbonamento annuale per il 2025, cartaceo, alle riviste "Terra è vita" e "Informatore zootecnico" edite dalla Società New Business Media s.r.l. DGR n. 197/2024. Art. 50, co. 1, lett. b) del D.lgs n. 36/2023 e ss.mm.ii.</t>
+          <t>Avviso di post informazione: Determina a contrarre e affidamento alla società Sikura Srl per la fornitura di dotazioni tecniche per i dipendenti della Direzione Agroalimentare addetti alle funzioni di vigilanza e controllo sulle produzioni agricole ed agroalimentari. CIG B900F94F3D. Art. 50, comma 1, lett. b) dello stesso D.Lgs. n. 36/2023.</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -57370,15 +57368,19 @@
           <t>Direzione Agroalimentare</t>
         </is>
       </c>
-      <c r="F879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
       <c r="G879" s="2" t="n">
-        <v>178</v>
+        <v>2005</v>
       </c>
       <c r="H879" s="3" t="n">
-        <v>45758</v>
+        <v>45989</v>
       </c>
       <c r="I879" s="3" t="n">
-        <v>47575</v>
+        <v>47818</v>
       </c>
       <c r="K879" t="inlineStr">
         <is>
@@ -57397,7 +57399,7 @@
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>Affidamento diretto per l’acquisto dell’abbonamento annuale per il 2025, cartaceo, alle riviste “Terra è vita” e “Informatore zootecnico” edite dalla Società New Business Media s.r.l. DGR n. 197/2024. CIG B6470B3C0B FORNITORE: Società New Business Media s.r.l. NORMATIVA DI RIFERIMENTO: Art. 50, co. 1, lett. b) e art. 85 del D.lgs n. 36/2023 e ss.mm.ii Link a BNDCP (Banca Nazionale dei Contratti Pubblici) ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la Sig.ra Daria Scaggiante al seguente numero di telefono: 041 2795548.</t>
+          <t>CIG: B900F94F3D FORNITORE: Sikura Srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’:Trasparenza ai fini del Codice dei Contratti. ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la dott.ssa Giada Solin al seguente numero di telefono: 041 2795540.</t>
         </is>
       </c>
       <c r="O879" s="4" t="inlineStr">
@@ -57414,7 +57416,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino - Ristrutturazione e riconversione vigneti e l'impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023</t>
+          <t>Avviso per la presentazione delle candidature all'iscrizione nell'elenco regionale degli Esperti per l'erogazione dei servizi di IVC. (In attuazione della DGR n. 627/2022, della DGR n. 352/2024 e della DGR n. 1302/2025)</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -57429,22 +57431,16 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G880" s="2" t="n">
-        <v>19800</v>
-      </c>
+          <t>Direzione Lavoro</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" s="2" t="n"/>
       <c r="H880" s="3" t="n">
-        <v>45771</v>
+        <v>46171</v>
       </c>
       <c r="I880" s="3" t="n">
-        <v>47597</v>
+        <v>47848</v>
       </c>
       <c r="K880" t="inlineStr">
         <is>
@@ -57453,7 +57449,7 @@
       </c>
       <c r="L880" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M880" t="inlineStr">
@@ -57463,7 +57459,7 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>Determina a contrarre e affidamento a Bioprogramm srl dello studio di valutazione preliminare - screening di prevalutazione (Livello I), inerente interventi previsti dal bando OCM Vino – Ristrutturazione e riconversione vigneti e l’impianto di oliveti e frutteti da realizzarsi sul territorio della Regione del Veneto. Art. 50, co 1, lett. b), del D.lgs 36/2023. CIG: B683E5105D CUP: H11J25000140008 FORNITORE: Bioprogramm srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’: Avviso pubblico ai sensi dell’art. 29 del D.Lgs. n. 50/2016. IMPORTO: Euro 19.800,00 Link a BNDCP (Banca Nazionale dei Contratti Pubblici)…</t>
+          <t>Con il DDR n. 108 del 19 marzo 2026 , in attuazione della DGR n. 1302 del 20 ottobre 2025, si definiscono i termini e le modalità di presentazione delle candidature a svolgere il ruolo di Esperto per l’erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link: https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. Maggiori informazioni alla pagina web: IVC - Individuazione Validazione e Certificazione delle…</t>
         </is>
       </c>
       <c r="O880" s="4" t="inlineStr">
@@ -57480,7 +57476,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Avviso di post informazione: Determina a contrarre e affidamento alla società Sikura Srl per la fornitura di dotazioni tecniche per i dipendenti della Direzione Agroalimentare addetti alle funzioni di vigilanza e controllo sulle produzioni agricole ed agroalimentari. CIG B900F94F3D. Art. 50, comma 1, lett. b) dello stesso D.Lgs. n. 36/2023.</t>
+          <t>Aggiornamento dell'Avviso per la presentazione delle domande di autorizzazione all'esercizio del ruolo di Soggetto Titolato IVC ed iscrizione nel relativo Elenco, approvato con DDR n. 522/2025 e recepimento delle modifiche introdotte dalla DGR n. 1302/2025</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -57495,22 +57491,16 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G881" s="2" t="n">
-        <v>2005</v>
-      </c>
+          <t>Direzione Lavoro</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" s="2" t="n"/>
       <c r="H881" s="3" t="n">
-        <v>45989</v>
+        <v>46182</v>
       </c>
       <c r="I881" s="3" t="n">
-        <v>47818</v>
+        <v>47848</v>
       </c>
       <c r="K881" t="inlineStr">
         <is>
@@ -57519,7 +57509,7 @@
       </c>
       <c r="L881" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M881" t="inlineStr">
@@ -57529,7 +57519,7 @@
       </c>
       <c r="N881" t="inlineStr">
         <is>
-          <t>CIG: B900F94F3D FORNITORE: Sikura Srl NORMATIVA DI RIFERIMENTO: Art. 50, co 1, lett. b), del D.lgs 36/2023. FINALITA’:Trasparenza ai fini del Codice dei Contratti. ULTERIORI INFORMAZIONI: Per ulteriori informazioni contattare la dott.ssa Giada Solin al seguente numero di telefono: 041 2795540.</t>
+          <t>Con il DDR 203 del 15/05/2026 , in attuazione della DGR n. 1302/2025, si approva l’aggiornamento dell’Avviso per la presentazione delle domande di autorizzazione all’esercizio del ruolo di Soggetto Titolato alla erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. L’accesso al sistema informativo IVC-Titolati è consentito esclusivamente ai soggetti…</t>
         </is>
       </c>
       <c r="O881" s="4" t="inlineStr">
@@ -57546,7 +57536,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Avviso per la presentazione delle candidature all'iscrizione nell'elenco regionale degli Esperti per l'erogazione dei servizi di IVC. (In attuazione della DGR n. 627/2022, della DGR n. 352/2024 e della DGR n. 1302/2025)</t>
+          <t>Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11.</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -57561,16 +57551,22 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr"/>
-      <c r="G882" s="2" t="n"/>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="n">
+        <v>1403511</v>
+      </c>
       <c r="H882" s="3" t="n">
-        <v>46171</v>
+        <v>45287</v>
       </c>
       <c r="I882" s="3" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="K882" t="inlineStr">
         <is>
@@ -57579,7 +57575,7 @@
       </c>
       <c r="L882" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M882" t="inlineStr">
@@ -57589,7 +57585,7 @@
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>Con il DDR n. 108 del 19 marzo 2026 , in attuazione della DGR n. 1302 del 20 ottobre 2025, si definiscono i termini e le modalità di presentazione delle candidature a svolgere il ruolo di Esperto per l’erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link: https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. Maggiori informazioni alla pagina web: IVC - Individuazione Validazione e Certificazione delle…</t>
+          <t>Estratto del Bando-Avviso-Finanziamento : Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11. Ente Affidante: Regione del Veneto – Direzione Agroalimentare Affidamento a Organismo in house: Veneto Innovazione Spa Settori di attività : Innovazione e promozione economica Precedente gestore di servizio: Veneto Sviluppo Spa Durata: dal 01/01/2024 al 31/12/2032 Importo complessivo dell’affidamento: 1.403.510,76 Provvedimento di affidamento dell’incarico: DGR n. 1600 del 19/12/2023…</t>
         </is>
       </c>
       <c r="O882" s="4" t="inlineStr">
@@ -57606,7 +57602,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Aggiornamento dell'Avviso per la presentazione delle domande di autorizzazione all'esercizio del ruolo di Soggetto Titolato IVC ed iscrizione nel relativo Elenco, approvato con DDR n. 522/2025 e recepimento delle modifiche introdotte dalla DGR n. 1302/2025</t>
+          <t>Decreto di istituzione dell'Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell'art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto "Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36".</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -57621,25 +57617,29 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F883" t="inlineStr"/>
+          <t>Direzione Acquisti, AA.GG. e SOS affidamento servizi e forniture</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Albi e registri</t>
+        </is>
+      </c>
       <c r="G883" s="2" t="n"/>
       <c r="H883" s="3" t="n">
-        <v>46182</v>
+        <v>45643</v>
       </c>
       <c r="I883" s="3" t="n">
-        <v>47848</v>
+        <v>73050</v>
       </c>
       <c r="K883" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L883" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M883" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>Con il DDR 203 del 15/05/2026 , in attuazione della DGR n. 1302/2025, si approva l’aggiornamento dell’Avviso per la presentazione delle domande di autorizzazione all’esercizio del ruolo di Soggetto Titolato alla erogazione dei Servizi di Individuazione, Validazione e Certificazione delle Competenze (IVC) ed iscrizione nel relativo Elenco. Le istanze devono essere presentate attraverso l’apposita piattaforma, disponibile al link https://formazione.regione.veneto.it/ivc/ Allo stesso link è possibile scaricare il manuale di utilizzo della piattaforma stessa. L’accesso al sistema informativo IVC-Titolati è consentito esclusivamente ai soggetti…</t>
+          <t>Decreto di istituzione dell’Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell’art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto “Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36”.</t>
         </is>
       </c>
       <c r="O883" s="4" t="inlineStr">
@@ -57666,7 +57666,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11.</t>
+          <t>Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -57681,31 +57681,29 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
+          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G884" s="2" t="n">
-        <v>1403511</v>
-      </c>
+          <t>Albi e registri</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="n"/>
       <c r="H884" s="3" t="n">
-        <v>45287</v>
+        <v>45401</v>
       </c>
       <c r="I884" s="3" t="n">
-        <v>48579</v>
+        <v>73050</v>
       </c>
       <c r="K884" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L884" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Attività produttive | Comunicazione e informazione | Demanio e patrimonio | Enti locali | Territorio</t>
         </is>
       </c>
       <c r="M884" t="inlineStr">
@@ -57715,7 +57713,7 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>Estratto del Bando-Avviso-Finanziamento : Accordo per l'affidamento a Veneto Innovazione S.p.A. della gestione di strumenti di finanza agevolata attivati tramite risorse regionali nel settore primario. D.lgs. n. 36/2023, art. 7 e L.R. n. 14/2023, art. 11. Ente Affidante: Regione del Veneto – Direzione Agroalimentare Affidamento a Organismo in house: Veneto Innovazione Spa Settori di attività : Innovazione e promozione economica Precedente gestore di servizio: Veneto Sviluppo Spa Durata: dal 01/01/2024 al 31/12/2032 Importo complessivo dell’affidamento: 1.403.510,76 Provvedimento di affidamento dell’incarico: DGR n. 1600 del 19/12/2023…</t>
+          <t>“Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto” (DGR n. 376 del 09/04/2024). L'Avviso è finalizzato alla rilevazione sul territorio regionale di “ opportunità di insediamento ”, costituite da aree edificabili ed edifici esistenti a vocazione produttiva, di proprietà pubblica o privata, da poter promuovere presso nuovi possibili investitori, anche esteri, attraverso iniziative dedicate e la loro valorizzazione in occasione di eventi di promozione su scala regionale, nazionale e internazionale. L'iniziativa è attuata in coerenza con il “Programma di attività per lo sviluppo di una…</t>
         </is>
       </c>
       <c r="O884" s="4" t="inlineStr">
@@ -57727,40 +57725,43 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Decreto di istituzione dell'Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell'art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto "Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36".</t>
+          <t>PR Veneto FESR 2021-27 · Azione 1.3.6 · Internazionalizzazione</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Avviso</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>Direzione Acquisti, AA.GG. e SOS affidamento servizi e forniture</t>
+          <t>Sviluppo Economico, Ricerca e Innovazione</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G885" s="2" t="n"/>
-      <c r="H885" s="3" t="n">
-        <v>45643</v>
-      </c>
-      <c r="I885" s="3" t="n">
-        <v>73050</v>
+          <t>Sovvenzione</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H885" s="3" t="n"/>
+      <c r="I885" s="3" t="n"/>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Dicembre 2026</t>
+        </is>
       </c>
       <c r="K885" t="inlineStr">
         <is>
@@ -57769,17 +57770,17 @@
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M885" t="inlineStr">
         <is>
-          <t>Portale Bandi Regione Veneto</t>
+          <t>Calendario inviti FESR 2021-27</t>
         </is>
       </c>
       <c r="N885" t="inlineStr">
         <is>
-          <t>Decreto di istituzione dell’Elenco di Operatori economici, che si propongono quali fornitori di beni e/o prestatori di servizi, esecutori di lavori o di incarichi professionali, ai sensi dell’art. 50 e Allegato II.1, del D.lgs. 36/2023, in attuazione della Deliberazione della Giunta Regionale n. 671 del 18 giugno 2024 avente ad oggetto “Indirizzi operativi per la gestione delle procedure semplificate di acquisizione di servizi, forniture e lavori sotto la soglia di rilevanza europea per le esigenze della Regione del Veneto. Artt. 45 - 55 e Allegati II.1 e II. 2 al Decreto Legislativo 31 marzo 2023 n. 36”.</t>
+          <t>1.3.6  Sostegno ai programmi di internazionalizzazione delle PMI — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
         </is>
       </c>
       <c r="O885" s="4" t="inlineStr">
@@ -57791,59 +57792,63 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto</t>
+          <t>PR Veneto FESR 2021-27 · Azione 1.3.11 Sub B) · Nuove imprese culturali</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Avviso</t>
+          <t>Previsto</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
+          <t>Cultura</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Albi e registri</t>
-        </is>
-      </c>
-      <c r="G886" s="2" t="n"/>
-      <c r="H886" s="3" t="n">
-        <v>45401</v>
-      </c>
-      <c r="I886" s="3" t="n">
-        <v>73050</v>
+          <t>Sovvenzione</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="n">
+        <v>4294000</v>
+      </c>
+      <c r="H886" s="3" t="n"/>
+      <c r="I886" s="3" t="n"/>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Gennaio 2027</t>
+        </is>
       </c>
       <c r="K886" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L886" t="inlineStr">
         <is>
-          <t>Attività produttive | Comunicazione e informazione | Demanio e patrimonio | Enti locali | Territorio</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M886" t="inlineStr">
         <is>
-          <t>Portale Bandi Regione Veneto</t>
+          <t>Calendario inviti FESR 2021-27</t>
         </is>
       </c>
       <c r="N886" t="inlineStr">
         <is>
-          <t>“Manifestazione di interesse finalizzata alla mappatura di opportunità insediative e di investimento in Veneto” (DGR n. 376 del 09/04/2024). L'Avviso è finalizzato alla rilevazione sul territorio regionale di “ opportunità di insediamento ”, costituite da aree edificabili ed edifici esistenti a vocazione produttiva, di proprietà pubblica o privata, da poter promuovere presso nuovi possibili investitori, anche esteri, attraverso iniziative dedicate e la loro valorizzazione in occasione di eventi di promozione su scala regionale, nazionale e internazionale. L'iniziativa è attuata in coerenza con il “Programma di attività per lo sviluppo di una…</t>
+          <t>1.3.11 Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo. 
+Sub azione A - Consolidamento di imprese esistenti — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
         </is>
       </c>
       <c r="O886" s="4" t="inlineStr">
@@ -57860,7 +57865,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 1.3.6 · Internazionalizzazione</t>
+          <t>PR Veneto FESR 2021-27 · Azione 2.5 · Resilienza Idrica</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -57875,7 +57880,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>Sviluppo Economico, Ricerca e Innovazione</t>
+          <t>Difesa del Suolo</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
@@ -57884,18 +57889,18 @@
         </is>
       </c>
       <c r="G887" s="2" t="n">
-        <v>3000000</v>
+        <v>28000000</v>
       </c>
       <c r="H887" s="3" t="n"/>
       <c r="I887" s="3" t="n"/>
       <c r="J887" t="inlineStr">
         <is>
-          <t>Dicembre 2026</t>
+          <t>Ottobre – Dicembre 2026</t>
         </is>
       </c>
       <c r="K887" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L887" t="inlineStr">
@@ -57910,7 +57915,7 @@
       </c>
       <c r="N887" t="inlineStr">
         <is>
-          <t>1.3.6  Sostegno ai programmi di internazionalizzazione delle PMI — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
+          <t>2.5. Resilienza Idrica — Promuovere l'accesso sicuro all’acqua, la sua gestione sostenibile, compresa la gestione integrata delle risorse idriche e la resilienza idrica Beneficiari: Regione del Veneto e/o Enti Pubblici Vigilati ai sensi dell’art. 22, c. 1, lett. a) del D.Lgs 33/2013 dalla medesima Regione del Veneto</t>
         </is>
       </c>
       <c r="O887" s="4" t="inlineStr">
@@ -57927,7 +57932,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 1.3.11 Sub B) · Nuove imprese culturali</t>
+          <t>PR Veneto FESR 2021-27 · Azione 2.1.1 · Housing sociale</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -57942,7 +57947,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Edilizia Residenziale Pubblica</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -57950,19 +57955,17 @@
           <t>Sovvenzione</t>
         </is>
       </c>
-      <c r="G888" s="2" t="n">
-        <v>4294000</v>
-      </c>
+      <c r="G888" s="2" t="n"/>
       <c r="H888" s="3" t="n"/>
       <c r="I888" s="3" t="n"/>
       <c r="J888" t="inlineStr">
         <is>
-          <t>Gennaio 2027</t>
+          <t>Settembre - Ottobre 2026</t>
         </is>
       </c>
       <c r="K888" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L888" t="inlineStr">
@@ -57977,8 +57980,7 @@
       </c>
       <c r="N888" t="inlineStr">
         <is>
-          <t>1.3.11 Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo. 
-Sub azione A - Consolidamento di imprese esistenti — Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR) Beneficiari: Micro, Piccole e Medie Imprese (PMI)</t>
+          <t xml:space="preserve"> Beneficiari: Nuclei familiari che si trovano in particolari situazioni di disagio economico e soggetti che, per motivi economici o sociali, non possono accedere a soluzioni abitative a condizioni di mercato</t>
         </is>
       </c>
       <c r="O888" s="4" t="inlineStr">
@@ -57995,7 +57997,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 2.5 · Resilienza Idrica</t>
+          <t>PR Veneto FESR 2021-27 · Azione 4.2.1 · Infrastrutture per formazione e istruzione</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -58010,7 +58012,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>Difesa del Suolo</t>
+          <t>Edilizia residenziale pubblica, ospedaliera e a finalità collettive</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
@@ -58019,13 +58021,13 @@
         </is>
       </c>
       <c r="G889" s="2" t="n">
-        <v>28000000</v>
+        <v>7063373</v>
       </c>
       <c r="H889" s="3" t="n"/>
       <c r="I889" s="3" t="n"/>
       <c r="J889" t="inlineStr">
         <is>
-          <t>Ottobre – Dicembre 2026</t>
+          <t>Ottobre 2026</t>
         </is>
       </c>
       <c r="K889" t="inlineStr">
@@ -58045,7 +58047,7 @@
       </c>
       <c r="N889" t="inlineStr">
         <is>
-          <t>2.5. Resilienza Idrica — Promuovere l'accesso sicuro all’acqua, la sua gestione sostenibile, compresa la gestione integrata delle risorse idriche e la resilienza idrica Beneficiari: Regione del Veneto e/o Enti Pubblici Vigilati ai sensi dell’art. 22, c. 1, lett. a) del D.Lgs 33/2013 dalla medesima Regione del Veneto</t>
+          <t>4.2.1 VET Innovation 2026 — Migliorare la parità di accesso a servizi di qualità e inclusivi nel campo dell'istruzione, della formazione e dell'apprendimento permanente mediante lo sviluppo di infrastrutture accessibili, anche promuovendo la resilienza dell'istruzione e della formazione online e a distanza (FESR) Beneficiari: Soggetti iscritti nell’elenco di cui alla L.R. n. 19 del 09/08/2002 (“Istituzione dell'elenco regionale degli organismi di formazione accreditati”) per l’ambito dell’Obbligo Formativo</t>
         </is>
       </c>
       <c r="O889" s="4" t="inlineStr">
@@ -58062,7 +58064,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 2.1.1 · Housing sociale</t>
+          <t>PR Veneto FSE+ 2021-27 · Politiche attive per soggetti svantaggiati</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -58077,20 +58079,22 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>Edilizia Residenziale Pubblica</t>
+          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Sovvenzione</t>
-        </is>
-      </c>
-      <c r="G890" s="2" t="n"/>
+          <t>Invito FSE+</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="n">
+        <v>10000000</v>
+      </c>
       <c r="H890" s="3" t="n"/>
       <c r="I890" s="3" t="n"/>
       <c r="J890" t="inlineStr">
         <is>
-          <t>Settembre - Ottobre 2026</t>
+          <t>nov-26</t>
         </is>
       </c>
       <c r="K890" t="inlineStr">
@@ -58100,17 +58104,17 @@
       </c>
       <c r="L890" t="inlineStr">
         <is>
-          <t>FESR</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="M890" t="inlineStr">
         <is>
-          <t>Calendario inviti FESR 2021-27</t>
+          <t>Calendario inviti FSE+</t>
         </is>
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beneficiari: Nuclei familiari che si trovano in particolari situazioni di disagio economico e soggetti che, per motivi economici o sociali, non possono accedere a soluzioni abitative a condizioni di mercato</t>
+          <t>Incentivare l’inclusione attiva, per promuovere le pari opportunità, la non discriminazione e la partecipazione attiva, e migliorare l’occupabilità, in particolare dei gruppi svantaggiati Richiedenti: Soggetti accreditati Formazione superiore Soggetti accreditati Servizi per il lavoro</t>
         </is>
       </c>
       <c r="O890" s="4" t="inlineStr">
@@ -58127,7 +58131,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-27 · Azione 4.2.1 · Infrastrutture per formazione e istruzione</t>
+          <t>PR Veneto FSE+ 2021-27 · Borse Universitarie STEM</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -58142,22 +58146,22 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>Edilizia residenziale pubblica, ospedaliera e a finalità collettive</t>
+          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>Sovvenzione</t>
+          <t>Invito FSE+</t>
         </is>
       </c>
       <c r="G891" s="2" t="n">
-        <v>7063373</v>
+        <v>10000000</v>
       </c>
       <c r="H891" s="3" t="n"/>
       <c r="I891" s="3" t="n"/>
       <c r="J891" t="inlineStr">
         <is>
-          <t>Ottobre 2026</t>
+          <t>nov-26</t>
         </is>
       </c>
       <c r="K891" t="inlineStr">
@@ -58167,17 +58171,17 @@
       </c>
       <c r="L891" t="inlineStr">
         <is>
-          <t>FESR</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="M891" t="inlineStr">
         <is>
-          <t>Calendario inviti FESR 2021-27</t>
+          <t>Calendario inviti FSE+</t>
         </is>
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>4.2.1 VET Innovation 2026 — Migliorare la parità di accesso a servizi di qualità e inclusivi nel campo dell'istruzione, della formazione e dell'apprendimento permanente mediante lo sviluppo di infrastrutture accessibili, anche promuovendo la resilienza dell'istruzione e della formazione online e a distanza (FESR) Beneficiari: Soggetti iscritti nell’elenco di cui alla L.R. n. 19 del 09/08/2002 (“Istituzione dell'elenco regionale degli organismi di formazione accreditati”) per l’ambito dell’Obbligo Formativo</t>
+          <t>Migliorare l'accesso all'occupazione e le misure di attivazione per tutte le persone in cerca di lavoro, in particolare i giovani, soprattutto attraverso l'attuazione della garanzia per i giovani, i disoccupati di lungo periodo e i gruppi svantaggiati nel mercato del lavoro, nonché delle persone inattive, anche mediante la promozione del lavoro autonomo e dell'economia sociale Richiedenti: Destinatari finali</t>
         </is>
       </c>
       <c r="O891" s="4" t="inlineStr">
@@ -58194,7 +58198,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Politiche attive per soggetti svantaggiati</t>
+          <t>PR Veneto FSE+ 2021-27 · Formazione Continua</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -58218,13 +58222,13 @@
         </is>
       </c>
       <c r="G892" s="2" t="n">
-        <v>10000000</v>
+        <v>13000000</v>
       </c>
       <c r="H892" s="3" t="n"/>
       <c r="I892" s="3" t="n"/>
       <c r="J892" t="inlineStr">
         <is>
-          <t>nov-26</t>
+          <t>ott-26</t>
         </is>
       </c>
       <c r="K892" t="inlineStr">
@@ -58244,7 +58248,7 @@
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>Incentivare l’inclusione attiva, per promuovere le pari opportunità, la non discriminazione e la partecipazione attiva, e migliorare l’occupabilità, in particolare dei gruppi svantaggiati Richiedenti: Soggetti accreditati Formazione superiore Soggetti accreditati Servizi per il lavoro</t>
+          <t>Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure un ambiente di lavoro sano e adeguato che tenga conto dei rischi per la salute Richiedenti: Soggetti accreditati Formazione continua</t>
         </is>
       </c>
       <c r="O892" s="4" t="inlineStr">
@@ -58256,17 +58260,17 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Borse Universitarie STEM</t>
+          <t>Bando PR FESR 21-27 · Azione 1.2.1 · Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasform</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Bando</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -58276,42 +58280,35 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
+          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>Invito FSE+</t>
-        </is>
-      </c>
-      <c r="G893" s="2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="H893" s="3" t="n"/>
-      <c r="I893" s="3" t="n"/>
-      <c r="J893" t="inlineStr">
-        <is>
-          <t>nov-26</t>
-        </is>
-      </c>
-      <c r="K893" t="inlineStr">
-        <is>
-          <t>Ente</t>
-        </is>
-      </c>
+          <t>Digitalizzazione, Regione del Veneto</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="n"/>
+      <c r="H893" s="3" t="n">
+        <v>45300</v>
+      </c>
+      <c r="I893" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="K893" t="inlineStr"/>
       <c r="L893" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M893" t="inlineStr">
         <is>
-          <t>Calendario inviti FSE+</t>
+          <t>Veneto Coesione (Opportunità)</t>
         </is>
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>Migliorare l'accesso all'occupazione e le misure di attivazione per tutte le persone in cerca di lavoro, in particolare i giovani, soprattutto attraverso l'attuazione della garanzia per i giovani, i disoccupati di lungo periodo e i gruppi svantaggiati nel mercato del lavoro, nonché delle persone inattive, anche mediante la promozione del lavoro autonomo e dell'economia sociale Richiedenti: Destinatari finali</t>
+          <t>Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasformazione digitale per cittadini imprese e PA</t>
         </is>
       </c>
       <c r="O893" s="4" t="inlineStr">
@@ -58323,17 +58320,17 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>PR Veneto FSE+ 2021-27 · Formazione Continua</t>
+          <t>Bando PR FESR 21-27 · Azione 1.2.2 · Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei ser</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Bando</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -58343,42 +58340,35 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>Regione del Veneto · Autorità di Gestione FSE+</t>
+          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>Invito FSE+</t>
-        </is>
-      </c>
-      <c r="G894" s="2" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="H894" s="3" t="n"/>
-      <c r="I894" s="3" t="n"/>
-      <c r="J894" t="inlineStr">
-        <is>
-          <t>ott-26</t>
-        </is>
-      </c>
-      <c r="K894" t="inlineStr">
-        <is>
-          <t>Ente</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Digitalizzazione, Regione del Veneto </t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="n"/>
+      <c r="H894" s="3" t="n">
+        <v>45300</v>
+      </c>
+      <c r="I894" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="K894" t="inlineStr"/>
       <c r="L894" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>FESR</t>
         </is>
       </c>
       <c r="M894" t="inlineStr">
         <is>
-          <t>Calendario inviti FSE+</t>
+          <t>Veneto Coesione (Opportunità)</t>
         </is>
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure un ambiente di lavoro sano e adeguato che tenga conto dei rischi per la salute Richiedenti: Soggetti accreditati Formazione continua</t>
+          <t>Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei servizi della pubblica amministrazione a vantaggio di cittadini e imprese ed in continuità</t>
         </is>
       </c>
       <c r="O894" s="4" t="inlineStr">
@@ -58395,7 +58385,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.2.1 · Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasform</t>
+          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Region</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -58415,15 +58405,15 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Digitalizzazione, Regione del Veneto</t>
+          <t>Accesso al credito, PMI</t>
         </is>
       </c>
       <c r="G895" s="2" t="n"/>
       <c r="H895" s="3" t="n">
-        <v>45300</v>
+        <v>45846</v>
       </c>
       <c r="I895" s="3" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="K895" t="inlineStr"/>
       <c r="L895" t="inlineStr">
@@ -58438,7 +58428,7 @@
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>Bando a titolarità regionale, Sostenere e cogliere le opportunità della trasformazione digitale per cittadini imprese e PA</t>
+          <t>Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Regionale Liquidità - Azione 1.3.3</t>
         </is>
       </c>
       <c r="O895" s="4" t="inlineStr">
@@ -58455,7 +58445,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.2.2 · Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei ser</t>
+          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -58475,15 +58465,15 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digitalizzazione, Regione del Veneto </t>
+          <t>Accesso al credito, PMI</t>
         </is>
       </c>
       <c r="G896" s="2" t="n"/>
       <c r="H896" s="3" t="n">
-        <v>45300</v>
+        <v>45835</v>
       </c>
       <c r="I896" s="3" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="K896" t="inlineStr"/>
       <c r="L896" t="inlineStr">
@@ -58498,7 +58488,7 @@
       </c>
       <c r="N896" t="inlineStr">
         <is>
-          <t>Bando a titolarità regionale, Sostenere e sviluppare la digitalizzazione dei servizi della pubblica amministrazione a vantaggio di cittadini e imprese ed in continuità</t>
+          <t>Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
         </is>
       </c>
       <c r="O896" s="4" t="inlineStr">
@@ -58515,7 +58505,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Region</t>
+          <t>Progetti PR FESR 21-27 · Azione 2.4.3 · Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi d</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -58535,12 +58525,12 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>Accesso al credito, PMI</t>
+          <t>Bacini e opere di laminazione, Regione del Veneto</t>
         </is>
       </c>
       <c r="G897" s="2" t="n"/>
       <c r="H897" s="3" t="n">
-        <v>45846</v>
+        <v>45535</v>
       </c>
       <c r="I897" s="3" t="n">
         <v>46752</v>
@@ -58558,7 +58548,7 @@
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>Fondo di garanzia per le piccole e medie imprese - Sezione FESR del Fondo Regionale Liquidità - Azione 1.3.3</t>
+          <t>Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi della rete idrografica principale anche con ealizzazione di opere di laminazione delle piene, Approvazione elenco degli interventi da finanziare.</t>
         </is>
       </c>
       <c r="O897" s="4" t="inlineStr">
@@ -58567,128 +58557,8 @@
         </is>
       </c>
     </row>
-    <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t>Aperto</t>
-        </is>
-      </c>
-      <c r="B898" t="inlineStr">
-        <is>
-          <t>Bando PR FESR 21-27 · Azione 1.3.3 · Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
-        </is>
-      </c>
-      <c r="C898" t="inlineStr">
-        <is>
-          <t>Bando</t>
-        </is>
-      </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>Finanziamenti</t>
-        </is>
-      </c>
-      <c r="E898" t="inlineStr">
-        <is>
-          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
-        </is>
-      </c>
-      <c r="F898" t="inlineStr">
-        <is>
-          <t>Accesso al credito, PMI</t>
-        </is>
-      </c>
-      <c r="G898" s="2" t="n"/>
-      <c r="H898" s="3" t="n">
-        <v>45835</v>
-      </c>
-      <c r="I898" s="3" t="n">
-        <v>46752</v>
-      </c>
-      <c r="K898" t="inlineStr"/>
-      <c r="L898" t="inlineStr">
-        <is>
-          <t>FESR</t>
-        </is>
-      </c>
-      <c r="M898" t="inlineStr">
-        <is>
-          <t>Veneto Coesione (Opportunità)</t>
-        </is>
-      </c>
-      <c r="N898" t="inlineStr">
-        <is>
-          <t>Fondo di garanzia per le piccole e medie imprese - Sezione overbooking</t>
-        </is>
-      </c>
-      <c r="O898" s="4" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t>Aperto</t>
-        </is>
-      </c>
-      <c r="B899" t="inlineStr">
-        <is>
-          <t>Progetti PR FESR 21-27 · Azione 2.4.3 · Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi d</t>
-        </is>
-      </c>
-      <c r="C899" t="inlineStr">
-        <is>
-          <t>Bando</t>
-        </is>
-      </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>Finanziamenti</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>Regione del Veneto · Programmazione FESR/FSE+</t>
-        </is>
-      </c>
-      <c r="F899" t="inlineStr">
-        <is>
-          <t>Bacini e opere di laminazione, Regione del Veneto</t>
-        </is>
-      </c>
-      <c r="G899" s="2" t="n"/>
-      <c r="H899" s="3" t="n">
-        <v>45535</v>
-      </c>
-      <c r="I899" s="3" t="n">
-        <v>46752</v>
-      </c>
-      <c r="K899" t="inlineStr"/>
-      <c r="L899" t="inlineStr">
-        <is>
-          <t>FESR</t>
-        </is>
-      </c>
-      <c r="M899" t="inlineStr">
-        <is>
-          <t>Veneto Coesione (Opportunità)</t>
-        </is>
-      </c>
-      <c r="N899" t="inlineStr">
-        <is>
-          <t>Progetti a titolarità regionale, Interventi strutturali e strategici sui fiumi della rete idrografica principale anche con ealizzazione di opere di laminazione delle piene, Approvazione elenco degli interventi da finanziare.</t>
-        </is>
-      </c>
-      <c r="O899" s="4" t="inlineStr">
-        <is>
-          <t>Apri</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O899"/>
+  <autoFilter ref="A1:O897"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -59586,8 +59456,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O895" r:id="rId894"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O896" r:id="rId895"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O897" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O898" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O899" r:id="rId898"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59626,7 +59494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:54</t>
+          <t>2026-10-29 11:11</t>
         </is>
       </c>
     </row>
@@ -59637,7 +59505,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="4">
@@ -59648,7 +59516,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/docs/data/bandi_veneto.xlsx
+++ b/docs/data/bandi_veneto.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bando a sostegno di interventi di rimozione e smaltimento di rifiuti</t>
+          <t>Approvazione del Programma regionale di tutela delle denominazioni di origine e delle indicazioni geografiche protette dei vini e dei prodotti agroalimentari veneti, disciplinate dal Regolamento (UE) n. 2024/1143, nonché del bando per l'accesso ai contributi a sostegno delle attività di tutela, annualità 2026, realizzate dai Consorzi di tutela riconosciuti. Legge regionale 5 aprile 2013, n. 3, art. 28.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
+          <t>Direzione Agroalimentare</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>577000</v>
+        <v>100000</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>46308</v>
+        <v>46276</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ambiente</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BANDO RIVOLTO ALLE AMMINISTRAZIONI COMUNALI DEL VENETO CHE INDIVIDUA LE MODALITÀ DI ASSEGNAZIONE DI CONTRIBUTI DERIVANTI DAL TRASFERIMENTO DI COMPETENZE DI CUI AL D.LGS 31 MARZO 1998, N. 112, A SOSTEGNO DI INTERVENTI DI RIMOZIONE E SMALTIMENTO DI RIFIUTI.</t>
+          <t>Approvazione del Programma regionale di tutela delle denominazioni di origine e delle indicazioni geografiche protette dei vini e dei prodotti agroalimentari veneti, disciplinate dal Regolamento (UE) n. 2024/1143, nonché del bando per l'accesso ai contributi a sostegno delle attività di tutela, annualità 2026, realizzate dai Consorzi di tutela riconosciuti. Legge regionale 5 aprile 2013, n. 3, art. 28. NORMATIVA DI RIFERIMENTO: Regolamento (UE) n.2024/1143, Legge regionale 5 aprile 2013, n. 3, art. 28. DGR 953 dell'11 settembre 2026 FINALITA’: Sostegno nelle azioni di tutela e vigilanza realizzate dai Consorzi nell’ambito dei rispettivi…</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Approvazione del Programma regionale di tutela delle denominazioni di origine e delle indicazioni geografiche protette dei vini e dei prodotti agroalimentari veneti, disciplinate dal Regolamento (UE) n. 2024/1143, nonché del bando per l'accesso ai contributi a sostegno delle attività di tutela, annualità 2026, realizzate dai Consorzi di tutela riconosciuti. Legge regionale 5 aprile 2013, n. 3, art. 28.</t>
+          <t>Iniziativa fieristica finalizzata alla promozione e vendita dei prodotti del commercio equo e solidale - Anno 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,31 +621,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Contributo</t>
-        </is>
-      </c>
+          <t>Unità Organizzativa Cooperazione Internazionale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" s="2" t="n">
-        <v>100000</v>
+        <v>25000</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>46276</v>
+        <v>46297</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Relazioni internazionali</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -655,7 +651,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Approvazione del Programma regionale di tutela delle denominazioni di origine e delle indicazioni geografiche protette dei vini e dei prodotti agroalimentari veneti, disciplinate dal Regolamento (UE) n. 2024/1143, nonché del bando per l'accesso ai contributi a sostegno delle attività di tutela, annualità 2026, realizzate dai Consorzi di tutela riconosciuti. Legge regionale 5 aprile 2013, n. 3, art. 28. NORMATIVA DI RIFERIMENTO: Regolamento (UE) n.2024/1143, Legge regionale 5 aprile 2013, n. 3, art. 28. DGR 953 dell'11 settembre 2026 FINALITA’: Sostegno nelle azioni di tutela e vigilanza realizzate dai Consorzi nell’ambito dei rispettivi…</t>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per la realizzazione, di un evento fieristico per la promozione del commercio equo e solidale prevista dall’art. 8 della L.R. 22 gennaio 2010, n. 6. DGR n. 1020 del 16 settembre 2026: “Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile per il triennio 2026-2028. Programmazione degli interventi per l'annualità 2026. L.R. 21 giugno 2018, n. 21”. Azione 1) Interventi a supporto del commercio equo e solidale. L.R. 22 gennaio 2010, n. 6.</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -672,7 +668,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Iniziativa fieristica finalizzata alla promozione e vendita dei prodotti del commercio equo e solidale - Anno 2026</t>
+          <t>Formazione per la decarbonizzazione. Trasformare la sostenibilità energetica in un vantaggio competitivo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -687,27 +683,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Cooperazione Internazionale</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Direzione Formazione e Istruzione</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finanziamento</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="n">
-        <v>25000</v>
+        <v>13000000</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46327</v>
+        <v>46331</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Relazioni internazionali</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per la realizzazione, di un evento fieristico per la promozione del commercio equo e solidale prevista dall’art. 8 della L.R. 22 gennaio 2010, n. 6. DGR n. 1020 del 16 settembre 2026: “Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile per il triennio 2026-2028. Programmazione degli interventi per l'annualità 2026. L.R. 21 giugno 2018, n. 21”. Azione 1) Interventi a supporto del commercio equo e solidale. L.R. 22 gennaio 2010, n. 6.</t>
+          <t>Approvazione avviso pubblico “Formazione per la decarbonizzazione. Trasformare la sostenibilità energetica in un vantaggio competitivo” nell’ambito del PR Veneto FSE+ 2021-2027, Obiettivo “Investimenti per l'occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1.8.2022 - Priorità 6 "Competitività per la decarbonizzazione"- Obiettivo specifico d) ESO 4.4. “Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure ambienti di lavoro sani e adeguati che tengano conto dei rischi per la salute (FSE+)”, contenente criteri,…</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Formazione per la decarbonizzazione. Trasformare la sostenibilità energetica in un vantaggio competitivo</t>
+          <t>PR Veneto FESR 2121-2027 Interventi di recupero, promozione e valorizzazione delle aree interne attraverso interventi ad alto impatto culturale.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,31 +749,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Direzione Formazione e Istruzione</t>
+          <t>Direzione Cultura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finanziamento</t>
+          <t>Contributo</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13000000</v>
+        <v>5850000</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>46301</v>
+        <v>46210</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>46331</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Cittadino Ente</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Cultura</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Approvazione avviso pubblico “Formazione per la decarbonizzazione. Trasformare la sostenibilità energetica in un vantaggio competitivo” nell’ambito del PR Veneto FSE+ 2021-2027, Obiettivo “Investimenti per l'occupazione e la crescita” - Decisione di esecuzione della Commissione europea n. C(2022)5655 del 1.8.2022 - Priorità 6 "Competitività per la decarbonizzazione"- Obiettivo specifico d) ESO 4.4. “Promuovere l'adattamento dei lavoratori, delle imprese e degli imprenditori ai cambiamenti, un invecchiamento attivo e sano, come pure ambienti di lavoro sani e adeguati che tengano conto dei rischi per la salute (FSE+)”, contenente criteri,…</t>
+          <t>PR Veneto FESR 2021-2027, Priorità 5 Un'Europa più vicina ai cittadini attraverso la promozione dello sviluppo sostenibile e integrato di tutti i tipi di territorio e delle iniziative locali. Obiettivo Specifico 5.2 “Promuovere lo sviluppo sociale, economico e ambientale integrato e inclusivo a livello locale, la cultura, il patrimonio naturale, il turismo sostenibile e la sicurezza nelle aree diverse da quelle urbane. Azione 5.2.2 Interventi di recupero, promozione e valorizzazione delle aree interne attraverso interventi ad alto impatto culturale. Approvazione del bando “Interventi di recupero, promozione e valorizzazione delle aree…</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2121-2027 Interventi di recupero, promozione e valorizzazione delle aree interne attraverso interventi ad alto impatto culturale.</t>
+          <t>Progetti di diffusione del commercio equo e solidale - Anno 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Direzione Cultura</t>
+          <t>Unità Organizzativa Cooperazione Internazionale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5850000</v>
+        <v>85000</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>46210</v>
+        <v>46301</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>46331</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Relazioni internazionali</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027, Priorità 5 Un'Europa più vicina ai cittadini attraverso la promozione dello sviluppo sostenibile e integrato di tutti i tipi di territorio e delle iniziative locali. Obiettivo Specifico 5.2 “Promuovere lo sviluppo sociale, economico e ambientale integrato e inclusivo a livello locale, la cultura, il patrimonio naturale, il turismo sostenibile e la sicurezza nelle aree diverse da quelle urbane. Azione 5.2.2 Interventi di recupero, promozione e valorizzazione delle aree interne attraverso interventi ad alto impatto culturale. Approvazione del bando “Interventi di recupero, promozione e valorizzazione delle aree…</t>
+          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per i progetti di diffusione del commercio equo e solidale per l’anno 2026. DGR n. 1020 del 16 settembre 2026 “Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile per il triennio 2026-2028. Programmazione degli interventi per l'annualità 2026”. Azione 1) Interventi di sostegno del commercio equo e solidale. L.R. 22 gennaio 2010, n. 6.</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Progetti di diffusione del commercio equo e solidale - Anno 2026</t>
+          <t>Bando per la presentazione di progetti in materia di storia e cultura del Veneto - ASF 2026/2027</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Cooperazione Internazionale</t>
+          <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>85000</v>
+        <v>49500</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>46301</v>
+        <v>46280</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Relazioni internazionali</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Approvazione del Bando e della modulistica per la presentazione delle richieste di contributo per i progetti di diffusione del commercio equo e solidale per l’anno 2026. DGR n. 1020 del 16 settembre 2026 “Piano di attuazione degli interventi di promozione dei diritti umani e della cooperazione allo sviluppo sostenibile per il triennio 2026-2028. Programmazione degli interventi per l'annualità 2026”. Azione 1) Interventi di sostegno del commercio equo e solidale. L.R. 22 gennaio 2010, n. 6.</t>
+          <t>Sviluppo delle competenze in materia di storia e cultura del Veneto nelle Istituzioni scolastiche, statali e paritarie, del primo e del secondo ciclo di istruzione e nelle Scuole di Formazione Professionale del Veneto. Approvazione Avviso pubblico e Direttiva per la presentazione di progetti formativi da realizzare nell'anno scolastico-formativo 2026-2027. L.R. 31 marzo 2017, n. 8, art.2.</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>In scadenza</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bando per la presentazione di progetti in materia di storia e cultura del Veneto - ASF 2026/2027</t>
+          <t>Bando Melken prevenzione delle predazioni da lupo in malga con recinzioni elettrificate: analisi delle modifiche del pascolamento, del pascolo e degli episodi di attacco (FSCRI_RM_1750 beneficiari privati)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -947,31 +947,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Direzione Formazione e Istruzione</t>
+          <t>Direzione Foreste, Programmazione e Gestione Faunistico-Venatoria</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Contributo</t>
+          <t>Finanziamento</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>49500</v>
+        <v>1000000</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>46280</v>
+        <v>46248</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46332</v>
+        <v>46349</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Sviluppo delle competenze in materia di storia e cultura del Veneto nelle Istituzioni scolastiche, statali e paritarie, del primo e del secondo ciclo di istruzione e nelle Scuole di Formazione Professionale del Veneto. Approvazione Avviso pubblico e Direttiva per la presentazione di progetti formativi da realizzare nell'anno scolastico-formativo 2026-2027. L.R. 31 marzo 2017, n. 8, art.2.</t>
+          <t>Fondo Sviluppo e Coesione (FSC) 2021-2027. Accordo per la coesione tra il Governo e la Regione del Veneto - Area tematica 5 Ambiente e Risorse Naturali – Linea di intervento 05.05 Natura e Biodiversità. Bando “Melken prevenzione delle predazioni da lupo in malga con recinzioni elettrificate: analisi delle modifiche del pascolamento, del pascolo e degli episodi di attacco" (FSCRI_RM_1750 beneficiari privati) approvato con DGR n. 820 del 28/07/2026.</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bando Melken prevenzione delle predazioni da lupo in malga con recinzioni elettrificate: analisi delle modifiche del pascolamento, del pascolo e degli episodi di attacco (FSCRI_RM_1750 beneficiari privati)</t>
+          <t>Bando Melken. Nuovi metodi di prevenzione delle predazioni da lupo in malga (ID FSCRI_RI_418 beneficiari pubblici)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>46248</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Fondo Sviluppo e Coesione (FSC) 2021-2027. Accordo per la coesione tra il Governo e la Regione del Veneto - Area tematica 5 Ambiente e Risorse Naturali – Linea di intervento 05.05 Natura e Biodiversità. Bando “Melken prevenzione delle predazioni da lupo in malga con recinzioni elettrificate: analisi delle modifiche del pascolamento, del pascolo e degli episodi di attacco" (FSCRI_RM_1750 beneficiari privati) approvato con DGR n. 820 del 28/07/2026.</t>
+          <t>Fondo Sviluppo e Coesione (FSC) 2021-2027. Accordo per la coesione tra il Governo e la Regione del Veneto - Area tematica 5 Ambiente e Risorse Naturali – Linea di intervento 05.05 Natura e Biodiversità. Bando "Melken. Nuovi metodi di prevenzione delle predazioni da lupo in malga" (ID FSCRI_RI_418 beneficiari pubblici) approvato con DGR n. 820 del 28/07/2026.</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bando Melken. Nuovi metodi di prevenzione delle predazioni da lupo in malga (ID FSCRI_RI_418 beneficiari pubblici)</t>
+          <t>Azione 2.8.4 "TPL-Sistemi di Trasporto Intelligenti: bigliettazione unica e infomobilità". Approvazione del Bando per l'attuazione dell'Azione 2.8.4 "TPL - Sistemi di Trasporto intelligenti: bigliettazione unica e infomobilità", nell'ambito dello Sviluppo Urbano Sostenibile (SUS) rivolto alle Aziende titolari dei contratti di servizio per la gestione dei servizi minimi di TPL.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1079,31 +1079,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Direzione Foreste, Programmazione e Gestione Faunistico-Venatoria</t>
+          <t>Direzione Infrastrutture e Trasporti</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finanziamento</t>
+          <t>Contributo</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>400000</v>
+        <v>11075447</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>46248</v>
+        <v>46294</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46349</v>
+        <v>46359</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Fondo Sviluppo e Coesione (FSC) 2021-2027. Accordo per la coesione tra il Governo e la Regione del Veneto - Area tematica 5 Ambiente e Risorse Naturali – Linea di intervento 05.05 Natura e Biodiversità. Bando "Melken. Nuovi metodi di prevenzione delle predazioni da lupo in malga" (ID FSCRI_RI_418 beneficiari pubblici) approvato con DGR n. 820 del 28/07/2026.</t>
+          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 3 "Un'Europa più connessa attraverso la mobilità urbana sostenibile", OS 2.8 "Promuovere la mobilità urbana multimodale sostenibile quale parte della transizione verso un'economia a zero emissioni nette di carbonio", Azione 2.8.4 "TPL-Sistemi di Trasporto Intelligenti: bigliettazione unica e infomobilità". Approvazione del Bando per l'attuazione dell'Azione 2.8.4 "TPL - Sistemi di Trasporto intelligenti: bigliettazione unica e infomobilità", nell'ambito dello Sviluppo Urbano Sostenibile (SUS) rivolto alle Aziende titolari dei contratti di servizio per la gestione dei servizi minimi di TPL.</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Azione 2.8.4 "TPL-Sistemi di Trasporto Intelligenti: bigliettazione unica e infomobilità". Approvazione del Bando per l'attuazione dell'Azione 2.8.4 "TPL - Sistemi di Trasporto intelligenti: bigliettazione unica e infomobilità", nell'ambito dello Sviluppo Urbano Sostenibile (SUS) rivolto alle Aziende titolari dei contratti di servizio per la gestione dei servizi minimi di TPL.</t>
+          <t>Concorso - "Uso consapevole della rete internet e dei social media - 2^a edizione" A.S.F. 2026-2027</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture e Trasporti</t>
+          <t>Direzione Formazione e Istruzione</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1154,22 +1154,22 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11075447</v>
+        <v>7000</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>46294</v>
+        <v>46280</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 3 "Un'Europa più connessa attraverso la mobilità urbana sostenibile", OS 2.8 "Promuovere la mobilità urbana multimodale sostenibile quale parte della transizione verso un'economia a zero emissioni nette di carbonio", Azione 2.8.4 "TPL-Sistemi di Trasporto Intelligenti: bigliettazione unica e infomobilità". Approvazione del Bando per l'attuazione dell'Azione 2.8.4 "TPL - Sistemi di Trasporto intelligenti: bigliettazione unica e infomobilità", nell'ambito dello Sviluppo Urbano Sostenibile (SUS) rivolto alle Aziende titolari dei contratti di servizio per la gestione dei servizi minimi di TPL.</t>
+          <t>Approvazione dell'Avviso pubblico e della Direttiva relativi al concorso di idee "Uso consapevole della reteinternet e dei social media - 2a edizione" rivolto a studenti e studentesse delle Scuole primarie e secondarie di primo e secondo grado, statali e paritarie, e delle Scuole di Formazione Professionale del Veneto - Anno scolastico e formativo 2026/2027. L.R. n. 24/2024. DGR n. 75 del 27 gennaio 2025. DGR n. 778 dell'8 luglio 2025.</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concorso - "Uso consapevole della rete internet e dei social media - 2^a edizione" A.S.F. 2026-2027</t>
+          <t>Indizione della procedura a evidenza pubblica per il conferimento della concessione mineraria di acqua termale n. 158 denominata "GOETHE" in Comune di Pescantina (VR).</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1206,36 +1206,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Direzione Formazione e Istruzione</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contributo</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>7000</v>
-      </c>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="3" t="n">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46360</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Ente</t>
-        </is>
-      </c>
+        <v>46380</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Ambiente | Territorio</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1245,7 +1239,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Approvazione dell'Avviso pubblico e della Direttiva relativi al concorso di idee "Uso consapevole della reteinternet e dei social media - 2a edizione" rivolto a studenti e studentesse delle Scuole primarie e secondarie di primo e secondo grado, statali e paritarie, e delle Scuole di Formazione Professionale del Veneto - Anno scolastico e formativo 2026/2027. L.R. n. 24/2024. DGR n. 75 del 27 gennaio 2025. DGR n. 778 dell'8 luglio 2025.</t>
+          <t>Con DDR 18479 del 15/09/2026 è stata indetta la procedura a evidenza pubblica per il conferimento della concessione di acqua termale denominata “GOETHE” in Comune di Pescantina (VR) al fine di individuare l’operatore economico a cui assegnare la concessione. Inoltre è stato approvato il disciplinare di gara contenente i criteri per il conferimento ed è stato differito il termine di scadenza della concessione. Le domande potranno essere inviate entro il termine perentorio di 90 giorni dalla pubblicazione sul B.U.R. del Veneto del provvedimento di indizione della procedura ( Bur n. 129 del 25 settembre 2026 ).</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1262,7 +1256,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indizione della procedura a evidenza pubblica per il conferimento della concessione mineraria di acqua termale n. 158 denominata "GOETHE" in Comune di Pescantina (VR).</t>
+          <t>Proroga al 29/12/2026 dei termini di presentazione delle domande di saldo e di conclusione dei progetti ed integrazione del Bando approvato con DGR n. 338 del 29/03/2023</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1272,30 +1266,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+          <t>Unità Organizzativa Lavori Pubblici</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bando di gara</t>
+          <t>Contributo</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="3" t="n">
-        <v>46290</v>
+        <v>46233</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46380</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>46385</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio</t>
+          <t>Lavori pubblici</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1305,7 +1303,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Con DDR 18479 del 15/09/2026 è stata indetta la procedura a evidenza pubblica per il conferimento della concessione di acqua termale denominata “GOETHE” in Comune di Pescantina (VR) al fine di individuare l’operatore economico a cui assegnare la concessione. Inoltre è stato approvato il disciplinare di gara contenente i criteri per il conferimento ed è stato differito il termine di scadenza della concessione. Le domande potranno essere inviate entro il termine perentorio di 90 giorni dalla pubblicazione sul B.U.R. del Veneto del provvedimento di indizione della procedura ( Bur n. 129 del 25 settembre 2026 ).</t>
+          <t>Proroga dei termini di presentazione delle domande di saldo e di conclusione dei progetti. Programma Regionale Veneto FESR 2021-2027. Priorità 2 “Un’Europa resiliente, più verde e a basse emissioni di carbonio ma in transizione verso un’energia pulita ed equa, di investimenti verdi e blu, dell’economia circolare, dell’adattamento ai cambiamenti climatici e della loro mitigazione, della gestione e prevenzione dei rischi nonché della mobilità urbana sostenibile” , OS iv “Promuovere l’adattamento ai cambiamenti climatici, la prevenzione dei rischi di catastrofe, e la resilienza, prendendo in considerazione approcci ecosistemici”, Azione 2.4.2…</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1322,7 +1320,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Proroga al 29/12/2026 dei termini di presentazione delle domande di saldo e di conclusione dei progetti ed integrazione del Bando approvato con DGR n. 338 del 29/03/2023</t>
+          <t>Programma Garanzia di Occupabilità dei Lavoratori GOL - Adeguamento e ulteriore finanziamento dell'Avviso pubblico n. 5 per la presentazione dei progetti finalizzati all'attuazione del Percorso 5 Ricollocazione collettiva</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1337,29 +1335,31 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Lavori Pubblici</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contributo</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2991375</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>46233</v>
+        <v>45870</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46385</v>
+        <v>46387</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Lavori pubblici</t>
+          <t>Lavoro</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Proroga dei termini di presentazione delle domande di saldo e di conclusione dei progetti. Programma Regionale Veneto FESR 2021-2027. Priorità 2 “Un’Europa resiliente, più verde e a basse emissioni di carbonio ma in transizione verso un’energia pulita ed equa, di investimenti verdi e blu, dell’economia circolare, dell’adattamento ai cambiamenti climatici e della loro mitigazione, della gestione e prevenzione dei rischi nonché della mobilità urbana sostenibile” , OS iv “Promuovere l’adattamento ai cambiamenti climatici, la prevenzione dei rischi di catastrofe, e la resilienza, prendendo in considerazione approcci ecosistemici”, Azione 2.4.2…</t>
+          <t>Con Deliberazione n. 882 del 29 luglio 2025 si stanziano le risorse delle annualità 2023-2024-2025 del Programma GOL (PNRR) per l'attuazione del Percorso 5 Ricollocazione collettiva. Inoltre tale provvedimento aggiorna l'Avviso pubblico n. 5 di cui alla DGR n. 601/2023 di attuazione del Percorso 5. Le principali innovazioni riguardano nello specifico: introduzione di percorsi individuali o individualizzati di formazione per il rafforzamento delle competenze specifiche dei beneficiari; coinvolgimento di minimo 4 beneficiari nel progetto. Nel caso non fosse possibile coinvolgere tale numero minimo, potranno essere comunque presentati progetti…</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Programma Garanzia di Occupabilità dei Lavoratori GOL - Adeguamento e ulteriore finanziamento dell'Avviso pubblico n. 5 per la presentazione dei progetti finalizzati all'attuazione del Percorso 5 Ricollocazione collettiva</t>
+          <t>Bando Gemellaggi degli Enti territoriali locali 2026 - Approvazione dei risultati d'istruttoria e della relativa graduatoria delle istanze presentate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1401,31 +1401,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
+          <t>Direzione Relazioni Internazionali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finanziamento</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>2991375</v>
-      </c>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="3" t="n">
-        <v>45870</v>
+        <v>46304</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Lavoro</t>
+          <t>Relazioni internazionali</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1435,7 +1433,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Con Deliberazione n. 882 del 29 luglio 2025 si stanziano le risorse delle annualità 2023-2024-2025 del Programma GOL (PNRR) per l'attuazione del Percorso 5 Ricollocazione collettiva. Inoltre tale provvedimento aggiorna l'Avviso pubblico n. 5 di cui alla DGR n. 601/2023 di attuazione del Percorso 5. Le principali innovazioni riguardano nello specifico: introduzione di percorsi individuali o individualizzati di formazione per il rafforzamento delle competenze specifiche dei beneficiari; coinvolgimento di minimo 4 beneficiari nel progetto. Nel caso non fosse possibile coinvolgere tale numero minimo, potranno essere comunque presentati progetti…</t>
+          <t>Bando per la concessione di contributi a sostegno dei gemellaggi degli Enti territoriali locali del Veneto con omologhi esteri - Anno 2026. Legge regionale 12 marzo 2025, n. 3. D.G.R. n. 640 del 30 giugno 2026. Approvazione dei risultati d'istruttoria e della relativa graduatoria delle istanze presentate e assunzione dei relativi impegni di spesa.</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1452,7 +1450,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bando Gemellaggi degli Enti territoriali locali 2026 - Approvazione dei risultati d'istruttoria e della relativa graduatoria delle istanze presentate</t>
+          <t>PR FESR 2021-2027 Azione 1.3.7 Sostegno alla competitività del sistema commerciale e valorizzazione dei distretti del commercio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1467,7 +1465,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Direzione Relazioni Internazionali</t>
+          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1475,21 +1473,23 @@
           <t>Contributo</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="2" t="n">
+        <v>10000000</v>
+      </c>
       <c r="H16" s="3" t="n">
-        <v>46304</v>
+        <v>46192</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46387</v>
+        <v>46399</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Ente Impresa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Relazioni internazionali</t>
+          <t>Attività produttive | FESR</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Bando per la concessione di contributi a sostegno dei gemellaggi degli Enti territoriali locali del Veneto con omologhi esteri - Anno 2026. Legge regionale 12 marzo 2025, n. 3. D.G.R. n. 640 del 30 giugno 2026. Approvazione dei risultati d'istruttoria e della relativa graduatoria delle istanze presentate e assunzione dei relativi impegni di spesa.</t>
+          <t>Il Bando a supporto di progetti finalizzati alla rigenerazione urbana e alla ripresa economica nell'ambito dei distretti del commercio - Anno 2026 (DGR n. 484/2026) , dà attuazione al PR FESR 2021-2027 della Regione del Veneto , Obiettivo Specifico 1.3 “Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR)”, Azione 1.3.7 “Sostegno alla competitività del sistema commerciale e valorizzazione dei distretti del commercio”. Con il presente Bando la Regione del Veneto, in coerenza con le politiche attive indirizzate alla salvaguardia e alla…</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PR FESR 2021-2027 Azione 1.3.7 Sostegno alla competitività del sistema commerciale e valorizzazione dei distretti del commercio</t>
+          <t>Complemento regionale per lo sviluppo rurale 2023-2027 per il Veneto. Bando di apertura termini DGR n. 990/2026.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1531,31 +1531,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Contributo</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>10000000</v>
-      </c>
+          <t>Direzione Sviluppo Rurale e Agroambiente</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="3" t="n">
-        <v>46192</v>
+        <v>46297</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>46399</v>
+        <v>46402</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ente Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Attività produttive | FESR</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,7 +1559,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Il Bando a supporto di progetti finalizzati alla rigenerazione urbana e alla ripresa economica nell'ambito dei distretti del commercio - Anno 2026 (DGR n. 484/2026) , dà attuazione al PR FESR 2021-2027 della Regione del Veneto , Obiettivo Specifico 1.3 “Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi (FESR)”, Azione 1.3.7 “Sostegno alla competitività del sistema commerciale e valorizzazione dei distretti del commercio”. Con il presente Bando la Regione del Veneto, in coerenza con le politiche attive indirizzate alla salvaguardia e alla…</t>
+          <t>La Giunta regionale del Veneto, con deliberazione n. 990 del 15 settembre 2026 , ha approvato l’attivazione dei bandi relativi ai seguenti interventi del Complemento regionale per lo sviluppo rurale 2023-2027 (CSR) per il Veneto: I bandi sono pubblicati nel Bollettino Ufficiale della Regione del Veneto n. 135 del 2 ottobre 2026 . Testi dei bandi per intervento e azione SRD01 – Investimenti produttivi agricoli per la competitività delle aziende agricole – PG Risorse a bando: 20.000.000,00 Scadenza bando: 15 gennaio 2027 SRD02 – Investimenti produttivi agricoli per ambiente, clima e benessere animale Azione A Investimenti per la mitigazione…</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1582,7 +1576,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Complemento regionale per lo sviluppo rurale 2023-2027 per il Veneto. Bando di apertura termini DGR n. 990/2026.</t>
+          <t>PR Veneto FESR 2021-2027 Azione 1.3.11 sub A - Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo - Sub A "Consolidamento di imprese esistenti" - II edizione</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1597,25 +1591,31 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Direzione Sviluppo Rurale e Agroambiente</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" s="2" t="n"/>
+          <t>Direzione Cultura</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>4294000</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>46297</v>
+        <v>46287</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46402</v>
+        <v>46406</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Cultura</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>La Giunta regionale del Veneto, con deliberazione n. 990 del 15 settembre 2026 , ha approvato l’attivazione dei bandi relativi ai seguenti interventi del Complemento regionale per lo sviluppo rurale 2023-2027 (CSR) per il Veneto: I bandi sono pubblicati nel Bollettino Ufficiale della Regione del Veneto n. 135 del 2 ottobre 2026 . Testi dei bandi per intervento e azione SRD01 – Investimenti produttivi agricoli per la competitività delle aziende agricole – PG Risorse a bando: 20.000.000,00 Scadenza bando: 15 gennaio 2027 SRD02 – Investimenti produttivi agricoli per ambiente, clima e benessere animale Azione A Investimenti per la mitigazione…</t>
+          <t>PR Veneto FESR 2021-2027, Priorità 1 “Un'Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle tecnologie dell'informazione e della comunicazione (TIC)”. Obiettivo Specifico 1.3 “Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi. Azione 1.3.11 “Interventi a sostegno delle imprese culturali, creative e dell’audiovisivo. Sub A - Consolidamento di imprese esistenti”. Approvazione “Bando Azione 1.3.11 Interventi a sostegno delle imprese…</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 Azione 1.3.11 sub A - Interventi a sostegno delle imprese culturali, creative e dell'audiovisivo - Sub A "Consolidamento di imprese esistenti" - II edizione</t>
+          <t>Concorso per studenti - Commemorazione del Giorno del Ricordo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1657,31 +1657,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Direzione Cultura</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Contributo</t>
-        </is>
-      </c>
+          <t>Direzione Formazione e Istruzione</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" s="2" t="n">
-        <v>4294000</v>
+        <v>11000</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46287</v>
+        <v>46301</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46406</v>
+        <v>46416</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1691,7 +1687,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027, Priorità 1 “Un'Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle tecnologie dell'informazione e della comunicazione (TIC)”. Obiettivo Specifico 1.3 “Rafforzare la crescita sostenibile e la competitività delle PMI e la creazione di posti di lavoro nelle PMI, anche grazie agli investimenti produttivi. Azione 1.3.11 “Interventi a sostegno delle imprese culturali, creative e dell’audiovisivo. Sub A - Consolidamento di imprese esistenti”. Approvazione “Bando Azione 1.3.11 Interventi a sostegno delle imprese…</t>
+          <t>Commemorazione del Giorno del Ricordo. Approvazione Avviso pubblico e Direttiva relativi al concorso per i migliori elaborati realizzati dagli studenti delle Scuole primarie e secondarie di primo e secondo grado, statali e paritarie, e delle Scuole di Formazione Professionale del Veneto, sul tema "Gli italiani delle due sponde dell'Adriatico, a ottant'anni dal Trattato di Parigi, uniti sotto la comune bandiera europea, guardano insieme a un futuro di rinascita culturale e sociale" nell'anno scolastico e formativo 2026/2027. DGR n. 911 del 25.08.2026.</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1708,7 +1704,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Concorso per studenti - Commemorazione del Giorno del Ricordo</t>
+          <t>PR Veneto FESR 2021-2027 Azione 1.3.11 Sub C - "Interventi a favore della produzione cinematografica e audiovisiva"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1723,27 +1719,31 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Direzione Formazione e Istruzione</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Direzione Beni Attività Culturali E Sport</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n">
-        <v>11000</v>
+        <v>3680000</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46301</v>
+        <v>46142</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46416</v>
+        <v>46420</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Cultura</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Commemorazione del Giorno del Ricordo. Approvazione Avviso pubblico e Direttiva relativi al concorso per i migliori elaborati realizzati dagli studenti delle Scuole primarie e secondarie di primo e secondo grado, statali e paritarie, e delle Scuole di Formazione Professionale del Veneto, sul tema "Gli italiani delle due sponde dell'Adriatico, a ottant'anni dal Trattato di Parigi, uniti sotto la comune bandiera europea, guardano insieme a un futuro di rinascita culturale e sociale" nell'anno scolastico e formativo 2026/2027. DGR n. 911 del 25.08.2026.</t>
+          <t>PR Veneto FESR 2021-2027. Priorità 1 OS 1.3 Azione 1.3.11 “Interventi a sostegno delle imprese culturali, creative e dell’audiovisivo - Sub C - Produzione audiovisiva". Approvazione bando anno 2026 “Erogazione di contributi a favore della produzione cinematografica e audiovisiva”. La domanda va presentata esclusivamente per via telematica utilizzando il seguente link: https://www.regione.veneto.it/web/programmi-comunitari/sistemainformativofondirve dalle ore 10:00 del 12 maggio 2026 alle ore 17:00 del 30 giugno 2026 - Primo sportello importo - € 1.840.000,00 dalle ore 10:00 del 1 dicembre 2026 alle ore 17:00 del 2 febbraio 2027 - Secondo…</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 Azione 1.3.11 Sub C - "Interventi a favore della produzione cinematografica e audiovisiva"</t>
+          <t>Indizione della procedura a evidenza pubblica per il conferimento della concessione mineraria di bentonite, caolino, terre refrattarie, terre da sbianca, argille per porcellana e terraglia forte n. 307 denominata "COSTA BENEDETTA" in Comune di Sarego (VI) e per il rilascio dell'autorizzazione a eseguire i lavori di coltivazione. Approvazione del disciplinare.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1780,27 +1780,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Direzione Beni Attività Culturali E Sport</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Contributo</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>3680000</v>
-      </c>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="3" t="n">
-        <v>46142</v>
+        <v>46311</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46420</v>
+        <v>46431</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1809,7 +1807,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Ambiente | Attività produttive | Territorio</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1819,7 +1817,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027. Priorità 1 OS 1.3 Azione 1.3.11 “Interventi a sostegno delle imprese culturali, creative e dell’audiovisivo - Sub C - Produzione audiovisiva". Approvazione bando anno 2026 “Erogazione di contributi a favore della produzione cinematografica e audiovisiva”. La domanda va presentata esclusivamente per via telematica utilizzando il seguente link: https://www.regione.veneto.it/web/programmi-comunitari/sistemainformativofondirve dalle ore 10:00 del 12 maggio 2026 alle ore 17:00 del 30 giugno 2026 - Primo sportello importo - € 1.840.000,00 dalle ore 10:00 del 1 dicembre 2026 alle ore 17:00 del 2 febbraio 2027 - Secondo…</t>
+          <t>Con DDR 18867 del 23/09/2026 è stata indetta una procedura a evidenza pubblica per la selezione dell’operatore economico cui conferire la concessione mineraria di bentonite, caolino, terre refrattarie, terre da sbianca, argille per porcellana e terraglia forte n. 307 denominata "COSTA BENEDETTA" in Comune di Sarego (VI) e per il rilascio delle autorizzazioni necessarie a eseguire i lavori di coltivazione È stato, inoltre, approvato il disciplinare di gara contenente i criteri per il conferimento, definito nell'Allegato A del decreto di indizione. La domanda di assegnazione della concessione e di autorizzazione ad eseguire i lavori di…</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1831,12 +1829,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indizione della procedura a evidenza pubblica per il conferimento della concessione mineraria di bentonite, caolino, terre refrattarie, terre da sbianca, argille per porcellana e terraglia forte n. 307 denominata "COSTA BENEDETTA" in Comune di Sarego (VI) e per il rilascio dell'autorizzazione a eseguire i lavori di coltivazione. Approvazione del disciplinare.</t>
+          <t>Bando per l'evoluzione delle destinazioni turistiche venete in Smart Tourism Destination - terza edizione. DGR 992 del 15 settembre 2026. Azione 1.2.4 terza edizione</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1851,7 +1849,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1859,21 +1857,23 @@
           <t>Bando di gara</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="2" t="n">
+        <v>2500000</v>
+      </c>
       <c r="H22" s="3" t="n">
-        <v>46311</v>
+        <v>46283</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46431</v>
+        <v>46471</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ambiente | Attività produttive | Territorio</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Con DDR 18867 del 23/09/2026 è stata indetta una procedura a evidenza pubblica per la selezione dell’operatore economico cui conferire la concessione mineraria di bentonite, caolino, terre refrattarie, terre da sbianca, argille per porcellana e terraglia forte n. 307 denominata "COSTA BENEDETTA" in Comune di Sarego (VI) e per il rilascio delle autorizzazioni necessarie a eseguire i lavori di coltivazione È stato, inoltre, approvato il disciplinare di gara contenente i criteri per il conferimento, definito nell'Allegato A del decreto di indizione. La domanda di assegnazione della concessione e di autorizzazione ad eseguire i lavori di…</t>
+          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 1 “Un’Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle TIC” OS 1.2 “Permettere ai cittadini, alle imprese, alle organizzazioni di ricerca e alle autorità pubbliche di cogliere i vantaggi della digitalizzazione” Azione 1.2.4 “Organizzazione dell’offerta turistica sul digitale attraverso l’utilizzo del DMS regionale e azioni pilota per Ecosistema Digitale Veneto”. Approvazione “Bando per l’evoluzione delle destinazioni turistiche venete in Smart Tourism Destination” - terza edizione.…</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bando per l'evoluzione delle destinazioni turistiche venete in Smart Tourism Destination - terza edizione. DGR 992 del 15 settembre 2026. Azione 1.2.4 terza edizione</t>
+          <t>Avvio di selezione "a sportello" di interventi urgenti di edilizia scolastica da sostenere finanziariamente con fondi regionali negli anni 2026-2027. Legge regionale n. 59/1999, art. 3-bis.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1910,36 +1910,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Unità Organizzativa Edilizia Pubblica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bando di gara</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>2500000</v>
-      </c>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="3" t="n">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46471</v>
+        <v>46660</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Edilizia scolastica</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1949,7 +1947,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Programma Regionale Veneto FESR 2021-2027. Priorità 1 “Un’Europa più competitiva e intelligente attraverso la promozione di una trasformazione economica innovativa e intelligente e della connettività regionale alle TIC” OS 1.2 “Permettere ai cittadini, alle imprese, alle organizzazioni di ricerca e alle autorità pubbliche di cogliere i vantaggi della digitalizzazione” Azione 1.2.4 “Organizzazione dell’offerta turistica sul digitale attraverso l’utilizzo del DMS regionale e azioni pilota per Ecosistema Digitale Veneto”. Approvazione “Bando per l’evoluzione delle destinazioni turistiche venete in Smart Tourism Destination” - terza edizione.…</t>
+          <t>Il presente provvedimento avvia nell’anno in corso una procedura di selezione "a sportello" per interventi urgenti di edilizia scolastica di competenza dei Comuni o di Istituzioni scolastiche paritarie non commerciali riferiti agli anni 2026-2027, da sostenere finanziariamente con risorse del bilancio regionale 2027, fino ad esaurimento delle risorse stanziate.</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1966,7 +1964,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Avvio di selezione "a sportello" di interventi urgenti di edilizia scolastica da sostenere finanziariamente con fondi regionali negli anni 2026-2027. Legge regionale n. 59/1999, art. 3-bis.</t>
+          <t>PR Veneto FESR 2021-2027. Fondo Veneto Competitività - Sezione Start up</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1981,29 +1979,31 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Edilizia Pubblica</t>
+          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Contributo</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
+          <t>Finanziamento</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>14000000</v>
+      </c>
       <c r="H24" s="3" t="n">
-        <v>46266</v>
+        <v>45643</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46660</v>
+        <v>47483</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Edilizia scolastica</t>
+          <t>Attività produttive | Europa | FESR</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Il presente provvedimento avvia nell’anno in corso una procedura di selezione "a sportello" per interventi urgenti di edilizia scolastica di competenza dei Comuni o di Istituzioni scolastiche paritarie non commerciali riferiti agli anni 2026-2027, da sostenere finanziariamente con risorse del bilancio regionale 2027, fino ad esaurimento delle risorse stanziate.</t>
+          <t>Con DGR n. 1476 del 12 dicembre 2024, sono state approvate le Disposizioni operative per l'attuazione della "Sezione Start up" del "Fondo Veneto Competitività", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come Strumento finanziario, sostiene gli investimenti a supporto dell’autoimprenditorialità e del consolidamento di nuove imprese, nei settori del manifatturiero, dei servizi e del commercio, che siano correlati a progetti aventi ad oggetto contenuti di interesse trasversale quali: innovazione, digitalizzazione, transizione verso…</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027. Fondo Veneto Competitività - Sezione Start up</t>
+          <t>PR Veneto FESR 2021-2027. Fondo Veneto Ricerca, Sviluppo e Innovazione - Sezione Innovazione nelle PMI.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2045,19 +2045,13 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Finanziamento</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>14000000</v>
-      </c>
+          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="2" t="n"/>
       <c r="H25" s="3" t="n">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>47483</v>
@@ -2069,7 +2063,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Attività produttive | Europa | FESR</t>
+          <t>Attività produttive | FESR | Ricerca e innovazione</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2079,7 +2073,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Con DGR n. 1476 del 12 dicembre 2024, sono state approvate le Disposizioni operative per l'attuazione della "Sezione Start up" del "Fondo Veneto Competitività", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come Strumento finanziario, sostiene gli investimenti a supporto dell’autoimprenditorialità e del consolidamento di nuove imprese, nei settori del manifatturiero, dei servizi e del commercio, che siano correlati a progetti aventi ad oggetto contenuti di interesse trasversale quali: innovazione, digitalizzazione, transizione verso…</t>
+          <t>Con DGR n. 1477 del 12 dicembre 2024 , sono state approvate le Disposizioni operative per l'attuazione della "Sezione Innovazione nelle PMI" del "Fondo Veneto Ricerca, Sviluppo e Innovazione", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La “Sezione Innovazione nelle PMI” dà attuazione al PR Veneto FESR, Priorità 1, OS 1.1 - Azione 1.1.3. “Sostegno agli investimenti e alle attività di ricerca e di innovazione delle PMI – Sub. B "Sostegno alle attività di ricerca e di innovazione delle PMI". La Sezione, che si configura come Strumento finanziario, persegue…</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2096,7 +2090,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027. Fondo Veneto Ricerca, Sviluppo e Innovazione - Sezione Innovazione nelle PMI.</t>
+          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2114,10 +2108,16 @@
           <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Contributo</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>31000000</v>
+      </c>
       <c r="H26" s="3" t="n">
-        <v>45646</v>
+        <v>45629</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>47483</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Attività produttive | FESR | Ricerca e innovazione</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Con DGR n. 1477 del 12 dicembre 2024 , sono state approvate le Disposizioni operative per l'attuazione della "Sezione Innovazione nelle PMI" del "Fondo Veneto Ricerca, Sviluppo e Innovazione", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La “Sezione Innovazione nelle PMI” dà attuazione al PR Veneto FESR, Priorità 1, OS 1.1 - Azione 1.1.3. “Sostegno agli investimenti e alle attività di ricerca e di innovazione delle PMI – Sub. B "Sostegno alle attività di ricerca e di innovazione delle PMI". La Sezione, che si configura come Strumento finanziario, persegue…</t>
+          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Fondo Veneto Energia - Sezione Efficientamento energetico delle imprese</t>
+          <t>PR Veneto FESR 2021-2027. Fondo Veneto Competitività - Sezione Transizione</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2171,19 +2171,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Direzione Ricerca Innovazione E Competitivita' Energetica</t>
+          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Contributo</t>
+          <t>Finanziamento</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>31000000</v>
+        <v>40000000</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>45629</v>
+        <v>45282</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>47483</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Attività produttive | Europa | FESR | Ricerca e innovazione</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Con DGR n. 1418 del 28 novembre 2024, sono state approvate le Disposizioni Operative per l’attuazione della “Sezione Efficientamento energetico delle imprese” del “Fondo Veneto Energia”, a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A. La Sezione, che si configura come strumento finanziario, è destinata a promuovere azioni mirate a migliorare l'efficienza energetica del tessuto produttivo veneto, in termini di riduzione dei consumi energetici e di minori emissioni di gas a effetto serra, nonché a potenziare l'utilizzo di energia da fonti rinnovabili. La “Sezione…</t>
+          <t>Con DGR n. 1567 del 12 dicembre 2023, sono state approvate le Disposizioni operative per l'attuazione della "Sezione Transizione" del "Fondo Veneto Competitività", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A., successivamente aggiornate con DGR n. 757 dell'8 luglio 2025 , Allegato B. La Sezione, che si configura come Strumento finanziario, persegue l’obiettivo di migliorare i livelli di competitività delle imprese mediante l’introduzione di innovazioni tecnologiche di prodotto e di processo, il sostegno agli investimenti in tecnologie avanzate, la promozione e…</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Chiuso</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027. Fondo Veneto Competitività - Sezione Transizione</t>
+          <t>Bando a sostegno di interventi di rimozione e smaltimento di rifiuti</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2237,31 +2237,31 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Direzione Industria Artigianato Commercio E Servizi E Internazionalizzazione Delle Imprese</t>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finanziamento</t>
+          <t>Contributo</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40000000</v>
+        <v>577000</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>45282</v>
+        <v>46308</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>47483</v>
+        <v>46325</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Attività produttive | Europa | FESR | Ricerca e innovazione</t>
+          <t>Ambiente</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Con DGR n. 1567 del 12 dicembre 2023, sono state approvate le Disposizioni operative per l'attuazione della "Sezione Transizione" del "Fondo Veneto Competitività", a sua volta incluso nel “Fondo di Partecipazione PR Veneto FESR 2021-2027” affidato alla gestione di Veneto Innovazione S.p.A., successivamente aggiornate con DGR n. 757 dell'8 luglio 2025 , Allegato B. La Sezione, che si configura come Strumento finanziario, persegue l’obiettivo di migliorare i livelli di competitività delle imprese mediante l’introduzione di innovazioni tecnologiche di prodotto e di processo, il sostegno agli investimenti in tecnologie avanzate, la promozione e…</t>
+          <t>BANDO RIVOLTO ALLE AMMINISTRAZIONI COMUNALI DEL VENETO CHE INDIVIDUA LE MODALITÀ DI ASSEGNAZIONE DI CONTRIBUTI DERIVANTI DAL TRASFERIMENTO DI COMPETENZE DI CUI AL D.LGS 31 MARZO 1998, N. 112, A SOSTEGNO DI INTERVENTI DI RIMOZIONE E SMALTIMENTO DI RIFIUTI.</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -52306,7 +52306,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di supporto all'istruttoria in materia di aiuti di Stato a favore del Programma Interreg VI A Italia-Croazia 2021-2027</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -52316,36 +52316,36 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>Unità Organizzativa AdG Italia - Croazia</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G801" s="2" t="n">
-        <v>19500</v>
+        <v>1500</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>46052</v>
+        <v>46294</v>
       </c>
       <c r="I801" s="3" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
         <is>
-          <t>Affari generali | Europa | FESR | Interreg</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
@@ -52355,7 +52355,7 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>Con il decreto del Direttore dell'Unità Organizzativa AdG Italia-Croazia n. 268 del 23 dicembre 2025, si è proceduto all'affidamento diretto del servizio di supporto all'istruttoria in materia di aiuti di Stato delle proposte progettuali di tipo Standard, pervenute in risposta al terzo bando del Programma Interreg VI A Italia-Croazia 2021-2027, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. n. 36/2023 e s.m.i. Con Decreto del Direttore dell'Unità organizzativa AdG Italia-Croazia n. 148 del 6 luglio 2026 si è disposta la sostituzione del RUP per il contratto in oggetto, a seguito della nomina del nuovo Direttore della U.O. AdG…</t>
+          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
         </is>
       </c>
       <c r="O801" s="4" t="inlineStr">
@@ -52372,7 +52372,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica dei Lavori RO-M0156 - ing. Fabio Muraro</t>
+          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -52387,31 +52387,31 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Demanio e Gestione del Patrimonio</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Avviso di alienazione</t>
         </is>
       </c>
       <c r="G802" s="2" t="n">
-        <v>1500</v>
+        <v>4237500</v>
       </c>
       <c r="H802" s="3" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I802" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K802" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L802" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Demanio e patrimonio</t>
         </is>
       </c>
       <c r="M802" t="inlineStr">
@@ -52421,7 +52421,7 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>Affidamento del servizio di verifica del progetto dell Intervento di ricostruzione morfologica negli ambiti lagunari Ramo A in laguna di Barbamarco in Comune di Porto Tolle (RO) nell'ambito dell'accordo quadro degli Interventi di ripristino difese a mare, pennelli e dune costiere in Provincia di Rovigo O.C.D.P.C. n. 836/2022 ex O.C.D.P.C. n. 558/2018. - RO-M0156. APPTEL G04147 - ing. Fabio Muraro</t>
+          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
         </is>
       </c>
       <c r="O802" s="4" t="inlineStr">
@@ -52438,7 +52438,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>SECONDO AVVISO DI ASTA PUBBLICA PER ALIENAZIONE DEL COMPENDIO IMMOBILIARE DENOMINATO ¿VILLA RIETTI ROTA¿</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -52453,31 +52453,31 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>Direzione Demanio e Gestione del Patrimonio</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Avviso di alienazione</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G803" s="2" t="n">
-        <v>4237500</v>
+        <v>5800</v>
       </c>
       <c r="H803" s="3" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="I803" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K803" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L803" t="inlineStr">
         <is>
-          <t>Demanio e patrimonio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M803" t="inlineStr">
@@ -52487,7 +52487,7 @@
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>Alienazione del complesso immobiliare di proprietà regionale denominato "Villa Rietti Rota" situato in Comune di Motta di Livenza (TV) fraz.Villanova in via Zampagnon 2. Indizione secondo esperimento d'asta.</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
         </is>
       </c>
       <c r="O803" s="4" t="inlineStr">
@@ -52504,7 +52504,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori RO-Q0172.- ing. Alessandro Cavalletto</t>
+          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -52514,36 +52514,36 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Turismo e Marketing Territoriale</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G804" s="2" t="n">
-        <v>5800</v>
+        <v>55000</v>
       </c>
       <c r="H804" s="3" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="I804" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K804" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L804" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Promozione enogastronomica | Turismo</t>
         </is>
       </c>
       <c r="M804" t="inlineStr">
@@ -52553,7 +52553,7 @@
       </c>
       <c r="N804" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di progettazione ed esecuzione Lavori per gli Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 - Accordo Quadro" - Fiume Adige. RO-Q0172.- APPTEL G04066 - CUI L80007580279202500042 - ing. Alessandro Cavalletto</t>
+          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
         </is>
       </c>
       <c r="O804" s="4" t="inlineStr">
@@ -52570,7 +52570,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Partecipazione regionale a "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026)</t>
+          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -52585,7 +52585,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>Direzione Turismo e Marketing Territoriale</t>
+          <t>Direzione Lavoro</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
@@ -52594,22 +52594,22 @@
         </is>
       </c>
       <c r="G805" s="2" t="n">
-        <v>55000</v>
+        <v>938</v>
       </c>
       <c r="H805" s="3" t="n">
-        <v>46283</v>
+        <v>46294</v>
       </c>
       <c r="I805" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K805" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>Promozione enogastronomica | Turismo</t>
+          <t>Pari opportunità</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
@@ -52619,7 +52619,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>Affidamento diretto tramite piattaforma APPTEL, ai sensi dell'art. 50, comma 1, lett. b) del D.Lgs. 36/2023, all’operatore economico Slow Food Promozione Srl Società Benefit (C.F./P.I. 02220020040) del servizio di organizzazione dell'area istituzionale della Regione del Veneto alla manifestazione "Terra Madre Salone del Gusto 2026" (Torino 24-28 settembre 2026). CIG BCE2F56177 – CUP H18J26000090002. Impegno di spesa sul bilancio di previsione 2026-2028. Programma Promozionale del Settore Primario anno 2026. DGR n. 424 del 28 maggio 2026. Legge regionale 14 marzo 1980, n. 16 e ss.mm.ii . Codice ID Apptel G04111. 1. LINK PUBBLICITA' A VALORE…</t>
+          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
         </is>
       </c>
       <c r="O805" s="4" t="inlineStr">
@@ -52636,7 +52636,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Affidamento diretto a Sara Armellin di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -52646,36 +52646,30 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Direzione Lavoro</t>
-        </is>
-      </c>
-      <c r="F806" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G806" s="2" t="n">
-        <v>938</v>
-      </c>
+          <t>U.O. Genio Civile Venezia</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" s="2" t="n"/>
       <c r="H806" s="3" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I806" s="3" t="n">
-        <v>46326</v>
+        <v>46328</v>
       </c>
       <c r="K806" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>Pari opportunità</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -52685,7 +52679,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento, ai sensi dell'art. 50, comma 1, lett. b) del D.lgs. n. 36/2023, di un servizio di consulenza per la comunicazione in occasione della conferenza stampa della Commissione regionale per la realizzazione delle pari opportunità tra uomo e donna, prevista per il 2 settembre 2026, di presentazione dei corsi per docenti delle scuole dell'infanzia sui temi dell’affettività e del rispetto degli altri. Impegno di spesa e liquidazione sul bilancio per l'esercizio 2026. Per informazioni: https://dettaglio-cig.anticorruzione.it/cig/BCB0530338…</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
         </is>
       </c>
       <c r="O806" s="4" t="inlineStr">
@@ -52702,7 +52696,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza del Sig. Valerio Giampietro per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 035.N).</t>
+          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -52745,7 +52739,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di un'area di complessivi mq 1.299,28 in Comune di Jesolo (VE), località Cortellazzo, sulla sponda destra della foce del fiume Piave, finalizzata al mantenimento di un bilancione da pesca con annesso capanno per finalità di pesca sportiva (Rif. prat. 035.N – ID Concessione S.I.D. 2022P000504).</t>
+          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
         </is>
       </c>
       <c r="O807" s="4" t="inlineStr">
@@ -52762,7 +52756,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Pubblicazione, ex art. 18 reg.esec.cod.nav., dell'istanza di "Società Agricola ITALVIVAI" per il rilascio di una concessione del pubblico demanio marittimo, ai sensi dell'art. 36 c.n. (pratica 336.N)</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -52777,25 +52771,31 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>U.O. Genio Civile Venezia</t>
-        </is>
-      </c>
-      <c r="F808" t="inlineStr"/>
-      <c r="G808" s="2" t="n"/>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Avviso di post informazione</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="n">
+        <v>2075</v>
+      </c>
       <c r="H808" s="3" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="I808" s="3" t="n">
-        <v>46328</v>
+        <v>46333</v>
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L808" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
@@ -52805,7 +52805,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>DEMANIO MARITTIMO - Avviso pubblico ai sensi dell'art. 18 del Regolamento per l'esecuzione del Codice della Navigazione (D.P.R. 15 febbraio 1952, n. 328), per la presentazione di eventuali osservazioni, opposizioni e/o domande concorrenti relative all'istanza di rilascio di concessione demaniale marittima per l'occupazione e l’uso di uno specchio acqueo di 500.000 mq, situato nel mare territoriale antistante il litorale dell'isola di Pellestrina del Comune di Venezia, finalizzata al mantenimento dell’attività produttiva di mitilicoltura (Rif. prat. 336.N – ID Concessione S.I.D. 2020W010032).</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
         </is>
       </c>
       <c r="O808" s="4" t="inlineStr">
@@ -52822,7 +52822,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione - RO-I0183 - dott. Diego Piotto</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -52837,31 +52837,25 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
-        </is>
-      </c>
-      <c r="F809" t="inlineStr">
-        <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G809" s="2" t="n">
-        <v>2075</v>
-      </c>
+          <t>Direzione Infrastrutture E Trasporti</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" s="2" t="n"/>
       <c r="H809" s="3" t="n">
-        <v>46301</v>
+        <v>46275</v>
       </c>
       <c r="I809" s="3" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Mobilità e trasporti</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
@@ -52871,7 +52865,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza in fase di esecuzione nell'ambito dei Lavori di rimozione alberature schiantate in alveo e prossime allo schianto lungo le arginature del Canalbianco tra i comuni di Frassinelle Polesine e Pincara RO-I0183 O.C.D.P.C. n. 1025/2023 - O.C.D.P.C. n. 1173/2025. - dott. Diego Piotto</t>
+          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
         </is>
       </c>
       <c r="O809" s="4" t="inlineStr">
@@ -52888,7 +52882,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -52903,13 +52897,17 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Direzione Infrastrutture E Trasporti</t>
-        </is>
-      </c>
-      <c r="F810" t="inlineStr"/>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
       <c r="G810" s="2" t="n"/>
       <c r="H810" s="3" t="n">
-        <v>46275</v>
+        <v>46304</v>
       </c>
       <c r="I810" s="3" t="n">
         <v>46335</v>
@@ -52921,7 +52919,7 @@
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>Mobilità e trasporti</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -52931,7 +52929,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>Unità di navigazione RV 30294 (1V 3253) denominata Alessandra di proprietà dell'Impresa DRAGOMAR SRL di Porto Viro (RO). Procedimento di dismissione di bandiera dal data base regionale. Richiesta pubblicazione avviso.</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
         </is>
       </c>
       <c r="O810" s="4" t="inlineStr">
@@ -52948,7 +52946,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP "PIAVE". Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -52963,29 +52961,27 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G811" s="2" t="n"/>
+          <t>Direzione Comunicazione E Informazione</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" s="2" t="n">
+        <v>55000</v>
+      </c>
       <c r="H811" s="3" t="n">
-        <v>46304</v>
+        <v>46290</v>
       </c>
       <c r="I811" s="3" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Comunicazione e informazione</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -52995,7 +52991,7 @@
       </c>
       <c r="N811" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Piave DOP con sede legale in via Nazionale, 57/A – Busche di Cesiomaggiore (BL), con nota del 16 settembre 2026 ha chiesto alla Direzione Agroalimentare e servizio fitosanitario l’approvazione della seguente richiesta di modifica ordinaria del disciplinare di produzione della DOP “PIAVE”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di…</t>
+          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
         </is>
       </c>
       <c r="O811" s="4" t="inlineStr">
@@ -53012,7 +53008,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Affidamento diretto - impegni di spesa e liquidazioni a favore di Adn-Kronos Spa</t>
+          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -53022,32 +53018,36 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Direzione Comunicazione E Informazione</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr"/>
+          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
       <c r="G812" s="2" t="n">
-        <v>55000</v>
+        <v>382342</v>
       </c>
       <c r="H812" s="3" t="n">
-        <v>46290</v>
+        <v>46318</v>
       </c>
       <c r="I812" s="3" t="n">
-        <v>46336</v>
+        <v>46338</v>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Comunicazione e informazione</t>
+          <t>Sociale</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -53057,7 +53057,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>Affidamento diretto esperito mediante la piattaforma di approvvigionamento digitale della Regione del Veneto APPTEL, articolo 50, comma 1, lettera b) del Decreto Legislativo 31 marzo 2023, n. 36 e ss.mm.ii., impegni e liquidazioni della spesa, a favore di Agenzia Adn-Kronos Spa, per il servizio di realizzazione del progetto di comunicazione “Il Laboratorio Veneto nel Panorama Nazionale e l’impatto dei servizi sul territorio”. CIG BC94B8488C – APPTEL G04049. URL per Piattaforma Valore Legale: https://pubblicitalegale.anticorruzione.it/esiti/d8211b2f-2eda-4a5c-8e8f-1298d020bcd0 URL per Piattaforma APPTEL- Portale Acquisti della Regione del…</t>
+          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
         </is>
       </c>
       <c r="O812" s="4" t="inlineStr">
@@ -53074,7 +53074,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>AVVISO PUBBLICO per istituzione di nuovi Centri antiviolenza e apertura di nuovi sportelli territoriali anno 2026</t>
+          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -53084,21 +53084,17 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>Direzione Servizi Sociali, Terzo Settore e Sport</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>Avviso di contributo</t>
-        </is>
-      </c>
+          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr"/>
       <c r="G813" s="2" t="n">
-        <v>382342</v>
+        <v>299601</v>
       </c>
       <c r="H813" s="3" t="n">
         <v>46318</v>
@@ -53108,12 +53104,12 @@
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Sociale</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -53123,7 +53119,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>Si pubblica l'Avviso per la presentazione di istanze finalizzate all'istituzione di nuovi Centri antiviolenza e all'apertura di nuovi sportelli territoriali a valere sulle risorse del Decreto del Ministro per la Famiglia, la natalità e le pari opportunità del 28 novembre 2024, recante “Ripartizione delle risorse del Fondo per le politiche relative ai diritti e alle pari opportunità – Annualità 2024”, art. 4 e Tabella 3 e in attuazione della DGR n. 359 del 1° aprile 2025.</t>
+          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
         </is>
       </c>
       <c r="O813" s="4" t="inlineStr">
@@ -53140,7 +53136,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Nuova apertura termini avviso pubblico per la presentazione di manifestazioni d'interesse finalizzate alla raccolta di proposte progettuali per "Investimenti di acquacoltura sostenibile".</t>
+          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -53150,17 +53146,21 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Finanziamenti</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>Direzione Programmazione e Gestione Ittica, Bonifica e Irrigazione</t>
-        </is>
-      </c>
-      <c r="F814" t="inlineStr"/>
+          <t>Direzione Formazione E Istruzione</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Avviso di contributo</t>
+        </is>
+      </c>
       <c r="G814" s="2" t="n">
-        <v>299601</v>
+        <v>30000</v>
       </c>
       <c r="H814" s="3" t="n">
         <v>46318</v>
@@ -53170,12 +53170,12 @@
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Istruzione</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -53185,7 +53185,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>Riapertura dei termini per la presentazione delle comunicazioni di manifestazione di interesse in relazione a "Avviso pubblico per la presentazione di manifestazioni di interesse finalizzate alla raccolta di proposte progettuali, coerenti con quanto previsto nel Piano nazionale FEAMPA 2021-2027, ai sensi dell'art. 26, comma 1, lett. a) e dell'art. 27 "Investimenti per l'attività di acquacoltura sostenibile" del Reg. (UE) n. 2021/1139, da finanziare con fondi regionali." di cui alla DGR n. 739 del 21/07/2026.</t>
+          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
         </is>
       </c>
       <c r="O814" s="4" t="inlineStr">
@@ -53202,7 +53202,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Contributo regionale per l'acquisto di strumenti tecnologici destinati ad alunni ammalati</t>
+          <t>Avviso per la manifestazione di interesse per la gestione della soluzione informatica faunistico-venatoria (2027-2028)</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -53212,36 +53212,30 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Finanziamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>Direzione Formazione E Istruzione</t>
-        </is>
-      </c>
-      <c r="F815" t="inlineStr">
-        <is>
-          <t>Avviso di contributo</t>
-        </is>
-      </c>
-      <c r="G815" s="2" t="n">
-        <v>30000</v>
-      </c>
+          <t>Unità Organizzativa Pianificazione e Gestione Faunistico Venatoria</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" s="2" t="n"/>
       <c r="H815" s="3" t="n">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="I815" s="3" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Istruzione</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -53251,7 +53245,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>Avviso pubblico per la presentazione di domande di contributo regionale da parte delle scuole statali e paritarie di ogni ordine e grado e delle scuole di formazione professionale per l'acquisto, nell'anno scolastico 2026/2027, di strumenti tecnologici volti a consentire l'esercizio del diritto allo studio ad alunni ricoverati in ospedale o affetti da gravi patologie che, in ragione delle terapie domiciliari cui sono sottoposti, non possono frequentare regolarmente le attività scolastiche e formative. L.R. 14 marzo 2023, n. 3, art. 1, comma 1, lett. b) e art. 5.</t>
+          <t>Indagine di mercato per l'acquisizione di manifestazioni di interesse finalizzate all'individuazione di operatori economici interessati alla prosecuzione del servizio relativo all'attuale soluzione informatica/applicazione utilizzata per la gestione di attività in materia faunistico-venatoria – annualità 2027 e 2028.</t>
         </is>
       </c>
       <c r="O815" s="4" t="inlineStr">
@@ -53268,7 +53262,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Avviso per la manifestazione di interesse per la gestione della soluzione informatica faunistico-venatoria (2027-2028)</t>
+          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -53283,25 +53277,31 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Pianificazione e Gestione Faunistico Venatoria</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr"/>
-      <c r="G816" s="2" t="n"/>
+          <t>U.O. Servizi Forestali</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Conferenza di servizi</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="n">
+        <v>1400000</v>
+      </c>
       <c r="H816" s="3" t="n">
-        <v>46324</v>
+        <v>46297</v>
       </c>
       <c r="I816" s="3" t="n">
-        <v>46339</v>
+        <v>46340</v>
       </c>
       <c r="K816" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -53311,7 +53311,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>Indagine di mercato per l'acquisizione di manifestazioni di interesse finalizzate all'individuazione di operatori economici interessati alla prosecuzione del servizio relativo all'attuale soluzione informatica/applicazione utilizzata per la gestione di attività in materia faunistico-venatoria – annualità 2027 e 2028.</t>
+          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
         </is>
       </c>
       <c r="O816" s="4" t="inlineStr">
@@ -53323,12 +53323,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. INDIZIONE CONFERENZA DI SERVIZI</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -53343,31 +53343,31 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>U.O. Servizi Forestali</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Conferenza di servizi</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G817" s="2" t="n">
-        <v>1400000</v>
+        <v>6830</v>
       </c>
       <c r="H817" s="3" t="n">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="I817" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -53377,7 +53377,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>Indizione Conferenza di Servizi Decisoria semplificata e asincrona ai sensi degli art. 14 e 14-bis della Legge n. 241/1990 come modificati dal D.Lgs. 127/2016 per acquisizione pareri e nulla osta comunque denominati relativi al Progetto n. 1531: Interventi di Mitigazione del rischio idraulico sul Rio Val Fontana e sul Rio Salsa in località Mas del comune di Sedico II stralcio. Piano Triennale 2025-2027 - CUI: L80007580279202300036. Importo progetto: € 1.400.000,00 CUP: H58H25000090002 Codice GLP: FF-I1794.0</t>
+          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
         </is>
       </c>
       <c r="O817" s="4" t="inlineStr">
@@ -53389,12 +53389,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse RO-Q0172 - Tecnologica Group s.r.l.</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -53418,7 +53418,7 @@
         </is>
       </c>
       <c r="G818" s="2" t="n">
-        <v>6830</v>
+        <v>3900</v>
       </c>
       <c r="H818" s="3" t="n">
         <v>46308</v>
@@ -53443,7 +53443,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per il coordinamento della sicurezza csp e cse per i lavori del Canalbianco Interventi finalizzati alla riduzione del rischio idraulico sul circondario di competenza dell'U.O. Genio Civile di Rovigo - Annualità 2025 CUI L80007580279202500042 - RO-Q0172 APPTEL G04140 - Tecnologica Group s.r.l.</t>
+          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
         </is>
       </c>
       <c r="O818" s="4" t="inlineStr">
@@ -53455,12 +53455,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>In scadenza</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo - Milesi Group srl</t>
+          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -53475,31 +53475,29 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
-        </is>
-      </c>
-      <c r="G819" s="2" t="n">
-        <v>3900</v>
-      </c>
+          <t>Avviso di esproprio</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="n"/>
       <c r="H819" s="3" t="n">
-        <v>46308</v>
+        <v>46286</v>
       </c>
       <c r="I819" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -53509,7 +53507,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di materiale e la manutenzione dell'imbarcazione regionale Quick Silver 640 Weekend in dotazione alla U.O. Genio Civile Rovigo Mepa n. 6546503 - Milesi Group srl</t>
+          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
         </is>
       </c>
       <c r="O819" s="4" t="inlineStr">
@@ -53526,7 +53524,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Procedimento espropriativo in Comune di San Michele al Tagliamento ai sensi del D.P.R. n. 327/2001 e s.m.i.. Avviso di avvio delle procedure ai sensi degli articoli 11 e 16.</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -53541,29 +53539,29 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Direzione Difesa del Suolo e della Costa, SOS Lavori e Servizi Tecnici</t>
+          <t>Unità Organizzativa Genio Civile Verona</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>Avviso di esproprio</t>
+          <t>Avviso di preinformazione</t>
         </is>
       </c>
       <c r="G820" s="2" t="n"/>
       <c r="H820" s="3" t="n">
-        <v>46286</v>
+        <v>46311</v>
       </c>
       <c r="I820" s="3" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>Lavori pubblici | Territorio</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -53573,7 +53571,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>In attuazione di quanto disposto dagli articoli 11 e 16 del D.P.R. n. 327/2001 e s.m.i., si comunica l’avvio dei procedimenti amministrativi per l’apposizione del vincolo preordinato all’esproprio, nonché per l’approvazione del progetto dell’intervento denominato " Intervento di messa in sicurezza idraulica del basso corso del fiume Tagliamento - I stralcio - diaframmatura in destra idrografica finalizzata alla difesa di San Michele al Tagliamento" Opere di primo stralcio CUP: H82H18000200001, che comporta la dichiarazione di pubblica utilità dei lavori e delle espropriazioni e/o occupazioni temporanee in argomento. Le Ditte interessate…</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
         </is>
       </c>
       <c r="O820" s="4" t="inlineStr">
@@ -53585,12 +53583,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -53637,7 +53635,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di terreno demaniale ad uso sfalcio di prodotti erbosi e legnosi liberamente nascenti, posti in argine del fiume Tartaro - Canalbianco nel Comune di Bergantino in Provincia di Rovigo</t>
+          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
         </is>
       </c>
       <c r="O821" s="4" t="inlineStr">
@@ -53649,7 +53647,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -53713,12 +53711,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -53733,14 +53731,10 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Verona</t>
-        </is>
-      </c>
-      <c r="F823" t="inlineStr">
-        <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
+          <t>Direzione Agroalimentare</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr"/>
       <c r="G823" s="2" t="n"/>
       <c r="H823" s="3" t="n">
         <v>46311</v>
@@ -53750,12 +53744,12 @@
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Agricoltura e foreste</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -53765,7 +53759,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>Avviso di pubblicazione per l'affidamento in concessione di un lotto di bene demaniale di competenza della Regione Veneto</t>
+          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
         </is>
       </c>
       <c r="O823" s="4" t="inlineStr">
@@ -53777,12 +53771,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Richiesta di registrazione della IGP MELA DI VERONA. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -53825,7 +53819,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di registrazione della IGP “MELA DI VERONA”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Gruppo di Produttori IGP Mela di Verona con sede legale in Viale del Lavoro, 52 – Verona (VR), con nota del 03 luglio 2026 ha presentato la richiesta di registrazione della IGP “MELA DI VERONA”. Chiunque abbia interesse può presentare osservazioni alla richiesta di registrazione della IGP “MELA DI VERONA”, specificando nella comunicazione i seguenti dati: nome e cognome, impresa/organizzazione di appartenenza ed almeno un recapito (e-mail o numero di telefono).…</t>
+          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
         </is>
       </c>
       <c r="O824" s="4" t="inlineStr">
@@ -53842,7 +53836,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Richiesta di modifica ordinaria del disciplinare di produzione della DOP GRANA PADANO. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione.</t>
+          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -53857,20 +53851,24 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Direzione Agroalimentare</t>
-        </is>
-      </c>
-      <c r="F825" t="inlineStr"/>
+          <t>Unità Organizzativa Fitosanitario</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Avviso di preinformazione</t>
+        </is>
+      </c>
       <c r="G825" s="2" t="n"/>
       <c r="H825" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="I825" s="3" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
@@ -53885,7 +53883,7 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>TITOLO COMPLETO: Richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Regolamento (UE) 2024/1143 e Decreto MASAF 22 dicembre 2025. Pubblicazione disciplinare di produzione. Il Consorzio per la tutela del formaggio Grana Padano con sede legale in via XXIV Giugno, 8 – Desenzano del Garda (BS), con nota del 23 luglio 2026 ha presentato la richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”. Chiunque abbia interesse può presentare osservazioni alla richiesta di modifica ordinaria del disciplinare di produzione della DOP “GRANA PADANO”, specificando nella comunicazione i…</t>
+          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
         </is>
       </c>
       <c r="O825" s="4" t="inlineStr">
@@ -53897,12 +53895,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Indagine di mercato finalizzata all'acquisizione della manifestazione di interesse da parte di idonei operatori economici per il servizio di supporto all'attività istituzionale di redazione dei bollettini fitosanitari.</t>
+          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -53912,34 +53910,36 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Fitosanitario</t>
+          <t>Direzione Pianificazione Territoriale</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Avviso di preinformazione</t>
-        </is>
-      </c>
-      <c r="G826" s="2" t="n"/>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="n">
+        <v>4260</v>
+      </c>
       <c r="H826" s="3" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="I826" s="3" t="n">
-        <v>46343</v>
+        <v>46345</v>
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Cittadino Impresa</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="M826" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>Il Servizio Fitosanitario della Regione del Veneto, con la pubblicazione del presente avviso, intende avviare un’indagine di mercato finalizzata all’acquisizione della manifestazione di interesse da parte di idonei operatori economici per l’eventuale affidamento, ai sensi dell’art. 50, comma 1 lett. b), del D.lgs. n. 36/2023, del servizio di supporto all’attività istituzionale di redazione dei bollettini fitosanitari, comprensivo di ausilio alla realizzazione dei recapiti fitosanitari per le colture orticole, frutticole, viticole e olivicole ricadenti in tutte le province del Veneto.</t>
+          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
         </is>
       </c>
       <c r="O826" s="4" t="inlineStr">
@@ -53966,7 +53966,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Determina a contrarre e contestuale affidamento diretto, ai sensi dell'articolo 50, comma 1 lettera b) del Decreto Legislativo n. 36/2023, del "Servizio per l'organizzazione di una visita studio presso il Parco regionale della Lessinia". Impegno di spesa sul bilancio di previsione 2026-2028. L.R. n. 39/2001.</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -53976,27 +53976,27 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Direzione Pianificazione Territoriale</t>
+          <t>Unità Organizzativa Genio Civile Rovigo</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Affidamento diretto</t>
+          <t>Avviso di post informazione</t>
         </is>
       </c>
       <c r="G827" s="2" t="n">
-        <v>4260</v>
+        <v>4519</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I827" s="3" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="K827" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Ambiente | Lavori pubblici | Territorio</t>
         </is>
       </c>
       <c r="M827" t="inlineStr">
@@ -54015,7 +54015,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>Affidamento del servizio per l’organizzazione di una visita studio presso il Parco regionale della Lessinia. Importo euro 4.260,00 - CIG BD299C0A56 LINK BANCA DATI NAZIONALE CONTRATTI PUBBLICI: https://dettaglio-cig.anticorruzione.it/cig/BD299C0A56</t>
+          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
         </is>
       </c>
       <c r="O827" s="4" t="inlineStr">
@@ -54032,7 +54032,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena - MTX s.r.l.</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -54056,7 +54056,7 @@
         </is>
       </c>
       <c r="G828" s="2" t="n">
-        <v>4519</v>
+        <v>3824</v>
       </c>
       <c r="H828" s="3" t="n">
         <v>46315</v>
@@ -54081,7 +54081,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di aste idrometriche, materiale specifico per lo svolgimento del servizio di piena. Trattativa diretta Mepa n. 6576465. - MTX s.r.l.</t>
+          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
         </is>
       </c>
       <c r="O828" s="4" t="inlineStr">
@@ -54093,12 +54093,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -54108,36 +54108,36 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>Unità Organizzativa Genio Civile Rovigo</t>
+          <t>Avvocatura</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Avviso di post informazione</t>
+          <t>Affidamento diretto</t>
         </is>
       </c>
       <c r="G829" s="2" t="n">
-        <v>3824</v>
+        <v>39468</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>46315</v>
+        <v>46286</v>
       </c>
       <c r="I829" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>Cittadino Impresa</t>
+          <t>Cittadino</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
         <is>
-          <t>Ambiente | Lavori pubblici | Territorio</t>
+          <t>Affari generali</t>
         </is>
       </c>
       <c r="M829" t="inlineStr">
@@ -54147,7 +54147,7 @@
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>Affidamento della fornitura di un motore per l'imbarcazione regionale "Selva Marine mod. S.14" in dotazione alla U.O. Genio Civile Rovigo. Trattativa diretta Mepa n. 6555197 - Nautica Polesana s.r.l.</t>
+          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
         </is>
       </c>
       <c r="O829" s="4" t="inlineStr">
@@ -54164,7 +54164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese</t>
+          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -54188,10 +54188,10 @@
         </is>
       </c>
       <c r="G830" s="2" t="n">
-        <v>39468</v>
+        <v>1144</v>
       </c>
       <c r="H830" s="3" t="n">
-        <v>46286</v>
+        <v>46301</v>
       </c>
       <c r="I830" s="3" t="n">
         <v>46348</v>
@@ -54213,7 +54213,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>Affidamento incarico di assistenza legale innanzi alla giurisdizione inglese allo Studio Legale Associato Cedrini &amp; Zamagni. link: https://dettaglio-cig.anticorruzione.it/cig/BD0636E2B7</t>
+          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
         </is>
       </c>
       <c r="O830" s="4" t="inlineStr">
@@ -54230,7 +54230,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026</t>
+          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -54254,10 +54254,10 @@
         </is>
       </c>
       <c r="G831" s="2" t="n">
-        <v>1144</v>
+        <v>9155</v>
       </c>
       <c r="H831" s="3" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="I831" s="3" t="n">
         <v>46348</v>
@@ -54279,7 +54279,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di domiciliazione all'avv. Paolo Migliaccio, nella causa pendente innanzi al Tribunale di Roma, R.G. n. 38095/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD3B206451</t>
+          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
         </is>
       </c>
       <c r="O831" s="4" t="inlineStr">
@@ -54291,12 +54291,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026.</t>
+          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -54311,7 +54311,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>Avvocatura</t>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
@@ -54320,22 +54320,22 @@
         </is>
       </c>
       <c r="G832" s="2" t="n">
-        <v>9155</v>
+        <v>77000</v>
       </c>
       <c r="H832" s="3" t="n">
-        <v>46308</v>
+        <v>46318</v>
       </c>
       <c r="I832" s="3" t="n">
-        <v>46348</v>
+        <v>46356</v>
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t>Cittadino</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>Affari generali</t>
+          <t>Ambiente | Territorio | Turismo</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -54345,7 +54345,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>Affidamento incarico legale per attività di patrocinio all'avv. Carolina Brunazzetto e all'avv. Maria Luisa Miazzi, dello Studio Legale Miazzi Cester Rossi, nella causa pendente innanzi alla Corte di Cassazione, R.G. n. 20894/2026. Link: https://dettaglio-cig.anticorruzione.it/cig/BD4FA0A434</t>
+          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
         </is>
       </c>
       <c r="O832" s="4" t="inlineStr">
@@ -54357,12 +54357,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Aperto</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Veneto? Naturale!". Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei parchi del Veneto. Anno 2026.</t>
+          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -54372,36 +54372,30 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Gare e affidamenti</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>Affidamento diretto</t>
-        </is>
-      </c>
-      <c r="G833" s="2" t="n">
-        <v>77000</v>
-      </c>
+          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr"/>
+      <c r="G833" s="2" t="n"/>
       <c r="H833" s="3" t="n">
-        <v>46318</v>
+        <v>46161</v>
       </c>
       <c r="I833" s="3" t="n">
         <v>46356</v>
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t>Cittadino Ente Impresa</t>
+          <t>Ente</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>Ambiente | Territorio | Turismo</t>
+          <t>FESR | Protezione civile</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
@@ -54411,7 +54405,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>Decisione di contrarre, contestuale affidamento diretto ed impegno di spesa, ai sensi dell’art. 50, comma 1, lett. b), del D. Lgs. 31 marzo 2023, n. 36, relativo al servizio di “Ideazione, sviluppo e gestione della campagna di valorizzazione della rete regionale dei Parchi del Veneto – Anno 2026”, denominata “Veneto? Naturale!”. CUP H11G26000120002. CIG BD03570E7D. BDNCP: https://dettaglio-cig.anticorruzione.it/cig/BD03570E7D</t>
+          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
         </is>
       </c>
       <c r="O833" s="4" t="inlineStr">
@@ -54428,7 +54422,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>PR Veneto FESR 2021-2027 - Azione 2.4.1 - Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -54438,30 +54432,36 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Gare e affidamenti</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>Direzione Protezione Civile, Sicurezza E Polizia Locale</t>
-        </is>
-      </c>
-      <c r="F834" t="inlineStr"/>
-      <c r="G834" s="2" t="n"/>
+          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Affidamento diretto</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="n">
+        <v>28800</v>
+      </c>
       <c r="H834" s="3" t="n">
-        <v>46161</v>
+        <v>46304</v>
       </c>
       <c r="I834" s="3" t="n">
-        <v>46356</v>
+        <v>46361</v>
       </c>
       <c r="K834" t="inlineStr">
         <is>
-          <t>Ente</t>
+          <t>Cittadino Ente Impresa</t>
         </is>
       </c>
       <c r="L834" t="inlineStr">
         <is>
-          <t>FESR | Protezione civile</t>
+          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
         </is>
       </c>
       <c r="M834" t="inlineStr">
@@ -54471,7 +54471,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>DECRETO DEL DIRETTORE DELLA DIREZIONE PROTEZIONE CIVILE, SICUREZZA E POLIZIA LOCALE n. 195 del 27 aprile 2026 PR Veneto FESR 2021-2027. Priorità 2, OS 2.4, Azione 2.4.1 "Prevenzione del rischio da catastrofi ed aumento della resilienza - potenziamento delle strutture di comando e controllo (rete delle sale operative territoriali) e logistiche per la prevenzione e la gestione delle catastrofi". Approvazione degli esiti istruttori delle domande informatiche di sostegno per gli interventi a regia regionale ammessi al contributo con DGR n. 1269/2025.</t>
+          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
         </is>
       </c>
       <c r="O834" s="4" t="inlineStr">
@@ -54483,12 +54483,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Aperto</t>
+          <t>Nuovo</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 Laghetto del Frassino, IT3210013 Palude del Busatello, IT3210015 Palude di Pellegrina.</t>
+          <t>Affidamento dell'attività destinata alla realizzazione del coffee break durante lo svolgimento della seconda giornata formativa di Onboarding dedicata ai neoassunti della Regione del Veneto. Annullamento Decreto n. 443 del 24 settembre 2026. Nuovo impegno di spesa e relativa imputazione contabile. CUP H73I26000010002</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>Direzione Aria, Clima, Biodiversità e Parchi</t>
+          <t>Direzione Organizzazione E Personale</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -54512,13 +54512,13 @@
         </is>
       </c>
       <c r="G835" s="2" t="n">
-        <v>28800</v>
+        <v>1089</v>
       </c>
       <c r="H835" s="3" t="n">
-        <v>46304</v>
+        <v>46325</v>
       </c>
       <c r="I835" s="3" t="n">
-        <v>46361</v>
+        <v>46375</v>
       </c>
       <c r="K835" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
       </c>
       <c r="L835" t="inlineStr">
         <is>
-          <t>Agricoltura e foreste | Ambiente | FESR | Territorio</t>
+          <t>Formazione | Servizi di catering</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
@@ -54537,7 +54537,7 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>Decreto a contrarre e di aggiudicazione definitiva ed efficace per il servizio di “Revisione cartografica e aggiornamento dei Formulari Standard dei siti della Rete Natura 2000: IT3210003 – Laghetto del Frassino, IT3210013 – Palude del Busatello, IT3210015 – Palude di Pellegrina. CUP H69I26001030008. CIG BD0243459A”, finanziato dal Programma Operativo n. 5 dell’Assistenza tecnica al CSR 2023–2027, di cui alla DGR n. 453 del 18.04.2023 e DGR n. 742 del 21.07.2026, in attuazione dei Regolamenti (UE) n. 2021/2115 e n. 2021/2116. Link BDNP:https://dettaglio-cig.anticorruzione.it/cig/BD0243459A</t>
+          <t>Con il presente provvedimento si procede all’annullamento del Decreto n. 443 del 24 settembre 2026, all’acquisizione del servizio e all’assunzione dell’impegno di spesa per l’esecuzione dell’attività destinata alla realizzazione del coffee break durante lo svolgimento della seconda giornata formativa di Onboarding dedicata ai neoassunti della Regione del Veneto.</t>
         </is>
       </c>
       <c r="O835" s="4" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 11:05</t>
+          <t>2026-10-31 10:39</t>
         </is>
       </c>
     </row>
@@ -59309,7 +59309,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
